--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21738BF0-31DE-4282-832B-D263BA5CD1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A5D381-81CF-4C98-AFB7-517F30247E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A5D381-81CF-4C98-AFB7-517F30247E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC578F0-14F0-4E02-AFEB-37929045A32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="88">
   <si>
     <t>Company Name</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>Drew Template</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Jeremy Myers</t>
   </si>
 </sst>
 </file>
@@ -16851,106 +16857,712 @@
       </c>
     </row>
     <row r="583" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H583" s="2"/>
-      <c r="I583" s="1"/>
+      <c r="B583" t="s">
+        <v>35</v>
+      </c>
+      <c r="C583">
+        <v>77</v>
+      </c>
+      <c r="D583" t="s">
+        <v>36</v>
+      </c>
+      <c r="F583" t="s">
+        <v>86</v>
+      </c>
+      <c r="G583" t="s">
+        <v>13</v>
+      </c>
+      <c r="H583" s="2">
+        <v>0</v>
+      </c>
+      <c r="I583" s="1">
+        <v>46118.813078703701</v>
+      </c>
+      <c r="J583">
+        <v>1</v>
+      </c>
+      <c r="K583" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="584" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H584" s="2"/>
-      <c r="I584" s="1"/>
+      <c r="B584" t="s">
+        <v>35</v>
+      </c>
+      <c r="C584">
+        <v>745</v>
+      </c>
+      <c r="D584" t="s">
+        <v>38</v>
+      </c>
+      <c r="F584" t="s">
+        <v>86</v>
+      </c>
+      <c r="G584" t="s">
+        <v>10</v>
+      </c>
+      <c r="H584" s="2">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="I584" s="1">
+        <v>46118.813078703701</v>
+      </c>
+      <c r="J584">
+        <v>1</v>
+      </c>
+      <c r="K584" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="585" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H585" s="2"/>
-      <c r="I585" s="1"/>
+      <c r="B585" t="s">
+        <v>35</v>
+      </c>
+      <c r="C585">
+        <v>5058</v>
+      </c>
+      <c r="D585" t="s">
+        <v>83</v>
+      </c>
+      <c r="F585" t="s">
+        <v>86</v>
+      </c>
+      <c r="G585" t="s">
+        <v>13</v>
+      </c>
+      <c r="H585" s="2">
+        <v>0</v>
+      </c>
+      <c r="I585" s="1">
+        <v>46118.813773148147</v>
+      </c>
+      <c r="J585">
+        <v>1</v>
+      </c>
+      <c r="K585" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="586" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H586" s="2"/>
-      <c r="I586" s="1"/>
+      <c r="B586" t="s">
+        <v>35</v>
+      </c>
+      <c r="C586">
+        <v>622</v>
+      </c>
+      <c r="D586" t="s">
+        <v>39</v>
+      </c>
+      <c r="F586" t="s">
+        <v>86</v>
+      </c>
+      <c r="G586" t="s">
+        <v>13</v>
+      </c>
+      <c r="H586" s="2">
+        <v>0</v>
+      </c>
+      <c r="I586" s="1">
+        <v>46118.814467592594</v>
+      </c>
+      <c r="J586">
+        <v>1</v>
+      </c>
+      <c r="K586" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="587" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H587" s="2"/>
-      <c r="I587" s="1"/>
+      <c r="B587" t="s">
+        <v>35</v>
+      </c>
+      <c r="C587">
+        <v>5217</v>
+      </c>
+      <c r="D587" t="s">
+        <v>85</v>
+      </c>
+      <c r="F587" t="s">
+        <v>86</v>
+      </c>
+      <c r="G587" t="s">
+        <v>10</v>
+      </c>
+      <c r="H587" s="2">
+        <v>6.2268518518518515E-3</v>
+      </c>
+      <c r="I587" s="1">
+        <v>46118.814467592594</v>
+      </c>
+      <c r="J587">
+        <v>0</v>
+      </c>
+      <c r="K587" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="588" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H588" s="2"/>
-      <c r="I588" s="1"/>
+      <c r="B588" t="s">
+        <v>35</v>
+      </c>
+      <c r="C588">
+        <v>204</v>
+      </c>
+      <c r="D588" t="s">
+        <v>40</v>
+      </c>
+      <c r="F588" t="s">
+        <v>86</v>
+      </c>
+      <c r="G588" t="s">
+        <v>10</v>
+      </c>
+      <c r="H588" s="2">
+        <v>7.4421296296296293E-3</v>
+      </c>
+      <c r="I588" s="1">
+        <v>46118.815162037034</v>
+      </c>
+      <c r="J588">
+        <v>1</v>
+      </c>
+      <c r="K588" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="589" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H589" s="2"/>
-      <c r="I589" s="1"/>
+      <c r="B589" t="s">
+        <v>35</v>
+      </c>
+      <c r="C589">
+        <v>205</v>
+      </c>
+      <c r="D589" t="s">
+        <v>41</v>
+      </c>
+      <c r="F589" t="s">
+        <v>86</v>
+      </c>
+      <c r="G589" t="s">
+        <v>10</v>
+      </c>
+      <c r="H589" s="2">
+        <v>7.2106481481481483E-3</v>
+      </c>
+      <c r="I589" s="1">
+        <v>46118.81585648148</v>
+      </c>
+      <c r="J589">
+        <v>1</v>
+      </c>
+      <c r="K589" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="590" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H590" s="2"/>
-      <c r="I590" s="1"/>
+      <c r="B590" t="s">
+        <v>35</v>
+      </c>
+      <c r="C590">
+        <v>3741</v>
+      </c>
+      <c r="D590" t="s">
+        <v>78</v>
+      </c>
+      <c r="E590" t="s">
+        <v>63</v>
+      </c>
+      <c r="F590" t="s">
+        <v>86</v>
+      </c>
+      <c r="G590" t="s">
+        <v>10</v>
+      </c>
+      <c r="H590" s="2">
+        <v>8.0787037037037043E-3</v>
+      </c>
+      <c r="I590" s="1">
+        <v>46118.834722222222</v>
+      </c>
+      <c r="J590">
+        <v>1</v>
+      </c>
+      <c r="K590" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="591" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H591" s="2"/>
-      <c r="I591" s="1"/>
+      <c r="B591" t="s">
+        <v>35</v>
+      </c>
+      <c r="C591">
+        <v>78</v>
+      </c>
+      <c r="D591" t="s">
+        <v>42</v>
+      </c>
+      <c r="F591" t="s">
+        <v>86</v>
+      </c>
+      <c r="G591" t="s">
+        <v>10</v>
+      </c>
+      <c r="H591" s="2">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I591" s="1">
+        <v>46118.835416666669</v>
+      </c>
+      <c r="J591">
+        <v>1</v>
+      </c>
+      <c r="K591" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="592" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H592" s="2"/>
-      <c r="I592" s="1"/>
-    </row>
-    <row r="593" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H593" s="2"/>
-      <c r="I593" s="1"/>
-    </row>
-    <row r="594" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B592" t="s">
+        <v>35</v>
+      </c>
+      <c r="C592">
+        <v>73</v>
+      </c>
+      <c r="D592" t="s">
+        <v>44</v>
+      </c>
+      <c r="F592" t="s">
+        <v>86</v>
+      </c>
+      <c r="G592" t="s">
+        <v>13</v>
+      </c>
+      <c r="H592" s="2">
+        <v>0</v>
+      </c>
+      <c r="I592" s="1">
+        <v>46118.836111111108</v>
+      </c>
+      <c r="J592">
+        <v>1</v>
+      </c>
+      <c r="K592" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="593" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B593" t="s">
+        <v>35</v>
+      </c>
+      <c r="C593">
+        <v>5037</v>
+      </c>
+      <c r="D593" t="s">
+        <v>84</v>
+      </c>
+      <c r="F593" t="s">
+        <v>86</v>
+      </c>
+      <c r="G593" t="s">
+        <v>14</v>
+      </c>
+      <c r="H593" s="2">
+        <v>0</v>
+      </c>
+      <c r="I593" s="1">
+        <v>46118.836111111108</v>
+      </c>
+      <c r="J593">
+        <v>0</v>
+      </c>
+      <c r="K593" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="594" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H594" s="2"/>
       <c r="I594" s="1"/>
-    </row>
-    <row r="595" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H595" s="2"/>
-      <c r="I595" s="1"/>
-    </row>
-    <row r="596" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H596" s="2"/>
-      <c r="I596" s="1"/>
-    </row>
-    <row r="597" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H597" s="2"/>
-      <c r="I597" s="1"/>
-    </row>
-    <row r="598" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H598" s="2"/>
-      <c r="I598" s="1"/>
-    </row>
-    <row r="599" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H599" s="2"/>
-      <c r="I599" s="1"/>
-    </row>
-    <row r="600" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H600" s="2"/>
-      <c r="I600" s="1"/>
-    </row>
-    <row r="601" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H601" s="2"/>
-      <c r="I601" s="1"/>
-    </row>
-    <row r="602" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H602" s="2"/>
-      <c r="I602" s="1"/>
-    </row>
-    <row r="603" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H603" s="2"/>
-      <c r="I603" s="1"/>
-    </row>
-    <row r="604" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H604" s="2"/>
-      <c r="I604" s="1"/>
-    </row>
-    <row r="605" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H605" s="2"/>
-      <c r="I605" s="1"/>
-    </row>
-    <row r="606" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H606" s="2"/>
-      <c r="I606" s="1"/>
-    </row>
-    <row r="607" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H607" s="2"/>
-      <c r="I607" s="1"/>
-    </row>
-    <row r="608" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K594" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="595" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B595" t="s">
+        <v>35</v>
+      </c>
+      <c r="C595">
+        <v>75</v>
+      </c>
+      <c r="D595" t="s">
+        <v>46</v>
+      </c>
+      <c r="F595" t="s">
+        <v>86</v>
+      </c>
+      <c r="G595" t="s">
+        <v>13</v>
+      </c>
+      <c r="H595" s="2">
+        <v>0</v>
+      </c>
+      <c r="I595" s="1">
+        <v>46118.836805555555</v>
+      </c>
+      <c r="J595">
+        <v>1</v>
+      </c>
+      <c r="K595" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="596" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B596" t="s">
+        <v>35</v>
+      </c>
+      <c r="C596">
+        <v>5409</v>
+      </c>
+      <c r="D596" t="s">
+        <v>87</v>
+      </c>
+      <c r="F596" t="s">
+        <v>86</v>
+      </c>
+      <c r="G596" t="s">
+        <v>13</v>
+      </c>
+      <c r="H596" s="2">
+        <v>0</v>
+      </c>
+      <c r="I596" s="1">
+        <v>46118.837500000001</v>
+      </c>
+      <c r="J596">
+        <v>1</v>
+      </c>
+      <c r="K596" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="597" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B597" t="s">
+        <v>35</v>
+      </c>
+      <c r="C597">
+        <v>5350</v>
+      </c>
+      <c r="D597" t="s">
+        <v>87</v>
+      </c>
+      <c r="F597" t="s">
+        <v>86</v>
+      </c>
+      <c r="G597" t="s">
+        <v>13</v>
+      </c>
+      <c r="H597" s="2">
+        <v>0</v>
+      </c>
+      <c r="I597" s="1">
+        <v>46118.837500000001</v>
+      </c>
+      <c r="J597">
+        <v>1</v>
+      </c>
+      <c r="K597" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="598" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B598" t="s">
+        <v>35</v>
+      </c>
+      <c r="C598">
+        <v>76</v>
+      </c>
+      <c r="D598" t="s">
+        <v>47</v>
+      </c>
+      <c r="F598" t="s">
+        <v>86</v>
+      </c>
+      <c r="G598" t="s">
+        <v>13</v>
+      </c>
+      <c r="H598" s="2">
+        <v>0</v>
+      </c>
+      <c r="I598" s="1">
+        <v>46118.838194444441</v>
+      </c>
+      <c r="J598">
+        <v>1</v>
+      </c>
+      <c r="K598" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="599" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B599" t="s">
+        <v>35</v>
+      </c>
+      <c r="C599">
+        <v>3726</v>
+      </c>
+      <c r="D599" t="s">
+        <v>79</v>
+      </c>
+      <c r="F599" t="s">
+        <v>86</v>
+      </c>
+      <c r="G599" t="s">
+        <v>10</v>
+      </c>
+      <c r="H599" s="2">
+        <v>1.0798611111111111E-2</v>
+      </c>
+      <c r="I599" s="1">
+        <v>46118.838888888888</v>
+      </c>
+      <c r="J599">
+        <v>1</v>
+      </c>
+      <c r="K599" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="600" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B600" t="s">
+        <v>35</v>
+      </c>
+      <c r="C600">
+        <v>614</v>
+      </c>
+      <c r="D600" t="s">
+        <v>48</v>
+      </c>
+      <c r="F600" t="s">
+        <v>86</v>
+      </c>
+      <c r="G600" t="s">
+        <v>13</v>
+      </c>
+      <c r="H600" s="2">
+        <v>0</v>
+      </c>
+      <c r="I600" s="1">
+        <v>46118.838888888888</v>
+      </c>
+      <c r="J600">
+        <v>1</v>
+      </c>
+      <c r="K600" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="601" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B601" t="s">
+        <v>35</v>
+      </c>
+      <c r="C601">
+        <v>772</v>
+      </c>
+      <c r="D601" t="s">
+        <v>49</v>
+      </c>
+      <c r="F601" t="s">
+        <v>86</v>
+      </c>
+      <c r="G601" t="s">
+        <v>13</v>
+      </c>
+      <c r="H601" s="2">
+        <v>0</v>
+      </c>
+      <c r="I601" s="1">
+        <v>46118.839583333334</v>
+      </c>
+      <c r="J601">
+        <v>1</v>
+      </c>
+      <c r="K601" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="602" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B602" t="s">
+        <v>35</v>
+      </c>
+      <c r="C602">
+        <v>623</v>
+      </c>
+      <c r="D602" t="s">
+        <v>50</v>
+      </c>
+      <c r="F602" t="s">
+        <v>86</v>
+      </c>
+      <c r="G602" t="s">
+        <v>13</v>
+      </c>
+      <c r="H602" s="2">
+        <v>0</v>
+      </c>
+      <c r="I602" s="1">
+        <v>46118.839583333334</v>
+      </c>
+      <c r="J602">
+        <v>1</v>
+      </c>
+      <c r="K602" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="603" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B603" t="s">
+        <v>35</v>
+      </c>
+      <c r="C603">
+        <v>72</v>
+      </c>
+      <c r="D603" t="s">
+        <v>51</v>
+      </c>
+      <c r="F603" t="s">
+        <v>86</v>
+      </c>
+      <c r="G603" t="s">
+        <v>13</v>
+      </c>
+      <c r="H603" s="2">
+        <v>0</v>
+      </c>
+      <c r="I603" s="1">
+        <v>46118.840277777781</v>
+      </c>
+      <c r="J603">
+        <v>1</v>
+      </c>
+      <c r="K603" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="604" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B604" t="s">
+        <v>35</v>
+      </c>
+      <c r="C604">
+        <v>245</v>
+      </c>
+      <c r="D604" t="s">
+        <v>52</v>
+      </c>
+      <c r="F604" t="s">
+        <v>86</v>
+      </c>
+      <c r="G604" t="s">
+        <v>10</v>
+      </c>
+      <c r="H604" s="2">
+        <v>9.3865740740740732E-3</v>
+      </c>
+      <c r="I604" s="1">
+        <v>46118.84097222222</v>
+      </c>
+      <c r="J604">
+        <v>1</v>
+      </c>
+      <c r="K604" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="605" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B605" t="s">
+        <v>35</v>
+      </c>
+      <c r="C605">
+        <v>84</v>
+      </c>
+      <c r="D605" t="s">
+        <v>55</v>
+      </c>
+      <c r="F605" t="s">
+        <v>86</v>
+      </c>
+      <c r="G605" t="s">
+        <v>10</v>
+      </c>
+      <c r="H605" s="2">
+        <v>8.8078703703703704E-3</v>
+      </c>
+      <c r="I605" s="1">
+        <v>46118.84097222222</v>
+      </c>
+      <c r="J605">
+        <v>0</v>
+      </c>
+      <c r="K605" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="606" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B606" t="s">
+        <v>35</v>
+      </c>
+      <c r="C606">
+        <v>3818</v>
+      </c>
+      <c r="D606" t="s">
+        <v>81</v>
+      </c>
+      <c r="F606" t="s">
+        <v>86</v>
+      </c>
+      <c r="G606" t="s">
+        <v>13</v>
+      </c>
+      <c r="H606" s="2">
+        <v>0</v>
+      </c>
+      <c r="I606" s="1">
+        <v>46118.841666666667</v>
+      </c>
+      <c r="J606">
+        <v>1</v>
+      </c>
+      <c r="K606" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="607" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B607" t="s">
+        <v>35</v>
+      </c>
+      <c r="C607">
+        <v>80</v>
+      </c>
+      <c r="D607" t="s">
+        <v>56</v>
+      </c>
+      <c r="F607" t="s">
+        <v>86</v>
+      </c>
+      <c r="G607" t="s">
+        <v>13</v>
+      </c>
+      <c r="H607" s="2">
+        <v>0</v>
+      </c>
+      <c r="I607" s="1">
+        <v>46118.841666666667</v>
+      </c>
+      <c r="J607">
+        <v>1</v>
+      </c>
+      <c r="K607" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="608" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H608" s="2"/>
       <c r="I608" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC578F0-14F0-4E02-AFEB-37929045A32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD709EB-9156-4E6C-928B-68B736E573AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="88">
   <si>
     <t>Company Name</t>
   </si>
@@ -16879,7 +16879,7 @@
         <v>46118.813078703701</v>
       </c>
       <c r="J583">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K583" t="s">
         <v>11</v>
@@ -16937,7 +16937,7 @@
         <v>46118.813773148147</v>
       </c>
       <c r="J585">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K585" t="s">
         <v>11</v>
@@ -16966,7 +16966,7 @@
         <v>46118.814467592594</v>
       </c>
       <c r="J586">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K586" t="s">
         <v>11</v>
@@ -17143,7 +17143,7 @@
         <v>46118.836111111108</v>
       </c>
       <c r="J592">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K592" t="s">
         <v>11</v>
@@ -17208,7 +17208,7 @@
         <v>46118.836805555555</v>
       </c>
       <c r="J595">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K595" t="s">
         <v>11</v>
@@ -17237,7 +17237,7 @@
         <v>46118.837500000001</v>
       </c>
       <c r="J596">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K596" t="s">
         <v>11</v>
@@ -17257,7 +17257,7 @@
         <v>86</v>
       </c>
       <c r="G597" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H597" s="2">
         <v>0</v>
@@ -17266,39 +17266,17 @@
         <v>46118.837500000001</v>
       </c>
       <c r="J597">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K597" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="598" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B598" t="s">
-        <v>35</v>
-      </c>
-      <c r="C598">
-        <v>76</v>
-      </c>
-      <c r="D598" t="s">
-        <v>47</v>
-      </c>
-      <c r="F598" t="s">
-        <v>86</v>
-      </c>
-      <c r="G598" t="s">
-        <v>13</v>
-      </c>
-      <c r="H598" s="2">
-        <v>0</v>
-      </c>
-      <c r="I598" s="1">
-        <v>46118.838194444441</v>
-      </c>
-      <c r="J598">
-        <v>1</v>
-      </c>
+      <c r="H598" s="2"/>
+      <c r="I598" s="1"/>
       <c r="K598" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="599" spans="2:11" x14ac:dyDescent="0.25">
@@ -17306,25 +17284,25 @@
         <v>35</v>
       </c>
       <c r="C599">
-        <v>3726</v>
+        <v>76</v>
       </c>
       <c r="D599" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="F599" t="s">
         <v>86</v>
       </c>
       <c r="G599" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H599" s="2">
-        <v>1.0798611111111111E-2</v>
+        <v>0</v>
       </c>
       <c r="I599" s="1">
-        <v>46118.838888888888</v>
+        <v>46118.838194444441</v>
       </c>
       <c r="J599">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K599" t="s">
         <v>11</v>
@@ -17335,19 +17313,19 @@
         <v>35</v>
       </c>
       <c r="C600">
-        <v>614</v>
+        <v>3726</v>
       </c>
       <c r="D600" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="F600" t="s">
         <v>86</v>
       </c>
       <c r="G600" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H600" s="2">
-        <v>0</v>
+        <v>1.0798611111111111E-2</v>
       </c>
       <c r="I600" s="1">
         <v>46118.838888888888</v>
@@ -17364,25 +17342,25 @@
         <v>35</v>
       </c>
       <c r="C601">
-        <v>772</v>
+        <v>614</v>
       </c>
       <c r="D601" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F601" t="s">
         <v>86</v>
       </c>
       <c r="G601" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H601" s="2">
-        <v>0</v>
+        <v>8.518518518518519E-3</v>
       </c>
       <c r="I601" s="1">
-        <v>46118.839583333334</v>
+        <v>46118.838888888888</v>
       </c>
       <c r="J601">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K601" t="s">
         <v>11</v>
@@ -17393,10 +17371,10 @@
         <v>35</v>
       </c>
       <c r="C602">
-        <v>623</v>
+        <v>772</v>
       </c>
       <c r="D602" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F602" t="s">
         <v>86</v>
@@ -17411,7 +17389,7 @@
         <v>46118.839583333334</v>
       </c>
       <c r="J602">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K602" t="s">
         <v>11</v>
@@ -17422,25 +17400,25 @@
         <v>35</v>
       </c>
       <c r="C603">
-        <v>72</v>
+        <v>623</v>
       </c>
       <c r="D603" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F603" t="s">
         <v>86</v>
       </c>
       <c r="G603" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H603" s="2">
-        <v>0</v>
+        <v>8.8541666666666664E-3</v>
       </c>
       <c r="I603" s="1">
-        <v>46118.840277777781</v>
+        <v>46118.839583333334</v>
       </c>
       <c r="J603">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K603" t="s">
         <v>11</v>
@@ -17451,25 +17429,25 @@
         <v>35</v>
       </c>
       <c r="C604">
-        <v>245</v>
+        <v>72</v>
       </c>
       <c r="D604" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F604" t="s">
         <v>86</v>
       </c>
       <c r="G604" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H604" s="2">
-        <v>9.3865740740740732E-3</v>
+        <v>0</v>
       </c>
       <c r="I604" s="1">
-        <v>46118.84097222222</v>
+        <v>46118.840277777781</v>
       </c>
       <c r="J604">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K604" t="s">
         <v>11</v>
@@ -17480,10 +17458,10 @@
         <v>35</v>
       </c>
       <c r="C605">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="D605" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F605" t="s">
         <v>86</v>
@@ -17492,13 +17470,13 @@
         <v>10</v>
       </c>
       <c r="H605" s="2">
-        <v>8.8078703703703704E-3</v>
+        <v>9.3865740740740732E-3</v>
       </c>
       <c r="I605" s="1">
         <v>46118.84097222222</v>
       </c>
       <c r="J605">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K605" t="s">
         <v>11</v>
@@ -17509,25 +17487,25 @@
         <v>35</v>
       </c>
       <c r="C606">
-        <v>3818</v>
+        <v>84</v>
       </c>
       <c r="D606" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F606" t="s">
         <v>86</v>
       </c>
       <c r="G606" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H606" s="2">
-        <v>0</v>
+        <v>8.8078703703703704E-3</v>
       </c>
       <c r="I606" s="1">
-        <v>46118.841666666667</v>
+        <v>46118.84097222222</v>
       </c>
       <c r="J606">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K606" t="s">
         <v>11</v>
@@ -17538,10 +17516,10 @@
         <v>35</v>
       </c>
       <c r="C607">
-        <v>80</v>
+        <v>3818</v>
       </c>
       <c r="D607" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F607" t="s">
         <v>86</v>
@@ -17556,15 +17534,40 @@
         <v>46118.841666666667</v>
       </c>
       <c r="J607">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K607" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="608" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H608" s="2"/>
-      <c r="I608" s="1"/>
+      <c r="B608" t="s">
+        <v>35</v>
+      </c>
+      <c r="C608">
+        <v>80</v>
+      </c>
+      <c r="D608" t="s">
+        <v>56</v>
+      </c>
+      <c r="F608" t="s">
+        <v>86</v>
+      </c>
+      <c r="G608" t="s">
+        <v>13</v>
+      </c>
+      <c r="H608" s="2">
+        <v>0</v>
+      </c>
+      <c r="I608" s="1">
+        <v>46118.841666666667</v>
+      </c>
+      <c r="J608">
+        <v>2</v>
+      </c>
+      <c r="K608" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="609" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H609" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD709EB-9156-4E6C-928B-68B736E573AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BB7BDD-77CC-42E5-BEE5-872FBEEF4CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16879,7 +16879,7 @@
         <v>46118.813078703701</v>
       </c>
       <c r="J583">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K583" t="s">
         <v>11</v>
@@ -16937,7 +16937,7 @@
         <v>46118.813773148147</v>
       </c>
       <c r="J585">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K585" t="s">
         <v>11</v>
@@ -16966,7 +16966,7 @@
         <v>46118.814467592594</v>
       </c>
       <c r="J586">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K586" t="s">
         <v>11</v>
@@ -17143,7 +17143,7 @@
         <v>46118.836111111108</v>
       </c>
       <c r="J592">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K592" t="s">
         <v>11</v>
@@ -17208,7 +17208,7 @@
         <v>46118.836805555555</v>
       </c>
       <c r="J595">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K595" t="s">
         <v>11</v>
@@ -17237,7 +17237,7 @@
         <v>46118.837500000001</v>
       </c>
       <c r="J596">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K596" t="s">
         <v>11</v>
@@ -17302,7 +17302,7 @@
         <v>46118.838194444441</v>
       </c>
       <c r="J599">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K599" t="s">
         <v>11</v>
@@ -17389,7 +17389,7 @@
         <v>46118.839583333334</v>
       </c>
       <c r="J602">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K602" t="s">
         <v>11</v>
@@ -17447,7 +17447,7 @@
         <v>46118.840277777781</v>
       </c>
       <c r="J604">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K604" t="s">
         <v>11</v>
@@ -17525,16 +17525,16 @@
         <v>86</v>
       </c>
       <c r="G607" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H607" s="2">
-        <v>0</v>
+        <v>7.6736111111111111E-3</v>
       </c>
       <c r="I607" s="1">
         <v>46118.841666666667</v>
       </c>
       <c r="J607">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K607" t="s">
         <v>11</v>
@@ -17563,7 +17563,7 @@
         <v>46118.841666666667</v>
       </c>
       <c r="J608">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K608" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BB7BDD-77CC-42E5-BEE5-872FBEEF4CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9AD955-6583-4160-98FD-0038C7C26CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="89">
   <si>
     <t>Company Name</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>Jeremy Myers</t>
+  </si>
+  <si>
+    <t>Drew Templet</t>
   </si>
 </sst>
 </file>
@@ -16879,7 +16882,7 @@
         <v>46118.813078703701</v>
       </c>
       <c r="J583">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K583" t="s">
         <v>11</v>
@@ -16937,7 +16940,7 @@
         <v>46118.813773148147</v>
       </c>
       <c r="J585">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K585" t="s">
         <v>11</v>
@@ -16966,7 +16969,7 @@
         <v>46118.814467592594</v>
       </c>
       <c r="J586">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K586" t="s">
         <v>11</v>
@@ -17143,7 +17146,7 @@
         <v>46118.836111111108</v>
       </c>
       <c r="J592">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K592" t="s">
         <v>11</v>
@@ -17208,7 +17211,7 @@
         <v>46118.836805555555</v>
       </c>
       <c r="J595">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K595" t="s">
         <v>11</v>
@@ -17237,7 +17240,7 @@
         <v>46118.837500000001</v>
       </c>
       <c r="J596">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K596" t="s">
         <v>11</v>
@@ -17293,48 +17296,26 @@
         <v>86</v>
       </c>
       <c r="G599" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H599" s="2">
-        <v>0</v>
+        <v>5.5208333333333333E-3</v>
       </c>
       <c r="I599" s="1">
         <v>46118.838194444441</v>
       </c>
       <c r="J599">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K599" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="600" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B600" t="s">
-        <v>35</v>
-      </c>
-      <c r="C600">
-        <v>3726</v>
-      </c>
-      <c r="D600" t="s">
-        <v>79</v>
-      </c>
-      <c r="F600" t="s">
-        <v>86</v>
-      </c>
-      <c r="G600" t="s">
-        <v>10</v>
-      </c>
-      <c r="H600" s="2">
-        <v>1.0798611111111111E-2</v>
-      </c>
-      <c r="I600" s="1">
-        <v>46118.838888888888</v>
-      </c>
-      <c r="J600">
-        <v>1</v>
-      </c>
+      <c r="H600" s="2"/>
+      <c r="I600" s="1"/>
       <c r="K600" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="601" spans="2:11" x14ac:dyDescent="0.25">
@@ -17342,10 +17323,10 @@
         <v>35</v>
       </c>
       <c r="C601">
-        <v>614</v>
+        <v>3726</v>
       </c>
       <c r="D601" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="F601" t="s">
         <v>86</v>
@@ -17354,13 +17335,13 @@
         <v>10</v>
       </c>
       <c r="H601" s="2">
-        <v>8.518518518518519E-3</v>
+        <v>1.0798611111111111E-2</v>
       </c>
       <c r="I601" s="1">
         <v>46118.838888888888</v>
       </c>
       <c r="J601">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K601" t="s">
         <v>11</v>
@@ -17371,25 +17352,25 @@
         <v>35</v>
       </c>
       <c r="C602">
-        <v>772</v>
+        <v>614</v>
       </c>
       <c r="D602" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F602" t="s">
         <v>86</v>
       </c>
       <c r="G602" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H602" s="2">
-        <v>0</v>
+        <v>8.518518518518519E-3</v>
       </c>
       <c r="I602" s="1">
-        <v>46118.839583333334</v>
+        <v>46118.838888888888</v>
       </c>
       <c r="J602">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K602" t="s">
         <v>11</v>
@@ -17400,25 +17381,25 @@
         <v>35</v>
       </c>
       <c r="C603">
-        <v>623</v>
+        <v>772</v>
       </c>
       <c r="D603" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F603" t="s">
         <v>86</v>
       </c>
       <c r="G603" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H603" s="2">
-        <v>8.8541666666666664E-3</v>
+        <v>0</v>
       </c>
       <c r="I603" s="1">
         <v>46118.839583333334</v>
       </c>
       <c r="J603">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K603" t="s">
         <v>11</v>
@@ -17429,25 +17410,25 @@
         <v>35</v>
       </c>
       <c r="C604">
-        <v>72</v>
+        <v>623</v>
       </c>
       <c r="D604" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F604" t="s">
         <v>86</v>
       </c>
       <c r="G604" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H604" s="2">
-        <v>0</v>
+        <v>8.8541666666666664E-3</v>
       </c>
       <c r="I604" s="1">
-        <v>46118.840277777781</v>
+        <v>46118.839583333334</v>
       </c>
       <c r="J604">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K604" t="s">
         <v>11</v>
@@ -17458,25 +17439,25 @@
         <v>35</v>
       </c>
       <c r="C605">
-        <v>245</v>
+        <v>72</v>
       </c>
       <c r="D605" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F605" t="s">
         <v>86</v>
       </c>
       <c r="G605" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H605" s="2">
-        <v>9.3865740740740732E-3</v>
+        <v>0</v>
       </c>
       <c r="I605" s="1">
-        <v>46118.84097222222</v>
+        <v>46118.840277777781</v>
       </c>
       <c r="J605">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K605" t="s">
         <v>11</v>
@@ -17487,10 +17468,10 @@
         <v>35</v>
       </c>
       <c r="C606">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="D606" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F606" t="s">
         <v>86</v>
@@ -17499,13 +17480,13 @@
         <v>10</v>
       </c>
       <c r="H606" s="2">
-        <v>8.8078703703703704E-3</v>
+        <v>9.3865740740740732E-3</v>
       </c>
       <c r="I606" s="1">
         <v>46118.84097222222</v>
       </c>
       <c r="J606">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K606" t="s">
         <v>11</v>
@@ -17516,10 +17497,10 @@
         <v>35</v>
       </c>
       <c r="C607">
-        <v>3818</v>
+        <v>84</v>
       </c>
       <c r="D607" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F607" t="s">
         <v>86</v>
@@ -17528,13 +17509,13 @@
         <v>10</v>
       </c>
       <c r="H607" s="2">
-        <v>7.6736111111111111E-3</v>
+        <v>8.8078703703703704E-3</v>
       </c>
       <c r="I607" s="1">
-        <v>46118.841666666667</v>
+        <v>46118.84097222222</v>
       </c>
       <c r="J607">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K607" t="s">
         <v>11</v>
@@ -17545,19 +17526,19 @@
         <v>35</v>
       </c>
       <c r="C608">
-        <v>80</v>
+        <v>3818</v>
       </c>
       <c r="D608" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F608" t="s">
         <v>86</v>
       </c>
       <c r="G608" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H608" s="2">
-        <v>0</v>
+        <v>7.6736111111111111E-3</v>
       </c>
       <c r="I608" s="1">
         <v>46118.841666666667</v>
@@ -17569,130 +17550,765 @@
         <v>11</v>
       </c>
     </row>
-    <row r="609" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H609" s="2"/>
-      <c r="I609" s="1"/>
-    </row>
-    <row r="610" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H610" s="2"/>
-      <c r="I610" s="1"/>
-    </row>
-    <row r="611" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H611" s="2"/>
-      <c r="I611" s="1"/>
-    </row>
-    <row r="612" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H612" s="2"/>
-      <c r="I612" s="1"/>
-    </row>
-    <row r="613" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H613" s="2"/>
-      <c r="I613" s="1"/>
-    </row>
-    <row r="614" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I614" s="1"/>
-    </row>
-    <row r="615" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H615" s="2"/>
-      <c r="I615" s="1"/>
-    </row>
-    <row r="616" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H616" s="2"/>
-      <c r="I616" s="1"/>
-    </row>
-    <row r="617" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H617" s="2"/>
-      <c r="I617" s="1"/>
-    </row>
-    <row r="618" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H618" s="2"/>
-      <c r="I618" s="1"/>
-    </row>
-    <row r="619" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H619" s="2"/>
-      <c r="I619" s="1"/>
-    </row>
-    <row r="620" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H620" s="2"/>
-      <c r="I620" s="1"/>
-    </row>
-    <row r="621" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B609" t="s">
+        <v>35</v>
+      </c>
+      <c r="C609">
+        <v>80</v>
+      </c>
+      <c r="D609" t="s">
+        <v>56</v>
+      </c>
+      <c r="F609" t="s">
+        <v>86</v>
+      </c>
+      <c r="G609" t="s">
+        <v>13</v>
+      </c>
+      <c r="H609" s="2">
+        <v>0</v>
+      </c>
+      <c r="I609" s="1">
+        <v>46118.841666666667</v>
+      </c>
+      <c r="J609">
+        <v>4</v>
+      </c>
+      <c r="K609" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="610" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B610" t="s">
+        <v>35</v>
+      </c>
+      <c r="C610">
+        <v>77</v>
+      </c>
+      <c r="D610" t="s">
+        <v>36</v>
+      </c>
+      <c r="F610" t="s">
+        <v>17</v>
+      </c>
+      <c r="G610" t="s">
+        <v>13</v>
+      </c>
+      <c r="H610" s="2">
+        <v>0</v>
+      </c>
+      <c r="I610" s="1">
+        <v>46146.730902777781</v>
+      </c>
+      <c r="J610">
+        <v>0</v>
+      </c>
+      <c r="K610" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="611" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B611" t="s">
+        <v>35</v>
+      </c>
+      <c r="C611">
+        <v>745</v>
+      </c>
+      <c r="D611" t="s">
+        <v>38</v>
+      </c>
+      <c r="F611" t="s">
+        <v>17</v>
+      </c>
+      <c r="G611" t="s">
+        <v>10</v>
+      </c>
+      <c r="H611" s="2">
+        <v>4.5717592592592589E-3</v>
+      </c>
+      <c r="I611" s="1">
+        <v>46146.730902777781</v>
+      </c>
+      <c r="J611">
+        <v>0</v>
+      </c>
+      <c r="K611" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="612" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B612" t="s">
+        <v>35</v>
+      </c>
+      <c r="C612">
+        <v>622</v>
+      </c>
+      <c r="D612" t="s">
+        <v>39</v>
+      </c>
+      <c r="F612" t="s">
+        <v>17</v>
+      </c>
+      <c r="G612" t="s">
+        <v>13</v>
+      </c>
+      <c r="H612" s="2">
+        <v>0</v>
+      </c>
+      <c r="I612" s="1">
+        <v>46146.73159722222</v>
+      </c>
+      <c r="J612">
+        <v>0</v>
+      </c>
+      <c r="K612" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="613" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B613" t="s">
+        <v>35</v>
+      </c>
+      <c r="C613">
+        <v>5217</v>
+      </c>
+      <c r="D613" t="s">
+        <v>85</v>
+      </c>
+      <c r="F613" t="s">
+        <v>17</v>
+      </c>
+      <c r="G613" t="s">
+        <v>13</v>
+      </c>
+      <c r="H613" s="2">
+        <v>0</v>
+      </c>
+      <c r="I613" s="1">
+        <v>46146.732291666667</v>
+      </c>
+      <c r="J613">
+        <v>0</v>
+      </c>
+      <c r="K613" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="614" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B614" t="s">
+        <v>35</v>
+      </c>
+      <c r="C614">
+        <v>5180</v>
+      </c>
+      <c r="D614" t="s">
+        <v>88</v>
+      </c>
+      <c r="F614" t="s">
+        <v>17</v>
+      </c>
+      <c r="G614" t="s">
+        <v>13</v>
+      </c>
+      <c r="H614">
+        <v>0</v>
+      </c>
+      <c r="I614" s="1">
+        <v>46146.732291666667</v>
+      </c>
+      <c r="J614">
+        <v>0</v>
+      </c>
+      <c r="K614" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="615" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B615" t="s">
+        <v>35</v>
+      </c>
+      <c r="C615">
+        <v>204</v>
+      </c>
+      <c r="D615" t="s">
+        <v>40</v>
+      </c>
+      <c r="F615" t="s">
+        <v>17</v>
+      </c>
+      <c r="G615" t="s">
+        <v>13</v>
+      </c>
+      <c r="H615" s="2">
+        <v>0</v>
+      </c>
+      <c r="I615" s="1">
+        <v>46146.732986111114</v>
+      </c>
+      <c r="J615">
+        <v>0</v>
+      </c>
+      <c r="K615" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="616" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B616" t="s">
+        <v>35</v>
+      </c>
+      <c r="C616">
+        <v>205</v>
+      </c>
+      <c r="D616" t="s">
+        <v>41</v>
+      </c>
+      <c r="F616" t="s">
+        <v>17</v>
+      </c>
+      <c r="G616" t="s">
+        <v>13</v>
+      </c>
+      <c r="H616" s="2">
+        <v>0</v>
+      </c>
+      <c r="I616" s="1">
+        <v>46146.732986111114</v>
+      </c>
+      <c r="J616">
+        <v>0</v>
+      </c>
+      <c r="K616" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="617" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B617" t="s">
+        <v>35</v>
+      </c>
+      <c r="C617">
+        <v>3741</v>
+      </c>
+      <c r="D617" t="s">
+        <v>78</v>
+      </c>
+      <c r="E617" t="s">
+        <v>63</v>
+      </c>
+      <c r="F617" t="s">
+        <v>17</v>
+      </c>
+      <c r="G617" t="s">
+        <v>13</v>
+      </c>
+      <c r="H617" s="2">
+        <v>0</v>
+      </c>
+      <c r="I617" s="1">
+        <v>46146.710185185184</v>
+      </c>
+      <c r="J617">
+        <v>0</v>
+      </c>
+      <c r="K617" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="618" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B618" t="s">
+        <v>35</v>
+      </c>
+      <c r="C618">
+        <v>78</v>
+      </c>
+      <c r="D618" t="s">
+        <v>42</v>
+      </c>
+      <c r="F618" t="s">
+        <v>17</v>
+      </c>
+      <c r="G618" t="s">
+        <v>13</v>
+      </c>
+      <c r="H618" s="2">
+        <v>0</v>
+      </c>
+      <c r="I618" s="1">
+        <v>46146.710879629631</v>
+      </c>
+      <c r="J618">
+        <v>0</v>
+      </c>
+      <c r="K618" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="619" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B619" t="s">
+        <v>35</v>
+      </c>
+      <c r="C619">
+        <v>73</v>
+      </c>
+      <c r="D619" t="s">
+        <v>44</v>
+      </c>
+      <c r="F619" t="s">
+        <v>17</v>
+      </c>
+      <c r="G619" t="s">
+        <v>13</v>
+      </c>
+      <c r="H619" s="2">
+        <v>0</v>
+      </c>
+      <c r="I619" s="1">
+        <v>46146.711574074077</v>
+      </c>
+      <c r="J619">
+        <v>0</v>
+      </c>
+      <c r="K619" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="620" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B620" t="s">
+        <v>35</v>
+      </c>
+      <c r="C620">
+        <v>5037</v>
+      </c>
+      <c r="D620" t="s">
+        <v>84</v>
+      </c>
+      <c r="F620" t="s">
+        <v>17</v>
+      </c>
+      <c r="G620" t="s">
+        <v>14</v>
+      </c>
+      <c r="H620" s="2">
+        <v>0</v>
+      </c>
+      <c r="I620" s="1">
+        <v>46146.711574074077</v>
+      </c>
+      <c r="J620">
+        <v>0</v>
+      </c>
+      <c r="K620" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="621" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H621" s="2"/>
       <c r="I621" s="1"/>
-    </row>
-    <row r="622" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H622" s="2"/>
-      <c r="I622" s="1"/>
-    </row>
-    <row r="623" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H623" s="2"/>
-      <c r="I623" s="1"/>
-    </row>
-    <row r="624" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H624" s="2"/>
-      <c r="I624" s="1"/>
-    </row>
-    <row r="625" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K621" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="622" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B622" t="s">
+        <v>35</v>
+      </c>
+      <c r="C622">
+        <v>75</v>
+      </c>
+      <c r="D622" t="s">
+        <v>46</v>
+      </c>
+      <c r="F622" t="s">
+        <v>17</v>
+      </c>
+      <c r="G622" t="s">
+        <v>13</v>
+      </c>
+      <c r="H622" s="2">
+        <v>0</v>
+      </c>
+      <c r="I622" s="1">
+        <v>46146.712268518517</v>
+      </c>
+      <c r="J622">
+        <v>0</v>
+      </c>
+      <c r="K622" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="623" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B623" t="s">
+        <v>35</v>
+      </c>
+      <c r="C623">
+        <v>5409</v>
+      </c>
+      <c r="D623" t="s">
+        <v>87</v>
+      </c>
+      <c r="F623" t="s">
+        <v>17</v>
+      </c>
+      <c r="G623" t="s">
+        <v>13</v>
+      </c>
+      <c r="H623" s="2">
+        <v>0</v>
+      </c>
+      <c r="I623" s="1">
+        <v>46146.712268518517</v>
+      </c>
+      <c r="J623">
+        <v>0</v>
+      </c>
+      <c r="K623" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="624" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B624" t="s">
+        <v>35</v>
+      </c>
+      <c r="C624">
+        <v>5350</v>
+      </c>
+      <c r="D624" t="s">
+        <v>87</v>
+      </c>
+      <c r="F624" t="s">
+        <v>17</v>
+      </c>
+      <c r="G624" t="s">
+        <v>12</v>
+      </c>
+      <c r="H624" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="I624" s="1">
+        <v>46146.712962962964</v>
+      </c>
+      <c r="J624">
+        <v>0</v>
+      </c>
+      <c r="K624" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="625" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H625" s="2"/>
       <c r="I625" s="1"/>
-    </row>
-    <row r="626" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H626" s="2"/>
-      <c r="I626" s="1"/>
-    </row>
-    <row r="627" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H627" s="2"/>
-      <c r="I627" s="1"/>
-    </row>
-    <row r="628" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H628" s="2"/>
-      <c r="I628" s="1"/>
-    </row>
-    <row r="629" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H629" s="2"/>
-      <c r="I629" s="1"/>
-    </row>
-    <row r="630" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H630" s="2"/>
-      <c r="I630" s="1"/>
-    </row>
-    <row r="631" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H631" s="2"/>
-      <c r="I631" s="1"/>
-    </row>
-    <row r="632" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H632" s="2"/>
-      <c r="I632" s="1"/>
-    </row>
-    <row r="633" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H633" s="2"/>
-      <c r="I633" s="1"/>
-    </row>
-    <row r="634" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H634" s="2"/>
-      <c r="I634" s="1"/>
-    </row>
-    <row r="635" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H635" s="2"/>
-      <c r="I635" s="1"/>
-    </row>
-    <row r="636" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K625" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="626" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B626" t="s">
+        <v>35</v>
+      </c>
+      <c r="C626">
+        <v>76</v>
+      </c>
+      <c r="D626" t="s">
+        <v>47</v>
+      </c>
+      <c r="F626" t="s">
+        <v>17</v>
+      </c>
+      <c r="G626" t="s">
+        <v>13</v>
+      </c>
+      <c r="H626" s="2">
+        <v>0</v>
+      </c>
+      <c r="I626" s="1">
+        <v>46146.71365740741</v>
+      </c>
+      <c r="J626">
+        <v>0</v>
+      </c>
+      <c r="K626" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="627" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B627" t="s">
+        <v>35</v>
+      </c>
+      <c r="C627">
+        <v>3726</v>
+      </c>
+      <c r="D627" t="s">
+        <v>79</v>
+      </c>
+      <c r="F627" t="s">
+        <v>17</v>
+      </c>
+      <c r="G627" t="s">
+        <v>13</v>
+      </c>
+      <c r="H627" s="2">
+        <v>0</v>
+      </c>
+      <c r="I627" s="1">
+        <v>46146.71365740741</v>
+      </c>
+      <c r="J627">
+        <v>0</v>
+      </c>
+      <c r="K627" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="628" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B628" t="s">
+        <v>35</v>
+      </c>
+      <c r="C628">
+        <v>614</v>
+      </c>
+      <c r="D628" t="s">
+        <v>48</v>
+      </c>
+      <c r="F628" t="s">
+        <v>17</v>
+      </c>
+      <c r="G628" t="s">
+        <v>13</v>
+      </c>
+      <c r="H628" s="2">
+        <v>0</v>
+      </c>
+      <c r="I628" s="1">
+        <v>46146.71435185185</v>
+      </c>
+      <c r="J628">
+        <v>0</v>
+      </c>
+      <c r="K628" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="629" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B629" t="s">
+        <v>35</v>
+      </c>
+      <c r="C629">
+        <v>772</v>
+      </c>
+      <c r="D629" t="s">
+        <v>49</v>
+      </c>
+      <c r="F629" t="s">
+        <v>17</v>
+      </c>
+      <c r="G629" t="s">
+        <v>13</v>
+      </c>
+      <c r="H629" s="2">
+        <v>0</v>
+      </c>
+      <c r="I629" s="1">
+        <v>46146.715046296296</v>
+      </c>
+      <c r="J629">
+        <v>0</v>
+      </c>
+      <c r="K629" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="630" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B630" t="s">
+        <v>35</v>
+      </c>
+      <c r="C630">
+        <v>623</v>
+      </c>
+      <c r="D630" t="s">
+        <v>50</v>
+      </c>
+      <c r="F630" t="s">
+        <v>17</v>
+      </c>
+      <c r="G630" t="s">
+        <v>13</v>
+      </c>
+      <c r="H630" s="2">
+        <v>0</v>
+      </c>
+      <c r="I630" s="1">
+        <v>46146.715046296296</v>
+      </c>
+      <c r="J630">
+        <v>0</v>
+      </c>
+      <c r="K630" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="631" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B631" t="s">
+        <v>35</v>
+      </c>
+      <c r="C631">
+        <v>72</v>
+      </c>
+      <c r="D631" t="s">
+        <v>51</v>
+      </c>
+      <c r="F631" t="s">
+        <v>17</v>
+      </c>
+      <c r="G631" t="s">
+        <v>13</v>
+      </c>
+      <c r="H631" s="2">
+        <v>0</v>
+      </c>
+      <c r="I631" s="1">
+        <v>46146.715740740743</v>
+      </c>
+      <c r="J631">
+        <v>0</v>
+      </c>
+      <c r="K631" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="632" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B632" t="s">
+        <v>35</v>
+      </c>
+      <c r="C632">
+        <v>245</v>
+      </c>
+      <c r="D632" t="s">
+        <v>52</v>
+      </c>
+      <c r="F632" t="s">
+        <v>17</v>
+      </c>
+      <c r="G632" t="s">
+        <v>13</v>
+      </c>
+      <c r="H632" s="2">
+        <v>0</v>
+      </c>
+      <c r="I632" s="1">
+        <v>46146.716435185182</v>
+      </c>
+      <c r="J632">
+        <v>0</v>
+      </c>
+      <c r="K632" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="633" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B633" t="s">
+        <v>35</v>
+      </c>
+      <c r="C633">
+        <v>84</v>
+      </c>
+      <c r="D633" t="s">
+        <v>55</v>
+      </c>
+      <c r="F633" t="s">
+        <v>17</v>
+      </c>
+      <c r="G633" t="s">
+        <v>13</v>
+      </c>
+      <c r="H633" s="2">
+        <v>0</v>
+      </c>
+      <c r="I633" s="1">
+        <v>46146.716435185182</v>
+      </c>
+      <c r="J633">
+        <v>0</v>
+      </c>
+      <c r="K633" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="634" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B634" t="s">
+        <v>35</v>
+      </c>
+      <c r="C634">
+        <v>3818</v>
+      </c>
+      <c r="D634" t="s">
+        <v>81</v>
+      </c>
+      <c r="F634" t="s">
+        <v>17</v>
+      </c>
+      <c r="G634" t="s">
+        <v>13</v>
+      </c>
+      <c r="H634" s="2">
+        <v>0</v>
+      </c>
+      <c r="I634" s="1">
+        <v>46146.717129629629</v>
+      </c>
+      <c r="J634">
+        <v>0</v>
+      </c>
+      <c r="K634" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="635" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B635" t="s">
+        <v>35</v>
+      </c>
+      <c r="C635">
+        <v>80</v>
+      </c>
+      <c r="D635" t="s">
+        <v>56</v>
+      </c>
+      <c r="F635" t="s">
+        <v>17</v>
+      </c>
+      <c r="G635" t="s">
+        <v>13</v>
+      </c>
+      <c r="H635" s="2">
+        <v>0</v>
+      </c>
+      <c r="I635" s="1">
+        <v>46146.717824074076</v>
+      </c>
+      <c r="J635">
+        <v>0</v>
+      </c>
+      <c r="K635" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="636" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H636" s="2"/>
       <c r="I636" s="1"/>
     </row>
-    <row r="637" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H637" s="2"/>
       <c r="I637" s="1"/>
     </row>
-    <row r="638" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H638" s="2"/>
       <c r="I638" s="1"/>
     </row>
-    <row r="639" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H639" s="2"/>
       <c r="I639" s="1"/>
     </row>
-    <row r="640" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H640" s="2"/>
       <c r="I640" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9AD955-6583-4160-98FD-0038C7C26CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20B5811-6D48-4AA3-AE33-7B5ACC04E768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -16873,16 +16873,16 @@
         <v>86</v>
       </c>
       <c r="G583" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H583" s="2">
-        <v>0</v>
+        <v>7.5347222222222222E-3</v>
       </c>
       <c r="I583" s="1">
         <v>46118.813078703701</v>
       </c>
       <c r="J583">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K583" t="s">
         <v>11</v>
@@ -16940,7 +16940,7 @@
         <v>46118.813773148147</v>
       </c>
       <c r="J585">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K585" t="s">
         <v>11</v>
@@ -16969,7 +16969,7 @@
         <v>46118.814467592594</v>
       </c>
       <c r="J586">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K586" t="s">
         <v>11</v>
@@ -17146,7 +17146,7 @@
         <v>46118.836111111108</v>
       </c>
       <c r="J592">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K592" t="s">
         <v>11</v>
@@ -17211,7 +17211,7 @@
         <v>46118.836805555555</v>
       </c>
       <c r="J595">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K595" t="s">
         <v>11</v>
@@ -17240,7 +17240,7 @@
         <v>46118.837500000001</v>
       </c>
       <c r="J596">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K596" t="s">
         <v>11</v>
@@ -17390,16 +17390,16 @@
         <v>86</v>
       </c>
       <c r="G603" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H603" s="2">
-        <v>0</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I603" s="1">
         <v>46118.839583333334</v>
       </c>
       <c r="J603">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K603" t="s">
         <v>11</v>
@@ -17457,7 +17457,7 @@
         <v>46118.840277777781</v>
       </c>
       <c r="J605">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K605" t="s">
         <v>11</v>
@@ -17573,7 +17573,7 @@
         <v>46118.841666666667</v>
       </c>
       <c r="J609">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K609" t="s">
         <v>11</v>
@@ -17593,10 +17593,10 @@
         <v>17</v>
       </c>
       <c r="G610" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H610" s="2">
-        <v>0</v>
+        <v>4.2592592592592595E-3</v>
       </c>
       <c r="I610" s="1">
         <v>46146.730902777781</v>
@@ -17738,10 +17738,10 @@
         <v>17</v>
       </c>
       <c r="G615" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H615" s="2">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I615" s="1">
         <v>46146.732986111114</v>
@@ -17767,10 +17767,10 @@
         <v>17</v>
       </c>
       <c r="G616" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H616" s="2">
-        <v>0</v>
+        <v>5.1967592592592595E-3</v>
       </c>
       <c r="I616" s="1">
         <v>46146.732986111114</v>
@@ -17828,10 +17828,10 @@
         <v>17</v>
       </c>
       <c r="G618" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H618" s="2">
-        <v>0</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I618" s="1">
         <v>46146.710879629631</v>
@@ -17980,10 +17980,10 @@
         <v>17</v>
       </c>
       <c r="G624" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H624" s="2">
-        <v>2.3148148148148149E-4</v>
+        <v>9.3981481481481485E-3</v>
       </c>
       <c r="I624" s="1">
         <v>46146.712962962964</v>
@@ -17996,10 +17996,32 @@
       </c>
     </row>
     <row r="625" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H625" s="2"/>
-      <c r="I625" s="1"/>
+      <c r="B625" t="s">
+        <v>35</v>
+      </c>
+      <c r="C625">
+        <v>76</v>
+      </c>
+      <c r="D625" t="s">
+        <v>47</v>
+      </c>
+      <c r="F625" t="s">
+        <v>17</v>
+      </c>
+      <c r="G625" t="s">
+        <v>13</v>
+      </c>
+      <c r="H625" s="2">
+        <v>0</v>
+      </c>
+      <c r="I625" s="1">
+        <v>46146.71365740741</v>
+      </c>
+      <c r="J625">
+        <v>0</v>
+      </c>
       <c r="K625" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="626" spans="2:11" x14ac:dyDescent="0.25">
@@ -18007,19 +18029,19 @@
         <v>35</v>
       </c>
       <c r="C626">
-        <v>76</v>
+        <v>3726</v>
       </c>
       <c r="D626" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F626" t="s">
         <v>17</v>
       </c>
       <c r="G626" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H626" s="2">
-        <v>0</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I626" s="1">
         <v>46146.71365740741</v>
@@ -18036,10 +18058,10 @@
         <v>35</v>
       </c>
       <c r="C627">
-        <v>3726</v>
+        <v>614</v>
       </c>
       <c r="D627" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="F627" t="s">
         <v>17</v>
@@ -18051,7 +18073,7 @@
         <v>0</v>
       </c>
       <c r="I627" s="1">
-        <v>46146.71365740741</v>
+        <v>46146.71435185185</v>
       </c>
       <c r="J627">
         <v>0</v>
@@ -18065,22 +18087,22 @@
         <v>35</v>
       </c>
       <c r="C628">
-        <v>614</v>
+        <v>772</v>
       </c>
       <c r="D628" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F628" t="s">
         <v>17</v>
       </c>
       <c r="G628" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H628" s="2">
-        <v>0</v>
+        <v>4.9305555555555552E-3</v>
       </c>
       <c r="I628" s="1">
-        <v>46146.71435185185</v>
+        <v>46146.715046296296</v>
       </c>
       <c r="J628">
         <v>0</v>
@@ -18094,19 +18116,19 @@
         <v>35</v>
       </c>
       <c r="C629">
-        <v>772</v>
+        <v>623</v>
       </c>
       <c r="D629" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F629" t="s">
         <v>17</v>
       </c>
       <c r="G629" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H629" s="2">
-        <v>0</v>
+        <v>5.2893518518518515E-3</v>
       </c>
       <c r="I629" s="1">
         <v>46146.715046296296</v>
@@ -18123,10 +18145,10 @@
         <v>35</v>
       </c>
       <c r="C630">
-        <v>623</v>
+        <v>72</v>
       </c>
       <c r="D630" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F630" t="s">
         <v>17</v>
@@ -18138,7 +18160,7 @@
         <v>0</v>
       </c>
       <c r="I630" s="1">
-        <v>46146.715046296296</v>
+        <v>46146.715740740743</v>
       </c>
       <c r="J630">
         <v>0</v>
@@ -18152,22 +18174,22 @@
         <v>35</v>
       </c>
       <c r="C631">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="D631" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F631" t="s">
         <v>17</v>
       </c>
       <c r="G631" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H631" s="2">
-        <v>0</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I631" s="1">
-        <v>46146.715740740743</v>
+        <v>46146.716435185182</v>
       </c>
       <c r="J631">
         <v>0</v>
@@ -18177,32 +18199,10 @@
       </c>
     </row>
     <row r="632" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B632" t="s">
-        <v>35</v>
-      </c>
-      <c r="C632">
-        <v>245</v>
-      </c>
-      <c r="D632" t="s">
-        <v>52</v>
-      </c>
-      <c r="F632" t="s">
-        <v>17</v>
-      </c>
-      <c r="G632" t="s">
-        <v>13</v>
-      </c>
-      <c r="H632" s="2">
-        <v>0</v>
-      </c>
-      <c r="I632" s="1">
-        <v>46146.716435185182</v>
-      </c>
-      <c r="J632">
-        <v>0</v>
-      </c>
+      <c r="H632" s="2"/>
+      <c r="I632" s="1"/>
       <c r="K632" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="633" spans="2:11" x14ac:dyDescent="0.25">
@@ -18248,10 +18248,10 @@
         <v>17</v>
       </c>
       <c r="G634" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H634" s="2">
-        <v>0</v>
+        <v>8.6574074074074071E-3</v>
       </c>
       <c r="I634" s="1">
         <v>46146.717129629629</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B69164-DC85-4B5E-AF51-247C3BBACA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBA63A6-FEDE-4993-B8DC-2938E2EE28E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -17660,7 +17660,7 @@
         <v>46146.73159722222</v>
       </c>
       <c r="J612">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K612" t="s">
         <v>11</v>
@@ -17718,7 +17718,7 @@
         <v>46146.732291666667</v>
       </c>
       <c r="J614">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K614" t="s">
         <v>11</v>
@@ -17799,16 +17799,16 @@
         <v>17</v>
       </c>
       <c r="G617" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H617" s="2">
-        <v>0</v>
+        <v>6.6782407407407407E-3</v>
       </c>
       <c r="I617" s="1">
         <v>46146.710185185184</v>
       </c>
       <c r="J617">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K617" t="s">
         <v>11</v>
@@ -17866,7 +17866,7 @@
         <v>46146.711574074077</v>
       </c>
       <c r="J619">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K619" t="s">
         <v>11</v>
@@ -17922,16 +17922,16 @@
         <v>17</v>
       </c>
       <c r="G622" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H622" s="2">
-        <v>0</v>
+        <v>4.3287037037037035E-3</v>
       </c>
       <c r="I622" s="1">
         <v>46146.712268518517</v>
       </c>
       <c r="J622">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K622" t="s">
         <v>11</v>
@@ -17960,7 +17960,7 @@
         <v>46146.712268518517</v>
       </c>
       <c r="J623">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K623" t="s">
         <v>11</v>
@@ -18018,7 +18018,7 @@
         <v>46146.71365740741</v>
       </c>
       <c r="J625">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K625" t="s">
         <v>11</v>
@@ -18163,7 +18163,7 @@
         <v>46146.715740740743</v>
       </c>
       <c r="J630">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K630" t="s">
         <v>11</v>
@@ -18219,10 +18219,10 @@
         <v>17</v>
       </c>
       <c r="G633" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H633" s="2">
-        <v>0</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I633" s="1">
         <v>46146.716435185182</v>
@@ -18286,7 +18286,7 @@
         <v>46146.717824074076</v>
       </c>
       <c r="J635">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K635" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFADB185-71E1-479F-8D8B-ABF4ADE1EF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAE63E0-95C9-437B-A782-B4B026AFE3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5929</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5925</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="92">
   <si>
     <t>Company Name</t>
   </si>
@@ -688,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K5929"/>
+  <dimension ref="B1:K5925"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -17911,10 +17911,32 @@
       </c>
     </row>
     <row r="621" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H621" s="2"/>
-      <c r="I621" s="1"/>
+      <c r="B621" t="s">
+        <v>35</v>
+      </c>
+      <c r="C621">
+        <v>75</v>
+      </c>
+      <c r="D621" t="s">
+        <v>46</v>
+      </c>
+      <c r="F621" t="s">
+        <v>17</v>
+      </c>
+      <c r="G621" t="s">
+        <v>10</v>
+      </c>
+      <c r="H621" s="2">
+        <v>4.3287037037037035E-3</v>
+      </c>
+      <c r="I621" s="1">
+        <v>46146.712268518517</v>
+      </c>
+      <c r="J621">
+        <v>2</v>
+      </c>
       <c r="K621" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="622" spans="2:11" x14ac:dyDescent="0.3">
@@ -17922,10 +17944,10 @@
         <v>35</v>
       </c>
       <c r="C622">
-        <v>75</v>
+        <v>5350</v>
       </c>
       <c r="D622" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="F622" t="s">
         <v>17</v>
@@ -17934,13 +17956,13 @@
         <v>10</v>
       </c>
       <c r="H622" s="2">
-        <v>4.3287037037037035E-3</v>
+        <v>9.3981481481481485E-3</v>
       </c>
       <c r="I622" s="1">
-        <v>46146.712268518517</v>
+        <v>46146.712962962964</v>
       </c>
       <c r="J622">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K622" t="s">
         <v>11</v>
@@ -17951,35 +17973,57 @@
         <v>35</v>
       </c>
       <c r="C623">
-        <v>5409</v>
+        <v>76</v>
       </c>
       <c r="D623" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F623" t="s">
         <v>17</v>
       </c>
       <c r="G623" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H623" s="2">
-        <v>1.9675925925925926E-4</v>
+        <v>0</v>
       </c>
       <c r="I623" s="1">
-        <v>46146.712268518517</v>
+        <v>46146.71365740741</v>
       </c>
       <c r="J623">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K623" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="624" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H624" s="2"/>
-      <c r="I624" s="1"/>
+      <c r="B624" t="s">
+        <v>35</v>
+      </c>
+      <c r="C624">
+        <v>3726</v>
+      </c>
+      <c r="D624" t="s">
+        <v>79</v>
+      </c>
+      <c r="F624" t="s">
+        <v>17</v>
+      </c>
+      <c r="G624" t="s">
+        <v>10</v>
+      </c>
+      <c r="H624" s="2">
+        <v>4.5717592592592589E-3</v>
+      </c>
+      <c r="I624" s="1">
+        <v>46146.71365740741</v>
+      </c>
+      <c r="J624">
+        <v>0</v>
+      </c>
       <c r="K624" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="625" spans="2:11" x14ac:dyDescent="0.3">
@@ -17987,10 +18031,10 @@
         <v>35</v>
       </c>
       <c r="C625">
-        <v>5350</v>
+        <v>614</v>
       </c>
       <c r="D625" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F625" t="s">
         <v>17</v>
@@ -17999,13 +18043,13 @@
         <v>10</v>
       </c>
       <c r="H625" s="2">
-        <v>9.3981481481481485E-3</v>
+        <v>4.7685185185185183E-3</v>
       </c>
       <c r="I625" s="1">
-        <v>46146.712962962964</v>
+        <v>46146.71435185185</v>
       </c>
       <c r="J625">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K625" t="s">
         <v>11</v>
@@ -18016,25 +18060,25 @@
         <v>35</v>
       </c>
       <c r="C626">
-        <v>76</v>
+        <v>772</v>
       </c>
       <c r="D626" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F626" t="s">
         <v>17</v>
       </c>
       <c r="G626" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H626" s="2">
-        <v>0</v>
+        <v>4.9305555555555552E-3</v>
       </c>
       <c r="I626" s="1">
-        <v>46146.71365740741</v>
+        <v>46146.715046296296</v>
       </c>
       <c r="J626">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K626" t="s">
         <v>11</v>
@@ -18045,10 +18089,10 @@
         <v>35</v>
       </c>
       <c r="C627">
-        <v>3726</v>
+        <v>623</v>
       </c>
       <c r="D627" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="F627" t="s">
         <v>17</v>
@@ -18057,10 +18101,10 @@
         <v>10</v>
       </c>
       <c r="H627" s="2">
-        <v>4.5717592592592589E-3</v>
+        <v>5.2893518518518515E-3</v>
       </c>
       <c r="I627" s="1">
-        <v>46146.71365740741</v>
+        <v>46146.715046296296</v>
       </c>
       <c r="J627">
         <v>0</v>
@@ -18074,25 +18118,25 @@
         <v>35</v>
       </c>
       <c r="C628">
-        <v>614</v>
+        <v>72</v>
       </c>
       <c r="D628" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F628" t="s">
         <v>17</v>
       </c>
       <c r="G628" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H628" s="2">
-        <v>4.7685185185185183E-3</v>
+        <v>0</v>
       </c>
       <c r="I628" s="1">
-        <v>46146.71435185185</v>
+        <v>46146.715740740743</v>
       </c>
       <c r="J628">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K628" t="s">
         <v>11</v>
@@ -18103,22 +18147,22 @@
         <v>35</v>
       </c>
       <c r="C629">
-        <v>772</v>
+        <v>245</v>
       </c>
       <c r="D629" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F629" t="s">
         <v>17</v>
       </c>
       <c r="G629" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H629" s="2">
-        <v>4.9305555555555552E-3</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I629" s="1">
-        <v>46146.715046296296</v>
+        <v>46146.716435185182</v>
       </c>
       <c r="J629">
         <v>0</v>
@@ -18132,10 +18176,10 @@
         <v>35</v>
       </c>
       <c r="C630">
-        <v>623</v>
+        <v>84</v>
       </c>
       <c r="D630" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F630" t="s">
         <v>17</v>
@@ -18144,13 +18188,13 @@
         <v>10</v>
       </c>
       <c r="H630" s="2">
-        <v>5.2893518518518515E-3</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I630" s="1">
-        <v>46146.715046296296</v>
+        <v>46146.716435185182</v>
       </c>
       <c r="J630">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K630" t="s">
         <v>11</v>
@@ -18161,25 +18205,25 @@
         <v>35</v>
       </c>
       <c r="C631">
-        <v>72</v>
+        <v>3818</v>
       </c>
       <c r="D631" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F631" t="s">
         <v>17</v>
       </c>
       <c r="G631" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H631" s="2">
-        <v>0</v>
+        <v>8.6574074074074071E-3</v>
       </c>
       <c r="I631" s="1">
-        <v>46146.715740740743</v>
+        <v>46146.717129629629</v>
       </c>
       <c r="J631">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K631" t="s">
         <v>11</v>
@@ -18190,25 +18234,25 @@
         <v>35</v>
       </c>
       <c r="C632">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="D632" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F632" t="s">
         <v>17</v>
       </c>
       <c r="G632" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H632" s="2">
-        <v>1.9675925925925926E-4</v>
+        <v>0</v>
       </c>
       <c r="I632" s="1">
-        <v>46146.716435185182</v>
+        <v>46146.717824074076</v>
       </c>
       <c r="J632">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K632" t="s">
         <v>11</v>
@@ -18222,61 +18266,17 @@
       </c>
     </row>
     <row r="634" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B634" t="s">
-        <v>35</v>
-      </c>
-      <c r="C634">
-        <v>84</v>
-      </c>
-      <c r="D634" t="s">
-        <v>55</v>
-      </c>
-      <c r="F634" t="s">
-        <v>17</v>
-      </c>
-      <c r="G634" t="s">
-        <v>10</v>
-      </c>
-      <c r="H634" s="2">
-        <v>6.6550925925925927E-3</v>
-      </c>
-      <c r="I634" s="1">
-        <v>46146.716435185182</v>
-      </c>
-      <c r="J634">
-        <v>1</v>
-      </c>
+      <c r="H634" s="2"/>
+      <c r="I634" s="1"/>
       <c r="K634" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="635" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B635" t="s">
-        <v>35</v>
-      </c>
-      <c r="C635">
-        <v>3818</v>
-      </c>
-      <c r="D635" t="s">
-        <v>81</v>
-      </c>
-      <c r="F635" t="s">
-        <v>17</v>
-      </c>
-      <c r="G635" t="s">
-        <v>10</v>
-      </c>
-      <c r="H635" s="2">
-        <v>8.6574074074074071E-3</v>
-      </c>
-      <c r="I635" s="1">
-        <v>46146.717129629629</v>
-      </c>
-      <c r="J635">
-        <v>0</v>
-      </c>
+      <c r="H635" s="2"/>
+      <c r="I635" s="1"/>
       <c r="K635" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="636" spans="2:11" x14ac:dyDescent="0.3">
@@ -18284,13 +18284,13 @@
         <v>35</v>
       </c>
       <c r="C636">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D636" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F636" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="G636" t="s">
         <v>13</v>
@@ -18299,10 +18299,10 @@
         <v>0</v>
       </c>
       <c r="I636" s="1">
-        <v>46146.717824074076</v>
+        <v>46176.418402777781</v>
       </c>
       <c r="J636">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K636" t="s">
         <v>11</v>
@@ -18371,22 +18371,22 @@
         <v>35</v>
       </c>
       <c r="C639">
-        <v>5604</v>
+        <v>622</v>
       </c>
       <c r="D639" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F639" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G639" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H639" s="2">
-        <v>1.3888888888888889E-4</v>
+        <v>0</v>
       </c>
       <c r="I639" s="1">
-        <v>46174.635185185187</v>
+        <v>46176.41909722222</v>
       </c>
       <c r="J639">
         <v>0</v>
@@ -18429,22 +18429,22 @@
         <v>35</v>
       </c>
       <c r="C641">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D641" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F641" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G641" t="s">
         <v>10</v>
       </c>
       <c r="H641" s="2">
-        <v>1.1145833333333334E-2</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I641" s="1">
-        <v>46174.63726851852</v>
+        <v>46176.419791666667</v>
       </c>
       <c r="J641">
         <v>0</v>
@@ -18458,10 +18458,10 @@
         <v>35</v>
       </c>
       <c r="C642">
-        <v>5037</v>
+        <v>205</v>
       </c>
       <c r="D642" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="F642" t="s">
         <v>89</v>
@@ -18470,10 +18470,10 @@
         <v>10</v>
       </c>
       <c r="H642" s="2">
-        <v>1.0486111111111111E-2</v>
+        <v>1.1145833333333334E-2</v>
       </c>
       <c r="I642" s="1">
-        <v>46174.639351851853</v>
+        <v>46174.63726851852</v>
       </c>
       <c r="J642">
         <v>0</v>
@@ -18487,22 +18487,25 @@
         <v>35</v>
       </c>
       <c r="C643">
-        <v>772</v>
+        <v>3741</v>
       </c>
       <c r="D643" t="s">
-        <v>49</v>
+        <v>78</v>
+      </c>
+      <c r="E643" t="s">
+        <v>63</v>
       </c>
       <c r="F643" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G643" t="s">
         <v>10</v>
       </c>
       <c r="H643" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>8.1134259259259267E-3</v>
       </c>
       <c r="I643" s="1">
-        <v>46174.642824074072</v>
+        <v>46176.420486111114</v>
       </c>
       <c r="J643">
         <v>0</v>
@@ -18516,22 +18519,22 @@
         <v>35</v>
       </c>
       <c r="C644">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="D644" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F644" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G644" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H644" s="2">
-        <v>6.4814814814814813E-3</v>
+        <v>0</v>
       </c>
       <c r="I644" s="1">
-        <v>46174.644212962965</v>
+        <v>46176.421180555553</v>
       </c>
       <c r="J644">
         <v>0</v>
@@ -18545,22 +18548,22 @@
         <v>35</v>
       </c>
       <c r="C645">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D645" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F645" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G645" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H645" s="2">
-        <v>6.2962962962962964E-3</v>
+        <v>0</v>
       </c>
       <c r="I645" s="1">
-        <v>46174.644907407404</v>
+        <v>46176.421180555553</v>
       </c>
       <c r="J645">
         <v>0</v>
@@ -18574,10 +18577,10 @@
         <v>35</v>
       </c>
       <c r="C646">
-        <v>3818</v>
+        <v>5037</v>
       </c>
       <c r="D646" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F646" t="s">
         <v>89</v>
@@ -18586,10 +18589,10 @@
         <v>10</v>
       </c>
       <c r="H646" s="2">
-        <v>7.013888888888889E-3</v>
+        <v>1.0486111111111111E-2</v>
       </c>
       <c r="I646" s="1">
-        <v>46174.645601851851</v>
+        <v>46174.639351851853</v>
       </c>
       <c r="J646">
         <v>0</v>
@@ -18603,10 +18606,10 @@
         <v>35</v>
       </c>
       <c r="C647">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D647" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F647" t="s">
         <v>91</v>
@@ -18618,7 +18621,7 @@
         <v>0</v>
       </c>
       <c r="I647" s="1">
-        <v>46176.418402777781</v>
+        <v>46176.421875</v>
       </c>
       <c r="J647">
         <v>0</v>
@@ -18632,10 +18635,10 @@
         <v>35</v>
       </c>
       <c r="C648">
-        <v>622</v>
+        <v>5409</v>
       </c>
       <c r="D648" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F648" t="s">
         <v>91</v>
@@ -18647,7 +18650,7 @@
         <v>0</v>
       </c>
       <c r="I648" s="1">
-        <v>46176.41909722222</v>
+        <v>46176.421875</v>
       </c>
       <c r="J648">
         <v>0</v>
@@ -18661,10 +18664,10 @@
         <v>35</v>
       </c>
       <c r="C649">
-        <v>5180</v>
+        <v>76</v>
       </c>
       <c r="D649" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F649" t="s">
         <v>91</v>
@@ -18676,7 +18679,7 @@
         <v>0</v>
       </c>
       <c r="I649" s="1">
-        <v>46176.419791666667</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J649">
         <v>0</v>
@@ -18690,22 +18693,22 @@
         <v>35</v>
       </c>
       <c r="C650">
-        <v>204</v>
+        <v>3726</v>
       </c>
       <c r="D650" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F650" t="s">
         <v>91</v>
       </c>
       <c r="G650" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H650" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>0</v>
       </c>
       <c r="I650" s="1">
-        <v>46176.419791666667</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J650">
         <v>0</v>
@@ -18719,13 +18722,10 @@
         <v>35</v>
       </c>
       <c r="C651">
-        <v>3741</v>
+        <v>614</v>
       </c>
       <c r="D651" t="s">
-        <v>78</v>
-      </c>
-      <c r="E651" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F651" t="s">
         <v>91</v>
@@ -18734,10 +18734,10 @@
         <v>10</v>
       </c>
       <c r="H651" s="2">
-        <v>8.1134259259259267E-3</v>
+        <v>7.789351851851852E-3</v>
       </c>
       <c r="I651" s="1">
-        <v>46176.420486111114</v>
+        <v>46176.423263888886</v>
       </c>
       <c r="J651">
         <v>0</v>
@@ -18751,22 +18751,22 @@
         <v>35</v>
       </c>
       <c r="C652">
-        <v>78</v>
+        <v>772</v>
       </c>
       <c r="D652" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F652" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G652" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H652" s="2">
-        <v>0</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I652" s="1">
-        <v>46176.421180555553</v>
+        <v>46174.642824074072</v>
       </c>
       <c r="J652">
         <v>0</v>
@@ -18780,10 +18780,10 @@
         <v>35</v>
       </c>
       <c r="C653">
-        <v>73</v>
+        <v>623</v>
       </c>
       <c r="D653" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F653" t="s">
         <v>91</v>
@@ -18795,7 +18795,7 @@
         <v>0</v>
       </c>
       <c r="I653" s="1">
-        <v>46176.421180555553</v>
+        <v>46176.423263888886</v>
       </c>
       <c r="J653">
         <v>0</v>
@@ -18809,10 +18809,10 @@
         <v>35</v>
       </c>
       <c r="C654">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D654" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F654" t="s">
         <v>91</v>
@@ -18824,7 +18824,7 @@
         <v>0</v>
       </c>
       <c r="I654" s="1">
-        <v>46176.421875</v>
+        <v>46176.423958333333</v>
       </c>
       <c r="J654">
         <v>0</v>
@@ -18838,22 +18838,22 @@
         <v>35</v>
       </c>
       <c r="C655">
-        <v>5409</v>
+        <v>245</v>
       </c>
       <c r="D655" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F655" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G655" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H655" s="2">
-        <v>0</v>
+        <v>6.4814814814814813E-3</v>
       </c>
       <c r="I655" s="1">
-        <v>46176.421875</v>
+        <v>46174.644212962965</v>
       </c>
       <c r="J655">
         <v>0</v>
@@ -18867,22 +18867,22 @@
         <v>35</v>
       </c>
       <c r="C656">
-        <v>5350</v>
+        <v>84</v>
       </c>
       <c r="D656" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F656" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G656" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H656" s="2">
-        <v>0</v>
+        <v>6.2962962962962964E-3</v>
       </c>
       <c r="I656" s="1">
-        <v>46176.422569444447</v>
+        <v>46174.644907407404</v>
       </c>
       <c r="J656">
         <v>0</v>
@@ -18896,22 +18896,22 @@
         <v>35</v>
       </c>
       <c r="C657">
-        <v>76</v>
+        <v>3818</v>
       </c>
       <c r="D657" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F657" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G657" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H657" s="2">
-        <v>0</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I657" s="1">
-        <v>46176.422569444447</v>
+        <v>46174.645601851851</v>
       </c>
       <c r="J657">
         <v>0</v>
@@ -18925,10 +18925,10 @@
         <v>35</v>
       </c>
       <c r="C658">
-        <v>3726</v>
+        <v>80</v>
       </c>
       <c r="D658" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F658" t="s">
         <v>91</v>
@@ -18940,7 +18940,7 @@
         <v>0</v>
       </c>
       <c r="I658" s="1">
-        <v>46176.422569444447</v>
+        <v>46176.42465277778</v>
       </c>
       <c r="J658">
         <v>0</v>
@@ -18950,120 +18950,20 @@
       </c>
     </row>
     <row r="659" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B659" t="s">
-        <v>35</v>
-      </c>
-      <c r="C659">
-        <v>614</v>
-      </c>
-      <c r="D659" t="s">
-        <v>48</v>
-      </c>
-      <c r="F659" t="s">
-        <v>91</v>
-      </c>
-      <c r="G659" t="s">
-        <v>10</v>
-      </c>
-      <c r="H659" s="2">
-        <v>7.789351851851852E-3</v>
-      </c>
-      <c r="I659" s="1">
-        <v>46176.423263888886</v>
-      </c>
-      <c r="J659">
-        <v>0</v>
-      </c>
-      <c r="K659" t="s">
-        <v>11</v>
-      </c>
+      <c r="H659" s="2"/>
+      <c r="I659" s="1"/>
     </row>
     <row r="660" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B660" t="s">
-        <v>35</v>
-      </c>
-      <c r="C660">
-        <v>623</v>
-      </c>
-      <c r="D660" t="s">
-        <v>50</v>
-      </c>
-      <c r="F660" t="s">
-        <v>91</v>
-      </c>
-      <c r="G660" t="s">
-        <v>13</v>
-      </c>
-      <c r="H660" s="2">
-        <v>0</v>
-      </c>
-      <c r="I660" s="1">
-        <v>46176.423263888886</v>
-      </c>
-      <c r="J660">
-        <v>0</v>
-      </c>
-      <c r="K660" t="s">
-        <v>11</v>
-      </c>
+      <c r="H660" s="2"/>
+      <c r="I660" s="1"/>
     </row>
     <row r="661" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B661" t="s">
-        <v>35</v>
-      </c>
-      <c r="C661">
-        <v>72</v>
-      </c>
-      <c r="D661" t="s">
-        <v>51</v>
-      </c>
-      <c r="F661" t="s">
-        <v>91</v>
-      </c>
-      <c r="G661" t="s">
-        <v>13</v>
-      </c>
-      <c r="H661" s="2">
-        <v>0</v>
-      </c>
-      <c r="I661" s="1">
-        <v>46176.423958333333</v>
-      </c>
-      <c r="J661">
-        <v>0</v>
-      </c>
-      <c r="K661" t="s">
-        <v>11</v>
-      </c>
+      <c r="H661" s="2"/>
+      <c r="I661" s="1"/>
     </row>
     <row r="662" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B662" t="s">
-        <v>35</v>
-      </c>
-      <c r="C662">
-        <v>80</v>
-      </c>
-      <c r="D662" t="s">
-        <v>56</v>
-      </c>
-      <c r="F662" t="s">
-        <v>91</v>
-      </c>
-      <c r="G662" t="s">
-        <v>13</v>
-      </c>
-      <c r="H662" s="2">
-        <v>0</v>
-      </c>
-      <c r="I662" s="1">
-        <v>46176.42465277778</v>
-      </c>
-      <c r="J662">
-        <v>0</v>
-      </c>
-      <c r="K662" t="s">
-        <v>11</v>
-      </c>
+      <c r="H662" s="2"/>
+      <c r="I662" s="1"/>
     </row>
     <row r="663" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H663" s="2"/>
@@ -19294,7 +19194,6 @@
       <c r="I719" s="1"/>
     </row>
     <row r="720" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H720" s="2"/>
       <c r="I720" s="1"/>
     </row>
     <row r="721" spans="8:9" x14ac:dyDescent="0.3">
@@ -19310,6 +19209,7 @@
       <c r="I723" s="1"/>
     </row>
     <row r="724" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H724" s="2"/>
       <c r="I724" s="1"/>
     </row>
     <row r="725" spans="8:9" x14ac:dyDescent="0.3">
@@ -19381,7 +19281,6 @@
       <c r="I741" s="1"/>
     </row>
     <row r="742" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H742" s="2"/>
       <c r="I742" s="1"/>
     </row>
     <row r="743" spans="8:9" x14ac:dyDescent="0.3">
@@ -19397,6 +19296,7 @@
       <c r="I745" s="1"/>
     </row>
     <row r="746" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H746" s="2"/>
       <c r="I746" s="1"/>
     </row>
     <row r="747" spans="8:9" x14ac:dyDescent="0.3">
@@ -19524,7 +19424,6 @@
       <c r="I777" s="1"/>
     </row>
     <row r="778" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H778" s="2"/>
       <c r="I778" s="1"/>
     </row>
     <row r="779" spans="8:9" x14ac:dyDescent="0.3">
@@ -19540,6 +19439,7 @@
       <c r="I781" s="1"/>
     </row>
     <row r="782" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H782" s="2"/>
       <c r="I782" s="1"/>
     </row>
     <row r="783" spans="8:9" x14ac:dyDescent="0.3">
@@ -19587,7 +19487,6 @@
       <c r="I793" s="1"/>
     </row>
     <row r="794" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H794" s="2"/>
       <c r="I794" s="1"/>
     </row>
     <row r="795" spans="8:9" x14ac:dyDescent="0.3">
@@ -19603,6 +19502,7 @@
       <c r="I797" s="1"/>
     </row>
     <row r="798" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H798" s="2"/>
       <c r="I798" s="1"/>
     </row>
     <row r="799" spans="8:9" x14ac:dyDescent="0.3">
@@ -19882,7 +19782,6 @@
       <c r="I867" s="1"/>
     </row>
     <row r="868" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H868" s="2"/>
       <c r="I868" s="1"/>
     </row>
     <row r="869" spans="8:9" x14ac:dyDescent="0.3">
@@ -19898,6 +19797,7 @@
       <c r="I871" s="1"/>
     </row>
     <row r="872" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H872" s="2"/>
       <c r="I872" s="1"/>
     </row>
     <row r="873" spans="8:9" x14ac:dyDescent="0.3">
@@ -19909,7 +19809,6 @@
       <c r="I874" s="1"/>
     </row>
     <row r="875" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H875" s="2"/>
       <c r="I875" s="1"/>
     </row>
     <row r="876" spans="8:9" x14ac:dyDescent="0.3">
@@ -19925,6 +19824,7 @@
       <c r="I878" s="1"/>
     </row>
     <row r="879" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H879" s="2"/>
       <c r="I879" s="1"/>
     </row>
     <row r="880" spans="8:9" x14ac:dyDescent="0.3">
@@ -20020,7 +19920,6 @@
       <c r="I902" s="1"/>
     </row>
     <row r="903" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H903" s="2"/>
       <c r="I903" s="1"/>
     </row>
     <row r="904" spans="8:9" x14ac:dyDescent="0.3">
@@ -20036,6 +19935,7 @@
       <c r="I906" s="1"/>
     </row>
     <row r="907" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H907" s="2"/>
       <c r="I907" s="1"/>
     </row>
     <row r="908" spans="8:9" x14ac:dyDescent="0.3">
@@ -20123,7 +20023,6 @@
       <c r="I928" s="1"/>
     </row>
     <row r="929" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H929" s="2"/>
       <c r="I929" s="1"/>
     </row>
     <row r="930" spans="8:9" x14ac:dyDescent="0.3">
@@ -20154,6 +20053,7 @@
       <c r="I936" s="1"/>
     </row>
     <row r="937" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H937" s="2"/>
       <c r="I937" s="1"/>
     </row>
     <row r="938" spans="8:9" x14ac:dyDescent="0.3">
@@ -20285,7 +20185,6 @@
       <c r="I969" s="1"/>
     </row>
     <row r="970" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H970" s="2"/>
       <c r="I970" s="1"/>
     </row>
     <row r="971" spans="8:9" x14ac:dyDescent="0.3">
@@ -20301,6 +20200,7 @@
       <c r="I973" s="1"/>
     </row>
     <row r="974" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H974" s="2"/>
       <c r="I974" s="1"/>
     </row>
     <row r="975" spans="8:9" x14ac:dyDescent="0.3">
@@ -20448,7 +20348,6 @@
       <c r="I1010" s="1"/>
     </row>
     <row r="1011" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1011" s="2"/>
       <c r="I1011" s="1"/>
     </row>
     <row r="1012" spans="8:9" x14ac:dyDescent="0.3">
@@ -20464,6 +20363,7 @@
       <c r="I1014" s="1"/>
     </row>
     <row r="1015" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1015" s="2"/>
       <c r="I1015" s="1"/>
     </row>
     <row r="1016" spans="8:9" x14ac:dyDescent="0.3">
@@ -20507,7 +20407,6 @@
       <c r="I1025" s="1"/>
     </row>
     <row r="1026" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1026" s="2"/>
       <c r="I1026" s="1"/>
     </row>
     <row r="1027" spans="8:9" x14ac:dyDescent="0.3">
@@ -20523,6 +20422,7 @@
       <c r="I1029" s="1"/>
     </row>
     <row r="1030" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1030" s="2"/>
       <c r="I1030" s="1"/>
     </row>
     <row r="1031" spans="8:9" x14ac:dyDescent="0.3">
@@ -20798,7 +20698,6 @@
       <c r="I1098" s="1"/>
     </row>
     <row r="1099" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
     </row>
     <row r="1100" spans="8:9" x14ac:dyDescent="0.3">
@@ -20814,6 +20713,7 @@
       <c r="I1102" s="1"/>
     </row>
     <row r="1103" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1103" s="2"/>
       <c r="I1103" s="1"/>
     </row>
     <row r="1104" spans="8:9" x14ac:dyDescent="0.3">
@@ -21181,7 +21081,6 @@
       <c r="I1194" s="1"/>
     </row>
     <row r="1195" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1195" s="2"/>
       <c r="I1195" s="1"/>
     </row>
     <row r="1196" spans="8:9" x14ac:dyDescent="0.3">
@@ -21197,6 +21096,7 @@
       <c r="I1198" s="1"/>
     </row>
     <row r="1199" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1199" s="2"/>
       <c r="I1199" s="1"/>
     </row>
     <row r="1200" spans="8:9" x14ac:dyDescent="0.3">
@@ -21376,7 +21276,6 @@
       <c r="I1243" s="1"/>
     </row>
     <row r="1244" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1244" s="2"/>
       <c r="I1244" s="1"/>
     </row>
     <row r="1245" spans="8:9" x14ac:dyDescent="0.3">
@@ -21392,6 +21291,7 @@
       <c r="I1247" s="1"/>
     </row>
     <row r="1248" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1248" s="2"/>
       <c r="I1248" s="1"/>
     </row>
     <row r="1249" spans="8:9" x14ac:dyDescent="0.3">
@@ -21415,7 +21315,6 @@
       <c r="I1253" s="1"/>
     </row>
     <row r="1254" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1254" s="2"/>
       <c r="I1254" s="1"/>
     </row>
     <row r="1255" spans="8:9" x14ac:dyDescent="0.3">
@@ -21427,10 +21326,10 @@
       <c r="I1256" s="1"/>
     </row>
     <row r="1257" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1257" s="2"/>
       <c r="I1257" s="1"/>
     </row>
     <row r="1258" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1258" s="2"/>
       <c r="I1258" s="1"/>
     </row>
     <row r="1259" spans="8:9" x14ac:dyDescent="0.3">
@@ -21442,6 +21341,7 @@
       <c r="I1260" s="1"/>
     </row>
     <row r="1261" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1261" s="2"/>
       <c r="I1261" s="1"/>
     </row>
     <row r="1262" spans="8:9" x14ac:dyDescent="0.3">
@@ -21477,7 +21377,6 @@
       <c r="I1269" s="1"/>
     </row>
     <row r="1270" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1270" s="2"/>
       <c r="I1270" s="1"/>
     </row>
     <row r="1271" spans="8:9" x14ac:dyDescent="0.3">
@@ -21493,6 +21392,7 @@
       <c r="I1273" s="1"/>
     </row>
     <row r="1274" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1274" s="2"/>
       <c r="I1274" s="1"/>
     </row>
     <row r="1275" spans="8:9" x14ac:dyDescent="0.3">
@@ -21580,7 +21480,6 @@
       <c r="I1295" s="1"/>
     </row>
     <row r="1296" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1296" s="2"/>
       <c r="I1296" s="1"/>
     </row>
     <row r="1297" spans="8:9" x14ac:dyDescent="0.3">
@@ -21596,6 +21495,7 @@
       <c r="I1299" s="1"/>
     </row>
     <row r="1300" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1300" s="2"/>
       <c r="I1300" s="1"/>
     </row>
     <row r="1301" spans="8:9" x14ac:dyDescent="0.3">
@@ -21679,7 +21579,6 @@
       <c r="I1320" s="1"/>
     </row>
     <row r="1321" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1321" s="2"/>
       <c r="I1321" s="1"/>
     </row>
     <row r="1322" spans="8:9" x14ac:dyDescent="0.3">
@@ -21695,6 +21594,7 @@
       <c r="I1324" s="1"/>
     </row>
     <row r="1325" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1325" s="2"/>
       <c r="I1325" s="1"/>
     </row>
     <row r="1326" spans="8:9" x14ac:dyDescent="0.3">
@@ -21758,7 +21658,6 @@
       <c r="I1340" s="1"/>
     </row>
     <row r="1341" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1341" s="2"/>
       <c r="I1341" s="1"/>
     </row>
     <row r="1342" spans="8:9" x14ac:dyDescent="0.3">
@@ -21774,6 +21673,7 @@
       <c r="I1344" s="1"/>
     </row>
     <row r="1345" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1345" s="2"/>
       <c r="I1345" s="1"/>
     </row>
     <row r="1346" spans="8:9" x14ac:dyDescent="0.3">
@@ -21789,7 +21689,6 @@
       <c r="I1348" s="1"/>
     </row>
     <row r="1349" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1349" s="2"/>
       <c r="I1349" s="1"/>
     </row>
     <row r="1350" spans="8:9" x14ac:dyDescent="0.3">
@@ -21805,6 +21704,7 @@
       <c r="I1352" s="1"/>
     </row>
     <row r="1353" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1353" s="2"/>
       <c r="I1353" s="1"/>
     </row>
     <row r="1354" spans="8:9" x14ac:dyDescent="0.3">
@@ -21812,7 +21712,6 @@
       <c r="I1354" s="1"/>
     </row>
     <row r="1355" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1355" s="2"/>
       <c r="I1355" s="1"/>
     </row>
     <row r="1356" spans="8:9" x14ac:dyDescent="0.3">
@@ -21828,6 +21727,7 @@
       <c r="I1358" s="1"/>
     </row>
     <row r="1359" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1359" s="2"/>
       <c r="I1359" s="1"/>
     </row>
     <row r="1360" spans="8:9" x14ac:dyDescent="0.3">
@@ -21871,7 +21771,6 @@
       <c r="I1369" s="1"/>
     </row>
     <row r="1370" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
     </row>
     <row r="1371" spans="8:9" x14ac:dyDescent="0.3">
@@ -21883,10 +21782,10 @@
       <c r="I1372" s="1"/>
     </row>
     <row r="1373" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1373" s="2"/>
       <c r="I1373" s="1"/>
     </row>
     <row r="1374" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1374" s="2"/>
       <c r="I1374" s="1"/>
     </row>
     <row r="1375" spans="8:9" x14ac:dyDescent="0.3">
@@ -21898,6 +21797,7 @@
       <c r="I1376" s="1"/>
     </row>
     <row r="1377" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1377" s="2"/>
       <c r="I1377" s="1"/>
     </row>
     <row r="1378" spans="8:9" x14ac:dyDescent="0.3">
@@ -21909,7 +21809,6 @@
       <c r="I1379" s="1"/>
     </row>
     <row r="1380" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1380" s="2"/>
       <c r="I1380" s="1"/>
     </row>
     <row r="1381" spans="8:9" x14ac:dyDescent="0.3">
@@ -21940,10 +21839,10 @@
       <c r="I1387" s="1"/>
     </row>
     <row r="1388" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1388" s="2"/>
       <c r="I1388" s="1"/>
     </row>
     <row r="1389" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1389" s="2"/>
       <c r="I1389" s="1"/>
     </row>
     <row r="1390" spans="8:9" x14ac:dyDescent="0.3">
@@ -21959,10 +21858,10 @@
       <c r="I1392" s="1"/>
     </row>
     <row r="1393" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1393" s="2"/>
       <c r="I1393" s="1"/>
     </row>
     <row r="1394" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1394" s="2"/>
       <c r="I1394" s="1"/>
     </row>
     <row r="1395" spans="8:9" x14ac:dyDescent="0.3">
@@ -21978,6 +21877,7 @@
       <c r="I1397" s="1"/>
     </row>
     <row r="1398" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1398" s="2"/>
       <c r="I1398" s="1"/>
     </row>
     <row r="1399" spans="8:9" x14ac:dyDescent="0.3">
@@ -22025,7 +21925,6 @@
       <c r="I1409" s="1"/>
     </row>
     <row r="1410" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1410" s="2"/>
       <c r="I1410" s="1"/>
     </row>
     <row r="1411" spans="8:9" x14ac:dyDescent="0.3">
@@ -22041,6 +21940,7 @@
       <c r="I1413" s="1"/>
     </row>
     <row r="1414" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1414" s="2"/>
       <c r="I1414" s="1"/>
     </row>
     <row r="1415" spans="8:9" x14ac:dyDescent="0.3">
@@ -22096,7 +21996,6 @@
       <c r="I1427" s="1"/>
     </row>
     <row r="1428" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1428" s="2"/>
       <c r="I1428" s="1"/>
     </row>
     <row r="1429" spans="8:9" x14ac:dyDescent="0.3">
@@ -22112,6 +22011,7 @@
       <c r="I1431" s="1"/>
     </row>
     <row r="1432" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1432" s="2"/>
       <c r="I1432" s="1"/>
     </row>
     <row r="1433" spans="8:9" x14ac:dyDescent="0.3">
@@ -22143,7 +22043,6 @@
       <c r="I1439" s="1"/>
     </row>
     <row r="1440" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1440" s="2"/>
       <c r="I1440" s="1"/>
     </row>
     <row r="1441" spans="8:9" x14ac:dyDescent="0.3">
@@ -22159,6 +22058,7 @@
       <c r="I1443" s="1"/>
     </row>
     <row r="1444" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1444" s="2"/>
       <c r="I1444" s="1"/>
     </row>
     <row r="1445" spans="8:9" x14ac:dyDescent="0.3">
@@ -22274,11 +22174,9 @@
       <c r="I1472" s="1"/>
     </row>
     <row r="1473" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1473" s="2"/>
       <c r="I1473" s="1"/>
     </row>
     <row r="1474" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1474" s="2"/>
       <c r="I1474" s="1"/>
     </row>
     <row r="1475" spans="8:9" x14ac:dyDescent="0.3">
@@ -22290,9 +22188,11 @@
       <c r="I1476" s="1"/>
     </row>
     <row r="1477" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1477" s="2"/>
       <c r="I1477" s="1"/>
     </row>
     <row r="1478" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1478" s="2"/>
       <c r="I1478" s="1"/>
     </row>
     <row r="1479" spans="8:9" x14ac:dyDescent="0.3">
@@ -22336,7 +22236,6 @@
       <c r="I1488" s="1"/>
     </row>
     <row r="1489" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1489" s="2"/>
       <c r="I1489" s="1"/>
     </row>
     <row r="1490" spans="8:9" x14ac:dyDescent="0.3">
@@ -22352,6 +22251,7 @@
       <c r="I1492" s="1"/>
     </row>
     <row r="1493" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1493" s="2"/>
       <c r="I1493" s="1"/>
     </row>
     <row r="1494" spans="8:9" x14ac:dyDescent="0.3">
@@ -22527,7 +22427,6 @@
       <c r="I1536" s="1"/>
     </row>
     <row r="1537" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1537" s="2"/>
       <c r="I1537" s="1"/>
     </row>
     <row r="1538" spans="8:9" x14ac:dyDescent="0.3">
@@ -22543,6 +22442,7 @@
       <c r="I1540" s="1"/>
     </row>
     <row r="1541" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1541" s="2"/>
       <c r="I1541" s="1"/>
     </row>
     <row r="1542" spans="8:9" x14ac:dyDescent="0.3">
@@ -22570,7 +22470,6 @@
       <c r="I1547" s="1"/>
     </row>
     <row r="1548" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1548" s="2"/>
       <c r="I1548" s="1"/>
     </row>
     <row r="1549" spans="8:9" x14ac:dyDescent="0.3">
@@ -22586,6 +22485,7 @@
       <c r="I1551" s="1"/>
     </row>
     <row r="1552" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1552" s="2"/>
       <c r="I1552" s="1"/>
     </row>
     <row r="1553" spans="8:9" x14ac:dyDescent="0.3">
@@ -22601,7 +22501,6 @@
       <c r="I1555" s="1"/>
     </row>
     <row r="1556" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1556" s="2"/>
       <c r="I1556" s="1"/>
     </row>
     <row r="1557" spans="8:9" x14ac:dyDescent="0.3">
@@ -22617,6 +22516,7 @@
       <c r="I1559" s="1"/>
     </row>
     <row r="1560" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1560" s="2"/>
       <c r="I1560" s="1"/>
     </row>
     <row r="1561" spans="8:9" x14ac:dyDescent="0.3">
@@ -22636,7 +22536,6 @@
       <c r="I1564" s="1"/>
     </row>
     <row r="1565" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
     </row>
     <row r="1566" spans="8:9" x14ac:dyDescent="0.3">
@@ -22652,6 +22551,7 @@
       <c r="I1568" s="1"/>
     </row>
     <row r="1569" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1569" s="2"/>
       <c r="I1569" s="1"/>
     </row>
     <row r="1570" spans="8:9" x14ac:dyDescent="0.3">
@@ -22659,7 +22559,6 @@
       <c r="I1570" s="1"/>
     </row>
     <row r="1571" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1571" s="2"/>
       <c r="I1571" s="1"/>
     </row>
     <row r="1572" spans="8:9" x14ac:dyDescent="0.3">
@@ -22675,6 +22574,7 @@
       <c r="I1574" s="1"/>
     </row>
     <row r="1575" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1575" s="2"/>
       <c r="I1575" s="1"/>
     </row>
     <row r="1576" spans="8:9" x14ac:dyDescent="0.3">
@@ -22738,11 +22638,9 @@
       <c r="I1590" s="1"/>
     </row>
     <row r="1591" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1591" s="2"/>
       <c r="I1591" s="1"/>
     </row>
     <row r="1592" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
     </row>
     <row r="1593" spans="8:9" x14ac:dyDescent="0.3">
@@ -22754,9 +22652,11 @@
       <c r="I1594" s="1"/>
     </row>
     <row r="1595" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1595" s="2"/>
       <c r="I1595" s="1"/>
     </row>
     <row r="1596" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1596" s="2"/>
       <c r="I1596" s="1"/>
     </row>
     <row r="1597" spans="8:9" x14ac:dyDescent="0.3">
@@ -22764,7 +22664,6 @@
       <c r="I1597" s="1"/>
     </row>
     <row r="1598" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1598" s="2"/>
       <c r="I1598" s="1"/>
     </row>
     <row r="1599" spans="8:9" x14ac:dyDescent="0.3">
@@ -22776,10 +22675,10 @@
       <c r="I1600" s="1"/>
     </row>
     <row r="1601" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1601" s="2"/>
       <c r="I1601" s="1"/>
     </row>
     <row r="1602" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1602" s="2"/>
       <c r="I1602" s="1"/>
     </row>
     <row r="1603" spans="8:9" x14ac:dyDescent="0.3">
@@ -22802,10 +22701,10 @@
       <c r="I1607" s="1"/>
     </row>
     <row r="1608" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1608" s="2"/>
       <c r="I1608" s="1"/>
     </row>
     <row r="1609" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1609" s="2"/>
       <c r="I1609" s="1"/>
     </row>
     <row r="1610" spans="8:9" x14ac:dyDescent="0.3">
@@ -22817,10 +22716,10 @@
       <c r="I1611" s="1"/>
     </row>
     <row r="1612" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1612" s="2"/>
       <c r="I1612" s="1"/>
     </row>
     <row r="1613" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1613" s="2"/>
       <c r="I1613" s="1"/>
     </row>
     <row r="1614" spans="8:9" x14ac:dyDescent="0.3">
@@ -22828,7 +22727,6 @@
       <c r="I1614" s="1"/>
     </row>
     <row r="1615" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1615" s="2"/>
       <c r="I1615" s="1"/>
     </row>
     <row r="1616" spans="8:9" x14ac:dyDescent="0.3">
@@ -22836,6 +22734,7 @@
       <c r="I1616" s="1"/>
     </row>
     <row r="1617" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1617" s="2"/>
       <c r="I1617" s="1"/>
     </row>
     <row r="1618" spans="8:9" x14ac:dyDescent="0.3">
@@ -22843,6 +22742,7 @@
       <c r="I1618" s="1"/>
     </row>
     <row r="1619" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1619" s="2"/>
       <c r="I1619" s="1"/>
     </row>
     <row r="1620" spans="8:9" x14ac:dyDescent="0.3">
@@ -22854,7 +22754,6 @@
       <c r="I1621" s="1"/>
     </row>
     <row r="1622" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1622" s="2"/>
       <c r="I1622" s="1"/>
     </row>
     <row r="1623" spans="8:9" x14ac:dyDescent="0.3">
@@ -22862,7 +22761,6 @@
       <c r="I1623" s="1"/>
     </row>
     <row r="1624" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
     </row>
     <row r="1625" spans="8:9" x14ac:dyDescent="0.3">
@@ -22877,6 +22775,7 @@
       <c r="I1627" s="1"/>
     </row>
     <row r="1628" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1628" s="2"/>
       <c r="I1628" s="1"/>
     </row>
     <row r="1629" spans="8:9" x14ac:dyDescent="0.3">
@@ -22884,10 +22783,10 @@
       <c r="I1629" s="1"/>
     </row>
     <row r="1630" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1630" s="2"/>
       <c r="I1630" s="1"/>
     </row>
     <row r="1631" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1631" s="2"/>
       <c r="I1631" s="1"/>
     </row>
     <row r="1632" spans="8:9" x14ac:dyDescent="0.3">
@@ -22899,7 +22798,6 @@
       <c r="I1633" s="1"/>
     </row>
     <row r="1634" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1634" s="2"/>
       <c r="I1634" s="1"/>
     </row>
     <row r="1635" spans="8:9" x14ac:dyDescent="0.3">
@@ -22914,9 +22812,11 @@
       <c r="I1637" s="1"/>
     </row>
     <row r="1638" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1638" s="2"/>
       <c r="I1638" s="1"/>
     </row>
     <row r="1639" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1639" s="2"/>
       <c r="I1639" s="1"/>
     </row>
     <row r="1640" spans="8:9" x14ac:dyDescent="0.3">
@@ -22960,7 +22860,6 @@
       <c r="I1649" s="1"/>
     </row>
     <row r="1650" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1650" s="2"/>
       <c r="I1650" s="1"/>
     </row>
     <row r="1651" spans="8:9" x14ac:dyDescent="0.3">
@@ -22991,6 +22890,7 @@
       <c r="I1657" s="1"/>
     </row>
     <row r="1658" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1658" s="2"/>
       <c r="I1658" s="1"/>
     </row>
     <row r="1659" spans="8:9" x14ac:dyDescent="0.3">
@@ -23582,11 +23482,9 @@
       <c r="I1805" s="1"/>
     </row>
     <row r="1806" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1806" s="2"/>
       <c r="I1806" s="1"/>
     </row>
     <row r="1807" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1807" s="2"/>
       <c r="I1807" s="1"/>
     </row>
     <row r="1808" spans="8:9" x14ac:dyDescent="0.3">
@@ -23594,7 +23492,6 @@
       <c r="I1808" s="1"/>
     </row>
     <row r="1809" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1809" s="2"/>
       <c r="I1809" s="1"/>
     </row>
     <row r="1810" spans="8:9" x14ac:dyDescent="0.3">
@@ -23608,6 +23505,7 @@
       <c r="I1812" s="1"/>
     </row>
     <row r="1813" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1813" s="2"/>
       <c r="I1813" s="1"/>
     </row>
     <row r="1814" spans="8:9" x14ac:dyDescent="0.3">
@@ -23621,13 +23519,14 @@
       <c r="I1816" s="1"/>
     </row>
     <row r="1817" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1817" s="2"/>
       <c r="I1817" s="1"/>
     </row>
     <row r="1818" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1818" s="2"/>
       <c r="I1818" s="1"/>
     </row>
     <row r="1819" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1819" s="2"/>
       <c r="I1819" s="1"/>
     </row>
     <row r="1820" spans="8:9" x14ac:dyDescent="0.3">
@@ -23638,11 +23537,9 @@
       <c r="I1821" s="1"/>
     </row>
     <row r="1822" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1822" s="2"/>
       <c r="I1822" s="1"/>
     </row>
     <row r="1823" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1823" s="2"/>
       <c r="I1823" s="1"/>
     </row>
     <row r="1824" spans="8:9" x14ac:dyDescent="0.3">
@@ -23659,7 +23556,6 @@
       <c r="I1827" s="1"/>
     </row>
     <row r="1828" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1828" s="2"/>
       <c r="I1828" s="1"/>
     </row>
     <row r="1829" spans="8:9" x14ac:dyDescent="0.3">
@@ -23669,9 +23565,11 @@
       <c r="I1830" s="1"/>
     </row>
     <row r="1831" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1831" s="2"/>
       <c r="I1831" s="1"/>
     </row>
     <row r="1832" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1832" s="2"/>
       <c r="I1832" s="1"/>
     </row>
     <row r="1833" spans="8:9" x14ac:dyDescent="0.3">
@@ -23685,24 +23583,24 @@
       <c r="I1835" s="1"/>
     </row>
     <row r="1836" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1836" s="2"/>
       <c r="I1836" s="1"/>
     </row>
     <row r="1837" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1837" s="2"/>
       <c r="I1837" s="1"/>
     </row>
     <row r="1838" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1838" s="2"/>
       <c r="I1838" s="1"/>
     </row>
     <row r="1839" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1839" s="2"/>
       <c r="I1839" s="1"/>
     </row>
     <row r="1840" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1840" s="2"/>
       <c r="I1840" s="1"/>
     </row>
     <row r="1841" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1841" s="2"/>
       <c r="I1841" s="1"/>
     </row>
     <row r="1842" spans="8:9" x14ac:dyDescent="0.3">
@@ -23710,6 +23608,7 @@
       <c r="I1842" s="1"/>
     </row>
     <row r="1843" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1843" s="2"/>
       <c r="I1843" s="1"/>
     </row>
     <row r="1844" spans="8:9" x14ac:dyDescent="0.3">
@@ -23717,14 +23616,13 @@
       <c r="I1844" s="1"/>
     </row>
     <row r="1845" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1845" s="2"/>
       <c r="I1845" s="1"/>
     </row>
     <row r="1846" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1846" s="2"/>
       <c r="I1846" s="1"/>
     </row>
     <row r="1847" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1847" s="2"/>
       <c r="I1847" s="1"/>
     </row>
     <row r="1848" spans="8:9" x14ac:dyDescent="0.3">
@@ -23736,13 +23634,13 @@
       <c r="I1849" s="1"/>
     </row>
     <row r="1850" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1850" s="2"/>
       <c r="I1850" s="1"/>
     </row>
     <row r="1851" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1851" s="1"/>
     </row>
     <row r="1852" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1852" s="2"/>
       <c r="I1852" s="1"/>
     </row>
     <row r="1853" spans="8:9" x14ac:dyDescent="0.3">
@@ -23750,17 +23648,16 @@
       <c r="I1853" s="1"/>
     </row>
     <row r="1854" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1854" s="2"/>
       <c r="I1854" s="1"/>
     </row>
     <row r="1855" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1855" s="2"/>
       <c r="I1855" s="1"/>
     </row>
     <row r="1856" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1856" s="1"/>
     </row>
     <row r="1857" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1857" s="2"/>
       <c r="I1857" s="1"/>
     </row>
     <row r="1858" spans="8:9" x14ac:dyDescent="0.3">
@@ -23771,12 +23668,14 @@
       <c r="I1859" s="1"/>
     </row>
     <row r="1860" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1860" s="2"/>
       <c r="I1860" s="1"/>
     </row>
     <row r="1861" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1861" s="1"/>
     </row>
     <row r="1862" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1862" s="2"/>
       <c r="I1862" s="1"/>
     </row>
     <row r="1863" spans="8:9" x14ac:dyDescent="0.3">
@@ -23788,14 +23687,13 @@
       <c r="I1864" s="1"/>
     </row>
     <row r="1865" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1865" s="2"/>
       <c r="I1865" s="1"/>
     </row>
     <row r="1866" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1866" s="2"/>
       <c r="I1866" s="1"/>
     </row>
     <row r="1867" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1867" s="2"/>
       <c r="I1867" s="1"/>
     </row>
     <row r="1868" spans="8:9" x14ac:dyDescent="0.3">
@@ -23803,10 +23701,10 @@
       <c r="I1868" s="1"/>
     </row>
     <row r="1869" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1869" s="2"/>
       <c r="I1869" s="1"/>
     </row>
     <row r="1870" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1870" s="2"/>
       <c r="I1870" s="1"/>
     </row>
     <row r="1871" spans="8:9" x14ac:dyDescent="0.3">
@@ -23817,17 +23715,16 @@
       <c r="I1872" s="1"/>
     </row>
     <row r="1873" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1873" s="2"/>
       <c r="I1873" s="1"/>
     </row>
     <row r="1874" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1874" s="2"/>
       <c r="I1874" s="1"/>
     </row>
     <row r="1875" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1875" s="1"/>
     </row>
     <row r="1876" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1876" s="2"/>
       <c r="I1876" s="1"/>
     </row>
     <row r="1877" spans="8:9" x14ac:dyDescent="0.3">
@@ -23835,23 +23732,24 @@
       <c r="I1877" s="1"/>
     </row>
     <row r="1878" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1878" s="2"/>
       <c r="I1878" s="1"/>
     </row>
     <row r="1879" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1879" s="1"/>
     </row>
     <row r="1880" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1880" s="2"/>
       <c r="I1880" s="1"/>
     </row>
     <row r="1881" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1881" s="2"/>
       <c r="I1881" s="1"/>
     </row>
     <row r="1882" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1882" s="2"/>
       <c r="I1882" s="1"/>
     </row>
     <row r="1883" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1883" s="2"/>
       <c r="I1883" s="1"/>
     </row>
     <row r="1884" spans="8:9" x14ac:dyDescent="0.3">
@@ -23865,7 +23763,6 @@
       <c r="I1886" s="1"/>
     </row>
     <row r="1887" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1887" s="2"/>
       <c r="I1887" s="1"/>
     </row>
     <row r="1888" spans="8:9" x14ac:dyDescent="0.3">
@@ -23873,6 +23770,7 @@
       <c r="I1888" s="1"/>
     </row>
     <row r="1889" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1889" s="2"/>
       <c r="I1889" s="1"/>
     </row>
     <row r="1890" spans="8:9" x14ac:dyDescent="0.3">
@@ -23890,9 +23788,11 @@
       <c r="I1893" s="1"/>
     </row>
     <row r="1894" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1894" s="2"/>
       <c r="I1894" s="1"/>
     </row>
     <row r="1895" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1895" s="2"/>
       <c r="I1895" s="1"/>
     </row>
     <row r="1896" spans="8:9" x14ac:dyDescent="0.3">
@@ -23900,7 +23800,6 @@
       <c r="I1896" s="1"/>
     </row>
     <row r="1897" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1897" s="2"/>
       <c r="I1897" s="1"/>
     </row>
     <row r="1898" spans="8:9" x14ac:dyDescent="0.3">
@@ -23912,10 +23811,10 @@
       <c r="I1899" s="1"/>
     </row>
     <row r="1900" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1900" s="2"/>
       <c r="I1900" s="1"/>
     </row>
     <row r="1901" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1901" s="2"/>
       <c r="I1901" s="1"/>
     </row>
     <row r="1902" spans="8:9" x14ac:dyDescent="0.3">
@@ -23942,6 +23841,7 @@
       <c r="I1907" s="1"/>
     </row>
     <row r="1908" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1908" s="2"/>
       <c r="I1908" s="1"/>
     </row>
     <row r="1909" spans="8:9" x14ac:dyDescent="0.3">
@@ -24013,7 +23913,6 @@
       <c r="I1925" s="1"/>
     </row>
     <row r="1926" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1926" s="2"/>
       <c r="I1926" s="1"/>
     </row>
     <row r="1927" spans="8:9" x14ac:dyDescent="0.3">
@@ -24021,7 +23920,6 @@
       <c r="I1927" s="1"/>
     </row>
     <row r="1928" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1928" s="2"/>
       <c r="I1928" s="1"/>
     </row>
     <row r="1929" spans="8:9" x14ac:dyDescent="0.3">
@@ -24032,10 +23930,10 @@
       <c r="I1930" s="1"/>
     </row>
     <row r="1931" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1931" s="2"/>
       <c r="I1931" s="1"/>
     </row>
     <row r="1932" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1932" s="2"/>
       <c r="I1932" s="1"/>
     </row>
     <row r="1933" spans="8:9" x14ac:dyDescent="0.3">
@@ -24046,17 +23944,17 @@
       <c r="I1934" s="1"/>
     </row>
     <row r="1935" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1935" s="2"/>
       <c r="I1935" s="1"/>
     </row>
     <row r="1936" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
     </row>
     <row r="1937" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
     </row>
     <row r="1938" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1938" s="2"/>
       <c r="I1938" s="1"/>
     </row>
     <row r="1939" spans="8:9" x14ac:dyDescent="0.3">
@@ -24070,23 +23968,24 @@
       <c r="I1941" s="1"/>
     </row>
     <row r="1942" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1942" s="2"/>
       <c r="I1942" s="1"/>
     </row>
     <row r="1943" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
     </row>
     <row r="1944" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1944" s="2"/>
       <c r="I1944" s="1"/>
     </row>
     <row r="1945" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1946" s="2"/>
       <c r="I1946" s="1"/>
     </row>
     <row r="1947" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1947" s="2"/>
       <c r="I1947" s="1"/>
     </row>
     <row r="1948" spans="8:9" x14ac:dyDescent="0.3">
@@ -24101,7 +24000,6 @@
       <c r="I1950" s="1"/>
     </row>
     <row r="1951" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1951" s="2"/>
       <c r="I1951" s="1"/>
     </row>
     <row r="1952" spans="8:9" x14ac:dyDescent="0.3">
@@ -24112,7 +24010,6 @@
       <c r="I1953" s="1"/>
     </row>
     <row r="1954" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1954" s="2"/>
       <c r="I1954" s="1"/>
     </row>
     <row r="1955" spans="8:9" x14ac:dyDescent="0.3">
@@ -24123,12 +24020,15 @@
       <c r="I1956" s="1"/>
     </row>
     <row r="1957" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
     </row>
     <row r="1958" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
     </row>
     <row r="1959" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1959" s="2"/>
       <c r="I1959" s="1"/>
     </row>
     <row r="1960" spans="8:9" x14ac:dyDescent="0.3">
@@ -24136,15 +24036,12 @@
       <c r="I1960" s="1"/>
     </row>
     <row r="1961" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1961" s="2"/>
       <c r="I1961" s="1"/>
     </row>
     <row r="1962" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1962" s="2"/>
       <c r="I1962" s="1"/>
     </row>
     <row r="1963" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1963" s="2"/>
       <c r="I1963" s="1"/>
     </row>
     <row r="1964" spans="8:9" x14ac:dyDescent="0.3">
@@ -24152,6 +24049,7 @@
       <c r="I1964" s="1"/>
     </row>
     <row r="1965" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
     </row>
     <row r="1966" spans="8:9" x14ac:dyDescent="0.3">
@@ -24169,17 +24067,17 @@
       <c r="I1969" s="1"/>
     </row>
     <row r="1970" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1970" s="2"/>
       <c r="I1970" s="1"/>
     </row>
     <row r="1971" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1971" s="2"/>
       <c r="I1971" s="1"/>
     </row>
     <row r="1972" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1972" s="2"/>
       <c r="I1972" s="1"/>
     </row>
     <row r="1973" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1973" s="2"/>
       <c r="I1973" s="1"/>
     </row>
     <row r="1974" spans="8:9" x14ac:dyDescent="0.3">
@@ -24194,6 +24092,7 @@
       <c r="I1976" s="1"/>
     </row>
     <row r="1977" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:9" x14ac:dyDescent="0.3">
@@ -24201,38 +24100,36 @@
       <c r="I1978" s="1"/>
     </row>
     <row r="1979" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1979" s="2"/>
       <c r="I1979" s="1"/>
     </row>
     <row r="1980" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1980" s="1"/>
     </row>
     <row r="1981" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1981" s="2"/>
       <c r="I1981" s="1"/>
     </row>
     <row r="1982" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1982" s="2"/>
       <c r="I1982" s="1"/>
     </row>
     <row r="1983" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
     </row>
     <row r="1984" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
     </row>
     <row r="1985" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1985" s="1"/>
     </row>
     <row r="1986" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
     </row>
     <row r="1987" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1987" s="2"/>
       <c r="I1987" s="1"/>
     </row>
     <row r="1988" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1988" s="2"/>
       <c r="I1988" s="1"/>
     </row>
     <row r="1989" spans="8:9" x14ac:dyDescent="0.3">
@@ -24243,16 +24140,17 @@
       <c r="I1990" s="1"/>
     </row>
     <row r="1991" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1991" s="2"/>
       <c r="I1991" s="1"/>
     </row>
     <row r="1992" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1992" s="1"/>
     </row>
     <row r="1993" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1994" s="2"/>
       <c r="I1994" s="1"/>
     </row>
     <row r="1995" spans="8:9" x14ac:dyDescent="0.3">
@@ -24281,6 +24179,7 @@
       <c r="I2001" s="1"/>
     </row>
     <row r="2002" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:9" x14ac:dyDescent="0.3">
@@ -24303,10 +24202,10 @@
       <c r="I2007" s="1"/>
     </row>
     <row r="2008" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
     </row>
     <row r="2009" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2009" s="2"/>
       <c r="I2009" s="1"/>
     </row>
     <row r="2010" spans="8:9" x14ac:dyDescent="0.3">
@@ -24314,7 +24213,6 @@
       <c r="I2010" s="1"/>
     </row>
     <row r="2011" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2011" s="2"/>
       <c r="I2011" s="1"/>
     </row>
     <row r="2012" spans="8:9" x14ac:dyDescent="0.3">
@@ -24325,7 +24223,6 @@
       <c r="I2013" s="1"/>
     </row>
     <row r="2014" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2014" s="2"/>
       <c r="I2014" s="1"/>
     </row>
     <row r="2015" spans="8:9" x14ac:dyDescent="0.3">
@@ -24339,16 +24236,18 @@
       <c r="I2017" s="1"/>
     </row>
     <row r="2018" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2018" s="2"/>
       <c r="I2018" s="1"/>
     </row>
     <row r="2019" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2019" s="2"/>
       <c r="I2019" s="1"/>
     </row>
     <row r="2020" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2020" s="2"/>
       <c r="I2020" s="1"/>
     </row>
     <row r="2021" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2021" s="2"/>
       <c r="I2021" s="1"/>
     </row>
     <row r="2022" spans="8:9" x14ac:dyDescent="0.3">
@@ -24367,7 +24266,6 @@
       <c r="I2025" s="1"/>
     </row>
     <row r="2026" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2026" s="2"/>
       <c r="I2026" s="1"/>
     </row>
     <row r="2027" spans="8:9" x14ac:dyDescent="0.3">
@@ -24378,10 +24276,10 @@
       <c r="I2028" s="1"/>
     </row>
     <row r="2029" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2029" s="2"/>
       <c r="I2029" s="1"/>
     </row>
     <row r="2030" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2030" s="2"/>
       <c r="I2030" s="1"/>
     </row>
     <row r="2031" spans="8:9" x14ac:dyDescent="0.3">
@@ -24389,13 +24287,14 @@
       <c r="I2031" s="1"/>
     </row>
     <row r="2032" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2032" s="2"/>
       <c r="I2032" s="1"/>
     </row>
     <row r="2033" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2033" s="2"/>
       <c r="I2033" s="1"/>
     </row>
     <row r="2034" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2034" s="2"/>
       <c r="I2034" s="1"/>
     </row>
     <row r="2035" spans="8:9" x14ac:dyDescent="0.3">
@@ -24403,7 +24302,6 @@
       <c r="I2035" s="1"/>
     </row>
     <row r="2036" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2036" s="2"/>
       <c r="I2036" s="1"/>
     </row>
     <row r="2037" spans="8:9" x14ac:dyDescent="0.3">
@@ -24414,7 +24312,6 @@
       <c r="I2038" s="1"/>
     </row>
     <row r="2039" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2039" s="2"/>
       <c r="I2039" s="1"/>
     </row>
     <row r="2040" spans="8:9" x14ac:dyDescent="0.3">
@@ -24431,26 +24328,28 @@
       <c r="I2043" s="1"/>
     </row>
     <row r="2044" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2044" s="2"/>
       <c r="I2044" s="1"/>
     </row>
     <row r="2045" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2045" s="2"/>
       <c r="I2045" s="1"/>
     </row>
     <row r="2046" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2046" s="1"/>
     </row>
     <row r="2047" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2047" s="2"/>
       <c r="I2047" s="1"/>
     </row>
     <row r="2048" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2048" s="2"/>
       <c r="I2048" s="1"/>
     </row>
     <row r="2049" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2049" s="2"/>
       <c r="I2049" s="1"/>
     </row>
     <row r="2050" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2050" s="2"/>
       <c r="I2050" s="1"/>
     </row>
     <row r="2051" spans="8:9" x14ac:dyDescent="0.3">
@@ -24461,7 +24360,6 @@
       <c r="I2052" s="1"/>
     </row>
     <row r="2053" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2053" s="2"/>
       <c r="I2053" s="1"/>
     </row>
     <row r="2054" spans="8:9" x14ac:dyDescent="0.3">
@@ -24469,17 +24367,17 @@
       <c r="I2054" s="1"/>
     </row>
     <row r="2055" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2055" s="2"/>
       <c r="I2055" s="1"/>
     </row>
     <row r="2056" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2056" s="2"/>
       <c r="I2056" s="1"/>
     </row>
     <row r="2057" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2057" s="2"/>
       <c r="I2057" s="1"/>
     </row>
     <row r="2058" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2058" s="2"/>
       <c r="I2058" s="1"/>
     </row>
     <row r="2059" spans="8:9" x14ac:dyDescent="0.3">
@@ -24500,17 +24398,16 @@
       <c r="I2063" s="1"/>
     </row>
     <row r="2064" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2064" s="2"/>
       <c r="I2064" s="1"/>
     </row>
     <row r="2065" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2065" s="2"/>
       <c r="I2065" s="1"/>
     </row>
     <row r="2066" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2066" s="1"/>
     </row>
     <row r="2067" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2067" s="2"/>
       <c r="I2067" s="1"/>
     </row>
     <row r="2068" spans="8:9" x14ac:dyDescent="0.3">
@@ -24520,16 +24417,17 @@
       <c r="I2069" s="1"/>
     </row>
     <row r="2070" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2070" s="2"/>
       <c r="I2070" s="1"/>
     </row>
     <row r="2071" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2071" s="2"/>
       <c r="I2071" s="1"/>
     </row>
     <row r="2072" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2072" s="1"/>
     </row>
     <row r="2073" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2073" s="2"/>
       <c r="I2073" s="1"/>
     </row>
     <row r="2074" spans="8:9" x14ac:dyDescent="0.3">
@@ -24540,6 +24438,7 @@
       <c r="I2075" s="1"/>
     </row>
     <row r="2076" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2076" s="2"/>
       <c r="I2076" s="1"/>
     </row>
     <row r="2077" spans="8:9" x14ac:dyDescent="0.3">
@@ -24547,38 +24446,37 @@
       <c r="I2077" s="1"/>
     </row>
     <row r="2078" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2078" s="2"/>
       <c r="I2078" s="1"/>
     </row>
     <row r="2079" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2079" s="1"/>
     </row>
     <row r="2080" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2080" s="2"/>
       <c r="I2080" s="1"/>
     </row>
     <row r="2081" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2081" s="2"/>
       <c r="I2081" s="1"/>
     </row>
     <row r="2082" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2082" s="2"/>
       <c r="I2082" s="1"/>
     </row>
     <row r="2083" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2083" s="2"/>
       <c r="I2083" s="1"/>
     </row>
     <row r="2084" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2084" s="2"/>
       <c r="I2084" s="1"/>
     </row>
     <row r="2085" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2085" s="2"/>
       <c r="I2085" s="1"/>
     </row>
     <row r="2086" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2086" s="2"/>
       <c r="I2086" s="1"/>
     </row>
     <row r="2087" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2087" s="2"/>
       <c r="I2087" s="1"/>
     </row>
     <row r="2088" spans="8:9" x14ac:dyDescent="0.3">
@@ -24586,23 +24484,23 @@
       <c r="I2088" s="1"/>
     </row>
     <row r="2089" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2089" s="2"/>
       <c r="I2089" s="1"/>
     </row>
     <row r="2090" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2090" s="1"/>
     </row>
     <row r="2091" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2091" s="2"/>
       <c r="I2091" s="1"/>
     </row>
     <row r="2092" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2092" s="2"/>
       <c r="I2092" s="1"/>
     </row>
     <row r="2093" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2093" s="1"/>
     </row>
     <row r="2094" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2094" s="2"/>
       <c r="I2094" s="1"/>
     </row>
     <row r="2095" spans="8:9" x14ac:dyDescent="0.3">
@@ -24610,9 +24508,11 @@
       <c r="I2095" s="1"/>
     </row>
     <row r="2096" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2096" s="2"/>
       <c r="I2096" s="1"/>
     </row>
     <row r="2097" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2097" s="2"/>
       <c r="I2097" s="1"/>
     </row>
     <row r="2098" spans="8:9" x14ac:dyDescent="0.3">
@@ -24628,7 +24528,6 @@
       <c r="I2100" s="1"/>
     </row>
     <row r="2101" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2101" s="2"/>
       <c r="I2101" s="1"/>
     </row>
     <row r="2102" spans="8:9" x14ac:dyDescent="0.3">
@@ -24640,7 +24539,6 @@
       <c r="I2103" s="1"/>
     </row>
     <row r="2104" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2104" s="2"/>
       <c r="I2104" s="1"/>
     </row>
     <row r="2105" spans="8:9" x14ac:dyDescent="0.3">
@@ -24651,13 +24549,13 @@
       <c r="I2106" s="1"/>
     </row>
     <row r="2107" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2107" s="2"/>
       <c r="I2107" s="1"/>
     </row>
     <row r="2108" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2108" s="1"/>
     </row>
     <row r="2109" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2109" s="2"/>
       <c r="I2109" s="1"/>
     </row>
     <row r="2110" spans="8:9" x14ac:dyDescent="0.3">
@@ -24665,9 +24563,11 @@
       <c r="I2110" s="1"/>
     </row>
     <row r="2111" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2111" s="2"/>
       <c r="I2111" s="1"/>
     </row>
     <row r="2112" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2112" s="2"/>
       <c r="I2112" s="1"/>
     </row>
     <row r="2113" spans="8:9" x14ac:dyDescent="0.3">
@@ -24675,7 +24575,6 @@
       <c r="I2113" s="1"/>
     </row>
     <row r="2114" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2114" s="2"/>
       <c r="I2114" s="1"/>
     </row>
     <row r="2115" spans="8:9" x14ac:dyDescent="0.3">
@@ -24691,14 +24590,13 @@
       <c r="I2117" s="1"/>
     </row>
     <row r="2118" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2118" s="2"/>
       <c r="I2118" s="1"/>
     </row>
     <row r="2119" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2119" s="2"/>
       <c r="I2119" s="1"/>
     </row>
     <row r="2120" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2120" s="2"/>
       <c r="I2120" s="1"/>
     </row>
     <row r="2121" spans="8:9" x14ac:dyDescent="0.3">
@@ -24706,20 +24604,21 @@
       <c r="I2121" s="1"/>
     </row>
     <row r="2122" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2122" s="2"/>
       <c r="I2122" s="1"/>
     </row>
     <row r="2123" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2123" s="2"/>
       <c r="I2123" s="1"/>
     </row>
     <row r="2124" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2124" s="2"/>
       <c r="I2124" s="1"/>
     </row>
     <row r="2125" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2125" s="2"/>
       <c r="I2125" s="1"/>
     </row>
     <row r="2126" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2126" s="2"/>
       <c r="I2126" s="1"/>
     </row>
     <row r="2127" spans="8:9" x14ac:dyDescent="0.3">
@@ -24727,18 +24626,16 @@
       <c r="I2127" s="1"/>
     </row>
     <row r="2128" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2128" s="2"/>
       <c r="I2128" s="1"/>
     </row>
     <row r="2129" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2129" s="2"/>
       <c r="I2129" s="1"/>
     </row>
     <row r="2130" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2130" s="2"/>
       <c r="I2130" s="1"/>
     </row>
     <row r="2131" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2131" s="2"/>
       <c r="I2131" s="1"/>
     </row>
     <row r="2132" spans="8:9" x14ac:dyDescent="0.3">
@@ -24749,12 +24646,15 @@
       <c r="I2133" s="1"/>
     </row>
     <row r="2134" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2134" s="2"/>
       <c r="I2134" s="1"/>
     </row>
     <row r="2135" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2135" s="2"/>
       <c r="I2135" s="1"/>
     </row>
     <row r="2136" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2136" s="2"/>
       <c r="I2136" s="1"/>
     </row>
     <row r="2137" spans="8:9" x14ac:dyDescent="0.3">
@@ -24770,15 +24670,12 @@
       <c r="I2139" s="1"/>
     </row>
     <row r="2140" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2140" s="2"/>
       <c r="I2140" s="1"/>
     </row>
     <row r="2141" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2141" s="2"/>
       <c r="I2141" s="1"/>
     </row>
     <row r="2142" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2142" s="2"/>
       <c r="I2142" s="1"/>
     </row>
     <row r="2143" spans="8:9" x14ac:dyDescent="0.3">
@@ -24789,6 +24686,7 @@
       <c r="I2144" s="1"/>
     </row>
     <row r="2145" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2145" s="2"/>
       <c r="I2145" s="1"/>
     </row>
     <row r="2146" spans="8:9" x14ac:dyDescent="0.3">
@@ -24806,6 +24704,7 @@
       <c r="I2149" s="1"/>
     </row>
     <row r="2150" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2150" s="2"/>
       <c r="I2150" s="1"/>
     </row>
     <row r="2151" spans="8:9" x14ac:dyDescent="0.3">
@@ -24816,27 +24715,26 @@
       <c r="I2152" s="1"/>
     </row>
     <row r="2153" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2153" s="2"/>
       <c r="I2153" s="1"/>
     </row>
     <row r="2154" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2154" s="2"/>
       <c r="I2154" s="1"/>
     </row>
     <row r="2155" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2155" s="2"/>
       <c r="I2155" s="1"/>
     </row>
     <row r="2156" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2156" s="1"/>
     </row>
     <row r="2157" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2157" s="2"/>
       <c r="I2157" s="1"/>
     </row>
     <row r="2158" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2158" s="1"/>
     </row>
     <row r="2159" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2159" s="2"/>
       <c r="I2159" s="1"/>
     </row>
     <row r="2160" spans="8:9" x14ac:dyDescent="0.3">
@@ -24854,13 +24752,14 @@
       <c r="I2163" s="1"/>
     </row>
     <row r="2164" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2164" s="2"/>
       <c r="I2164" s="1"/>
     </row>
     <row r="2165" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2165" s="2"/>
       <c r="I2165" s="1"/>
     </row>
     <row r="2166" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2166" s="2"/>
       <c r="I2166" s="1"/>
     </row>
     <row r="2167" spans="8:9" x14ac:dyDescent="0.3">
@@ -24872,6 +24771,7 @@
       <c r="I2168" s="1"/>
     </row>
     <row r="2169" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2169" s="2"/>
       <c r="I2169" s="1"/>
     </row>
     <row r="2170" spans="8:9" x14ac:dyDescent="0.3">
@@ -24883,7 +24783,6 @@
       <c r="I2171" s="1"/>
     </row>
     <row r="2172" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2172" s="2"/>
       <c r="I2172" s="1"/>
     </row>
     <row r="2173" spans="8:9" x14ac:dyDescent="0.3">
@@ -24914,6 +24813,7 @@
       <c r="I2179" s="1"/>
     </row>
     <row r="2180" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2180" s="2"/>
       <c r="I2180" s="1"/>
     </row>
     <row r="2181" spans="8:9" x14ac:dyDescent="0.3">
@@ -24937,7 +24837,6 @@
       <c r="I2185" s="1"/>
     </row>
     <row r="2186" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2186" s="2"/>
       <c r="I2186" s="1"/>
     </row>
     <row r="2187" spans="8:9" x14ac:dyDescent="0.3">
@@ -24953,6 +24852,7 @@
       <c r="I2189" s="1"/>
     </row>
     <row r="2190" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2190" s="2"/>
       <c r="I2190" s="1"/>
     </row>
     <row r="2191" spans="8:9" x14ac:dyDescent="0.3">
@@ -24988,7 +24888,6 @@
       <c r="I2198" s="1"/>
     </row>
     <row r="2199" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2199" s="2"/>
       <c r="I2199" s="1"/>
     </row>
     <row r="2200" spans="8:9" x14ac:dyDescent="0.3">
@@ -25004,6 +24903,7 @@
       <c r="I2202" s="1"/>
     </row>
     <row r="2203" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2203" s="2"/>
       <c r="I2203" s="1"/>
     </row>
     <row r="2204" spans="8:9" x14ac:dyDescent="0.3">
@@ -25047,7 +24947,6 @@
       <c r="I2213" s="1"/>
     </row>
     <row r="2214" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2214" s="2"/>
       <c r="I2214" s="1"/>
     </row>
     <row r="2215" spans="8:9" x14ac:dyDescent="0.3">
@@ -25078,6 +24977,7 @@
       <c r="I2221" s="1"/>
     </row>
     <row r="2222" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2222" s="2"/>
       <c r="I2222" s="1"/>
     </row>
     <row r="2223" spans="8:9" x14ac:dyDescent="0.3">
@@ -25109,7 +25009,6 @@
       <c r="I2229" s="1"/>
     </row>
     <row r="2230" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2230" s="2"/>
       <c r="I2230" s="1"/>
     </row>
     <row r="2231" spans="8:9" x14ac:dyDescent="0.3">
@@ -25125,6 +25024,7 @@
       <c r="I2233" s="1"/>
     </row>
     <row r="2234" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2234" s="2"/>
       <c r="I2234" s="1"/>
     </row>
     <row r="2235" spans="8:9" x14ac:dyDescent="0.3">
@@ -25144,7 +25044,6 @@
       <c r="I2238" s="1"/>
     </row>
     <row r="2239" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2239" s="2"/>
       <c r="I2239" s="1"/>
     </row>
     <row r="2240" spans="8:9" x14ac:dyDescent="0.3">
@@ -25156,10 +25055,10 @@
       <c r="I2241" s="1"/>
     </row>
     <row r="2242" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2242" s="2"/>
       <c r="I2242" s="1"/>
     </row>
     <row r="2243" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2243" s="2"/>
       <c r="I2243" s="1"/>
     </row>
     <row r="2244" spans="8:9" x14ac:dyDescent="0.3">
@@ -25171,6 +25070,7 @@
       <c r="I2245" s="1"/>
     </row>
     <row r="2246" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2246" s="2"/>
       <c r="I2246" s="1"/>
     </row>
     <row r="2247" spans="8:9" x14ac:dyDescent="0.3">
@@ -25190,7 +25090,6 @@
       <c r="I2250" s="1"/>
     </row>
     <row r="2251" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2251" s="2"/>
       <c r="I2251" s="1"/>
     </row>
     <row r="2252" spans="8:9" x14ac:dyDescent="0.3">
@@ -25206,6 +25105,7 @@
       <c r="I2254" s="1"/>
     </row>
     <row r="2255" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2255" s="2"/>
       <c r="I2255" s="1"/>
     </row>
     <row r="2256" spans="8:9" x14ac:dyDescent="0.3">
@@ -25213,7 +25113,6 @@
       <c r="I2256" s="1"/>
     </row>
     <row r="2257" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2257" s="2"/>
       <c r="I2257" s="1"/>
     </row>
     <row r="2258" spans="8:9" x14ac:dyDescent="0.3">
@@ -25229,6 +25128,7 @@
       <c r="I2260" s="1"/>
     </row>
     <row r="2261" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2261" s="2"/>
       <c r="I2261" s="1"/>
     </row>
     <row r="2262" spans="8:9" x14ac:dyDescent="0.3">
@@ -25312,7 +25212,6 @@
       <c r="I2281" s="1"/>
     </row>
     <row r="2282" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2282" s="2"/>
       <c r="I2282" s="1"/>
     </row>
     <row r="2283" spans="8:9" x14ac:dyDescent="0.3">
@@ -25343,6 +25242,7 @@
       <c r="I2289" s="1"/>
     </row>
     <row r="2290" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2290" s="2"/>
       <c r="I2290" s="1"/>
     </row>
     <row r="2291" spans="8:9" x14ac:dyDescent="0.3">
@@ -25398,7 +25298,6 @@
       <c r="I2303" s="1"/>
     </row>
     <row r="2304" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2304" s="2"/>
       <c r="I2304" s="1"/>
     </row>
     <row r="2305" spans="8:9" x14ac:dyDescent="0.3">
@@ -25414,6 +25313,7 @@
       <c r="I2307" s="1"/>
     </row>
     <row r="2308" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2308" s="2"/>
       <c r="I2308" s="1"/>
     </row>
     <row r="2309" spans="8:9" x14ac:dyDescent="0.3">
@@ -25445,7 +25345,6 @@
       <c r="I2315" s="1"/>
     </row>
     <row r="2316" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2316" s="2"/>
       <c r="I2316" s="1"/>
     </row>
     <row r="2317" spans="8:9" x14ac:dyDescent="0.3">
@@ -25461,6 +25360,7 @@
       <c r="I2319" s="1"/>
     </row>
     <row r="2320" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2320" s="2"/>
       <c r="I2320" s="1"/>
     </row>
     <row r="2321" spans="8:9" x14ac:dyDescent="0.3">
@@ -25544,7 +25444,6 @@
       <c r="I2340" s="1"/>
     </row>
     <row r="2341" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2341" s="2"/>
       <c r="I2341" s="1"/>
     </row>
     <row r="2342" spans="8:9" x14ac:dyDescent="0.3">
@@ -25552,7 +25451,6 @@
       <c r="I2342" s="1"/>
     </row>
     <row r="2343" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2343" s="2"/>
       <c r="I2343" s="1"/>
     </row>
     <row r="2344" spans="8:9" x14ac:dyDescent="0.3">
@@ -25560,6 +25458,7 @@
       <c r="I2344" s="1"/>
     </row>
     <row r="2345" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2345" s="2"/>
       <c r="I2345" s="1"/>
     </row>
     <row r="2346" spans="8:9" x14ac:dyDescent="0.3">
@@ -25567,6 +25466,7 @@
       <c r="I2346" s="1"/>
     </row>
     <row r="2347" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2347" s="2"/>
       <c r="I2347" s="1"/>
     </row>
     <row r="2348" spans="8:9" x14ac:dyDescent="0.3">
@@ -25618,7 +25518,6 @@
       <c r="I2359" s="1"/>
     </row>
     <row r="2360" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2360" s="2"/>
       <c r="I2360" s="1"/>
     </row>
     <row r="2361" spans="8:9" x14ac:dyDescent="0.3">
@@ -25634,6 +25533,7 @@
       <c r="I2363" s="1"/>
     </row>
     <row r="2364" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2364" s="2"/>
       <c r="I2364" s="1"/>
     </row>
     <row r="2365" spans="8:9" x14ac:dyDescent="0.3">
@@ -25693,7 +25593,6 @@
       <c r="I2378" s="1"/>
     </row>
     <row r="2379" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2379" s="2"/>
       <c r="I2379" s="1"/>
     </row>
     <row r="2380" spans="8:9" x14ac:dyDescent="0.3">
@@ -25709,6 +25608,7 @@
       <c r="I2382" s="1"/>
     </row>
     <row r="2383" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2383" s="2"/>
       <c r="I2383" s="1"/>
     </row>
     <row r="2384" spans="8:9" x14ac:dyDescent="0.3">
@@ -25748,7 +25648,6 @@
       <c r="I2392" s="1"/>
     </row>
     <row r="2393" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2393" s="2"/>
       <c r="I2393" s="1"/>
     </row>
     <row r="2394" spans="8:9" x14ac:dyDescent="0.3">
@@ -25764,6 +25663,7 @@
       <c r="I2396" s="1"/>
     </row>
     <row r="2397" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2397" s="2"/>
       <c r="I2397" s="1"/>
     </row>
     <row r="2398" spans="8:9" x14ac:dyDescent="0.3">
@@ -25799,7 +25699,6 @@
       <c r="I2405" s="1"/>
     </row>
     <row r="2406" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2406" s="2"/>
       <c r="I2406" s="1"/>
     </row>
     <row r="2407" spans="8:9" x14ac:dyDescent="0.3">
@@ -25815,10 +25714,10 @@
       <c r="I2409" s="1"/>
     </row>
     <row r="2410" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2410" s="2"/>
       <c r="I2410" s="1"/>
     </row>
     <row r="2411" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2411" s="2"/>
       <c r="I2411" s="1"/>
     </row>
     <row r="2412" spans="8:9" x14ac:dyDescent="0.3">
@@ -25830,10 +25729,10 @@
       <c r="I2413" s="1"/>
     </row>
     <row r="2414" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2414" s="2"/>
       <c r="I2414" s="1"/>
     </row>
     <row r="2415" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2415" s="2"/>
       <c r="I2415" s="1"/>
     </row>
     <row r="2416" spans="8:9" x14ac:dyDescent="0.3">
@@ -25841,10 +25740,10 @@
       <c r="I2416" s="1"/>
     </row>
     <row r="2417" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2417" s="2"/>
       <c r="I2417" s="1"/>
     </row>
     <row r="2418" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2418" s="2"/>
       <c r="I2418" s="1"/>
     </row>
     <row r="2419" spans="8:9" x14ac:dyDescent="0.3">
@@ -25882,10 +25781,10 @@
       <c r="I2427" s="1"/>
     </row>
     <row r="2428" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2428" s="2"/>
       <c r="I2428" s="1"/>
     </row>
     <row r="2429" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2429" s="2"/>
       <c r="I2429" s="1"/>
     </row>
     <row r="2430" spans="8:9" x14ac:dyDescent="0.3">
@@ -25897,6 +25796,7 @@
       <c r="I2431" s="1"/>
     </row>
     <row r="2432" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2432" s="2"/>
       <c r="I2432" s="1"/>
     </row>
     <row r="2433" spans="8:9" x14ac:dyDescent="0.3">
@@ -25916,15 +25816,12 @@
       <c r="I2436" s="1"/>
     </row>
     <row r="2437" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2437" s="2"/>
       <c r="I2437" s="1"/>
     </row>
     <row r="2438" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2438" s="2"/>
       <c r="I2438" s="1"/>
     </row>
     <row r="2439" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2439" s="2"/>
       <c r="I2439" s="1"/>
     </row>
     <row r="2440" spans="8:9" x14ac:dyDescent="0.3">
@@ -25932,12 +25829,15 @@
       <c r="I2440" s="1"/>
     </row>
     <row r="2441" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2441" s="2"/>
       <c r="I2441" s="1"/>
     </row>
     <row r="2442" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2442" s="2"/>
       <c r="I2442" s="1"/>
     </row>
     <row r="2443" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2443" s="2"/>
       <c r="I2443" s="1"/>
     </row>
     <row r="2444" spans="8:9" x14ac:dyDescent="0.3">
@@ -26001,7 +25901,6 @@
       <c r="I2458" s="1"/>
     </row>
     <row r="2459" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2459" s="2"/>
       <c r="I2459" s="1"/>
     </row>
     <row r="2460" spans="8:9" x14ac:dyDescent="0.3">
@@ -26017,6 +25916,7 @@
       <c r="I2462" s="1"/>
     </row>
     <row r="2463" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2463" s="2"/>
       <c r="I2463" s="1"/>
     </row>
     <row r="2464" spans="8:9" x14ac:dyDescent="0.3">
@@ -26052,7 +25952,6 @@
       <c r="I2471" s="1"/>
     </row>
     <row r="2472" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2472" s="2"/>
       <c r="I2472" s="1"/>
     </row>
     <row r="2473" spans="8:9" x14ac:dyDescent="0.3">
@@ -26068,6 +25967,7 @@
       <c r="I2475" s="1"/>
     </row>
     <row r="2476" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2476" s="2"/>
       <c r="I2476" s="1"/>
     </row>
     <row r="2477" spans="8:9" x14ac:dyDescent="0.3">
@@ -26095,7 +25995,6 @@
       <c r="I2482" s="1"/>
     </row>
     <row r="2483" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2483" s="2"/>
       <c r="I2483" s="1"/>
     </row>
     <row r="2484" spans="8:9" x14ac:dyDescent="0.3">
@@ -26111,10 +26010,10 @@
       <c r="I2486" s="1"/>
     </row>
     <row r="2487" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2487" s="2"/>
       <c r="I2487" s="1"/>
     </row>
     <row r="2488" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2488" s="2"/>
       <c r="I2488" s="1"/>
     </row>
     <row r="2489" spans="8:9" x14ac:dyDescent="0.3">
@@ -26130,6 +26029,7 @@
       <c r="I2491" s="1"/>
     </row>
     <row r="2492" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2492" s="2"/>
       <c r="I2492" s="1"/>
     </row>
     <row r="2493" spans="8:9" x14ac:dyDescent="0.3">
@@ -26137,11 +26037,9 @@
       <c r="I2493" s="1"/>
     </row>
     <row r="2494" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2494" s="2"/>
       <c r="I2494" s="1"/>
     </row>
     <row r="2495" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2495" s="2"/>
       <c r="I2495" s="1"/>
     </row>
     <row r="2496" spans="8:9" x14ac:dyDescent="0.3">
@@ -26153,9 +26051,11 @@
       <c r="I2497" s="1"/>
     </row>
     <row r="2498" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2498" s="2"/>
       <c r="I2498" s="1"/>
     </row>
     <row r="2499" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2499" s="2"/>
       <c r="I2499" s="1"/>
     </row>
     <row r="2500" spans="8:9" x14ac:dyDescent="0.3">
@@ -26199,7 +26099,6 @@
       <c r="I2509" s="1"/>
     </row>
     <row r="2510" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2510" s="2"/>
       <c r="I2510" s="1"/>
     </row>
     <row r="2511" spans="8:9" x14ac:dyDescent="0.3">
@@ -26215,6 +26114,7 @@
       <c r="I2513" s="1"/>
     </row>
     <row r="2514" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2514" s="2"/>
       <c r="I2514" s="1"/>
     </row>
     <row r="2515" spans="8:9" x14ac:dyDescent="0.3">
@@ -26258,7 +26158,6 @@
       <c r="I2524" s="1"/>
     </row>
     <row r="2525" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2525" s="2"/>
       <c r="I2525" s="1"/>
     </row>
     <row r="2526" spans="8:9" x14ac:dyDescent="0.3">
@@ -26274,6 +26173,7 @@
       <c r="I2528" s="1"/>
     </row>
     <row r="2529" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2529" s="2"/>
       <c r="I2529" s="1"/>
     </row>
     <row r="2530" spans="8:9" x14ac:dyDescent="0.3">
@@ -26309,7 +26209,6 @@
       <c r="I2537" s="1"/>
     </row>
     <row r="2538" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2538" s="2"/>
       <c r="I2538" s="1"/>
     </row>
     <row r="2539" spans="8:9" x14ac:dyDescent="0.3">
@@ -26321,10 +26220,10 @@
       <c r="I2540" s="1"/>
     </row>
     <row r="2541" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2541" s="2"/>
       <c r="I2541" s="1"/>
     </row>
     <row r="2542" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2542" s="2"/>
       <c r="I2542" s="1"/>
     </row>
     <row r="2543" spans="8:9" x14ac:dyDescent="0.3">
@@ -26336,6 +26235,7 @@
       <c r="I2544" s="1"/>
     </row>
     <row r="2545" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2545" s="2"/>
       <c r="I2545" s="1"/>
     </row>
     <row r="2546" spans="8:9" x14ac:dyDescent="0.3">
@@ -26375,7 +26275,6 @@
       <c r="I2554" s="1"/>
     </row>
     <row r="2555" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2555" s="2"/>
       <c r="I2555" s="1"/>
     </row>
     <row r="2556" spans="8:9" x14ac:dyDescent="0.3">
@@ -26391,10 +26290,10 @@
       <c r="I2558" s="1"/>
     </row>
     <row r="2559" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2559" s="2"/>
       <c r="I2559" s="1"/>
     </row>
     <row r="2560" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2560" s="2"/>
       <c r="I2560" s="1"/>
     </row>
     <row r="2561" spans="8:9" x14ac:dyDescent="0.3">
@@ -26425,6 +26324,7 @@
       <c r="I2567" s="1"/>
     </row>
     <row r="2568" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2568" s="2"/>
       <c r="I2568" s="1"/>
     </row>
     <row r="2569" spans="8:9" x14ac:dyDescent="0.3">
@@ -26460,7 +26360,6 @@
       <c r="I2576" s="1"/>
     </row>
     <row r="2577" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2577" s="2"/>
       <c r="I2577" s="1"/>
     </row>
     <row r="2578" spans="8:9" x14ac:dyDescent="0.3">
@@ -26476,6 +26375,7 @@
       <c r="I2580" s="1"/>
     </row>
     <row r="2581" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2581" s="2"/>
       <c r="I2581" s="1"/>
     </row>
     <row r="2582" spans="8:9" x14ac:dyDescent="0.3">
@@ -26511,7 +26411,6 @@
       <c r="I2589" s="1"/>
     </row>
     <row r="2590" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2590" s="2"/>
       <c r="I2590" s="1"/>
     </row>
     <row r="2591" spans="8:9" x14ac:dyDescent="0.3">
@@ -26519,7 +26418,6 @@
       <c r="I2591" s="1"/>
     </row>
     <row r="2592" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2592" s="2"/>
       <c r="I2592" s="1"/>
     </row>
     <row r="2593" spans="8:9" x14ac:dyDescent="0.3">
@@ -26527,6 +26425,7 @@
       <c r="I2593" s="1"/>
     </row>
     <row r="2594" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2594" s="2"/>
       <c r="I2594" s="1"/>
     </row>
     <row r="2595" spans="8:9" x14ac:dyDescent="0.3">
@@ -26534,6 +26433,7 @@
       <c r="I2595" s="1"/>
     </row>
     <row r="2596" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2596" s="2"/>
       <c r="I2596" s="1"/>
     </row>
     <row r="2597" spans="8:9" x14ac:dyDescent="0.3">
@@ -26545,7 +26445,6 @@
       <c r="I2598" s="1"/>
     </row>
     <row r="2599" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2599" s="2"/>
       <c r="I2599" s="1"/>
     </row>
     <row r="2600" spans="8:9" x14ac:dyDescent="0.3">
@@ -26561,6 +26460,7 @@
       <c r="I2602" s="1"/>
     </row>
     <row r="2603" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2603" s="2"/>
       <c r="I2603" s="1"/>
     </row>
     <row r="2604" spans="8:9" x14ac:dyDescent="0.3">
@@ -26584,7 +26484,6 @@
       <c r="I2608" s="1"/>
     </row>
     <row r="2609" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2609" s="2"/>
       <c r="I2609" s="1"/>
     </row>
     <row r="2610" spans="8:9" x14ac:dyDescent="0.3">
@@ -26600,6 +26499,7 @@
       <c r="I2612" s="1"/>
     </row>
     <row r="2613" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2613" s="2"/>
       <c r="I2613" s="1"/>
     </row>
     <row r="2614" spans="8:9" x14ac:dyDescent="0.3">
@@ -26663,7 +26563,6 @@
       <c r="I2628" s="1"/>
     </row>
     <row r="2629" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2629" s="2"/>
       <c r="I2629" s="1"/>
     </row>
     <row r="2630" spans="8:9" x14ac:dyDescent="0.3">
@@ -26675,10 +26574,10 @@
       <c r="I2631" s="1"/>
     </row>
     <row r="2632" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2632" s="2"/>
       <c r="I2632" s="1"/>
     </row>
     <row r="2633" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2633" s="2"/>
       <c r="I2633" s="1"/>
     </row>
     <row r="2634" spans="8:9" x14ac:dyDescent="0.3">
@@ -26690,6 +26589,7 @@
       <c r="I2635" s="1"/>
     </row>
     <row r="2636" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2636" s="2"/>
       <c r="I2636" s="1"/>
     </row>
     <row r="2637" spans="8:9" x14ac:dyDescent="0.3">
@@ -26709,7 +26609,6 @@
       <c r="I2640" s="1"/>
     </row>
     <row r="2641" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2641" s="2"/>
       <c r="I2641" s="1"/>
     </row>
     <row r="2642" spans="8:9" x14ac:dyDescent="0.3">
@@ -26725,6 +26624,7 @@
       <c r="I2644" s="1"/>
     </row>
     <row r="2645" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2645" s="2"/>
       <c r="I2645" s="1"/>
     </row>
     <row r="2646" spans="8:9" x14ac:dyDescent="0.3">
@@ -26744,7 +26644,6 @@
       <c r="I2649" s="1"/>
     </row>
     <row r="2650" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2650" s="2"/>
       <c r="I2650" s="1"/>
     </row>
     <row r="2651" spans="8:9" x14ac:dyDescent="0.3">
@@ -26752,7 +26651,6 @@
       <c r="I2651" s="1"/>
     </row>
     <row r="2652" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2652" s="2"/>
       <c r="I2652" s="1"/>
     </row>
     <row r="2653" spans="8:9" x14ac:dyDescent="0.3">
@@ -26760,6 +26658,7 @@
       <c r="I2653" s="1"/>
     </row>
     <row r="2654" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2654" s="2"/>
       <c r="I2654" s="1"/>
     </row>
     <row r="2655" spans="8:9" x14ac:dyDescent="0.3">
@@ -26767,6 +26666,7 @@
       <c r="I2655" s="1"/>
     </row>
     <row r="2656" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2656" s="2"/>
       <c r="I2656" s="1"/>
     </row>
     <row r="2657" spans="8:9" x14ac:dyDescent="0.3">
@@ -26778,7 +26678,6 @@
       <c r="I2658" s="1"/>
     </row>
     <row r="2659" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2659" s="2"/>
       <c r="I2659" s="1"/>
     </row>
     <row r="2660" spans="8:9" x14ac:dyDescent="0.3">
@@ -26790,10 +26689,10 @@
       <c r="I2661" s="1"/>
     </row>
     <row r="2662" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2662" s="2"/>
       <c r="I2662" s="1"/>
     </row>
     <row r="2663" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2663" s="2"/>
       <c r="I2663" s="1"/>
     </row>
     <row r="2664" spans="8:9" x14ac:dyDescent="0.3">
@@ -26805,6 +26704,7 @@
       <c r="I2665" s="1"/>
     </row>
     <row r="2666" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2666" s="2"/>
       <c r="I2666" s="1"/>
     </row>
     <row r="2667" spans="8:9" x14ac:dyDescent="0.3">
@@ -26820,11 +26720,9 @@
       <c r="I2669" s="1"/>
     </row>
     <row r="2670" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2670" s="2"/>
       <c r="I2670" s="1"/>
     </row>
     <row r="2671" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2671" s="2"/>
       <c r="I2671" s="1"/>
     </row>
     <row r="2672" spans="8:9" x14ac:dyDescent="0.3">
@@ -26836,9 +26734,11 @@
       <c r="I2673" s="1"/>
     </row>
     <row r="2674" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2674" s="2"/>
       <c r="I2674" s="1"/>
     </row>
     <row r="2675" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2675" s="2"/>
       <c r="I2675" s="1"/>
     </row>
     <row r="2676" spans="8:9" x14ac:dyDescent="0.3">
@@ -26870,7 +26770,6 @@
       <c r="I2682" s="1"/>
     </row>
     <row r="2683" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2683" s="2"/>
       <c r="I2683" s="1"/>
     </row>
     <row r="2684" spans="8:9" x14ac:dyDescent="0.3">
@@ -26886,6 +26785,7 @@
       <c r="I2686" s="1"/>
     </row>
     <row r="2687" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2687" s="2"/>
       <c r="I2687" s="1"/>
     </row>
     <row r="2688" spans="8:9" x14ac:dyDescent="0.3">
@@ -26893,7 +26793,6 @@
       <c r="I2688" s="1"/>
     </row>
     <row r="2689" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2689" s="2"/>
       <c r="I2689" s="1"/>
     </row>
     <row r="2690" spans="8:9" x14ac:dyDescent="0.3">
@@ -26909,6 +26808,7 @@
       <c r="I2692" s="1"/>
     </row>
     <row r="2693" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2693" s="2"/>
       <c r="I2693" s="1"/>
     </row>
     <row r="2694" spans="8:9" x14ac:dyDescent="0.3">
@@ -26960,7 +26860,6 @@
       <c r="I2705" s="1"/>
     </row>
     <row r="2706" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2706" s="2"/>
       <c r="I2706" s="1"/>
     </row>
     <row r="2707" spans="8:9" x14ac:dyDescent="0.3">
@@ -26976,6 +26875,7 @@
       <c r="I2709" s="1"/>
     </row>
     <row r="2710" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2710" s="2"/>
       <c r="I2710" s="1"/>
     </row>
     <row r="2711" spans="8:9" x14ac:dyDescent="0.3">
@@ -26995,7 +26895,6 @@
       <c r="I2714" s="1"/>
     </row>
     <row r="2715" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2715" s="2"/>
       <c r="I2715" s="1"/>
     </row>
     <row r="2716" spans="8:9" x14ac:dyDescent="0.3">
@@ -27011,6 +26910,7 @@
       <c r="I2718" s="1"/>
     </row>
     <row r="2719" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2719" s="2"/>
       <c r="I2719" s="1"/>
     </row>
     <row r="2720" spans="8:9" x14ac:dyDescent="0.3">
@@ -27042,7 +26942,6 @@
       <c r="I2726" s="1"/>
     </row>
     <row r="2727" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2727" s="2"/>
       <c r="I2727" s="1"/>
     </row>
     <row r="2728" spans="8:9" x14ac:dyDescent="0.3">
@@ -27058,6 +26957,7 @@
       <c r="I2730" s="1"/>
     </row>
     <row r="2731" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2731" s="2"/>
       <c r="I2731" s="1"/>
     </row>
     <row r="2732" spans="8:9" x14ac:dyDescent="0.3">
@@ -27117,7 +27017,6 @@
       <c r="I2745" s="1"/>
     </row>
     <row r="2746" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2746" s="2"/>
       <c r="I2746" s="1"/>
     </row>
     <row r="2747" spans="8:9" x14ac:dyDescent="0.3">
@@ -27133,10 +27032,10 @@
       <c r="I2749" s="1"/>
     </row>
     <row r="2750" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2750" s="2"/>
       <c r="I2750" s="1"/>
     </row>
     <row r="2751" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2751" s="2"/>
       <c r="I2751" s="1"/>
     </row>
     <row r="2752" spans="8:9" x14ac:dyDescent="0.3">
@@ -27152,6 +27051,7 @@
       <c r="I2754" s="1"/>
     </row>
     <row r="2755" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2755" s="2"/>
       <c r="I2755" s="1"/>
     </row>
     <row r="2756" spans="8:9" x14ac:dyDescent="0.3">
@@ -27255,7 +27155,6 @@
       <c r="I2780" s="1"/>
     </row>
     <row r="2781" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2781" s="2"/>
       <c r="I2781" s="1"/>
     </row>
     <row r="2782" spans="8:9" x14ac:dyDescent="0.3">
@@ -27271,6 +27170,7 @@
       <c r="I2784" s="1"/>
     </row>
     <row r="2785" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2785" s="2"/>
       <c r="I2785" s="1"/>
     </row>
     <row r="2786" spans="8:9" x14ac:dyDescent="0.3">
@@ -27318,11 +27218,9 @@
       <c r="I2796" s="1"/>
     </row>
     <row r="2797" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2797" s="2"/>
       <c r="I2797" s="1"/>
     </row>
     <row r="2798" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2798" s="2"/>
       <c r="I2798" s="1"/>
     </row>
     <row r="2799" spans="8:9" x14ac:dyDescent="0.3">
@@ -27334,9 +27232,11 @@
       <c r="I2800" s="1"/>
     </row>
     <row r="2801" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2801" s="2"/>
       <c r="I2801" s="1"/>
     </row>
     <row r="2802" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2802" s="2"/>
       <c r="I2802" s="1"/>
     </row>
     <row r="2803" spans="8:9" x14ac:dyDescent="0.3">
@@ -27352,11 +27252,9 @@
       <c r="I2805" s="1"/>
     </row>
     <row r="2806" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2806" s="2"/>
       <c r="I2806" s="1"/>
     </row>
     <row r="2807" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2807" s="2"/>
       <c r="I2807" s="1"/>
     </row>
     <row r="2808" spans="8:9" x14ac:dyDescent="0.3">
@@ -27368,9 +27266,11 @@
       <c r="I2809" s="1"/>
     </row>
     <row r="2810" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2810" s="2"/>
       <c r="I2810" s="1"/>
     </row>
     <row r="2811" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2811" s="2"/>
       <c r="I2811" s="1"/>
     </row>
     <row r="2812" spans="8:9" x14ac:dyDescent="0.3">
@@ -27458,7 +27358,6 @@
       <c r="I2832" s="1"/>
     </row>
     <row r="2833" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2833" s="2"/>
       <c r="I2833" s="1"/>
     </row>
     <row r="2834" spans="8:9" x14ac:dyDescent="0.3">
@@ -27474,6 +27373,7 @@
       <c r="I2836" s="1"/>
     </row>
     <row r="2837" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2837" s="2"/>
       <c r="I2837" s="1"/>
     </row>
     <row r="2838" spans="8:9" x14ac:dyDescent="0.3">
@@ -27485,7 +27385,6 @@
       <c r="I2839" s="1"/>
     </row>
     <row r="2840" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2840" s="2"/>
       <c r="I2840" s="1"/>
     </row>
     <row r="2841" spans="8:9" x14ac:dyDescent="0.3">
@@ -27501,6 +27400,7 @@
       <c r="I2843" s="1"/>
     </row>
     <row r="2844" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2844" s="2"/>
       <c r="I2844" s="1"/>
     </row>
     <row r="2845" spans="8:9" x14ac:dyDescent="0.3">
@@ -27656,7 +27556,6 @@
       <c r="I2882" s="1"/>
     </row>
     <row r="2883" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2883" s="2"/>
       <c r="I2883" s="1"/>
     </row>
     <row r="2884" spans="8:9" x14ac:dyDescent="0.3">
@@ -27672,6 +27571,7 @@
       <c r="I2886" s="1"/>
     </row>
     <row r="2887" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2887" s="2"/>
       <c r="I2887" s="1"/>
     </row>
     <row r="2888" spans="8:9" x14ac:dyDescent="0.3">
@@ -27691,7 +27591,6 @@
       <c r="I2891" s="1"/>
     </row>
     <row r="2892" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2892" s="2"/>
       <c r="I2892" s="1"/>
     </row>
     <row r="2893" spans="8:9" x14ac:dyDescent="0.3">
@@ -27699,14 +27598,13 @@
       <c r="I2893" s="1"/>
     </row>
     <row r="2894" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2894" s="2"/>
       <c r="I2894" s="1"/>
     </row>
     <row r="2895" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2895" s="2"/>
       <c r="I2895" s="1"/>
     </row>
     <row r="2896" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2896" s="2"/>
       <c r="I2896" s="1"/>
     </row>
     <row r="2897" spans="8:9" x14ac:dyDescent="0.3">
@@ -27714,9 +27612,11 @@
       <c r="I2897" s="1"/>
     </row>
     <row r="2898" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2898" s="2"/>
       <c r="I2898" s="1"/>
     </row>
     <row r="2899" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2899" s="2"/>
       <c r="I2899" s="1"/>
     </row>
     <row r="2900" spans="8:9" x14ac:dyDescent="0.3">
@@ -27732,7 +27632,6 @@
       <c r="I2902" s="1"/>
     </row>
     <row r="2903" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2903" s="2"/>
       <c r="I2903" s="1"/>
     </row>
     <row r="2904" spans="8:9" x14ac:dyDescent="0.3">
@@ -27763,6 +27662,7 @@
       <c r="I2910" s="1"/>
     </row>
     <row r="2911" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2911" s="2"/>
       <c r="I2911" s="1"/>
     </row>
     <row r="2912" spans="8:9" x14ac:dyDescent="0.3">
@@ -27786,7 +27686,6 @@
       <c r="I2916" s="1"/>
     </row>
     <row r="2917" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2917" s="2"/>
       <c r="I2917" s="1"/>
     </row>
     <row r="2918" spans="8:9" x14ac:dyDescent="0.3">
@@ -27798,10 +27697,10 @@
       <c r="I2919" s="1"/>
     </row>
     <row r="2920" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2920" s="2"/>
       <c r="I2920" s="1"/>
     </row>
     <row r="2921" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2921" s="2"/>
       <c r="I2921" s="1"/>
     </row>
     <row r="2922" spans="8:9" x14ac:dyDescent="0.3">
@@ -27813,6 +27712,7 @@
       <c r="I2923" s="1"/>
     </row>
     <row r="2924" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2924" s="2"/>
       <c r="I2924" s="1"/>
     </row>
     <row r="2925" spans="8:9" x14ac:dyDescent="0.3">
@@ -27940,7 +27840,6 @@
       <c r="I2955" s="1"/>
     </row>
     <row r="2956" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2956" s="2"/>
       <c r="I2956" s="1"/>
     </row>
     <row r="2957" spans="8:9" x14ac:dyDescent="0.3">
@@ -27956,6 +27855,7 @@
       <c r="I2959" s="1"/>
     </row>
     <row r="2960" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2960" s="2"/>
       <c r="I2960" s="1"/>
     </row>
     <row r="2961" spans="8:9" x14ac:dyDescent="0.3">
@@ -28023,7 +27923,6 @@
       <c r="I2976" s="1"/>
     </row>
     <row r="2977" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2977" s="2"/>
       <c r="I2977" s="1"/>
     </row>
     <row r="2978" spans="8:9" x14ac:dyDescent="0.3">
@@ -28039,6 +27938,7 @@
       <c r="I2980" s="1"/>
     </row>
     <row r="2981" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2981" s="2"/>
       <c r="I2981" s="1"/>
     </row>
     <row r="2982" spans="8:9" x14ac:dyDescent="0.3">
@@ -28074,7 +27974,6 @@
       <c r="I2989" s="1"/>
     </row>
     <row r="2990" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2990" s="2"/>
       <c r="I2990" s="1"/>
     </row>
     <row r="2991" spans="8:9" x14ac:dyDescent="0.3">
@@ -28090,6 +27989,7 @@
       <c r="I2993" s="1"/>
     </row>
     <row r="2994" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2994" s="2"/>
       <c r="I2994" s="1"/>
     </row>
     <row r="2995" spans="8:9" x14ac:dyDescent="0.3">
@@ -28233,7 +28133,6 @@
       <c r="I3029" s="1"/>
     </row>
     <row r="3030" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3030" s="2"/>
       <c r="I3030" s="1"/>
     </row>
     <row r="3031" spans="8:9" x14ac:dyDescent="0.3">
@@ -28249,6 +28148,7 @@
       <c r="I3033" s="1"/>
     </row>
     <row r="3034" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3034" s="2"/>
       <c r="I3034" s="1"/>
     </row>
     <row r="3035" spans="8:9" x14ac:dyDescent="0.3">
@@ -28292,7 +28192,6 @@
       <c r="I3044" s="1"/>
     </row>
     <row r="3045" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3045" s="2"/>
       <c r="I3045" s="1"/>
     </row>
     <row r="3046" spans="8:9" x14ac:dyDescent="0.3">
@@ -28308,6 +28207,7 @@
       <c r="I3048" s="1"/>
     </row>
     <row r="3049" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3049" s="2"/>
       <c r="I3049" s="1"/>
     </row>
     <row r="3050" spans="8:9" x14ac:dyDescent="0.3">
@@ -28435,7 +28335,6 @@
       <c r="I3080" s="1"/>
     </row>
     <row r="3081" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3081" s="2"/>
       <c r="I3081" s="1"/>
     </row>
     <row r="3082" spans="8:9" x14ac:dyDescent="0.3">
@@ -28451,6 +28350,7 @@
       <c r="I3084" s="1"/>
     </row>
     <row r="3085" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3085" s="2"/>
       <c r="I3085" s="1"/>
     </row>
     <row r="3086" spans="8:9" x14ac:dyDescent="0.3">
@@ -28554,7 +28454,6 @@
       <c r="I3110" s="1"/>
     </row>
     <row r="3111" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3111" s="2"/>
       <c r="I3111" s="1"/>
     </row>
     <row r="3112" spans="8:9" x14ac:dyDescent="0.3">
@@ -28570,6 +28469,7 @@
       <c r="I3114" s="1"/>
     </row>
     <row r="3115" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3115" s="2"/>
       <c r="I3115" s="1"/>
     </row>
     <row r="3116" spans="8:9" x14ac:dyDescent="0.3">
@@ -28685,7 +28585,6 @@
       <c r="I3143" s="1"/>
     </row>
     <row r="3144" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3144" s="2"/>
       <c r="I3144" s="1"/>
     </row>
     <row r="3145" spans="8:9" x14ac:dyDescent="0.3">
@@ -28701,10 +28600,10 @@
       <c r="I3147" s="1"/>
     </row>
     <row r="3148" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3148" s="2"/>
       <c r="I3148" s="1"/>
     </row>
     <row r="3149" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3149" s="2"/>
       <c r="I3149" s="1"/>
     </row>
     <row r="3150" spans="8:9" x14ac:dyDescent="0.3">
@@ -28716,10 +28615,10 @@
       <c r="I3151" s="1"/>
     </row>
     <row r="3152" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3152" s="2"/>
       <c r="I3152" s="1"/>
     </row>
     <row r="3153" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3153" s="2"/>
       <c r="I3153" s="1"/>
     </row>
     <row r="3154" spans="8:9" x14ac:dyDescent="0.3">
@@ -28731,6 +28630,7 @@
       <c r="I3155" s="1"/>
     </row>
     <row r="3156" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3156" s="2"/>
       <c r="I3156" s="1"/>
     </row>
     <row r="3157" spans="8:9" x14ac:dyDescent="0.3">
@@ -28738,7 +28638,6 @@
       <c r="I3157" s="1"/>
     </row>
     <row r="3158" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3158" s="2"/>
       <c r="I3158" s="1"/>
     </row>
     <row r="3159" spans="8:9" x14ac:dyDescent="0.3">
@@ -28754,6 +28653,7 @@
       <c r="I3161" s="1"/>
     </row>
     <row r="3162" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3162" s="2"/>
       <c r="I3162" s="1"/>
     </row>
     <row r="3163" spans="8:9" x14ac:dyDescent="0.3">
@@ -28777,7 +28677,6 @@
       <c r="I3167" s="1"/>
     </row>
     <row r="3168" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3168" s="2"/>
       <c r="I3168" s="1"/>
     </row>
     <row r="3169" spans="8:9" x14ac:dyDescent="0.3">
@@ -28793,6 +28692,7 @@
       <c r="I3171" s="1"/>
     </row>
     <row r="3172" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3172" s="2"/>
       <c r="I3172" s="1"/>
     </row>
     <row r="3173" spans="8:9" x14ac:dyDescent="0.3">
@@ -29296,7 +29196,6 @@
       <c r="I3297" s="1"/>
     </row>
     <row r="3298" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3298" s="2"/>
       <c r="I3298" s="1"/>
     </row>
     <row r="3299" spans="8:9" x14ac:dyDescent="0.3">
@@ -29312,6 +29211,7 @@
       <c r="I3301" s="1"/>
     </row>
     <row r="3302" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3302" s="2"/>
       <c r="I3302" s="1"/>
     </row>
     <row r="3303" spans="8:9" x14ac:dyDescent="0.3">
@@ -29435,7 +29335,6 @@
       <c r="I3332" s="1"/>
     </row>
     <row r="3333" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3333" s="2"/>
       <c r="I3333" s="1"/>
     </row>
     <row r="3334" spans="8:9" x14ac:dyDescent="0.3">
@@ -29451,6 +29350,7 @@
       <c r="I3336" s="1"/>
     </row>
     <row r="3337" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3337" s="2"/>
       <c r="I3337" s="1"/>
     </row>
     <row r="3338" spans="8:9" x14ac:dyDescent="0.3">
@@ -29558,7 +29458,6 @@
       <c r="I3363" s="1"/>
     </row>
     <row r="3364" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3364" s="2"/>
       <c r="I3364" s="1"/>
     </row>
     <row r="3365" spans="8:9" x14ac:dyDescent="0.3">
@@ -29574,6 +29473,7 @@
       <c r="I3367" s="1"/>
     </row>
     <row r="3368" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3368" s="2"/>
       <c r="I3368" s="1"/>
     </row>
     <row r="3369" spans="8:9" x14ac:dyDescent="0.3">
@@ -29593,7 +29493,6 @@
       <c r="I3372" s="1"/>
     </row>
     <row r="3373" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3373" s="2"/>
       <c r="I3373" s="1"/>
     </row>
     <row r="3374" spans="8:9" x14ac:dyDescent="0.3">
@@ -29609,6 +29508,7 @@
       <c r="I3376" s="1"/>
     </row>
     <row r="3377" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3377" s="2"/>
       <c r="I3377" s="1"/>
     </row>
     <row r="3378" spans="8:9" x14ac:dyDescent="0.3">
@@ -29724,7 +29624,6 @@
       <c r="I3405" s="1"/>
     </row>
     <row r="3406" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3406" s="2"/>
       <c r="I3406" s="1"/>
     </row>
     <row r="3407" spans="8:9" x14ac:dyDescent="0.3">
@@ -29740,6 +29639,7 @@
       <c r="I3409" s="1"/>
     </row>
     <row r="3410" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3410" s="2"/>
       <c r="I3410" s="1"/>
     </row>
     <row r="3411" spans="8:9" x14ac:dyDescent="0.3">
@@ -29747,7 +29647,6 @@
       <c r="I3411" s="1"/>
     </row>
     <row r="3412" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3412" s="2"/>
       <c r="I3412" s="1"/>
     </row>
     <row r="3413" spans="8:9" x14ac:dyDescent="0.3">
@@ -29763,6 +29662,7 @@
       <c r="I3415" s="1"/>
     </row>
     <row r="3416" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3416" s="2"/>
       <c r="I3416" s="1"/>
     </row>
     <row r="3417" spans="8:9" x14ac:dyDescent="0.3">
@@ -30202,7 +30102,6 @@
       <c r="I3525" s="1"/>
     </row>
     <row r="3526" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3526" s="2"/>
       <c r="I3526" s="1"/>
     </row>
     <row r="3527" spans="8:9" x14ac:dyDescent="0.3">
@@ -30218,6 +30117,7 @@
       <c r="I3529" s="1"/>
     </row>
     <row r="3530" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3530" s="2"/>
       <c r="I3530" s="1"/>
     </row>
     <row r="3531" spans="8:9" x14ac:dyDescent="0.3">
@@ -30265,7 +30165,6 @@
       <c r="I3541" s="1"/>
     </row>
     <row r="3542" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3542" s="2"/>
       <c r="I3542" s="1"/>
     </row>
     <row r="3543" spans="8:9" x14ac:dyDescent="0.3">
@@ -30281,6 +30180,7 @@
       <c r="I3545" s="1"/>
     </row>
     <row r="3546" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3546" s="2"/>
       <c r="I3546" s="1"/>
     </row>
     <row r="3547" spans="8:9" x14ac:dyDescent="0.3">
@@ -30400,7 +30300,6 @@
       <c r="I3575" s="1"/>
     </row>
     <row r="3576" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3576" s="2"/>
       <c r="I3576" s="1"/>
     </row>
     <row r="3577" spans="8:9" x14ac:dyDescent="0.3">
@@ -30416,6 +30315,7 @@
       <c r="I3579" s="1"/>
     </row>
     <row r="3580" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3580" s="2"/>
       <c r="I3580" s="1"/>
     </row>
     <row r="3581" spans="8:9" x14ac:dyDescent="0.3">
@@ -30523,7 +30423,6 @@
       <c r="I3606" s="1"/>
     </row>
     <row r="3607" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3607" s="2"/>
       <c r="I3607" s="1"/>
     </row>
     <row r="3608" spans="8:9" x14ac:dyDescent="0.3">
@@ -30539,6 +30438,7 @@
       <c r="I3610" s="1"/>
     </row>
     <row r="3611" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3611" s="2"/>
       <c r="I3611" s="1"/>
     </row>
     <row r="3612" spans="8:9" x14ac:dyDescent="0.3">
@@ -30638,11 +30538,9 @@
       <c r="I3635" s="1"/>
     </row>
     <row r="3636" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3636" s="2"/>
       <c r="I3636" s="1"/>
     </row>
     <row r="3637" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3637" s="2"/>
       <c r="I3637" s="1"/>
     </row>
     <row r="3638" spans="8:9" x14ac:dyDescent="0.3">
@@ -30654,9 +30552,11 @@
       <c r="I3639" s="1"/>
     </row>
     <row r="3640" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3640" s="2"/>
       <c r="I3640" s="1"/>
     </row>
     <row r="3641" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3641" s="2"/>
       <c r="I3641" s="1"/>
     </row>
     <row r="3642" spans="8:9" x14ac:dyDescent="0.3">
@@ -30668,11 +30568,9 @@
       <c r="I3643" s="1"/>
     </row>
     <row r="3644" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3644" s="2"/>
       <c r="I3644" s="1"/>
     </row>
     <row r="3645" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3645" s="2"/>
       <c r="I3645" s="1"/>
     </row>
     <row r="3646" spans="8:9" x14ac:dyDescent="0.3">
@@ -30680,13 +30578,14 @@
       <c r="I3646" s="1"/>
     </row>
     <row r="3647" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3647" s="2"/>
       <c r="I3647" s="1"/>
     </row>
     <row r="3648" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3648" s="2"/>
       <c r="I3648" s="1"/>
     </row>
     <row r="3649" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3649" s="2"/>
       <c r="I3649" s="1"/>
     </row>
     <row r="3650" spans="8:9" x14ac:dyDescent="0.3">
@@ -30694,6 +30593,7 @@
       <c r="I3650" s="1"/>
     </row>
     <row r="3651" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3651" s="2"/>
       <c r="I3651" s="1"/>
     </row>
     <row r="3652" spans="8:9" x14ac:dyDescent="0.3">
@@ -30945,7 +30845,6 @@
       <c r="I3713" s="1"/>
     </row>
     <row r="3714" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3714" s="2"/>
       <c r="I3714" s="1"/>
     </row>
     <row r="3715" spans="8:9" x14ac:dyDescent="0.3">
@@ -30961,6 +30860,7 @@
       <c r="I3717" s="1"/>
     </row>
     <row r="3718" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3718" s="2"/>
       <c r="I3718" s="1"/>
     </row>
     <row r="3719" spans="8:9" x14ac:dyDescent="0.3">
@@ -31200,7 +31100,6 @@
       <c r="I3777" s="1"/>
     </row>
     <row r="3778" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3778" s="2"/>
       <c r="I3778" s="1"/>
     </row>
     <row r="3779" spans="8:9" x14ac:dyDescent="0.3">
@@ -31216,6 +31115,7 @@
       <c r="I3781" s="1"/>
     </row>
     <row r="3782" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3782" s="2"/>
       <c r="I3782" s="1"/>
     </row>
     <row r="3783" spans="8:9" x14ac:dyDescent="0.3">
@@ -31247,7 +31147,6 @@
       <c r="I3789" s="1"/>
     </row>
     <row r="3790" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3790" s="2"/>
       <c r="I3790" s="1"/>
     </row>
     <row r="3791" spans="8:9" x14ac:dyDescent="0.3">
@@ -31263,6 +31162,7 @@
       <c r="I3793" s="1"/>
     </row>
     <row r="3794" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3794" s="2"/>
       <c r="I3794" s="1"/>
     </row>
     <row r="3795" spans="8:9" x14ac:dyDescent="0.3">
@@ -31282,7 +31182,6 @@
       <c r="I3798" s="1"/>
     </row>
     <row r="3799" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3799" s="2"/>
       <c r="I3799" s="1"/>
     </row>
     <row r="3800" spans="8:9" x14ac:dyDescent="0.3">
@@ -31298,6 +31197,7 @@
       <c r="I3802" s="1"/>
     </row>
     <row r="3803" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3803" s="2"/>
       <c r="I3803" s="1"/>
     </row>
     <row r="3804" spans="8:9" x14ac:dyDescent="0.3">
@@ -31505,7 +31405,6 @@
       <c r="I3854" s="1"/>
     </row>
     <row r="3855" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3855" s="2"/>
       <c r="I3855" s="1"/>
     </row>
     <row r="3856" spans="8:9" x14ac:dyDescent="0.3">
@@ -31521,6 +31420,7 @@
       <c r="I3858" s="1"/>
     </row>
     <row r="3859" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3859" s="2"/>
       <c r="I3859" s="1"/>
     </row>
     <row r="3860" spans="8:9" x14ac:dyDescent="0.3">
@@ -31620,7 +31520,6 @@
       <c r="I3883" s="1"/>
     </row>
     <row r="3884" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3884" s="2"/>
       <c r="I3884" s="1"/>
     </row>
     <row r="3885" spans="8:9" x14ac:dyDescent="0.3">
@@ -31636,6 +31535,7 @@
       <c r="I3887" s="1"/>
     </row>
     <row r="3888" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3888" s="2"/>
       <c r="I3888" s="1"/>
     </row>
     <row r="3889" spans="8:9" x14ac:dyDescent="0.3">
@@ -31647,7 +31547,6 @@
       <c r="I3890" s="1"/>
     </row>
     <row r="3891" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3891" s="2"/>
       <c r="I3891" s="1"/>
     </row>
     <row r="3892" spans="8:9" x14ac:dyDescent="0.3">
@@ -31663,6 +31562,7 @@
       <c r="I3894" s="1"/>
     </row>
     <row r="3895" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3895" s="2"/>
       <c r="I3895" s="1"/>
     </row>
     <row r="3896" spans="8:9" x14ac:dyDescent="0.3">
@@ -31794,7 +31694,6 @@
       <c r="I3927" s="1"/>
     </row>
     <row r="3928" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3928" s="2"/>
       <c r="I3928" s="1"/>
     </row>
     <row r="3929" spans="8:9" x14ac:dyDescent="0.3">
@@ -31810,6 +31709,7 @@
       <c r="I3931" s="1"/>
     </row>
     <row r="3932" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3932" s="2"/>
       <c r="I3932" s="1"/>
     </row>
     <row r="3933" spans="8:9" x14ac:dyDescent="0.3">
@@ -32113,7 +32013,6 @@
       <c r="I4007" s="1"/>
     </row>
     <row r="4008" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4008" s="2"/>
       <c r="I4008" s="1"/>
     </row>
     <row r="4009" spans="8:9" x14ac:dyDescent="0.3">
@@ -32129,6 +32028,7 @@
       <c r="I4011" s="1"/>
     </row>
     <row r="4012" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4012" s="2"/>
       <c r="I4012" s="1"/>
     </row>
     <row r="4013" spans="8:9" x14ac:dyDescent="0.3">
@@ -32232,7 +32132,6 @@
       <c r="I4037" s="1"/>
     </row>
     <row r="4038" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4038" s="2"/>
       <c r="I4038" s="1"/>
     </row>
     <row r="4039" spans="8:9" x14ac:dyDescent="0.3">
@@ -32248,6 +32147,7 @@
       <c r="I4041" s="1"/>
     </row>
     <row r="4042" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4042" s="2"/>
       <c r="I4042" s="1"/>
     </row>
     <row r="4043" spans="8:9" x14ac:dyDescent="0.3">
@@ -32307,7 +32207,6 @@
       <c r="I4056" s="1"/>
     </row>
     <row r="4057" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4057" s="2"/>
       <c r="I4057" s="1"/>
     </row>
     <row r="4058" spans="8:9" x14ac:dyDescent="0.3">
@@ -32323,6 +32222,7 @@
       <c r="I4060" s="1"/>
     </row>
     <row r="4061" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4061" s="2"/>
       <c r="I4061" s="1"/>
     </row>
     <row r="4062" spans="8:9" x14ac:dyDescent="0.3">
@@ -32478,7 +32378,6 @@
       <c r="I4099" s="1"/>
     </row>
     <row r="4100" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4100" s="2"/>
       <c r="I4100" s="1"/>
     </row>
     <row r="4101" spans="8:9" x14ac:dyDescent="0.3">
@@ -32494,6 +32393,7 @@
       <c r="I4103" s="1"/>
     </row>
     <row r="4104" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4104" s="2"/>
       <c r="I4104" s="1"/>
     </row>
     <row r="4105" spans="8:9" x14ac:dyDescent="0.3">
@@ -32605,7 +32505,6 @@
       <c r="I4131" s="1"/>
     </row>
     <row r="4132" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4132" s="2"/>
       <c r="I4132" s="1"/>
     </row>
     <row r="4133" spans="8:9" x14ac:dyDescent="0.3">
@@ -32617,10 +32516,10 @@
       <c r="I4134" s="1"/>
     </row>
     <row r="4135" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4135" s="2"/>
       <c r="I4135" s="1"/>
     </row>
     <row r="4136" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4136" s="2"/>
       <c r="I4136" s="1"/>
     </row>
     <row r="4137" spans="8:9" x14ac:dyDescent="0.3">
@@ -32632,6 +32531,7 @@
       <c r="I4138" s="1"/>
     </row>
     <row r="4139" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4139" s="2"/>
       <c r="I4139" s="1"/>
     </row>
     <row r="4140" spans="8:9" x14ac:dyDescent="0.3">
@@ -32643,7 +32543,6 @@
       <c r="I4141" s="1"/>
     </row>
     <row r="4142" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4142" s="2"/>
       <c r="I4142" s="1"/>
     </row>
     <row r="4143" spans="8:9" x14ac:dyDescent="0.3">
@@ -32659,6 +32558,7 @@
       <c r="I4145" s="1"/>
     </row>
     <row r="4146" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4146" s="2"/>
       <c r="I4146" s="1"/>
     </row>
     <row r="4147" spans="8:9" x14ac:dyDescent="0.3">
@@ -33178,7 +33078,6 @@
       <c r="I4275" s="1"/>
     </row>
     <row r="4276" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4276" s="2"/>
       <c r="I4276" s="1"/>
     </row>
     <row r="4277" spans="8:9" x14ac:dyDescent="0.3">
@@ -33194,6 +33093,7 @@
       <c r="I4279" s="1"/>
     </row>
     <row r="4280" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4280" s="2"/>
       <c r="I4280" s="1"/>
     </row>
     <row r="4281" spans="8:9" x14ac:dyDescent="0.3">
@@ -33205,7 +33105,6 @@
       <c r="I4282" s="1"/>
     </row>
     <row r="4283" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4283" s="2"/>
       <c r="I4283" s="1"/>
     </row>
     <row r="4284" spans="8:9" x14ac:dyDescent="0.3">
@@ -33221,6 +33120,7 @@
       <c r="I4286" s="1"/>
     </row>
     <row r="4287" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4287" s="2"/>
       <c r="I4287" s="1"/>
     </row>
     <row r="4288" spans="8:9" x14ac:dyDescent="0.3">
@@ -33500,7 +33400,6 @@
       <c r="I4356" s="1"/>
     </row>
     <row r="4357" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4357" s="2"/>
       <c r="I4357" s="1"/>
     </row>
     <row r="4358" spans="8:9" x14ac:dyDescent="0.3">
@@ -33516,6 +33415,7 @@
       <c r="I4360" s="1"/>
     </row>
     <row r="4361" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4361" s="2"/>
       <c r="I4361" s="1"/>
     </row>
     <row r="4362" spans="8:9" x14ac:dyDescent="0.3">
@@ -33643,11 +33543,9 @@
       <c r="I4392" s="1"/>
     </row>
     <row r="4393" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4393" s="2"/>
       <c r="I4393" s="1"/>
     </row>
     <row r="4394" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4394" s="2"/>
       <c r="I4394" s="1"/>
     </row>
     <row r="4395" spans="8:9" x14ac:dyDescent="0.3">
@@ -33659,9 +33557,11 @@
       <c r="I4396" s="1"/>
     </row>
     <row r="4397" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4397" s="2"/>
       <c r="I4397" s="1"/>
     </row>
     <row r="4398" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4398" s="2"/>
       <c r="I4398" s="1"/>
     </row>
     <row r="4399" spans="8:9" x14ac:dyDescent="0.3">
@@ -33693,7 +33593,6 @@
       <c r="I4405" s="1"/>
     </row>
     <row r="4406" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4406" s="2"/>
       <c r="I4406" s="1"/>
     </row>
     <row r="4407" spans="8:9" x14ac:dyDescent="0.3">
@@ -33709,6 +33608,7 @@
       <c r="I4409" s="1"/>
     </row>
     <row r="4410" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4410" s="2"/>
       <c r="I4410" s="1"/>
     </row>
     <row r="4411" spans="8:9" x14ac:dyDescent="0.3">
@@ -33720,7 +33620,6 @@
       <c r="I4412" s="1"/>
     </row>
     <row r="4413" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4413" s="2"/>
       <c r="I4413" s="1"/>
     </row>
     <row r="4414" spans="8:9" x14ac:dyDescent="0.3">
@@ -33736,6 +33635,7 @@
       <c r="I4416" s="1"/>
     </row>
     <row r="4417" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4417" s="2"/>
       <c r="I4417" s="1"/>
     </row>
     <row r="4418" spans="8:9" x14ac:dyDescent="0.3">
@@ -34059,7 +33959,6 @@
       <c r="I4497" s="1"/>
     </row>
     <row r="4498" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4498" s="2"/>
       <c r="I4498" s="1"/>
     </row>
     <row r="4499" spans="8:9" x14ac:dyDescent="0.3">
@@ -34075,6 +33974,7 @@
       <c r="I4501" s="1"/>
     </row>
     <row r="4502" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4502" s="2"/>
       <c r="I4502" s="1"/>
     </row>
     <row r="4503" spans="8:9" x14ac:dyDescent="0.3">
@@ -34102,7 +34002,6 @@
       <c r="I4508" s="1"/>
     </row>
     <row r="4509" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4509" s="2"/>
       <c r="I4509" s="1"/>
     </row>
     <row r="4510" spans="8:9" x14ac:dyDescent="0.3">
@@ -34118,6 +34017,7 @@
       <c r="I4512" s="1"/>
     </row>
     <row r="4513" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4513" s="2"/>
       <c r="I4513" s="1"/>
     </row>
     <row r="4514" spans="8:9" x14ac:dyDescent="0.3">
@@ -34205,7 +34105,6 @@
       <c r="I4534" s="1"/>
     </row>
     <row r="4535" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4535" s="2"/>
       <c r="I4535" s="1"/>
     </row>
     <row r="4536" spans="8:9" x14ac:dyDescent="0.3">
@@ -34221,6 +34120,7 @@
       <c r="I4538" s="1"/>
     </row>
     <row r="4539" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4539" s="2"/>
       <c r="I4539" s="1"/>
     </row>
     <row r="4540" spans="8:9" x14ac:dyDescent="0.3">
@@ -34256,7 +34156,6 @@
       <c r="I4547" s="1"/>
     </row>
     <row r="4548" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4548" s="2"/>
       <c r="I4548" s="1"/>
     </row>
     <row r="4549" spans="8:9" x14ac:dyDescent="0.3">
@@ -34272,6 +34171,7 @@
       <c r="I4551" s="1"/>
     </row>
     <row r="4552" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4552" s="2"/>
       <c r="I4552" s="1"/>
     </row>
     <row r="4553" spans="8:9" x14ac:dyDescent="0.3">
@@ -34615,7 +34515,6 @@
       <c r="I4637" s="1"/>
     </row>
     <row r="4638" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4638" s="2"/>
       <c r="I4638" s="1"/>
     </row>
     <row r="4639" spans="8:9" x14ac:dyDescent="0.3">
@@ -34627,10 +34526,10 @@
       <c r="I4640" s="1"/>
     </row>
     <row r="4641" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4641" s="2"/>
       <c r="I4641" s="1"/>
     </row>
     <row r="4642" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4642" s="2"/>
       <c r="I4642" s="1"/>
     </row>
     <row r="4643" spans="8:9" x14ac:dyDescent="0.3">
@@ -34642,6 +34541,7 @@
       <c r="I4644" s="1"/>
     </row>
     <row r="4645" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4645" s="2"/>
       <c r="I4645" s="1"/>
     </row>
     <row r="4646" spans="8:9" x14ac:dyDescent="0.3">
@@ -34749,7 +34649,6 @@
       <c r="I4671" s="1"/>
     </row>
     <row r="4672" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4672" s="2"/>
       <c r="I4672" s="1"/>
     </row>
     <row r="4673" spans="8:9" x14ac:dyDescent="0.3">
@@ -34765,6 +34664,7 @@
       <c r="I4675" s="1"/>
     </row>
     <row r="4676" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4676" s="2"/>
       <c r="I4676" s="1"/>
     </row>
     <row r="4677" spans="8:9" x14ac:dyDescent="0.3">
@@ -34840,7 +34740,6 @@
       <c r="I4694" s="1"/>
     </row>
     <row r="4695" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4695" s="2"/>
       <c r="I4695" s="1"/>
     </row>
     <row r="4696" spans="8:9" x14ac:dyDescent="0.3">
@@ -34856,6 +34755,7 @@
       <c r="I4698" s="1"/>
     </row>
     <row r="4699" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4699" s="2"/>
       <c r="I4699" s="1"/>
     </row>
     <row r="4700" spans="8:9" x14ac:dyDescent="0.3">
@@ -35115,7 +35015,6 @@
       <c r="I4763" s="1"/>
     </row>
     <row r="4764" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4764" s="2"/>
       <c r="I4764" s="1"/>
     </row>
     <row r="4765" spans="8:9" x14ac:dyDescent="0.3">
@@ -35131,6 +35030,7 @@
       <c r="I4767" s="1"/>
     </row>
     <row r="4768" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4768" s="2"/>
       <c r="I4768" s="1"/>
     </row>
     <row r="4769" spans="8:9" x14ac:dyDescent="0.3">
@@ -35270,7 +35170,6 @@
       <c r="I4802" s="1"/>
     </row>
     <row r="4803" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4803" s="2"/>
       <c r="I4803" s="1"/>
     </row>
     <row r="4804" spans="8:9" x14ac:dyDescent="0.3">
@@ -35286,6 +35185,7 @@
       <c r="I4806" s="1"/>
     </row>
     <row r="4807" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4807" s="2"/>
       <c r="I4807" s="1"/>
     </row>
     <row r="4808" spans="8:9" x14ac:dyDescent="0.3">
@@ -35321,7 +35221,6 @@
       <c r="I4815" s="1"/>
     </row>
     <row r="4816" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4816" s="2"/>
       <c r="I4816" s="1"/>
     </row>
     <row r="4817" spans="8:9" x14ac:dyDescent="0.3">
@@ -35337,6 +35236,7 @@
       <c r="I4819" s="1"/>
     </row>
     <row r="4820" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4820" s="2"/>
       <c r="I4820" s="1"/>
     </row>
     <row r="4821" spans="8:9" x14ac:dyDescent="0.3">
@@ -35476,7 +35376,6 @@
       <c r="I4854" s="1"/>
     </row>
     <row r="4855" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4855" s="2"/>
       <c r="I4855" s="1"/>
     </row>
     <row r="4856" spans="8:9" x14ac:dyDescent="0.3">
@@ -35492,6 +35391,7 @@
       <c r="I4858" s="1"/>
     </row>
     <row r="4859" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4859" s="2"/>
       <c r="I4859" s="1"/>
     </row>
     <row r="4860" spans="8:9" x14ac:dyDescent="0.3">
@@ -35539,7 +35439,6 @@
       <c r="I4870" s="1"/>
     </row>
     <row r="4871" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4871" s="2"/>
       <c r="I4871" s="1"/>
     </row>
     <row r="4872" spans="8:9" x14ac:dyDescent="0.3">
@@ -35555,6 +35454,7 @@
       <c r="I4874" s="1"/>
     </row>
     <row r="4875" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4875" s="2"/>
       <c r="I4875" s="1"/>
     </row>
     <row r="4876" spans="8:9" x14ac:dyDescent="0.3">
@@ -35622,7 +35522,6 @@
       <c r="I4891" s="1"/>
     </row>
     <row r="4892" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4892" s="2"/>
       <c r="I4892" s="1"/>
     </row>
     <row r="4893" spans="8:9" x14ac:dyDescent="0.3">
@@ -35638,6 +35537,7 @@
       <c r="I4895" s="1"/>
     </row>
     <row r="4896" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4896" s="2"/>
       <c r="I4896" s="1"/>
     </row>
     <row r="4897" spans="8:9" x14ac:dyDescent="0.3">
@@ -35669,7 +35569,6 @@
       <c r="I4903" s="1"/>
     </row>
     <row r="4904" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4904" s="2"/>
       <c r="I4904" s="1"/>
     </row>
     <row r="4905" spans="8:9" x14ac:dyDescent="0.3">
@@ -35681,10 +35580,10 @@
       <c r="I4906" s="1"/>
     </row>
     <row r="4907" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4907" s="2"/>
       <c r="I4907" s="1"/>
     </row>
     <row r="4908" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4908" s="2"/>
       <c r="I4908" s="1"/>
     </row>
     <row r="4909" spans="8:9" x14ac:dyDescent="0.3">
@@ -35696,6 +35595,7 @@
       <c r="I4910" s="1"/>
     </row>
     <row r="4911" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4911" s="2"/>
       <c r="I4911" s="1"/>
     </row>
     <row r="4912" spans="8:9" x14ac:dyDescent="0.3">
@@ -35763,7 +35663,6 @@
       <c r="I4927" s="1"/>
     </row>
     <row r="4928" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4928" s="2"/>
       <c r="I4928" s="1"/>
     </row>
     <row r="4929" spans="8:9" x14ac:dyDescent="0.3">
@@ -35779,6 +35678,7 @@
       <c r="I4931" s="1"/>
     </row>
     <row r="4932" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4932" s="2"/>
       <c r="I4932" s="1"/>
     </row>
     <row r="4933" spans="8:9" x14ac:dyDescent="0.3">
@@ -36042,7 +35942,6 @@
       <c r="I4997" s="1"/>
     </row>
     <row r="4998" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4998" s="2"/>
       <c r="I4998" s="1"/>
     </row>
     <row r="4999" spans="8:9" x14ac:dyDescent="0.3">
@@ -36058,6 +35957,7 @@
       <c r="I5001" s="1"/>
     </row>
     <row r="5002" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5002" s="2"/>
       <c r="I5002" s="1"/>
     </row>
     <row r="5003" spans="8:9" x14ac:dyDescent="0.3">
@@ -36121,7 +36021,6 @@
       <c r="I5017" s="1"/>
     </row>
     <row r="5018" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5018" s="2"/>
       <c r="I5018" s="1"/>
     </row>
     <row r="5019" spans="8:9" x14ac:dyDescent="0.3">
@@ -36137,6 +36036,7 @@
       <c r="I5021" s="1"/>
     </row>
     <row r="5022" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5022" s="2"/>
       <c r="I5022" s="1"/>
     </row>
     <row r="5023" spans="8:9" x14ac:dyDescent="0.3">
@@ -36168,7 +36068,6 @@
       <c r="I5029" s="1"/>
     </row>
     <row r="5030" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5030" s="2"/>
       <c r="I5030" s="1"/>
     </row>
     <row r="5031" spans="8:9" x14ac:dyDescent="0.3">
@@ -36184,6 +36083,7 @@
       <c r="I5033" s="1"/>
     </row>
     <row r="5034" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5034" s="2"/>
       <c r="I5034" s="1"/>
     </row>
     <row r="5035" spans="8:9" x14ac:dyDescent="0.3">
@@ -36271,7 +36171,6 @@
       <c r="I5055" s="1"/>
     </row>
     <row r="5056" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5056" s="2"/>
       <c r="I5056" s="1"/>
     </row>
     <row r="5057" spans="8:9" x14ac:dyDescent="0.3">
@@ -36287,6 +36186,7 @@
       <c r="I5059" s="1"/>
     </row>
     <row r="5060" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5060" s="2"/>
       <c r="I5060" s="1"/>
     </row>
     <row r="5061" spans="8:9" x14ac:dyDescent="0.3">
@@ -36318,7 +36218,6 @@
       <c r="I5067" s="1"/>
     </row>
     <row r="5068" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5068" s="2"/>
       <c r="I5068" s="1"/>
     </row>
     <row r="5069" spans="8:9" x14ac:dyDescent="0.3">
@@ -36334,6 +36233,7 @@
       <c r="I5071" s="1"/>
     </row>
     <row r="5072" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5072" s="2"/>
       <c r="I5072" s="1"/>
     </row>
     <row r="5073" spans="8:9" x14ac:dyDescent="0.3">
@@ -36349,7 +36249,6 @@
       <c r="I5075" s="1"/>
     </row>
     <row r="5076" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5076" s="2"/>
       <c r="I5076" s="1"/>
     </row>
     <row r="5077" spans="8:9" x14ac:dyDescent="0.3">
@@ -36365,6 +36264,7 @@
       <c r="I5079" s="1"/>
     </row>
     <row r="5080" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5080" s="2"/>
       <c r="I5080" s="1"/>
     </row>
     <row r="5081" spans="8:9" x14ac:dyDescent="0.3">
@@ -36480,7 +36380,6 @@
       <c r="I5108" s="1"/>
     </row>
     <row r="5109" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5109" s="2"/>
       <c r="I5109" s="1"/>
     </row>
     <row r="5110" spans="8:9" x14ac:dyDescent="0.3">
@@ -36496,6 +36395,7 @@
       <c r="I5112" s="1"/>
     </row>
     <row r="5113" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5113" s="2"/>
       <c r="I5113" s="1"/>
     </row>
     <row r="5114" spans="8:9" x14ac:dyDescent="0.3">
@@ -36699,7 +36599,6 @@
       <c r="I5163" s="1"/>
     </row>
     <row r="5164" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5164" s="2"/>
       <c r="I5164" s="1"/>
     </row>
     <row r="5165" spans="8:9" x14ac:dyDescent="0.3">
@@ -36715,6 +36614,7 @@
       <c r="I5167" s="1"/>
     </row>
     <row r="5168" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5168" s="2"/>
       <c r="I5168" s="1"/>
     </row>
     <row r="5169" spans="8:9" x14ac:dyDescent="0.3">
@@ -37030,7 +36930,6 @@
       <c r="I5246" s="1"/>
     </row>
     <row r="5247" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5247" s="2"/>
       <c r="I5247" s="1"/>
     </row>
     <row r="5248" spans="8:9" x14ac:dyDescent="0.3">
@@ -37046,6 +36945,7 @@
       <c r="I5250" s="1"/>
     </row>
     <row r="5251" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5251" s="2"/>
       <c r="I5251" s="1"/>
     </row>
     <row r="5252" spans="8:9" x14ac:dyDescent="0.3">
@@ -37061,7 +36961,6 @@
       <c r="I5254" s="1"/>
     </row>
     <row r="5255" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5255" s="2"/>
       <c r="I5255" s="1"/>
     </row>
     <row r="5256" spans="8:9" x14ac:dyDescent="0.3">
@@ -37069,7 +36968,6 @@
       <c r="I5256" s="1"/>
     </row>
     <row r="5257" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5257" s="2"/>
       <c r="I5257" s="1"/>
     </row>
     <row r="5258" spans="8:9" x14ac:dyDescent="0.3">
@@ -37077,6 +36975,7 @@
       <c r="I5258" s="1"/>
     </row>
     <row r="5259" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5259" s="2"/>
       <c r="I5259" s="1"/>
     </row>
     <row r="5260" spans="8:9" x14ac:dyDescent="0.3">
@@ -37084,6 +36983,7 @@
       <c r="I5260" s="1"/>
     </row>
     <row r="5261" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5261" s="2"/>
       <c r="I5261" s="1"/>
     </row>
     <row r="5262" spans="8:9" x14ac:dyDescent="0.3">
@@ -37255,7 +37155,6 @@
       <c r="I5303" s="1"/>
     </row>
     <row r="5304" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5304" s="2"/>
       <c r="I5304" s="1"/>
     </row>
     <row r="5305" spans="8:9" x14ac:dyDescent="0.3">
@@ -37271,6 +37170,7 @@
       <c r="I5307" s="1"/>
     </row>
     <row r="5308" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5308" s="2"/>
       <c r="I5308" s="1"/>
     </row>
     <row r="5309" spans="8:9" x14ac:dyDescent="0.3">
@@ -37294,7 +37194,6 @@
       <c r="I5313" s="1"/>
     </row>
     <row r="5314" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5314" s="2"/>
       <c r="I5314" s="1"/>
     </row>
     <row r="5315" spans="8:9" x14ac:dyDescent="0.3">
@@ -37310,6 +37209,7 @@
       <c r="I5317" s="1"/>
     </row>
     <row r="5318" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5318" s="2"/>
       <c r="I5318" s="1"/>
     </row>
     <row r="5319" spans="8:9" x14ac:dyDescent="0.3">
@@ -37689,7 +37589,6 @@
       <c r="I5412" s="1"/>
     </row>
     <row r="5413" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5413" s="2"/>
       <c r="I5413" s="1"/>
     </row>
     <row r="5414" spans="8:9" x14ac:dyDescent="0.3">
@@ -37705,18 +37604,16 @@
       <c r="I5416" s="1"/>
     </row>
     <row r="5417" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5417" s="2"/>
       <c r="I5417" s="1"/>
     </row>
     <row r="5418" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5418" s="2"/>
       <c r="I5418" s="1"/>
     </row>
     <row r="5419" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5419" s="2"/>
       <c r="I5419" s="1"/>
     </row>
     <row r="5420" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5420" s="2"/>
       <c r="I5420" s="1"/>
     </row>
     <row r="5421" spans="8:9" x14ac:dyDescent="0.3">
@@ -37724,9 +37621,11 @@
       <c r="I5421" s="1"/>
     </row>
     <row r="5422" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5422" s="2"/>
       <c r="I5422" s="1"/>
     </row>
     <row r="5423" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5423" s="2"/>
       <c r="I5423" s="1"/>
     </row>
     <row r="5424" spans="8:9" x14ac:dyDescent="0.3">
@@ -37745,6 +37644,7 @@
       <c r="I5427" s="1"/>
     </row>
     <row r="5428" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5428" s="2"/>
       <c r="I5428" s="1"/>
     </row>
     <row r="5429" spans="8:9" x14ac:dyDescent="0.3">
@@ -38076,7 +37976,6 @@
       <c r="I5510" s="1"/>
     </row>
     <row r="5511" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5511" s="2"/>
       <c r="I5511" s="1"/>
     </row>
     <row r="5512" spans="8:9" x14ac:dyDescent="0.3">
@@ -38088,10 +37987,10 @@
       <c r="I5513" s="1"/>
     </row>
     <row r="5514" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5514" s="2"/>
       <c r="I5514" s="1"/>
     </row>
     <row r="5515" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5515" s="2"/>
       <c r="I5515" s="1"/>
     </row>
     <row r="5516" spans="8:9" x14ac:dyDescent="0.3">
@@ -38103,6 +38002,7 @@
       <c r="I5517" s="1"/>
     </row>
     <row r="5518" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5518" s="2"/>
       <c r="I5518" s="1"/>
     </row>
     <row r="5519" spans="8:9" x14ac:dyDescent="0.3">
@@ -38150,7 +38050,6 @@
       <c r="I5529" s="1"/>
     </row>
     <row r="5530" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5530" s="2"/>
       <c r="I5530" s="1"/>
     </row>
     <row r="5531" spans="8:9" x14ac:dyDescent="0.3">
@@ -38166,6 +38065,7 @@
       <c r="I5533" s="1"/>
     </row>
     <row r="5534" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5534" s="2"/>
       <c r="I5534" s="1"/>
     </row>
     <row r="5535" spans="8:9" x14ac:dyDescent="0.3">
@@ -38197,7 +38097,6 @@
       <c r="I5541" s="1"/>
     </row>
     <row r="5542" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5542" s="2"/>
       <c r="I5542" s="1"/>
     </row>
     <row r="5543" spans="8:9" x14ac:dyDescent="0.3">
@@ -38213,10 +38112,10 @@
       <c r="I5545" s="1"/>
     </row>
     <row r="5546" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5546" s="2"/>
       <c r="I5546" s="1"/>
     </row>
     <row r="5547" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5547" s="2"/>
       <c r="I5547" s="1"/>
     </row>
     <row r="5548" spans="8:9" x14ac:dyDescent="0.3">
@@ -38232,6 +38131,7 @@
       <c r="I5550" s="1"/>
     </row>
     <row r="5551" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5551" s="2"/>
       <c r="I5551" s="1"/>
     </row>
     <row r="5552" spans="8:9" x14ac:dyDescent="0.3">
@@ -38307,7 +38207,6 @@
       <c r="I5569" s="1"/>
     </row>
     <row r="5570" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5570" s="2"/>
       <c r="I5570" s="1"/>
     </row>
     <row r="5571" spans="8:9" x14ac:dyDescent="0.3">
@@ -38323,6 +38222,7 @@
       <c r="I5573" s="1"/>
     </row>
     <row r="5574" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5574" s="2"/>
       <c r="I5574" s="1"/>
     </row>
     <row r="5575" spans="8:9" x14ac:dyDescent="0.3">
@@ -38570,7 +38470,6 @@
       <c r="I5635" s="1"/>
     </row>
     <row r="5636" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5636" s="2"/>
       <c r="I5636" s="1"/>
     </row>
     <row r="5637" spans="8:9" x14ac:dyDescent="0.3">
@@ -38586,6 +38485,7 @@
       <c r="I5639" s="1"/>
     </row>
     <row r="5640" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5640" s="2"/>
       <c r="I5640" s="1"/>
     </row>
     <row r="5641" spans="8:9" x14ac:dyDescent="0.3">
@@ -38725,7 +38625,6 @@
       <c r="I5674" s="1"/>
     </row>
     <row r="5675" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5675" s="2"/>
       <c r="I5675" s="1"/>
     </row>
     <row r="5676" spans="8:9" x14ac:dyDescent="0.3">
@@ -38741,6 +38640,7 @@
       <c r="I5678" s="1"/>
     </row>
     <row r="5679" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5679" s="2"/>
       <c r="I5679" s="1"/>
     </row>
     <row r="5680" spans="8:9" x14ac:dyDescent="0.3">
@@ -38764,11 +38664,9 @@
       <c r="I5684" s="1"/>
     </row>
     <row r="5685" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5685" s="2"/>
       <c r="I5685" s="1"/>
     </row>
     <row r="5686" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5686" s="2"/>
       <c r="I5686" s="1"/>
     </row>
     <row r="5687" spans="8:9" x14ac:dyDescent="0.3">
@@ -38780,9 +38678,11 @@
       <c r="I5688" s="1"/>
     </row>
     <row r="5689" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5689" s="2"/>
       <c r="I5689" s="1"/>
     </row>
     <row r="5690" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5690" s="2"/>
       <c r="I5690" s="1"/>
     </row>
     <row r="5691" spans="8:9" x14ac:dyDescent="0.3">
@@ -38878,7 +38778,6 @@
       <c r="I5713" s="1"/>
     </row>
     <row r="5714" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5714" s="2"/>
       <c r="I5714" s="1"/>
     </row>
     <row r="5715" spans="8:9" x14ac:dyDescent="0.3">
@@ -38894,6 +38793,7 @@
       <c r="I5717" s="1"/>
     </row>
     <row r="5718" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5718" s="2"/>
       <c r="I5718" s="1"/>
     </row>
     <row r="5719" spans="8:9" x14ac:dyDescent="0.3">
@@ -38953,7 +38853,6 @@
       <c r="I5732" s="1"/>
     </row>
     <row r="5733" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5733" s="2"/>
       <c r="I5733" s="1"/>
     </row>
     <row r="5734" spans="8:9" x14ac:dyDescent="0.3">
@@ -38969,6 +38868,7 @@
       <c r="I5736" s="1"/>
     </row>
     <row r="5737" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5737" s="2"/>
       <c r="I5737" s="1"/>
     </row>
     <row r="5738" spans="8:9" x14ac:dyDescent="0.3">
@@ -39004,7 +38904,6 @@
       <c r="I5745" s="1"/>
     </row>
     <row r="5746" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5746" s="2"/>
       <c r="I5746" s="1"/>
     </row>
     <row r="5747" spans="8:9" x14ac:dyDescent="0.3">
@@ -39020,6 +38919,7 @@
       <c r="I5749" s="1"/>
     </row>
     <row r="5750" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5750" s="2"/>
       <c r="I5750" s="1"/>
     </row>
     <row r="5751" spans="8:9" x14ac:dyDescent="0.3">
@@ -39047,11 +38947,9 @@
       <c r="I5756" s="1"/>
     </row>
     <row r="5757" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5757" s="2"/>
       <c r="I5757" s="1"/>
     </row>
     <row r="5758" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5758" s="2"/>
       <c r="I5758" s="1"/>
     </row>
     <row r="5759" spans="8:9" x14ac:dyDescent="0.3">
@@ -39063,13 +38961,14 @@
       <c r="I5760" s="1"/>
     </row>
     <row r="5761" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5761" s="2"/>
       <c r="I5761" s="1"/>
     </row>
     <row r="5762" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5762" s="2"/>
       <c r="I5762" s="1"/>
     </row>
     <row r="5763" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5763" s="2"/>
       <c r="I5763" s="1"/>
     </row>
     <row r="5764" spans="8:9" x14ac:dyDescent="0.3">
@@ -39085,6 +38984,7 @@
       <c r="I5766" s="1"/>
     </row>
     <row r="5767" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5767" s="2"/>
       <c r="I5767" s="1"/>
     </row>
     <row r="5768" spans="8:9" x14ac:dyDescent="0.3">
@@ -39144,11 +39044,9 @@
       <c r="I5781" s="1"/>
     </row>
     <row r="5782" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5782" s="2"/>
       <c r="I5782" s="1"/>
     </row>
     <row r="5783" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5783" s="2"/>
       <c r="I5783" s="1"/>
     </row>
     <row r="5784" spans="8:9" x14ac:dyDescent="0.3">
@@ -39160,9 +39058,11 @@
       <c r="I5785" s="1"/>
     </row>
     <row r="5786" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5786" s="2"/>
       <c r="I5786" s="1"/>
     </row>
     <row r="5787" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5787" s="2"/>
       <c r="I5787" s="1"/>
     </row>
     <row r="5788" spans="8:9" x14ac:dyDescent="0.3">
@@ -39210,7 +39110,6 @@
       <c r="I5798" s="1"/>
     </row>
     <row r="5799" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5799" s="2"/>
       <c r="I5799" s="1"/>
     </row>
     <row r="5800" spans="8:9" x14ac:dyDescent="0.3">
@@ -39226,10 +39125,10 @@
       <c r="I5802" s="1"/>
     </row>
     <row r="5803" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5803" s="2"/>
       <c r="I5803" s="1"/>
     </row>
     <row r="5804" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5804" s="2"/>
       <c r="I5804" s="1"/>
     </row>
     <row r="5805" spans="8:9" x14ac:dyDescent="0.3">
@@ -39245,6 +39144,7 @@
       <c r="I5807" s="1"/>
     </row>
     <row r="5808" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5808" s="2"/>
       <c r="I5808" s="1"/>
     </row>
     <row r="5809" spans="8:9" x14ac:dyDescent="0.3">
@@ -39260,7 +39160,6 @@
       <c r="I5811" s="1"/>
     </row>
     <row r="5812" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5812" s="2"/>
       <c r="I5812" s="1"/>
     </row>
     <row r="5813" spans="8:9" x14ac:dyDescent="0.3">
@@ -39276,6 +39175,7 @@
       <c r="I5815" s="1"/>
     </row>
     <row r="5816" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5816" s="2"/>
       <c r="I5816" s="1"/>
     </row>
     <row r="5817" spans="8:9" x14ac:dyDescent="0.3">
@@ -39363,7 +39263,6 @@
       <c r="I5837" s="1"/>
     </row>
     <row r="5838" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5838" s="2"/>
       <c r="I5838" s="1"/>
     </row>
     <row r="5839" spans="8:9" x14ac:dyDescent="0.3">
@@ -39379,6 +39278,7 @@
       <c r="I5841" s="1"/>
     </row>
     <row r="5842" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5842" s="2"/>
       <c r="I5842" s="1"/>
     </row>
     <row r="5843" spans="8:9" x14ac:dyDescent="0.3">
@@ -39402,7 +39302,6 @@
       <c r="I5847" s="1"/>
     </row>
     <row r="5848" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5848" s="2"/>
       <c r="I5848" s="1"/>
     </row>
     <row r="5849" spans="8:9" x14ac:dyDescent="0.3">
@@ -39448,6 +39347,7 @@
       <c r="I5859" s="1"/>
     </row>
     <row r="5860" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5860" s="2"/>
       <c r="I5860" s="1"/>
     </row>
     <row r="5861" spans="8:9" x14ac:dyDescent="0.3">
@@ -39455,7 +39355,6 @@
       <c r="I5861" s="1"/>
     </row>
     <row r="5862" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5862" s="2"/>
       <c r="I5862" s="1"/>
     </row>
     <row r="5863" spans="8:9" x14ac:dyDescent="0.3">
@@ -39471,6 +39370,7 @@
       <c r="I5865" s="1"/>
     </row>
     <row r="5866" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5866" s="2"/>
       <c r="I5866" s="1"/>
     </row>
     <row r="5867" spans="8:9" x14ac:dyDescent="0.3">
@@ -39486,7 +39386,6 @@
       <c r="I5869" s="1"/>
     </row>
     <row r="5870" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5870" s="2"/>
       <c r="I5870" s="1"/>
     </row>
     <row r="5871" spans="8:9" x14ac:dyDescent="0.3">
@@ -39502,6 +39401,7 @@
       <c r="I5873" s="1"/>
     </row>
     <row r="5874" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5874" s="2"/>
       <c r="I5874" s="1"/>
     </row>
     <row r="5875" spans="8:9" x14ac:dyDescent="0.3">
@@ -39509,7 +39409,6 @@
       <c r="I5875" s="1"/>
     </row>
     <row r="5876" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5876" s="2"/>
       <c r="I5876" s="1"/>
     </row>
     <row r="5877" spans="8:9" x14ac:dyDescent="0.3">
@@ -39525,6 +39424,7 @@
       <c r="I5879" s="1"/>
     </row>
     <row r="5880" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5880" s="2"/>
       <c r="I5880" s="1"/>
     </row>
     <row r="5881" spans="8:9" x14ac:dyDescent="0.3">
@@ -39580,7 +39480,6 @@
       <c r="I5893" s="1"/>
     </row>
     <row r="5894" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5894" s="2"/>
       <c r="I5894" s="1"/>
     </row>
     <row r="5895" spans="8:9" x14ac:dyDescent="0.3">
@@ -39596,6 +39495,7 @@
       <c r="I5897" s="1"/>
     </row>
     <row r="5898" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5898" s="2"/>
       <c r="I5898" s="1"/>
     </row>
     <row r="5899" spans="8:9" x14ac:dyDescent="0.3">
@@ -39635,7 +39535,6 @@
       <c r="I5907" s="1"/>
     </row>
     <row r="5908" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5908" s="2"/>
       <c r="I5908" s="1"/>
     </row>
     <row r="5909" spans="8:9" x14ac:dyDescent="0.3">
@@ -39651,6 +39550,7 @@
       <c r="I5911" s="1"/>
     </row>
     <row r="5912" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5912" s="2"/>
       <c r="I5912" s="1"/>
     </row>
     <row r="5913" spans="8:9" x14ac:dyDescent="0.3">
@@ -39678,11 +39578,9 @@
       <c r="I5918" s="1"/>
     </row>
     <row r="5919" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5919" s="2"/>
       <c r="I5919" s="1"/>
     </row>
     <row r="5920" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5920" s="2"/>
       <c r="I5920" s="1"/>
     </row>
     <row r="5921" spans="8:9" x14ac:dyDescent="0.3">
@@ -39703,21 +39601,10 @@
       <c r="H5925" s="2"/>
       <c r="I5925" s="1"/>
     </row>
-    <row r="5926" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5926" s="2"/>
-      <c r="I5926" s="1"/>
-    </row>
-    <row r="5927" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I5927" s="1"/>
-    </row>
-    <row r="5928" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I5928" s="1"/>
-    </row>
-    <row r="5929" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5929" s="2"/>
-      <c r="I5929" s="1"/>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B610:K635">
+    <sortCondition ref="B610:B635"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAE63E0-95C9-437B-A782-B4B026AFE3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B43BE6-72C7-4D89-89C0-9FF189CBAE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3180" uniqueCount="92">
   <si>
     <t>Company Name</t>
   </si>
@@ -16498,7 +16498,7 @@
         <v>24</v>
       </c>
       <c r="G569" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H569" s="2">
         <v>3.1250000000000001E-4</v>
@@ -16514,10 +16514,32 @@
       </c>
     </row>
     <row r="570" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H570" s="2"/>
-      <c r="I570" s="1"/>
+      <c r="B570" t="s">
+        <v>35</v>
+      </c>
+      <c r="C570">
+        <v>73</v>
+      </c>
+      <c r="D570" t="s">
+        <v>44</v>
+      </c>
+      <c r="F570" t="s">
+        <v>24</v>
+      </c>
+      <c r="G570" t="s">
+        <v>13</v>
+      </c>
+      <c r="H570" s="2">
+        <v>0</v>
+      </c>
+      <c r="I570" s="1">
+        <v>46083.797685185185</v>
+      </c>
+      <c r="J570">
+        <v>3</v>
+      </c>
       <c r="K570" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="571" spans="2:11" x14ac:dyDescent="0.3">
@@ -16525,25 +16547,25 @@
         <v>35</v>
       </c>
       <c r="C571">
-        <v>73</v>
+        <v>5037</v>
       </c>
       <c r="D571" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="F571" t="s">
         <v>24</v>
       </c>
       <c r="G571" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H571" s="2">
-        <v>0</v>
+        <v>5.3125000000000004E-3</v>
       </c>
       <c r="I571" s="1">
         <v>46083.797685185185</v>
       </c>
       <c r="J571">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K571" t="s">
         <v>11</v>
@@ -16554,10 +16576,10 @@
         <v>35</v>
       </c>
       <c r="C572">
-        <v>5037</v>
+        <v>75</v>
       </c>
       <c r="D572" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="F572" t="s">
         <v>24</v>
@@ -16566,13 +16588,13 @@
         <v>10</v>
       </c>
       <c r="H572" s="2">
-        <v>5.3125000000000004E-3</v>
+        <v>4.7337962962962967E-3</v>
       </c>
       <c r="I572" s="1">
-        <v>46083.797685185185</v>
+        <v>46083.798379629632</v>
       </c>
       <c r="J572">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K572" t="s">
         <v>11</v>
@@ -16583,10 +16605,10 @@
         <v>35</v>
       </c>
       <c r="C573">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D573" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F573" t="s">
         <v>24</v>
@@ -16595,10 +16617,10 @@
         <v>10</v>
       </c>
       <c r="H573" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>6.8055555555555551E-3</v>
       </c>
       <c r="I573" s="1">
-        <v>46083.798379629632</v>
+        <v>46083.799074074072</v>
       </c>
       <c r="J573">
         <v>2</v>
@@ -16612,10 +16634,10 @@
         <v>35</v>
       </c>
       <c r="C574">
-        <v>76</v>
+        <v>3726</v>
       </c>
       <c r="D574" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F574" t="s">
         <v>24</v>
@@ -16624,13 +16646,13 @@
         <v>10</v>
       </c>
       <c r="H574" s="2">
-        <v>6.8055555555555551E-3</v>
+        <v>4.340277777777778E-3</v>
       </c>
       <c r="I574" s="1">
         <v>46083.799074074072</v>
       </c>
       <c r="J574">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K574" t="s">
         <v>11</v>
@@ -16641,10 +16663,10 @@
         <v>35</v>
       </c>
       <c r="C575">
-        <v>3726</v>
+        <v>772</v>
       </c>
       <c r="D575" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="F575" t="s">
         <v>24</v>
@@ -16653,10 +16675,10 @@
         <v>10</v>
       </c>
       <c r="H575" s="2">
-        <v>4.340277777777778E-3</v>
+        <v>5.2199074074074075E-3</v>
       </c>
       <c r="I575" s="1">
-        <v>46083.799074074072</v>
+        <v>46083.799768518518</v>
       </c>
       <c r="J575">
         <v>0</v>
@@ -16670,10 +16692,10 @@
         <v>35</v>
       </c>
       <c r="C576">
-        <v>772</v>
+        <v>623</v>
       </c>
       <c r="D576" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F576" t="s">
         <v>24</v>
@@ -16682,7 +16704,7 @@
         <v>10</v>
       </c>
       <c r="H576" s="2">
-        <v>5.2199074074074075E-3</v>
+        <v>5.7175925925925927E-3</v>
       </c>
       <c r="I576" s="1">
         <v>46083.799768518518</v>
@@ -16699,25 +16721,25 @@
         <v>35</v>
       </c>
       <c r="C577">
-        <v>623</v>
+        <v>72</v>
       </c>
       <c r="D577" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F577" t="s">
         <v>24</v>
       </c>
       <c r="G577" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H577" s="2">
-        <v>5.7175925925925927E-3</v>
+        <v>0</v>
       </c>
       <c r="I577" s="1">
-        <v>46083.799768518518</v>
+        <v>46083.800462962965</v>
       </c>
       <c r="J577">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K577" t="s">
         <v>11</v>
@@ -16728,25 +16750,25 @@
         <v>35</v>
       </c>
       <c r="C578">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="D578" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F578" t="s">
         <v>24</v>
       </c>
       <c r="G578" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H578" s="2">
-        <v>0</v>
+        <v>4.0162037037037041E-3</v>
       </c>
       <c r="I578" s="1">
-        <v>46083.800462962965</v>
+        <v>46083.801157407404</v>
       </c>
       <c r="J578">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K578" t="s">
         <v>11</v>
@@ -16757,10 +16779,10 @@
         <v>35</v>
       </c>
       <c r="C579">
-        <v>245</v>
+        <v>84</v>
       </c>
       <c r="D579" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F579" t="s">
         <v>24</v>
@@ -16769,7 +16791,7 @@
         <v>10</v>
       </c>
       <c r="H579" s="2">
-        <v>4.0162037037037041E-3</v>
+        <v>5.2199074074074075E-3</v>
       </c>
       <c r="I579" s="1">
         <v>46083.801157407404</v>
@@ -16786,10 +16808,10 @@
         <v>35</v>
       </c>
       <c r="C580">
-        <v>84</v>
+        <v>3818</v>
       </c>
       <c r="D580" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F580" t="s">
         <v>24</v>
@@ -16798,10 +16820,10 @@
         <v>10</v>
       </c>
       <c r="H580" s="2">
-        <v>5.2199074074074075E-3</v>
+        <v>4.1087962962962962E-3</v>
       </c>
       <c r="I580" s="1">
-        <v>46083.801157407404</v>
+        <v>46083.801851851851</v>
       </c>
       <c r="J580">
         <v>0</v>
@@ -16815,25 +16837,25 @@
         <v>35</v>
       </c>
       <c r="C581">
-        <v>3818</v>
+        <v>80</v>
       </c>
       <c r="D581" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F581" t="s">
         <v>24</v>
       </c>
       <c r="G581" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H581" s="2">
-        <v>4.1087962962962962E-3</v>
+        <v>0</v>
       </c>
       <c r="I581" s="1">
-        <v>46083.801851851851</v>
+        <v>46083.802546296298</v>
       </c>
       <c r="J581">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K581" t="s">
         <v>11</v>
@@ -16844,25 +16866,25 @@
         <v>35</v>
       </c>
       <c r="C582">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D582" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F582" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="G582" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H582" s="2">
-        <v>0</v>
+        <v>7.5347222222222222E-3</v>
       </c>
       <c r="I582" s="1">
-        <v>46083.802546296298</v>
+        <v>46118.813078703701</v>
       </c>
       <c r="J582">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K582" t="s">
         <v>11</v>
@@ -16873,10 +16895,10 @@
         <v>35</v>
       </c>
       <c r="C583">
-        <v>77</v>
+        <v>745</v>
       </c>
       <c r="D583" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F583" t="s">
         <v>86</v>
@@ -16885,13 +16907,13 @@
         <v>10</v>
       </c>
       <c r="H583" s="2">
-        <v>7.5347222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="I583" s="1">
         <v>46118.813078703701</v>
       </c>
       <c r="J583">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K583" t="s">
         <v>11</v>
@@ -16902,25 +16924,25 @@
         <v>35</v>
       </c>
       <c r="C584">
-        <v>745</v>
+        <v>5058</v>
       </c>
       <c r="D584" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="F584" t="s">
         <v>86</v>
       </c>
       <c r="G584" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H584" s="2">
-        <v>6.9444444444444441E-3</v>
+        <v>0</v>
       </c>
       <c r="I584" s="1">
-        <v>46118.813078703701</v>
+        <v>46118.813773148147</v>
       </c>
       <c r="J584">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K584" t="s">
         <v>11</v>
@@ -16931,10 +16953,10 @@
         <v>35</v>
       </c>
       <c r="C585">
-        <v>5058</v>
+        <v>622</v>
       </c>
       <c r="D585" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="F585" t="s">
         <v>86</v>
@@ -16946,7 +16968,7 @@
         <v>0</v>
       </c>
       <c r="I585" s="1">
-        <v>46118.813773148147</v>
+        <v>46118.814467592594</v>
       </c>
       <c r="J585">
         <v>5</v>
@@ -16960,25 +16982,25 @@
         <v>35</v>
       </c>
       <c r="C586">
-        <v>622</v>
+        <v>5217</v>
       </c>
       <c r="D586" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F586" t="s">
         <v>86</v>
       </c>
       <c r="G586" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H586" s="2">
-        <v>0</v>
+        <v>6.2268518518518515E-3</v>
       </c>
       <c r="I586" s="1">
         <v>46118.814467592594</v>
       </c>
       <c r="J586">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K586" t="s">
         <v>11</v>
@@ -16989,10 +17011,10 @@
         <v>35</v>
       </c>
       <c r="C587">
-        <v>5217</v>
+        <v>204</v>
       </c>
       <c r="D587" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="F587" t="s">
         <v>86</v>
@@ -17001,13 +17023,13 @@
         <v>10</v>
       </c>
       <c r="H587" s="2">
-        <v>6.2268518518518515E-3</v>
+        <v>7.4421296296296293E-3</v>
       </c>
       <c r="I587" s="1">
-        <v>46118.814467592594</v>
+        <v>46118.815162037034</v>
       </c>
       <c r="J587">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K587" t="s">
         <v>11</v>
@@ -17018,10 +17040,10 @@
         <v>35</v>
       </c>
       <c r="C588">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D588" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F588" t="s">
         <v>86</v>
@@ -17030,10 +17052,10 @@
         <v>10</v>
       </c>
       <c r="H588" s="2">
-        <v>7.4421296296296293E-3</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I588" s="1">
-        <v>46118.815162037034</v>
+        <v>46118.81585648148</v>
       </c>
       <c r="J588">
         <v>1</v>
@@ -17047,10 +17069,13 @@
         <v>35</v>
       </c>
       <c r="C589">
-        <v>205</v>
+        <v>3741</v>
       </c>
       <c r="D589" t="s">
-        <v>41</v>
+        <v>78</v>
+      </c>
+      <c r="E589" t="s">
+        <v>63</v>
       </c>
       <c r="F589" t="s">
         <v>86</v>
@@ -17059,10 +17084,10 @@
         <v>10</v>
       </c>
       <c r="H589" s="2">
-        <v>7.2106481481481483E-3</v>
+        <v>8.0787037037037043E-3</v>
       </c>
       <c r="I589" s="1">
-        <v>46118.81585648148</v>
+        <v>46118.834722222222</v>
       </c>
       <c r="J589">
         <v>1</v>
@@ -17076,13 +17101,10 @@
         <v>35</v>
       </c>
       <c r="C590">
-        <v>3741</v>
+        <v>78</v>
       </c>
       <c r="D590" t="s">
-        <v>78</v>
-      </c>
-      <c r="E590" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F590" t="s">
         <v>86</v>
@@ -17091,10 +17113,10 @@
         <v>10</v>
       </c>
       <c r="H590" s="2">
-        <v>8.0787037037037043E-3</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I590" s="1">
-        <v>46118.834722222222</v>
+        <v>46118.835416666669</v>
       </c>
       <c r="J590">
         <v>1</v>
@@ -17108,25 +17130,25 @@
         <v>35</v>
       </c>
       <c r="C591">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D591" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F591" t="s">
         <v>86</v>
       </c>
       <c r="G591" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H591" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>0</v>
       </c>
       <c r="I591" s="1">
-        <v>46118.835416666669</v>
+        <v>46118.836111111108</v>
       </c>
       <c r="J591">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K591" t="s">
         <v>11</v>
@@ -17137,16 +17159,16 @@
         <v>35</v>
       </c>
       <c r="C592">
-        <v>73</v>
+        <v>5037</v>
       </c>
       <c r="D592" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="F592" t="s">
         <v>86</v>
       </c>
       <c r="G592" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H592" s="2">
         <v>0</v>
@@ -17155,7 +17177,7 @@
         <v>46118.836111111108</v>
       </c>
       <c r="J592">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K592" t="s">
         <v>11</v>
@@ -17166,35 +17188,57 @@
         <v>35</v>
       </c>
       <c r="C593">
-        <v>5037</v>
+        <v>75</v>
       </c>
       <c r="D593" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="F593" t="s">
         <v>86</v>
       </c>
       <c r="G593" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H593" s="2">
         <v>0</v>
       </c>
       <c r="I593" s="1">
-        <v>46118.836111111108</v>
+        <v>46118.836805555555</v>
       </c>
       <c r="J593">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K593" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="594" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H594" s="2"/>
-      <c r="I594" s="1"/>
+      <c r="B594" t="s">
+        <v>35</v>
+      </c>
+      <c r="C594">
+        <v>5350</v>
+      </c>
+      <c r="D594" t="s">
+        <v>87</v>
+      </c>
+      <c r="F594" t="s">
+        <v>86</v>
+      </c>
+      <c r="G594" t="s">
+        <v>10</v>
+      </c>
+      <c r="H594" s="2">
+        <v>0</v>
+      </c>
+      <c r="I594" s="1">
+        <v>46118.837500000001</v>
+      </c>
+      <c r="J594">
+        <v>2</v>
+      </c>
       <c r="K594" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="595" spans="2:11" x14ac:dyDescent="0.3">
@@ -17202,25 +17246,25 @@
         <v>35</v>
       </c>
       <c r="C595">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D595" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F595" t="s">
         <v>86</v>
       </c>
       <c r="G595" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H595" s="2">
-        <v>0</v>
+        <v>5.5208333333333333E-3</v>
       </c>
       <c r="I595" s="1">
-        <v>46118.836805555555</v>
+        <v>46118.838194444441</v>
       </c>
       <c r="J595">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K595" t="s">
         <v>11</v>
@@ -17231,25 +17275,25 @@
         <v>35</v>
       </c>
       <c r="C596">
-        <v>5409</v>
+        <v>3726</v>
       </c>
       <c r="D596" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F596" t="s">
         <v>86</v>
       </c>
       <c r="G596" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H596" s="2">
-        <v>0</v>
+        <v>1.0798611111111111E-2</v>
       </c>
       <c r="I596" s="1">
-        <v>46118.837500000001</v>
+        <v>46118.838888888888</v>
       </c>
       <c r="J596">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K596" t="s">
         <v>11</v>
@@ -17260,22 +17304,22 @@
         <v>35</v>
       </c>
       <c r="C597">
-        <v>5350</v>
+        <v>614</v>
       </c>
       <c r="D597" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F597" t="s">
         <v>86</v>
       </c>
       <c r="G597" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H597" s="2">
-        <v>0</v>
+        <v>8.518518518518519E-3</v>
       </c>
       <c r="I597" s="1">
-        <v>46118.837500000001</v>
+        <v>46118.838888888888</v>
       </c>
       <c r="J597">
         <v>2</v>
@@ -17285,10 +17329,32 @@
       </c>
     </row>
     <row r="598" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H598" s="2"/>
-      <c r="I598" s="1"/>
+      <c r="B598" t="s">
+        <v>35</v>
+      </c>
+      <c r="C598">
+        <v>772</v>
+      </c>
+      <c r="D598" t="s">
+        <v>49</v>
+      </c>
+      <c r="F598" t="s">
+        <v>86</v>
+      </c>
+      <c r="G598" t="s">
+        <v>10</v>
+      </c>
+      <c r="H598" s="2">
+        <v>8.0439814814814818E-3</v>
+      </c>
+      <c r="I598" s="1">
+        <v>46118.839583333334</v>
+      </c>
+      <c r="J598">
+        <v>5</v>
+      </c>
       <c r="K598" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="599" spans="2:11" x14ac:dyDescent="0.3">
@@ -17296,35 +17362,57 @@
         <v>35</v>
       </c>
       <c r="C599">
-        <v>76</v>
+        <v>623</v>
       </c>
       <c r="D599" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F599" t="s">
         <v>86</v>
       </c>
       <c r="G599" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H599" s="2">
-        <v>5.5208333333333333E-3</v>
+        <v>8.8541666666666664E-3</v>
       </c>
       <c r="I599" s="1">
-        <v>46118.838194444441</v>
+        <v>46118.839583333334</v>
       </c>
       <c r="J599">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K599" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="600" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H600" s="2"/>
-      <c r="I600" s="1"/>
+      <c r="B600" t="s">
+        <v>35</v>
+      </c>
+      <c r="C600">
+        <v>72</v>
+      </c>
+      <c r="D600" t="s">
+        <v>51</v>
+      </c>
+      <c r="F600" t="s">
+        <v>86</v>
+      </c>
+      <c r="G600" t="s">
+        <v>13</v>
+      </c>
+      <c r="H600" s="2">
+        <v>0</v>
+      </c>
+      <c r="I600" s="1">
+        <v>46118.840277777781</v>
+      </c>
+      <c r="J600">
+        <v>5</v>
+      </c>
       <c r="K600" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="601" spans="2:11" x14ac:dyDescent="0.3">
@@ -17332,10 +17420,10 @@
         <v>35</v>
       </c>
       <c r="C601">
-        <v>3726</v>
+        <v>245</v>
       </c>
       <c r="D601" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="F601" t="s">
         <v>86</v>
@@ -17344,10 +17432,10 @@
         <v>10</v>
       </c>
       <c r="H601" s="2">
-        <v>1.0798611111111111E-2</v>
+        <v>9.3865740740740732E-3</v>
       </c>
       <c r="I601" s="1">
-        <v>46118.838888888888</v>
+        <v>46118.84097222222</v>
       </c>
       <c r="J601">
         <v>1</v>
@@ -17361,10 +17449,10 @@
         <v>35</v>
       </c>
       <c r="C602">
-        <v>614</v>
+        <v>84</v>
       </c>
       <c r="D602" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F602" t="s">
         <v>86</v>
@@ -17373,13 +17461,13 @@
         <v>10</v>
       </c>
       <c r="H602" s="2">
-        <v>8.518518518518519E-3</v>
+        <v>8.8078703703703704E-3</v>
       </c>
       <c r="I602" s="1">
-        <v>46118.838888888888</v>
+        <v>46118.84097222222</v>
       </c>
       <c r="J602">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K602" t="s">
         <v>11</v>
@@ -17390,10 +17478,10 @@
         <v>35</v>
       </c>
       <c r="C603">
-        <v>772</v>
+        <v>3818</v>
       </c>
       <c r="D603" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="F603" t="s">
         <v>86</v>
@@ -17402,13 +17490,13 @@
         <v>10</v>
       </c>
       <c r="H603" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>7.6736111111111111E-3</v>
       </c>
       <c r="I603" s="1">
-        <v>46118.839583333334</v>
+        <v>46118.841666666667</v>
       </c>
       <c r="J603">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K603" t="s">
         <v>11</v>
@@ -17419,25 +17507,25 @@
         <v>35</v>
       </c>
       <c r="C604">
-        <v>623</v>
+        <v>80</v>
       </c>
       <c r="D604" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F604" t="s">
         <v>86</v>
       </c>
       <c r="G604" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H604" s="2">
-        <v>8.8541666666666664E-3</v>
+        <v>0</v>
       </c>
       <c r="I604" s="1">
-        <v>46118.839583333334</v>
+        <v>46118.841666666667</v>
       </c>
       <c r="J604">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K604" t="s">
         <v>11</v>
@@ -17448,25 +17536,25 @@
         <v>35</v>
       </c>
       <c r="C605">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D605" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="F605" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="G605" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H605" s="2">
-        <v>0</v>
+        <v>4.2592592592592595E-3</v>
       </c>
       <c r="I605" s="1">
-        <v>46118.840277777781</v>
+        <v>46146.730902777781</v>
       </c>
       <c r="J605">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K605" t="s">
         <v>11</v>
@@ -17477,25 +17565,25 @@
         <v>35</v>
       </c>
       <c r="C606">
-        <v>245</v>
+        <v>745</v>
       </c>
       <c r="D606" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F606" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="G606" t="s">
         <v>10</v>
       </c>
       <c r="H606" s="2">
-        <v>9.3865740740740732E-3</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I606" s="1">
-        <v>46118.84097222222</v>
+        <v>46146.730902777781</v>
       </c>
       <c r="J606">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K606" t="s">
         <v>11</v>
@@ -17506,25 +17594,25 @@
         <v>35</v>
       </c>
       <c r="C607">
-        <v>84</v>
+        <v>622</v>
       </c>
       <c r="D607" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F607" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="G607" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H607" s="2">
-        <v>8.8078703703703704E-3</v>
+        <v>0</v>
       </c>
       <c r="I607" s="1">
-        <v>46118.84097222222</v>
+        <v>46146.73159722222</v>
       </c>
       <c r="J607">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K607" t="s">
         <v>11</v>
@@ -17535,25 +17623,25 @@
         <v>35</v>
       </c>
       <c r="C608">
-        <v>3818</v>
+        <v>5217</v>
       </c>
       <c r="D608" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F608" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="G608" t="s">
         <v>10</v>
       </c>
       <c r="H608" s="2">
-        <v>7.6736111111111111E-3</v>
+        <v>5.8564814814814816E-3</v>
       </c>
       <c r="I608" s="1">
-        <v>46118.841666666667</v>
+        <v>46146.732291666667</v>
       </c>
       <c r="J608">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K608" t="s">
         <v>11</v>
@@ -17564,25 +17652,25 @@
         <v>35</v>
       </c>
       <c r="C609">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="D609" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F609" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="G609" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H609" s="2">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I609" s="1">
-        <v>46118.841666666667</v>
+        <v>46146.732986111114</v>
       </c>
       <c r="J609">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K609" t="s">
         <v>11</v>
@@ -17593,10 +17681,10 @@
         <v>35</v>
       </c>
       <c r="C610">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="D610" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F610" t="s">
         <v>17</v>
@@ -17605,10 +17693,10 @@
         <v>10</v>
       </c>
       <c r="H610" s="2">
-        <v>4.2592592592592595E-3</v>
+        <v>5.1967592592592595E-3</v>
       </c>
       <c r="I610" s="1">
-        <v>46146.730902777781</v>
+        <v>46146.732986111114</v>
       </c>
       <c r="J610">
         <v>0</v>
@@ -17622,10 +17710,13 @@
         <v>35</v>
       </c>
       <c r="C611">
-        <v>745</v>
+        <v>3741</v>
       </c>
       <c r="D611" t="s">
-        <v>38</v>
+        <v>78</v>
+      </c>
+      <c r="E611" t="s">
+        <v>63</v>
       </c>
       <c r="F611" t="s">
         <v>17</v>
@@ -17634,13 +17725,13 @@
         <v>10</v>
       </c>
       <c r="H611" s="2">
-        <v>4.5717592592592589E-3</v>
+        <v>6.6782407407407407E-3</v>
       </c>
       <c r="I611" s="1">
-        <v>46146.730902777781</v>
+        <v>46146.710185185184</v>
       </c>
       <c r="J611">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K611" t="s">
         <v>11</v>
@@ -17651,25 +17742,25 @@
         <v>35</v>
       </c>
       <c r="C612">
-        <v>622</v>
+        <v>78</v>
       </c>
       <c r="D612" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F612" t="s">
         <v>17</v>
       </c>
       <c r="G612" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H612" s="2">
-        <v>0</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I612" s="1">
-        <v>46146.73159722222</v>
+        <v>46146.710879629631</v>
       </c>
       <c r="J612">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K612" t="s">
         <v>11</v>
@@ -17680,25 +17771,25 @@
         <v>35</v>
       </c>
       <c r="C613">
-        <v>5217</v>
+        <v>73</v>
       </c>
       <c r="D613" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F613" t="s">
         <v>17</v>
       </c>
       <c r="G613" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H613" s="2">
-        <v>5.8564814814814816E-3</v>
+        <v>0</v>
       </c>
       <c r="I613" s="1">
-        <v>46146.732291666667</v>
+        <v>46146.711574074077</v>
       </c>
       <c r="J613">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K613" t="s">
         <v>11</v>
@@ -17709,25 +17800,25 @@
         <v>35</v>
       </c>
       <c r="C614">
-        <v>5180</v>
+        <v>5037</v>
       </c>
       <c r="D614" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F614" t="s">
         <v>17</v>
       </c>
       <c r="G614" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H614">
         <v>0</v>
       </c>
       <c r="I614" s="1">
-        <v>46146.732291666667</v>
+        <v>46146.711574074077</v>
       </c>
       <c r="J614">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K614" t="s">
         <v>11</v>
@@ -17738,10 +17829,10 @@
         <v>35</v>
       </c>
       <c r="C615">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="D615" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F615" t="s">
         <v>17</v>
@@ -17750,13 +17841,13 @@
         <v>10</v>
       </c>
       <c r="H615" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>4.3287037037037035E-3</v>
       </c>
       <c r="I615" s="1">
-        <v>46146.732986111114</v>
+        <v>46146.712268518517</v>
       </c>
       <c r="J615">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K615" t="s">
         <v>11</v>
@@ -17767,10 +17858,10 @@
         <v>35</v>
       </c>
       <c r="C616">
-        <v>205</v>
+        <v>5409</v>
       </c>
       <c r="D616" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="F616" t="s">
         <v>17</v>
@@ -17779,13 +17870,13 @@
         <v>10</v>
       </c>
       <c r="H616" s="2">
-        <v>5.1967592592592595E-3</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I616" s="1">
-        <v>46146.732986111114</v>
+        <v>46146.712268518517</v>
       </c>
       <c r="J616">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K616" t="s">
         <v>11</v>
@@ -17796,13 +17887,10 @@
         <v>35</v>
       </c>
       <c r="C617">
-        <v>3741</v>
+        <v>5350</v>
       </c>
       <c r="D617" t="s">
-        <v>78</v>
-      </c>
-      <c r="E617" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F617" t="s">
         <v>17</v>
@@ -17811,13 +17899,13 @@
         <v>10</v>
       </c>
       <c r="H617" s="2">
-        <v>6.6782407407407407E-3</v>
+        <v>9.3981481481481485E-3</v>
       </c>
       <c r="I617" s="1">
-        <v>46146.710185185184</v>
+        <v>46146.712962962964</v>
       </c>
       <c r="J617">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K617" t="s">
         <v>11</v>
@@ -17828,25 +17916,25 @@
         <v>35</v>
       </c>
       <c r="C618">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D618" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F618" t="s">
         <v>17</v>
       </c>
       <c r="G618" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H618" s="2">
-        <v>6.7013888888888887E-3</v>
+        <v>0</v>
       </c>
       <c r="I618" s="1">
-        <v>46146.710879629631</v>
+        <v>46146.71365740741</v>
       </c>
       <c r="J618">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K618" t="s">
         <v>11</v>
@@ -17857,25 +17945,25 @@
         <v>35</v>
       </c>
       <c r="C619">
-        <v>73</v>
+        <v>3726</v>
       </c>
       <c r="D619" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F619" t="s">
         <v>17</v>
       </c>
       <c r="G619" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H619" s="2">
-        <v>0</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I619" s="1">
-        <v>46146.711574074077</v>
+        <v>46146.71365740741</v>
       </c>
       <c r="J619">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K619" t="s">
         <v>11</v>
@@ -17886,25 +17974,25 @@
         <v>35</v>
       </c>
       <c r="C620">
-        <v>5037</v>
+        <v>614</v>
       </c>
       <c r="D620" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F620" t="s">
         <v>17</v>
       </c>
       <c r="G620" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H620" s="2">
-        <v>0</v>
+        <v>4.7685185185185183E-3</v>
       </c>
       <c r="I620" s="1">
-        <v>46146.711574074077</v>
+        <v>46146.71435185185</v>
       </c>
       <c r="J620">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K620" t="s">
         <v>11</v>
@@ -17915,10 +18003,10 @@
         <v>35</v>
       </c>
       <c r="C621">
-        <v>75</v>
+        <v>772</v>
       </c>
       <c r="D621" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F621" t="s">
         <v>17</v>
@@ -17927,13 +18015,13 @@
         <v>10</v>
       </c>
       <c r="H621" s="2">
-        <v>4.3287037037037035E-3</v>
+        <v>4.9305555555555552E-3</v>
       </c>
       <c r="I621" s="1">
-        <v>46146.712268518517</v>
+        <v>46146.715046296296</v>
       </c>
       <c r="J621">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K621" t="s">
         <v>11</v>
@@ -17944,10 +18032,10 @@
         <v>35</v>
       </c>
       <c r="C622">
-        <v>5350</v>
+        <v>623</v>
       </c>
       <c r="D622" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="F622" t="s">
         <v>17</v>
@@ -17956,10 +18044,10 @@
         <v>10</v>
       </c>
       <c r="H622" s="2">
-        <v>9.3981481481481485E-3</v>
+        <v>5.2893518518518515E-3</v>
       </c>
       <c r="I622" s="1">
-        <v>46146.712962962964</v>
+        <v>46146.715046296296</v>
       </c>
       <c r="J622">
         <v>0</v>
@@ -17973,10 +18061,10 @@
         <v>35</v>
       </c>
       <c r="C623">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D623" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F623" t="s">
         <v>17</v>
@@ -17988,7 +18076,7 @@
         <v>0</v>
       </c>
       <c r="I623" s="1">
-        <v>46146.71365740741</v>
+        <v>46146.715740740743</v>
       </c>
       <c r="J623">
         <v>4</v>
@@ -18002,10 +18090,10 @@
         <v>35</v>
       </c>
       <c r="C624">
-        <v>3726</v>
+        <v>245</v>
       </c>
       <c r="D624" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="F624" t="s">
         <v>17</v>
@@ -18014,10 +18102,10 @@
         <v>10</v>
       </c>
       <c r="H624" s="2">
-        <v>4.5717592592592589E-3</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I624" s="1">
-        <v>46146.71365740741</v>
+        <v>46146.716435185182</v>
       </c>
       <c r="J624">
         <v>0</v>
@@ -18031,10 +18119,10 @@
         <v>35</v>
       </c>
       <c r="C625">
-        <v>614</v>
+        <v>84</v>
       </c>
       <c r="D625" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F625" t="s">
         <v>17</v>
@@ -18043,10 +18131,10 @@
         <v>10</v>
       </c>
       <c r="H625" s="2">
-        <v>4.7685185185185183E-3</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I625" s="1">
-        <v>46146.71435185185</v>
+        <v>46146.716435185182</v>
       </c>
       <c r="J625">
         <v>1</v>
@@ -18060,10 +18148,10 @@
         <v>35</v>
       </c>
       <c r="C626">
-        <v>772</v>
+        <v>3818</v>
       </c>
       <c r="D626" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="F626" t="s">
         <v>17</v>
@@ -18072,10 +18160,10 @@
         <v>10</v>
       </c>
       <c r="H626" s="2">
-        <v>4.9305555555555552E-3</v>
+        <v>8.6574074074074071E-3</v>
       </c>
       <c r="I626" s="1">
-        <v>46146.715046296296</v>
+        <v>46146.717129629629</v>
       </c>
       <c r="J626">
         <v>0</v>
@@ -18089,25 +18177,25 @@
         <v>35</v>
       </c>
       <c r="C627">
-        <v>623</v>
+        <v>80</v>
       </c>
       <c r="D627" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F627" t="s">
         <v>17</v>
       </c>
       <c r="G627" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H627" s="2">
-        <v>5.2893518518518515E-3</v>
+        <v>0</v>
       </c>
       <c r="I627" s="1">
-        <v>46146.715046296296</v>
+        <v>46146.717824074076</v>
       </c>
       <c r="J627">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K627" t="s">
         <v>11</v>
@@ -18118,25 +18206,25 @@
         <v>35</v>
       </c>
       <c r="C628">
-        <v>72</v>
+        <v>745</v>
       </c>
       <c r="D628" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F628" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G628" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H628" s="2">
-        <v>0</v>
+        <v>9.9189814814814817E-3</v>
       </c>
       <c r="I628" s="1">
-        <v>46146.715740740743</v>
+        <v>46174.633796296293</v>
       </c>
       <c r="J628">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K628" t="s">
         <v>11</v>
@@ -18147,22 +18235,22 @@
         <v>35</v>
       </c>
       <c r="C629">
-        <v>245</v>
+        <v>5586</v>
       </c>
       <c r="D629" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="F629" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G629" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H629" s="2">
-        <v>1.9675925925925926E-4</v>
+        <v>9.4212962962962957E-3</v>
       </c>
       <c r="I629" s="1">
-        <v>46146.716435185182</v>
+        <v>46174.63449074074</v>
       </c>
       <c r="J629">
         <v>0</v>
@@ -18176,25 +18264,25 @@
         <v>35</v>
       </c>
       <c r="C630">
-        <v>84</v>
+        <v>5217</v>
       </c>
       <c r="D630" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F630" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G630" t="s">
         <v>10</v>
       </c>
       <c r="H630" s="2">
-        <v>6.6550925925925927E-3</v>
+        <v>1.53125E-2</v>
       </c>
       <c r="I630" s="1">
-        <v>46146.716435185182</v>
+        <v>46174.635879629626</v>
       </c>
       <c r="J630">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K630" t="s">
         <v>11</v>
@@ -18205,22 +18293,22 @@
         <v>35</v>
       </c>
       <c r="C631">
-        <v>3818</v>
+        <v>205</v>
       </c>
       <c r="D631" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="F631" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G631" t="s">
         <v>10</v>
       </c>
       <c r="H631" s="2">
-        <v>8.6574074074074071E-3</v>
+        <v>1.1145833333333334E-2</v>
       </c>
       <c r="I631" s="1">
-        <v>46146.717129629629</v>
+        <v>46174.63726851852</v>
       </c>
       <c r="J631">
         <v>0</v>
@@ -18234,49 +18322,115 @@
         <v>35</v>
       </c>
       <c r="C632">
-        <v>80</v>
+        <v>5037</v>
       </c>
       <c r="D632" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="F632" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G632" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H632" s="2">
-        <v>0</v>
+        <v>1.0486111111111111E-2</v>
       </c>
       <c r="I632" s="1">
-        <v>46146.717824074076</v>
+        <v>46174.639351851853</v>
       </c>
       <c r="J632">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K632" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="633" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H633" s="2"/>
-      <c r="I633" s="1"/>
+      <c r="B633" t="s">
+        <v>35</v>
+      </c>
+      <c r="C633">
+        <v>772</v>
+      </c>
+      <c r="D633" t="s">
+        <v>49</v>
+      </c>
+      <c r="F633" t="s">
+        <v>89</v>
+      </c>
+      <c r="G633" t="s">
+        <v>10</v>
+      </c>
+      <c r="H633" s="2">
+        <v>8.0439814814814818E-3</v>
+      </c>
+      <c r="I633" s="1">
+        <v>46174.642824074072</v>
+      </c>
+      <c r="J633">
+        <v>0</v>
+      </c>
       <c r="K633" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="634" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H634" s="2"/>
-      <c r="I634" s="1"/>
+      <c r="B634" t="s">
+        <v>35</v>
+      </c>
+      <c r="C634">
+        <v>245</v>
+      </c>
+      <c r="D634" t="s">
+        <v>52</v>
+      </c>
+      <c r="F634" t="s">
+        <v>89</v>
+      </c>
+      <c r="G634" t="s">
+        <v>10</v>
+      </c>
+      <c r="H634" s="2">
+        <v>6.4814814814814813E-3</v>
+      </c>
+      <c r="I634" s="1">
+        <v>46174.644212962965</v>
+      </c>
+      <c r="J634">
+        <v>0</v>
+      </c>
       <c r="K634" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="635" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H635" s="2"/>
-      <c r="I635" s="1"/>
+      <c r="B635" t="s">
+        <v>35</v>
+      </c>
+      <c r="C635">
+        <v>84</v>
+      </c>
+      <c r="D635" t="s">
+        <v>55</v>
+      </c>
+      <c r="F635" t="s">
+        <v>89</v>
+      </c>
+      <c r="G635" t="s">
+        <v>10</v>
+      </c>
+      <c r="H635" s="2">
+        <v>6.2962962962962964E-3</v>
+      </c>
+      <c r="I635" s="1">
+        <v>46174.644907407404</v>
+      </c>
+      <c r="J635">
+        <v>0</v>
+      </c>
       <c r="K635" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="636" spans="2:11" x14ac:dyDescent="0.3">
@@ -18284,22 +18438,22 @@
         <v>35</v>
       </c>
       <c r="C636">
-        <v>77</v>
+        <v>3818</v>
       </c>
       <c r="D636" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F636" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G636" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H636" s="2">
-        <v>0</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I636" s="1">
-        <v>46176.418402777781</v>
+        <v>46174.645601851851</v>
       </c>
       <c r="J636">
         <v>0</v>
@@ -18313,25 +18467,25 @@
         <v>35</v>
       </c>
       <c r="C637">
-        <v>745</v>
+        <v>77</v>
       </c>
       <c r="D637" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F637" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G637" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H637" s="2">
-        <v>8.0208333333333329E-3</v>
+        <v>0</v>
       </c>
       <c r="I637" s="1">
-        <v>46174.633796296293</v>
+        <v>46176.418402777781</v>
       </c>
       <c r="J637">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K637" t="s">
         <v>11</v>
@@ -18342,25 +18496,25 @@
         <v>35</v>
       </c>
       <c r="C638">
-        <v>5586</v>
+        <v>622</v>
       </c>
       <c r="D638" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F638" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G638" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H638" s="2">
-        <v>9.4212962962962957E-3</v>
+        <v>0</v>
       </c>
       <c r="I638" s="1">
-        <v>46174.63449074074</v>
+        <v>46176.41909722222</v>
       </c>
       <c r="J638">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K638" t="s">
         <v>11</v>
@@ -18371,10 +18525,10 @@
         <v>35</v>
       </c>
       <c r="C639">
-        <v>622</v>
+        <v>5180</v>
       </c>
       <c r="D639" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="F639" t="s">
         <v>91</v>
@@ -18386,10 +18540,10 @@
         <v>0</v>
       </c>
       <c r="I639" s="1">
-        <v>46176.41909722222</v>
+        <v>46176.419791666667</v>
       </c>
       <c r="J639">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K639" t="s">
         <v>11</v>
@@ -18400,22 +18554,22 @@
         <v>35</v>
       </c>
       <c r="C640">
-        <v>5217</v>
+        <v>204</v>
       </c>
       <c r="D640" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="F640" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G640" t="s">
         <v>10</v>
       </c>
       <c r="H640" s="2">
-        <v>1.53125E-2</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I640" s="1">
-        <v>46174.635879629626</v>
+        <v>46176.419791666667</v>
       </c>
       <c r="J640">
         <v>0</v>
@@ -18429,10 +18583,13 @@
         <v>35</v>
       </c>
       <c r="C641">
-        <v>204</v>
+        <v>3741</v>
       </c>
       <c r="D641" t="s">
-        <v>40</v>
+        <v>78</v>
+      </c>
+      <c r="E641" t="s">
+        <v>63</v>
       </c>
       <c r="F641" t="s">
         <v>91</v>
@@ -18441,10 +18598,10 @@
         <v>10</v>
       </c>
       <c r="H641" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>8.1134259259259267E-3</v>
       </c>
       <c r="I641" s="1">
-        <v>46176.419791666667</v>
+        <v>46176.420486111114</v>
       </c>
       <c r="J641">
         <v>0</v>
@@ -18458,22 +18615,22 @@
         <v>35</v>
       </c>
       <c r="C642">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="D642" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F642" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G642" t="s">
         <v>10</v>
       </c>
       <c r="H642" s="2">
-        <v>1.1145833333333334E-2</v>
+        <v>1.275462962962963E-2</v>
       </c>
       <c r="I642" s="1">
-        <v>46174.63726851852</v>
+        <v>46176.421180555553</v>
       </c>
       <c r="J642">
         <v>0</v>
@@ -18487,28 +18644,25 @@
         <v>35</v>
       </c>
       <c r="C643">
-        <v>3741</v>
+        <v>73</v>
       </c>
       <c r="D643" t="s">
-        <v>78</v>
-      </c>
-      <c r="E643" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F643" t="s">
         <v>91</v>
       </c>
       <c r="G643" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H643" s="2">
-        <v>8.1134259259259267E-3</v>
+        <v>0</v>
       </c>
       <c r="I643" s="1">
-        <v>46176.420486111114</v>
+        <v>46176.421180555553</v>
       </c>
       <c r="J643">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K643" t="s">
         <v>11</v>
@@ -18519,10 +18673,10 @@
         <v>35</v>
       </c>
       <c r="C644">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D644" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F644" t="s">
         <v>91</v>
@@ -18534,10 +18688,10 @@
         <v>0</v>
       </c>
       <c r="I644" s="1">
-        <v>46176.421180555553</v>
+        <v>46176.421875</v>
       </c>
       <c r="J644">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K644" t="s">
         <v>11</v>
@@ -18548,10 +18702,10 @@
         <v>35</v>
       </c>
       <c r="C645">
-        <v>73</v>
+        <v>5350</v>
       </c>
       <c r="D645" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="F645" t="s">
         <v>91</v>
@@ -18563,10 +18717,10 @@
         <v>0</v>
       </c>
       <c r="I645" s="1">
-        <v>46176.421180555553</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J645">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K645" t="s">
         <v>11</v>
@@ -18577,25 +18731,25 @@
         <v>35</v>
       </c>
       <c r="C646">
-        <v>5037</v>
+        <v>76</v>
       </c>
       <c r="D646" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F646" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G646" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H646" s="2">
-        <v>1.0486111111111111E-2</v>
+        <v>0</v>
       </c>
       <c r="I646" s="1">
-        <v>46174.639351851853</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J646">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K646" t="s">
         <v>11</v>
@@ -18606,10 +18760,10 @@
         <v>35</v>
       </c>
       <c r="C647">
-        <v>75</v>
+        <v>3726</v>
       </c>
       <c r="D647" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="F647" t="s">
         <v>91</v>
@@ -18621,10 +18775,10 @@
         <v>0</v>
       </c>
       <c r="I647" s="1">
-        <v>46176.421875</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K647" t="s">
         <v>11</v>
@@ -18635,22 +18789,22 @@
         <v>35</v>
       </c>
       <c r="C648">
-        <v>5409</v>
+        <v>614</v>
       </c>
       <c r="D648" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F648" t="s">
         <v>91</v>
       </c>
       <c r="G648" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H648" s="2">
-        <v>0</v>
+        <v>7.789351851851852E-3</v>
       </c>
       <c r="I648" s="1">
-        <v>46176.421875</v>
+        <v>46176.423263888886</v>
       </c>
       <c r="J648">
         <v>0</v>
@@ -18664,25 +18818,25 @@
         <v>35</v>
       </c>
       <c r="C649">
-        <v>76</v>
+        <v>623</v>
       </c>
       <c r="D649" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F649" t="s">
         <v>91</v>
       </c>
       <c r="G649" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H649" s="2">
-        <v>0</v>
+        <v>7.3495370370370372E-3</v>
       </c>
       <c r="I649" s="1">
-        <v>46176.422569444447</v>
+        <v>46176.423263888886</v>
       </c>
       <c r="J649">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K649" t="s">
         <v>11</v>
@@ -18693,10 +18847,10 @@
         <v>35</v>
       </c>
       <c r="C650">
-        <v>3726</v>
+        <v>72</v>
       </c>
       <c r="D650" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F650" t="s">
         <v>91</v>
@@ -18708,10 +18862,10 @@
         <v>0</v>
       </c>
       <c r="I650" s="1">
-        <v>46176.422569444447</v>
+        <v>46176.423958333333</v>
       </c>
       <c r="J650">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K650" t="s">
         <v>11</v>
@@ -18722,25 +18876,25 @@
         <v>35</v>
       </c>
       <c r="C651">
-        <v>614</v>
+        <v>80</v>
       </c>
       <c r="D651" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F651" t="s">
         <v>91</v>
       </c>
       <c r="G651" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H651" s="2">
-        <v>7.789351851851852E-3</v>
+        <v>0</v>
       </c>
       <c r="I651" s="1">
-        <v>46176.423263888886</v>
+        <v>46176.42465277778</v>
       </c>
       <c r="J651">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K651" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B43BE6-72C7-4D89-89C0-9FF189CBAE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFD68EB-B08D-44FA-A6F6-B2A6131A6D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5925</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5924</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="92">
   <si>
     <t>Company Name</t>
   </si>
@@ -688,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K5925"/>
+  <dimension ref="B1:K5924"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -18847,10 +18847,10 @@
         <v>35</v>
       </c>
       <c r="C650">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D650" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F650" t="s">
         <v>91</v>
@@ -18862,7 +18862,7 @@
         <v>0</v>
       </c>
       <c r="I650" s="1">
-        <v>46176.423958333333</v>
+        <v>46176.42465277778</v>
       </c>
       <c r="J650">
         <v>1</v>
@@ -18876,25 +18876,25 @@
         <v>35</v>
       </c>
       <c r="C651">
-        <v>80</v>
+        <v>772</v>
       </c>
       <c r="D651" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F651" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G651" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H651" s="2">
-        <v>0</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I651" s="1">
-        <v>46176.42465277778</v>
+        <v>46174.642824074072</v>
       </c>
       <c r="J651">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K651" t="s">
         <v>11</v>
@@ -18905,22 +18905,22 @@
         <v>35</v>
       </c>
       <c r="C652">
-        <v>772</v>
+        <v>623</v>
       </c>
       <c r="D652" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F652" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G652" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H652" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>0</v>
       </c>
       <c r="I652" s="1">
-        <v>46174.642824074072</v>
+        <v>46176.423263888886</v>
       </c>
       <c r="J652">
         <v>0</v>
@@ -18934,10 +18934,10 @@
         <v>35</v>
       </c>
       <c r="C653">
-        <v>623</v>
+        <v>72</v>
       </c>
       <c r="D653" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F653" t="s">
         <v>91</v>
@@ -18949,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="I653" s="1">
-        <v>46176.423263888886</v>
+        <v>46176.423958333333</v>
       </c>
       <c r="J653">
         <v>0</v>
@@ -18963,22 +18963,22 @@
         <v>35</v>
       </c>
       <c r="C654">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="D654" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F654" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G654" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H654" s="2">
-        <v>0</v>
+        <v>6.4814814814814813E-3</v>
       </c>
       <c r="I654" s="1">
-        <v>46176.423958333333</v>
+        <v>46174.644212962965</v>
       </c>
       <c r="J654">
         <v>0</v>
@@ -18992,10 +18992,10 @@
         <v>35</v>
       </c>
       <c r="C655">
-        <v>245</v>
+        <v>84</v>
       </c>
       <c r="D655" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F655" t="s">
         <v>89</v>
@@ -19004,10 +19004,10 @@
         <v>10</v>
       </c>
       <c r="H655" s="2">
-        <v>6.4814814814814813E-3</v>
+        <v>6.2962962962962964E-3</v>
       </c>
       <c r="I655" s="1">
-        <v>46174.644212962965</v>
+        <v>46174.644907407404</v>
       </c>
       <c r="J655">
         <v>0</v>
@@ -19021,10 +19021,10 @@
         <v>35</v>
       </c>
       <c r="C656">
-        <v>84</v>
+        <v>3818</v>
       </c>
       <c r="D656" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F656" t="s">
         <v>89</v>
@@ -19033,10 +19033,10 @@
         <v>10</v>
       </c>
       <c r="H656" s="2">
-        <v>6.2962962962962964E-3</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I656" s="1">
-        <v>46174.644907407404</v>
+        <v>46174.645601851851</v>
       </c>
       <c r="J656">
         <v>0</v>
@@ -19050,22 +19050,22 @@
         <v>35</v>
       </c>
       <c r="C657">
-        <v>3818</v>
+        <v>80</v>
       </c>
       <c r="D657" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F657" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G657" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H657" s="2">
-        <v>7.013888888888889E-3</v>
+        <v>0</v>
       </c>
       <c r="I657" s="1">
-        <v>46174.645601851851</v>
+        <v>46176.42465277778</v>
       </c>
       <c r="J657">
         <v>0</v>
@@ -19075,33 +19075,8 @@
       </c>
     </row>
     <row r="658" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B658" t="s">
-        <v>35</v>
-      </c>
-      <c r="C658">
-        <v>80</v>
-      </c>
-      <c r="D658" t="s">
-        <v>56</v>
-      </c>
-      <c r="F658" t="s">
-        <v>91</v>
-      </c>
-      <c r="G658" t="s">
-        <v>13</v>
-      </c>
-      <c r="H658" s="2">
-        <v>0</v>
-      </c>
-      <c r="I658" s="1">
-        <v>46176.42465277778</v>
-      </c>
-      <c r="J658">
-        <v>0</v>
-      </c>
-      <c r="K658" t="s">
-        <v>11</v>
-      </c>
+      <c r="H658" s="2"/>
+      <c r="I658" s="1"/>
     </row>
     <row r="659" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H659" s="2"/>
@@ -19344,10 +19319,10 @@
       <c r="I718" s="1"/>
     </row>
     <row r="719" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H719" s="2"/>
       <c r="I719" s="1"/>
     </row>
     <row r="720" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H720" s="2"/>
       <c r="I720" s="1"/>
     </row>
     <row r="721" spans="8:9" x14ac:dyDescent="0.3">
@@ -19431,10 +19406,10 @@
       <c r="I740" s="1"/>
     </row>
     <row r="741" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H741" s="2"/>
       <c r="I741" s="1"/>
     </row>
     <row r="742" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H742" s="2"/>
       <c r="I742" s="1"/>
     </row>
     <row r="743" spans="8:9" x14ac:dyDescent="0.3">
@@ -19574,10 +19549,10 @@
       <c r="I776" s="1"/>
     </row>
     <row r="777" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H777" s="2"/>
       <c r="I777" s="1"/>
     </row>
     <row r="778" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H778" s="2"/>
       <c r="I778" s="1"/>
     </row>
     <row r="779" spans="8:9" x14ac:dyDescent="0.3">
@@ -19637,10 +19612,10 @@
       <c r="I792" s="1"/>
     </row>
     <row r="793" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H793" s="2"/>
       <c r="I793" s="1"/>
     </row>
     <row r="794" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H794" s="2"/>
       <c r="I794" s="1"/>
     </row>
     <row r="795" spans="8:9" x14ac:dyDescent="0.3">
@@ -19932,10 +19907,10 @@
       <c r="I866" s="1"/>
     </row>
     <row r="867" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H867" s="2"/>
       <c r="I867" s="1"/>
     </row>
     <row r="868" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H868" s="2"/>
       <c r="I868" s="1"/>
     </row>
     <row r="869" spans="8:9" x14ac:dyDescent="0.3">
@@ -19959,10 +19934,10 @@
       <c r="I873" s="1"/>
     </row>
     <row r="874" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H874" s="2"/>
       <c r="I874" s="1"/>
     </row>
     <row r="875" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H875" s="2"/>
       <c r="I875" s="1"/>
     </row>
     <row r="876" spans="8:9" x14ac:dyDescent="0.3">
@@ -20070,10 +20045,10 @@
       <c r="I901" s="1"/>
     </row>
     <row r="902" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H902" s="2"/>
       <c r="I902" s="1"/>
     </row>
     <row r="903" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H903" s="2"/>
       <c r="I903" s="1"/>
     </row>
     <row r="904" spans="8:9" x14ac:dyDescent="0.3">
@@ -20173,10 +20148,10 @@
       <c r="I927" s="1"/>
     </row>
     <row r="928" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H928" s="2"/>
       <c r="I928" s="1"/>
     </row>
     <row r="929" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H929" s="2"/>
       <c r="I929" s="1"/>
     </row>
     <row r="930" spans="8:9" x14ac:dyDescent="0.3">
@@ -20188,10 +20163,10 @@
       <c r="I931" s="1"/>
     </row>
     <row r="932" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H932" s="2"/>
       <c r="I932" s="1"/>
     </row>
     <row r="933" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H933" s="2"/>
       <c r="I933" s="1"/>
     </row>
     <row r="934" spans="8:9" x14ac:dyDescent="0.3">
@@ -20335,10 +20310,10 @@
       <c r="I968" s="1"/>
     </row>
     <row r="969" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H969" s="2"/>
       <c r="I969" s="1"/>
     </row>
     <row r="970" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H970" s="2"/>
       <c r="I970" s="1"/>
     </row>
     <row r="971" spans="8:9" x14ac:dyDescent="0.3">
@@ -20498,10 +20473,10 @@
       <c r="I1009" s="1"/>
     </row>
     <row r="1010" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1010" s="2"/>
       <c r="I1010" s="1"/>
     </row>
     <row r="1011" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1011" s="2"/>
       <c r="I1011" s="1"/>
     </row>
     <row r="1012" spans="8:9" x14ac:dyDescent="0.3">
@@ -20557,10 +20532,10 @@
       <c r="I1024" s="1"/>
     </row>
     <row r="1025" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1025" s="2"/>
       <c r="I1025" s="1"/>
     </row>
     <row r="1026" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1026" s="2"/>
       <c r="I1026" s="1"/>
     </row>
     <row r="1027" spans="8:9" x14ac:dyDescent="0.3">
@@ -20848,10 +20823,10 @@
       <c r="I1097" s="1"/>
     </row>
     <row r="1098" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1098" s="2"/>
       <c r="I1098" s="1"/>
     </row>
     <row r="1099" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
     </row>
     <row r="1100" spans="8:9" x14ac:dyDescent="0.3">
@@ -21231,10 +21206,10 @@
       <c r="I1193" s="1"/>
     </row>
     <row r="1194" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
     </row>
     <row r="1195" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1195" s="2"/>
       <c r="I1195" s="1"/>
     </row>
     <row r="1196" spans="8:9" x14ac:dyDescent="0.3">
@@ -21426,10 +21401,10 @@
       <c r="I1242" s="1"/>
     </row>
     <row r="1243" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1243" s="2"/>
       <c r="I1243" s="1"/>
     </row>
     <row r="1244" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1244" s="2"/>
       <c r="I1244" s="1"/>
     </row>
     <row r="1245" spans="8:9" x14ac:dyDescent="0.3">
@@ -21465,10 +21440,10 @@
       <c r="I1252" s="1"/>
     </row>
     <row r="1253" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1253" s="2"/>
       <c r="I1253" s="1"/>
     </row>
     <row r="1254" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1254" s="2"/>
       <c r="I1254" s="1"/>
     </row>
     <row r="1255" spans="8:9" x14ac:dyDescent="0.3">
@@ -21476,10 +21451,10 @@
       <c r="I1255" s="1"/>
     </row>
     <row r="1256" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
     </row>
     <row r="1257" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1257" s="2"/>
       <c r="I1257" s="1"/>
     </row>
     <row r="1258" spans="8:9" x14ac:dyDescent="0.3">
@@ -21527,10 +21502,10 @@
       <c r="I1268" s="1"/>
     </row>
     <row r="1269" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1269" s="2"/>
       <c r="I1269" s="1"/>
     </row>
     <row r="1270" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1270" s="2"/>
       <c r="I1270" s="1"/>
     </row>
     <row r="1271" spans="8:9" x14ac:dyDescent="0.3">
@@ -21630,10 +21605,10 @@
       <c r="I1294" s="1"/>
     </row>
     <row r="1295" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1295" s="2"/>
       <c r="I1295" s="1"/>
     </row>
     <row r="1296" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1296" s="2"/>
       <c r="I1296" s="1"/>
     </row>
     <row r="1297" spans="8:9" x14ac:dyDescent="0.3">
@@ -21729,10 +21704,10 @@
       <c r="I1319" s="1"/>
     </row>
     <row r="1320" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1320" s="2"/>
       <c r="I1320" s="1"/>
     </row>
     <row r="1321" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1321" s="2"/>
       <c r="I1321" s="1"/>
     </row>
     <row r="1322" spans="8:9" x14ac:dyDescent="0.3">
@@ -21808,10 +21783,10 @@
       <c r="I1339" s="1"/>
     </row>
     <row r="1340" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1340" s="2"/>
       <c r="I1340" s="1"/>
     </row>
     <row r="1341" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1341" s="2"/>
       <c r="I1341" s="1"/>
     </row>
     <row r="1342" spans="8:9" x14ac:dyDescent="0.3">
@@ -21839,10 +21814,10 @@
       <c r="I1347" s="1"/>
     </row>
     <row r="1348" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1348" s="2"/>
       <c r="I1348" s="1"/>
     </row>
     <row r="1349" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1349" s="2"/>
       <c r="I1349" s="1"/>
     </row>
     <row r="1350" spans="8:9" x14ac:dyDescent="0.3">
@@ -21862,10 +21837,10 @@
       <c r="I1353" s="1"/>
     </row>
     <row r="1354" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1354" s="2"/>
       <c r="I1354" s="1"/>
     </row>
     <row r="1355" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1355" s="2"/>
       <c r="I1355" s="1"/>
     </row>
     <row r="1356" spans="8:9" x14ac:dyDescent="0.3">
@@ -21921,10 +21896,10 @@
       <c r="I1368" s="1"/>
     </row>
     <row r="1369" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1369" s="2"/>
       <c r="I1369" s="1"/>
     </row>
     <row r="1370" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
     </row>
     <row r="1371" spans="8:9" x14ac:dyDescent="0.3">
@@ -21932,10 +21907,10 @@
       <c r="I1371" s="1"/>
     </row>
     <row r="1372" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1372" s="2"/>
       <c r="I1372" s="1"/>
     </row>
     <row r="1373" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1373" s="2"/>
       <c r="I1373" s="1"/>
     </row>
     <row r="1374" spans="8:9" x14ac:dyDescent="0.3">
@@ -21959,10 +21934,10 @@
       <c r="I1378" s="1"/>
     </row>
     <row r="1379" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1379" s="2"/>
       <c r="I1379" s="1"/>
     </row>
     <row r="1380" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1380" s="2"/>
       <c r="I1380" s="1"/>
     </row>
     <row r="1381" spans="8:9" x14ac:dyDescent="0.3">
@@ -21974,10 +21949,10 @@
       <c r="I1382" s="1"/>
     </row>
     <row r="1383" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1383" s="2"/>
       <c r="I1383" s="1"/>
     </row>
     <row r="1384" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1384" s="2"/>
       <c r="I1384" s="1"/>
     </row>
     <row r="1385" spans="8:9" x14ac:dyDescent="0.3">
@@ -21993,10 +21968,10 @@
       <c r="I1387" s="1"/>
     </row>
     <row r="1388" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1388" s="2"/>
       <c r="I1388" s="1"/>
     </row>
     <row r="1389" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1389" s="2"/>
       <c r="I1389" s="1"/>
     </row>
     <row r="1390" spans="8:9" x14ac:dyDescent="0.3">
@@ -22012,10 +21987,10 @@
       <c r="I1392" s="1"/>
     </row>
     <row r="1393" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1393" s="2"/>
       <c r="I1393" s="1"/>
     </row>
     <row r="1394" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1394" s="2"/>
       <c r="I1394" s="1"/>
     </row>
     <row r="1395" spans="8:9" x14ac:dyDescent="0.3">
@@ -22075,10 +22050,10 @@
       <c r="I1408" s="1"/>
     </row>
     <row r="1409" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1409" s="2"/>
       <c r="I1409" s="1"/>
     </row>
     <row r="1410" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1410" s="2"/>
       <c r="I1410" s="1"/>
     </row>
     <row r="1411" spans="8:9" x14ac:dyDescent="0.3">
@@ -22146,10 +22121,10 @@
       <c r="I1426" s="1"/>
     </row>
     <row r="1427" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
     </row>
     <row r="1428" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1428" s="2"/>
       <c r="I1428" s="1"/>
     </row>
     <row r="1429" spans="8:9" x14ac:dyDescent="0.3">
@@ -22193,10 +22168,10 @@
       <c r="I1438" s="1"/>
     </row>
     <row r="1439" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1439" s="2"/>
       <c r="I1439" s="1"/>
     </row>
     <row r="1440" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1440" s="2"/>
       <c r="I1440" s="1"/>
     </row>
     <row r="1441" spans="8:9" x14ac:dyDescent="0.3">
@@ -22324,13 +22299,13 @@
       <c r="I1471" s="1"/>
     </row>
     <row r="1472" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1472" s="2"/>
       <c r="I1472" s="1"/>
     </row>
     <row r="1473" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1473" s="1"/>
     </row>
     <row r="1474" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1474" s="2"/>
       <c r="I1474" s="1"/>
     </row>
     <row r="1475" spans="8:9" x14ac:dyDescent="0.3">
@@ -22386,10 +22361,10 @@
       <c r="I1487" s="1"/>
     </row>
     <row r="1488" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1488" s="2"/>
       <c r="I1488" s="1"/>
     </row>
     <row r="1489" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1489" s="2"/>
       <c r="I1489" s="1"/>
     </row>
     <row r="1490" spans="8:9" x14ac:dyDescent="0.3">
@@ -22577,10 +22552,10 @@
       <c r="I1535" s="1"/>
     </row>
     <row r="1536" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1536" s="2"/>
       <c r="I1536" s="1"/>
     </row>
     <row r="1537" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1537" s="2"/>
       <c r="I1537" s="1"/>
     </row>
     <row r="1538" spans="8:9" x14ac:dyDescent="0.3">
@@ -22620,10 +22595,10 @@
       <c r="I1546" s="1"/>
     </row>
     <row r="1547" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1547" s="2"/>
       <c r="I1547" s="1"/>
     </row>
     <row r="1548" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1548" s="2"/>
       <c r="I1548" s="1"/>
     </row>
     <row r="1549" spans="8:9" x14ac:dyDescent="0.3">
@@ -22651,10 +22626,10 @@
       <c r="I1554" s="1"/>
     </row>
     <row r="1555" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1555" s="2"/>
       <c r="I1555" s="1"/>
     </row>
     <row r="1556" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1556" s="2"/>
       <c r="I1556" s="1"/>
     </row>
     <row r="1557" spans="8:9" x14ac:dyDescent="0.3">
@@ -22686,10 +22661,10 @@
       <c r="I1563" s="1"/>
     </row>
     <row r="1564" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1564" s="2"/>
       <c r="I1564" s="1"/>
     </row>
     <row r="1565" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
     </row>
     <row r="1566" spans="8:9" x14ac:dyDescent="0.3">
@@ -22709,10 +22684,10 @@
       <c r="I1569" s="1"/>
     </row>
     <row r="1570" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1570" s="2"/>
       <c r="I1570" s="1"/>
     </row>
     <row r="1571" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1571" s="2"/>
       <c r="I1571" s="1"/>
     </row>
     <row r="1572" spans="8:9" x14ac:dyDescent="0.3">
@@ -22788,13 +22763,13 @@
       <c r="I1589" s="1"/>
     </row>
     <row r="1590" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1590" s="2"/>
       <c r="I1590" s="1"/>
     </row>
     <row r="1591" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1591" s="1"/>
     </row>
     <row r="1592" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
     </row>
     <row r="1593" spans="8:9" x14ac:dyDescent="0.3">
@@ -22814,10 +22789,10 @@
       <c r="I1596" s="1"/>
     </row>
     <row r="1597" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1597" s="2"/>
       <c r="I1597" s="1"/>
     </row>
     <row r="1598" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1598" s="2"/>
       <c r="I1598" s="1"/>
     </row>
     <row r="1599" spans="8:9" x14ac:dyDescent="0.3">
@@ -22825,10 +22800,10 @@
       <c r="I1599" s="1"/>
     </row>
     <row r="1600" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1600" s="2"/>
       <c r="I1600" s="1"/>
     </row>
     <row r="1601" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1601" s="2"/>
       <c r="I1601" s="1"/>
     </row>
     <row r="1602" spans="8:9" x14ac:dyDescent="0.3">
@@ -22840,10 +22815,10 @@
       <c r="I1603" s="1"/>
     </row>
     <row r="1604" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1604" s="2"/>
       <c r="I1604" s="1"/>
     </row>
     <row r="1605" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1605" s="2"/>
       <c r="I1605" s="1"/>
     </row>
     <row r="1606" spans="8:9" x14ac:dyDescent="0.3">
@@ -22851,10 +22826,10 @@
       <c r="I1606" s="1"/>
     </row>
     <row r="1607" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1607" s="2"/>
       <c r="I1607" s="1"/>
     </row>
     <row r="1608" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1608" s="2"/>
       <c r="I1608" s="1"/>
     </row>
     <row r="1609" spans="8:9" x14ac:dyDescent="0.3">
@@ -22870,17 +22845,17 @@
       <c r="I1611" s="1"/>
     </row>
     <row r="1612" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1612" s="2"/>
       <c r="I1612" s="1"/>
     </row>
     <row r="1613" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1613" s="2"/>
       <c r="I1613" s="1"/>
     </row>
     <row r="1614" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1614" s="2"/>
       <c r="I1614" s="1"/>
     </row>
     <row r="1615" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1615" s="2"/>
       <c r="I1615" s="1"/>
     </row>
     <row r="1616" spans="8:9" x14ac:dyDescent="0.3">
@@ -22904,24 +22879,24 @@
       <c r="I1620" s="1"/>
     </row>
     <row r="1621" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1621" s="2"/>
       <c r="I1621" s="1"/>
     </row>
     <row r="1622" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1622" s="2"/>
       <c r="I1622" s="1"/>
     </row>
     <row r="1623" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1623" s="2"/>
       <c r="I1623" s="1"/>
     </row>
     <row r="1624" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
     </row>
     <row r="1625" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1625" s="2"/>
       <c r="I1625" s="1"/>
     </row>
     <row r="1626" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1626" s="2"/>
       <c r="I1626" s="1"/>
     </row>
     <row r="1627" spans="8:9" x14ac:dyDescent="0.3">
@@ -22937,10 +22912,10 @@
       <c r="I1629" s="1"/>
     </row>
     <row r="1630" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1630" s="2"/>
       <c r="I1630" s="1"/>
     </row>
     <row r="1631" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1631" s="2"/>
       <c r="I1631" s="1"/>
     </row>
     <row r="1632" spans="8:9" x14ac:dyDescent="0.3">
@@ -22948,13 +22923,13 @@
       <c r="I1632" s="1"/>
     </row>
     <row r="1633" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1633" s="2"/>
       <c r="I1633" s="1"/>
     </row>
     <row r="1634" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1634" s="1"/>
     </row>
     <row r="1635" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1635" s="2"/>
       <c r="I1635" s="1"/>
     </row>
     <row r="1636" spans="8:9" x14ac:dyDescent="0.3">
@@ -23010,10 +22985,10 @@
       <c r="I1648" s="1"/>
     </row>
     <row r="1649" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1649" s="2"/>
       <c r="I1649" s="1"/>
     </row>
     <row r="1650" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1650" s="2"/>
       <c r="I1650" s="1"/>
     </row>
     <row r="1651" spans="8:9" x14ac:dyDescent="0.3">
@@ -23025,10 +23000,10 @@
       <c r="I1652" s="1"/>
     </row>
     <row r="1653" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1653" s="2"/>
       <c r="I1653" s="1"/>
     </row>
     <row r="1654" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1654" s="2"/>
       <c r="I1654" s="1"/>
     </row>
     <row r="1655" spans="8:9" x14ac:dyDescent="0.3">
@@ -23632,17 +23607,16 @@
       <c r="I1804" s="1"/>
     </row>
     <row r="1805" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1805" s="2"/>
       <c r="I1805" s="1"/>
     </row>
     <row r="1806" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1806" s="1"/>
     </row>
     <row r="1807" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1807" s="2"/>
       <c r="I1807" s="1"/>
     </row>
     <row r="1808" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1808" s="2"/>
       <c r="I1808" s="1"/>
     </row>
     <row r="1809" spans="8:9" x14ac:dyDescent="0.3">
@@ -23652,6 +23626,7 @@
       <c r="I1810" s="1"/>
     </row>
     <row r="1811" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1811" s="2"/>
       <c r="I1811" s="1"/>
     </row>
     <row r="1812" spans="8:9" x14ac:dyDescent="0.3">
@@ -23659,20 +23634,20 @@
       <c r="I1812" s="1"/>
     </row>
     <row r="1813" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1813" s="2"/>
       <c r="I1813" s="1"/>
     </row>
     <row r="1814" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1814" s="1"/>
     </row>
     <row r="1815" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1815" s="2"/>
       <c r="I1815" s="1"/>
     </row>
     <row r="1816" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1816" s="2"/>
       <c r="I1816" s="1"/>
     </row>
     <row r="1817" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1817" s="2"/>
       <c r="I1817" s="1"/>
     </row>
     <row r="1818" spans="8:9" x14ac:dyDescent="0.3">
@@ -23684,7 +23659,6 @@
       <c r="I1819" s="1"/>
     </row>
     <row r="1820" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1820" s="2"/>
       <c r="I1820" s="1"/>
     </row>
     <row r="1821" spans="8:9" x14ac:dyDescent="0.3">
@@ -23694,10 +23668,10 @@
       <c r="I1822" s="1"/>
     </row>
     <row r="1823" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1823" s="2"/>
       <c r="I1823" s="1"/>
     </row>
     <row r="1824" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1824" s="2"/>
       <c r="I1824" s="1"/>
     </row>
     <row r="1825" spans="8:9" x14ac:dyDescent="0.3">
@@ -23716,6 +23690,7 @@
       <c r="I1829" s="1"/>
     </row>
     <row r="1830" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1830" s="2"/>
       <c r="I1830" s="1"/>
     </row>
     <row r="1831" spans="8:9" x14ac:dyDescent="0.3">
@@ -23723,20 +23698,20 @@
       <c r="I1831" s="1"/>
     </row>
     <row r="1832" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1832" s="2"/>
       <c r="I1832" s="1"/>
     </row>
     <row r="1833" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1833" s="1"/>
     </row>
     <row r="1834" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1834" s="2"/>
       <c r="I1834" s="1"/>
     </row>
     <row r="1835" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1835" s="2"/>
       <c r="I1835" s="1"/>
     </row>
     <row r="1836" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1836" s="2"/>
       <c r="I1836" s="1"/>
     </row>
     <row r="1837" spans="8:9" x14ac:dyDescent="0.3">
@@ -23744,17 +23719,17 @@
       <c r="I1837" s="1"/>
     </row>
     <row r="1838" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1838" s="2"/>
       <c r="I1838" s="1"/>
     </row>
     <row r="1839" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1839" s="2"/>
       <c r="I1839" s="1"/>
     </row>
     <row r="1840" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1840" s="2"/>
       <c r="I1840" s="1"/>
     </row>
     <row r="1841" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1841" s="2"/>
       <c r="I1841" s="1"/>
     </row>
     <row r="1842" spans="8:9" x14ac:dyDescent="0.3">
@@ -23770,13 +23745,13 @@
       <c r="I1844" s="1"/>
     </row>
     <row r="1845" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1845" s="2"/>
       <c r="I1845" s="1"/>
     </row>
     <row r="1846" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1846" s="1"/>
     </row>
     <row r="1847" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1847" s="2"/>
       <c r="I1847" s="1"/>
     </row>
     <row r="1848" spans="8:9" x14ac:dyDescent="0.3">
@@ -23788,24 +23763,23 @@
       <c r="I1849" s="1"/>
     </row>
     <row r="1850" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1850" s="2"/>
       <c r="I1850" s="1"/>
     </row>
     <row r="1851" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1851" s="1"/>
     </row>
     <row r="1852" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1852" s="2"/>
       <c r="I1852" s="1"/>
     </row>
     <row r="1853" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1853" s="2"/>
       <c r="I1853" s="1"/>
     </row>
     <row r="1854" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1854" s="2"/>
       <c r="I1854" s="1"/>
     </row>
     <row r="1855" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1855" s="2"/>
       <c r="I1855" s="1"/>
     </row>
     <row r="1856" spans="8:9" x14ac:dyDescent="0.3">
@@ -23815,6 +23789,7 @@
       <c r="I1857" s="1"/>
     </row>
     <row r="1858" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1858" s="2"/>
       <c r="I1858" s="1"/>
     </row>
     <row r="1859" spans="8:9" x14ac:dyDescent="0.3">
@@ -23822,10 +23797,10 @@
       <c r="I1859" s="1"/>
     </row>
     <row r="1860" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1860" s="2"/>
       <c r="I1860" s="1"/>
     </row>
     <row r="1861" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1861" s="2"/>
       <c r="I1861" s="1"/>
     </row>
     <row r="1862" spans="8:9" x14ac:dyDescent="0.3">
@@ -23841,27 +23816,27 @@
       <c r="I1864" s="1"/>
     </row>
     <row r="1865" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1865" s="2"/>
       <c r="I1865" s="1"/>
     </row>
     <row r="1866" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1866" s="1"/>
     </row>
     <row r="1867" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1867" s="2"/>
       <c r="I1867" s="1"/>
     </row>
     <row r="1868" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1868" s="2"/>
       <c r="I1868" s="1"/>
     </row>
     <row r="1869" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1869" s="2"/>
       <c r="I1869" s="1"/>
     </row>
     <row r="1870" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1870" s="2"/>
       <c r="I1870" s="1"/>
     </row>
     <row r="1871" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1871" s="2"/>
       <c r="I1871" s="1"/>
     </row>
     <row r="1872" spans="8:9" x14ac:dyDescent="0.3">
@@ -23869,7 +23844,6 @@
       <c r="I1872" s="1"/>
     </row>
     <row r="1873" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1873" s="2"/>
       <c r="I1873" s="1"/>
     </row>
     <row r="1874" spans="8:9" x14ac:dyDescent="0.3">
@@ -23879,6 +23853,7 @@
       <c r="I1875" s="1"/>
     </row>
     <row r="1876" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1876" s="2"/>
       <c r="I1876" s="1"/>
     </row>
     <row r="1877" spans="8:9" x14ac:dyDescent="0.3">
@@ -23886,20 +23861,20 @@
       <c r="I1877" s="1"/>
     </row>
     <row r="1878" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1878" s="2"/>
       <c r="I1878" s="1"/>
     </row>
     <row r="1879" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1879" s="2"/>
       <c r="I1879" s="1"/>
     </row>
     <row r="1880" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1880" s="2"/>
       <c r="I1880" s="1"/>
     </row>
     <row r="1881" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1881" s="1"/>
     </row>
     <row r="1882" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1882" s="2"/>
       <c r="I1882" s="1"/>
     </row>
     <row r="1883" spans="8:9" x14ac:dyDescent="0.3">
@@ -23907,7 +23882,6 @@
       <c r="I1883" s="1"/>
     </row>
     <row r="1884" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1884" s="2"/>
       <c r="I1884" s="1"/>
     </row>
     <row r="1885" spans="8:9" x14ac:dyDescent="0.3">
@@ -23917,6 +23891,7 @@
       <c r="I1886" s="1"/>
     </row>
     <row r="1887" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1887" s="2"/>
       <c r="I1887" s="1"/>
     </row>
     <row r="1888" spans="8:9" x14ac:dyDescent="0.3">
@@ -23924,13 +23899,13 @@
       <c r="I1888" s="1"/>
     </row>
     <row r="1889" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1889" s="2"/>
       <c r="I1889" s="1"/>
     </row>
     <row r="1890" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1890" s="1"/>
     </row>
     <row r="1891" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1891" s="2"/>
       <c r="I1891" s="1"/>
     </row>
     <row r="1892" spans="8:9" x14ac:dyDescent="0.3">
@@ -23950,10 +23925,10 @@
       <c r="I1895" s="1"/>
     </row>
     <row r="1896" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1896" s="2"/>
       <c r="I1896" s="1"/>
     </row>
     <row r="1897" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1897" s="2"/>
       <c r="I1897" s="1"/>
     </row>
     <row r="1898" spans="8:9" x14ac:dyDescent="0.3">
@@ -23961,10 +23936,10 @@
       <c r="I1898" s="1"/>
     </row>
     <row r="1899" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1899" s="2"/>
       <c r="I1899" s="1"/>
     </row>
     <row r="1900" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1900" s="2"/>
       <c r="I1900" s="1"/>
     </row>
     <row r="1901" spans="8:9" x14ac:dyDescent="0.3">
@@ -23976,10 +23951,10 @@
       <c r="I1902" s="1"/>
     </row>
     <row r="1903" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1903" s="2"/>
       <c r="I1903" s="1"/>
     </row>
     <row r="1904" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1904" s="2"/>
       <c r="I1904" s="1"/>
     </row>
     <row r="1905" spans="8:9" x14ac:dyDescent="0.3">
@@ -24063,27 +24038,27 @@
       <c r="I1924" s="1"/>
     </row>
     <row r="1925" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1925" s="2"/>
       <c r="I1925" s="1"/>
     </row>
     <row r="1926" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1926" s="2"/>
       <c r="I1926" s="1"/>
     </row>
     <row r="1927" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1927" s="2"/>
       <c r="I1927" s="1"/>
     </row>
     <row r="1928" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1928" s="2"/>
       <c r="I1928" s="1"/>
     </row>
     <row r="1929" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1929" s="2"/>
       <c r="I1929" s="1"/>
     </row>
     <row r="1930" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1930" s="1"/>
     </row>
     <row r="1931" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1931" s="2"/>
       <c r="I1931" s="1"/>
     </row>
     <row r="1932" spans="8:9" x14ac:dyDescent="0.3">
@@ -24091,20 +24066,20 @@
       <c r="I1932" s="1"/>
     </row>
     <row r="1933" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1933" s="2"/>
       <c r="I1933" s="1"/>
     </row>
     <row r="1934" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1934" s="2"/>
       <c r="I1934" s="1"/>
     </row>
     <row r="1935" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1935" s="2"/>
       <c r="I1935" s="1"/>
     </row>
     <row r="1936" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1936" s="1"/>
     </row>
     <row r="1937" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
     </row>
     <row r="1938" spans="8:9" x14ac:dyDescent="0.3">
@@ -24112,7 +24087,6 @@
       <c r="I1938" s="1"/>
     </row>
     <row r="1939" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1939" s="2"/>
       <c r="I1939" s="1"/>
     </row>
     <row r="1940" spans="8:9" x14ac:dyDescent="0.3">
@@ -24125,13 +24099,14 @@
       <c r="I1942" s="1"/>
     </row>
     <row r="1943" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
     </row>
     <row r="1944" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1944" s="2"/>
       <c r="I1944" s="1"/>
     </row>
     <row r="1945" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1945" s="2"/>
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:9" x14ac:dyDescent="0.3">
@@ -24143,21 +24118,20 @@
       <c r="I1947" s="1"/>
     </row>
     <row r="1948" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1948" s="2"/>
       <c r="I1948" s="1"/>
     </row>
     <row r="1949" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1949" s="2"/>
       <c r="I1949" s="1"/>
     </row>
     <row r="1950" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1950" s="2"/>
       <c r="I1950" s="1"/>
     </row>
     <row r="1951" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1951" s="2"/>
       <c r="I1951" s="1"/>
     </row>
     <row r="1952" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1952" s="2"/>
       <c r="I1952" s="1"/>
     </row>
     <row r="1953" spans="8:9" x14ac:dyDescent="0.3">
@@ -24167,6 +24141,7 @@
       <c r="I1954" s="1"/>
     </row>
     <row r="1955" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
     </row>
     <row r="1956" spans="8:9" x14ac:dyDescent="0.3">
@@ -24186,7 +24161,6 @@
       <c r="I1959" s="1"/>
     </row>
     <row r="1960" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1960" s="2"/>
       <c r="I1960" s="1"/>
     </row>
     <row r="1961" spans="8:9" x14ac:dyDescent="0.3">
@@ -24196,6 +24170,7 @@
       <c r="I1962" s="1"/>
     </row>
     <row r="1963" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1963" s="2"/>
       <c r="I1963" s="1"/>
     </row>
     <row r="1964" spans="8:9" x14ac:dyDescent="0.3">
@@ -24203,13 +24178,13 @@
       <c r="I1964" s="1"/>
     </row>
     <row r="1965" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
     </row>
     <row r="1966" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1966" s="1"/>
     </row>
     <row r="1967" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1967" s="2"/>
       <c r="I1967" s="1"/>
     </row>
     <row r="1968" spans="8:9" x14ac:dyDescent="0.3">
@@ -24225,13 +24200,13 @@
       <c r="I1970" s="1"/>
     </row>
     <row r="1971" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1971" s="2"/>
       <c r="I1971" s="1"/>
     </row>
     <row r="1972" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1972" s="1"/>
     </row>
     <row r="1973" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1973" s="2"/>
       <c r="I1973" s="1"/>
     </row>
     <row r="1974" spans="8:9" x14ac:dyDescent="0.3">
@@ -24239,10 +24214,10 @@
       <c r="I1974" s="1"/>
     </row>
     <row r="1975" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1975" s="2"/>
       <c r="I1975" s="1"/>
     </row>
     <row r="1976" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1976" s="2"/>
       <c r="I1976" s="1"/>
     </row>
     <row r="1977" spans="8:9" x14ac:dyDescent="0.3">
@@ -24250,7 +24225,6 @@
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1978" s="2"/>
       <c r="I1978" s="1"/>
     </row>
     <row r="1979" spans="8:9" x14ac:dyDescent="0.3">
@@ -24263,6 +24237,7 @@
       <c r="I1981" s="1"/>
     </row>
     <row r="1982" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1982" s="2"/>
       <c r="I1982" s="1"/>
     </row>
     <row r="1983" spans="8:9" x14ac:dyDescent="0.3">
@@ -24270,14 +24245,13 @@
       <c r="I1983" s="1"/>
     </row>
     <row r="1984" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
     </row>
     <row r="1985" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1985" s="2"/>
       <c r="I1985" s="1"/>
     </row>
     <row r="1986" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
     </row>
     <row r="1987" spans="8:9" x14ac:dyDescent="0.3">
@@ -24287,6 +24261,7 @@
       <c r="I1988" s="1"/>
     </row>
     <row r="1989" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1989" s="2"/>
       <c r="I1989" s="1"/>
     </row>
     <row r="1990" spans="8:9" x14ac:dyDescent="0.3">
@@ -24294,38 +24269,38 @@
       <c r="I1990" s="1"/>
     </row>
     <row r="1991" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1991" s="2"/>
       <c r="I1991" s="1"/>
     </row>
     <row r="1992" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1992" s="2"/>
       <c r="I1992" s="1"/>
     </row>
     <row r="1993" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1994" s="2"/>
       <c r="I1994" s="1"/>
     </row>
     <row r="1995" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1995" s="2"/>
       <c r="I1995" s="1"/>
     </row>
     <row r="1996" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1996" s="2"/>
       <c r="I1996" s="1"/>
     </row>
     <row r="1997" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1997" s="2"/>
       <c r="I1997" s="1"/>
     </row>
     <row r="1998" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1998" s="2"/>
       <c r="I1998" s="1"/>
     </row>
     <row r="1999" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1999" s="2"/>
       <c r="I1999" s="1"/>
     </row>
     <row r="2000" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
     </row>
     <row r="2001" spans="8:9" x14ac:dyDescent="0.3">
@@ -24337,10 +24312,10 @@
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2003" s="2"/>
       <c r="I2003" s="1"/>
     </row>
     <row r="2004" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2004" s="2"/>
       <c r="I2004" s="1"/>
     </row>
     <row r="2005" spans="8:9" x14ac:dyDescent="0.3">
@@ -24356,21 +24331,20 @@
       <c r="I2007" s="1"/>
     </row>
     <row r="2008" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
     </row>
     <row r="2009" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2009" s="2"/>
       <c r="I2009" s="1"/>
     </row>
     <row r="2010" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2010" s="2"/>
       <c r="I2010" s="1"/>
     </row>
     <row r="2011" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2011" s="2"/>
       <c r="I2011" s="1"/>
     </row>
     <row r="2012" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2012" s="2"/>
       <c r="I2012" s="1"/>
     </row>
     <row r="2013" spans="8:9" x14ac:dyDescent="0.3">
@@ -24380,13 +24354,14 @@
       <c r="I2014" s="1"/>
     </row>
     <row r="2015" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2015" s="2"/>
       <c r="I2015" s="1"/>
     </row>
     <row r="2016" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2016" s="2"/>
       <c r="I2016" s="1"/>
     </row>
     <row r="2017" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2017" s="2"/>
       <c r="I2017" s="1"/>
     </row>
     <row r="2018" spans="8:9" x14ac:dyDescent="0.3">
@@ -24394,10 +24369,10 @@
       <c r="I2018" s="1"/>
     </row>
     <row r="2019" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2019" s="2"/>
       <c r="I2019" s="1"/>
     </row>
     <row r="2020" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2020" s="2"/>
       <c r="I2020" s="1"/>
     </row>
     <row r="2021" spans="8:9" x14ac:dyDescent="0.3">
@@ -24409,27 +24384,27 @@
       <c r="I2022" s="1"/>
     </row>
     <row r="2023" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2023" s="2"/>
       <c r="I2023" s="1"/>
     </row>
     <row r="2024" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2024" s="2"/>
       <c r="I2024" s="1"/>
     </row>
     <row r="2025" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2025" s="2"/>
       <c r="I2025" s="1"/>
     </row>
     <row r="2026" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2026" s="2"/>
       <c r="I2026" s="1"/>
     </row>
     <row r="2027" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2027" s="2"/>
       <c r="I2027" s="1"/>
     </row>
     <row r="2028" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2028" s="1"/>
     </row>
     <row r="2029" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2029" s="2"/>
       <c r="I2029" s="1"/>
     </row>
     <row r="2030" spans="8:9" x14ac:dyDescent="0.3">
@@ -24445,21 +24420,20 @@
       <c r="I2032" s="1"/>
     </row>
     <row r="2033" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2033" s="2"/>
       <c r="I2033" s="1"/>
     </row>
     <row r="2034" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2034" s="2"/>
       <c r="I2034" s="1"/>
     </row>
     <row r="2035" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2035" s="2"/>
       <c r="I2035" s="1"/>
     </row>
     <row r="2036" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2036" s="2"/>
       <c r="I2036" s="1"/>
     </row>
     <row r="2037" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2037" s="2"/>
       <c r="I2037" s="1"/>
     </row>
     <row r="2038" spans="8:9" x14ac:dyDescent="0.3">
@@ -24469,33 +24443,34 @@
       <c r="I2039" s="1"/>
     </row>
     <row r="2040" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2040" s="2"/>
       <c r="I2040" s="1"/>
     </row>
     <row r="2041" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2041" s="2"/>
       <c r="I2041" s="1"/>
     </row>
     <row r="2042" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2042" s="1"/>
     </row>
     <row r="2043" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2043" s="2"/>
       <c r="I2043" s="1"/>
     </row>
     <row r="2044" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2044" s="2"/>
       <c r="I2044" s="1"/>
     </row>
     <row r="2045" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2045" s="1"/>
     </row>
     <row r="2046" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2046" s="2"/>
       <c r="I2046" s="1"/>
     </row>
     <row r="2047" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2047" s="2"/>
       <c r="I2047" s="1"/>
     </row>
     <row r="2048" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2048" s="2"/>
       <c r="I2048" s="1"/>
     </row>
     <row r="2049" spans="8:9" x14ac:dyDescent="0.3">
@@ -24507,20 +24482,20 @@
       <c r="I2050" s="1"/>
     </row>
     <row r="2051" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2051" s="2"/>
       <c r="I2051" s="1"/>
     </row>
     <row r="2052" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2052" s="1"/>
     </row>
     <row r="2053" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2053" s="2"/>
       <c r="I2053" s="1"/>
     </row>
     <row r="2054" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2054" s="2"/>
       <c r="I2054" s="1"/>
     </row>
     <row r="2055" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2055" s="2"/>
       <c r="I2055" s="1"/>
     </row>
     <row r="2056" spans="8:9" x14ac:dyDescent="0.3">
@@ -24528,13 +24503,13 @@
       <c r="I2056" s="1"/>
     </row>
     <row r="2057" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2057" s="2"/>
       <c r="I2057" s="1"/>
     </row>
     <row r="2058" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2058" s="1"/>
     </row>
     <row r="2059" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2059" s="2"/>
       <c r="I2059" s="1"/>
     </row>
     <row r="2060" spans="8:9" x14ac:dyDescent="0.3">
@@ -24542,7 +24517,6 @@
       <c r="I2060" s="1"/>
     </row>
     <row r="2061" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2061" s="2"/>
       <c r="I2061" s="1"/>
     </row>
     <row r="2062" spans="8:9" x14ac:dyDescent="0.3">
@@ -24558,26 +24532,27 @@
       <c r="I2065" s="1"/>
     </row>
     <row r="2066" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2066" s="2"/>
       <c r="I2066" s="1"/>
     </row>
     <row r="2067" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2067" s="2"/>
       <c r="I2067" s="1"/>
     </row>
     <row r="2068" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2068" s="1"/>
     </row>
     <row r="2069" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2069" s="2"/>
       <c r="I2069" s="1"/>
     </row>
     <row r="2070" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2070" s="2"/>
       <c r="I2070" s="1"/>
     </row>
     <row r="2071" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2071" s="1"/>
     </row>
     <row r="2072" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2072" s="2"/>
       <c r="I2072" s="1"/>
     </row>
     <row r="2073" spans="8:9" x14ac:dyDescent="0.3">
@@ -24585,10 +24560,10 @@
       <c r="I2073" s="1"/>
     </row>
     <row r="2074" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2074" s="2"/>
       <c r="I2074" s="1"/>
     </row>
     <row r="2075" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2075" s="2"/>
       <c r="I2075" s="1"/>
     </row>
     <row r="2076" spans="8:9" x14ac:dyDescent="0.3">
@@ -24596,7 +24571,6 @@
       <c r="I2076" s="1"/>
     </row>
     <row r="2077" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2077" s="2"/>
       <c r="I2077" s="1"/>
     </row>
     <row r="2078" spans="8:9" x14ac:dyDescent="0.3">
@@ -24609,6 +24583,7 @@
       <c r="I2080" s="1"/>
     </row>
     <row r="2081" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2081" s="2"/>
       <c r="I2081" s="1"/>
     </row>
     <row r="2082" spans="8:9" x14ac:dyDescent="0.3">
@@ -24624,33 +24599,33 @@
       <c r="I2084" s="1"/>
     </row>
     <row r="2085" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2085" s="2"/>
       <c r="I2085" s="1"/>
     </row>
     <row r="2086" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2086" s="1"/>
     </row>
     <row r="2087" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2087" s="2"/>
       <c r="I2087" s="1"/>
     </row>
     <row r="2088" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2088" s="2"/>
       <c r="I2088" s="1"/>
     </row>
     <row r="2089" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2089" s="1"/>
     </row>
     <row r="2090" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2090" s="2"/>
       <c r="I2090" s="1"/>
     </row>
     <row r="2091" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2091" s="2"/>
       <c r="I2091" s="1"/>
     </row>
     <row r="2092" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2092" s="1"/>
     </row>
     <row r="2093" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2093" s="2"/>
       <c r="I2093" s="1"/>
     </row>
     <row r="2094" spans="8:9" x14ac:dyDescent="0.3">
@@ -24678,10 +24653,10 @@
       <c r="I2099" s="1"/>
     </row>
     <row r="2100" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2100" s="2"/>
       <c r="I2100" s="1"/>
     </row>
     <row r="2101" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2101" s="2"/>
       <c r="I2101" s="1"/>
     </row>
     <row r="2102" spans="8:9" x14ac:dyDescent="0.3">
@@ -24689,23 +24664,23 @@
       <c r="I2102" s="1"/>
     </row>
     <row r="2103" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2103" s="2"/>
       <c r="I2103" s="1"/>
     </row>
     <row r="2104" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2104" s="1"/>
     </row>
     <row r="2105" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2105" s="2"/>
       <c r="I2105" s="1"/>
     </row>
     <row r="2106" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2106" s="2"/>
       <c r="I2106" s="1"/>
     </row>
     <row r="2107" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2107" s="1"/>
     </row>
     <row r="2108" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2108" s="2"/>
       <c r="I2108" s="1"/>
     </row>
     <row r="2109" spans="8:9" x14ac:dyDescent="0.3">
@@ -24725,10 +24700,10 @@
       <c r="I2112" s="1"/>
     </row>
     <row r="2113" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2113" s="2"/>
       <c r="I2113" s="1"/>
     </row>
     <row r="2114" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2114" s="2"/>
       <c r="I2114" s="1"/>
     </row>
     <row r="2115" spans="8:9" x14ac:dyDescent="0.3">
@@ -24744,20 +24719,20 @@
       <c r="I2117" s="1"/>
     </row>
     <row r="2118" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2118" s="2"/>
       <c r="I2118" s="1"/>
     </row>
     <row r="2119" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2119" s="1"/>
     </row>
     <row r="2120" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2120" s="2"/>
       <c r="I2120" s="1"/>
     </row>
     <row r="2121" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2121" s="2"/>
       <c r="I2121" s="1"/>
     </row>
     <row r="2122" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2122" s="2"/>
       <c r="I2122" s="1"/>
     </row>
     <row r="2123" spans="8:9" x14ac:dyDescent="0.3">
@@ -24765,10 +24740,10 @@
       <c r="I2123" s="1"/>
     </row>
     <row r="2124" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2124" s="2"/>
       <c r="I2124" s="1"/>
     </row>
     <row r="2125" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2125" s="2"/>
       <c r="I2125" s="1"/>
     </row>
     <row r="2126" spans="8:9" x14ac:dyDescent="0.3">
@@ -24776,14 +24751,13 @@
       <c r="I2126" s="1"/>
     </row>
     <row r="2127" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2127" s="2"/>
       <c r="I2127" s="1"/>
     </row>
     <row r="2128" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2128" s="2"/>
       <c r="I2128" s="1"/>
     </row>
     <row r="2129" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2129" s="2"/>
       <c r="I2129" s="1"/>
     </row>
     <row r="2130" spans="8:9" x14ac:dyDescent="0.3">
@@ -24793,6 +24767,7 @@
       <c r="I2131" s="1"/>
     </row>
     <row r="2132" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2132" s="2"/>
       <c r="I2132" s="1"/>
     </row>
     <row r="2133" spans="8:9" x14ac:dyDescent="0.3">
@@ -24820,7 +24795,6 @@
       <c r="I2138" s="1"/>
     </row>
     <row r="2139" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2139" s="2"/>
       <c r="I2139" s="1"/>
     </row>
     <row r="2140" spans="8:9" x14ac:dyDescent="0.3">
@@ -24830,27 +24804,28 @@
       <c r="I2141" s="1"/>
     </row>
     <row r="2142" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2142" s="2"/>
       <c r="I2142" s="1"/>
     </row>
     <row r="2143" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2143" s="2"/>
       <c r="I2143" s="1"/>
     </row>
     <row r="2144" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2144" s="2"/>
       <c r="I2144" s="1"/>
     </row>
     <row r="2145" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2145" s="2"/>
       <c r="I2145" s="1"/>
     </row>
     <row r="2146" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2146" s="2"/>
       <c r="I2146" s="1"/>
     </row>
     <row r="2147" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2147" s="2"/>
       <c r="I2147" s="1"/>
     </row>
     <row r="2148" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2148" s="2"/>
       <c r="I2148" s="1"/>
     </row>
     <row r="2149" spans="8:9" x14ac:dyDescent="0.3">
@@ -24862,7 +24837,6 @@
       <c r="I2150" s="1"/>
     </row>
     <row r="2151" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2151" s="2"/>
       <c r="I2151" s="1"/>
     </row>
     <row r="2152" spans="8:9" x14ac:dyDescent="0.3">
@@ -24878,27 +24852,28 @@
       <c r="I2155" s="1"/>
     </row>
     <row r="2156" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2156" s="2"/>
       <c r="I2156" s="1"/>
     </row>
     <row r="2157" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2157" s="2"/>
       <c r="I2157" s="1"/>
     </row>
     <row r="2158" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2158" s="2"/>
       <c r="I2158" s="1"/>
     </row>
     <row r="2159" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2159" s="2"/>
       <c r="I2159" s="1"/>
     </row>
     <row r="2160" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2160" s="2"/>
       <c r="I2160" s="1"/>
     </row>
     <row r="2161" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2161" s="2"/>
       <c r="I2161" s="1"/>
     </row>
     <row r="2162" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2162" s="2"/>
       <c r="I2162" s="1"/>
     </row>
     <row r="2163" spans="8:9" x14ac:dyDescent="0.3">
@@ -24906,10 +24881,10 @@
       <c r="I2163" s="1"/>
     </row>
     <row r="2164" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2164" s="2"/>
       <c r="I2164" s="1"/>
     </row>
     <row r="2165" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2165" s="2"/>
       <c r="I2165" s="1"/>
     </row>
     <row r="2166" spans="8:9" x14ac:dyDescent="0.3">
@@ -24933,10 +24908,10 @@
       <c r="I2170" s="1"/>
     </row>
     <row r="2171" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2171" s="2"/>
       <c r="I2171" s="1"/>
     </row>
     <row r="2172" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2172" s="2"/>
       <c r="I2172" s="1"/>
     </row>
     <row r="2173" spans="8:9" x14ac:dyDescent="0.3">
@@ -24948,10 +24923,10 @@
       <c r="I2174" s="1"/>
     </row>
     <row r="2175" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2175" s="2"/>
       <c r="I2175" s="1"/>
     </row>
     <row r="2176" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2176" s="2"/>
       <c r="I2176" s="1"/>
     </row>
     <row r="2177" spans="8:9" x14ac:dyDescent="0.3">
@@ -24987,10 +24962,10 @@
       <c r="I2184" s="1"/>
     </row>
     <row r="2185" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2185" s="2"/>
       <c r="I2185" s="1"/>
     </row>
     <row r="2186" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2186" s="2"/>
       <c r="I2186" s="1"/>
     </row>
     <row r="2187" spans="8:9" x14ac:dyDescent="0.3">
@@ -25038,10 +25013,10 @@
       <c r="I2197" s="1"/>
     </row>
     <row r="2198" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2198" s="2"/>
       <c r="I2198" s="1"/>
     </row>
     <row r="2199" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2199" s="2"/>
       <c r="I2199" s="1"/>
     </row>
     <row r="2200" spans="8:9" x14ac:dyDescent="0.3">
@@ -25097,10 +25072,10 @@
       <c r="I2212" s="1"/>
     </row>
     <row r="2213" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2213" s="2"/>
       <c r="I2213" s="1"/>
     </row>
     <row r="2214" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2214" s="2"/>
       <c r="I2214" s="1"/>
     </row>
     <row r="2215" spans="8:9" x14ac:dyDescent="0.3">
@@ -25112,10 +25087,10 @@
       <c r="I2216" s="1"/>
     </row>
     <row r="2217" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2217" s="2"/>
       <c r="I2217" s="1"/>
     </row>
     <row r="2218" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2218" s="2"/>
       <c r="I2218" s="1"/>
     </row>
     <row r="2219" spans="8:9" x14ac:dyDescent="0.3">
@@ -25159,10 +25134,10 @@
       <c r="I2228" s="1"/>
     </row>
     <row r="2229" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2229" s="2"/>
       <c r="I2229" s="1"/>
     </row>
     <row r="2230" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2230" s="2"/>
       <c r="I2230" s="1"/>
     </row>
     <row r="2231" spans="8:9" x14ac:dyDescent="0.3">
@@ -25194,10 +25169,10 @@
       <c r="I2237" s="1"/>
     </row>
     <row r="2238" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2238" s="2"/>
       <c r="I2238" s="1"/>
     </row>
     <row r="2239" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2239" s="2"/>
       <c r="I2239" s="1"/>
     </row>
     <row r="2240" spans="8:9" x14ac:dyDescent="0.3">
@@ -25205,10 +25180,10 @@
       <c r="I2240" s="1"/>
     </row>
     <row r="2241" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2241" s="2"/>
       <c r="I2241" s="1"/>
     </row>
     <row r="2242" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2242" s="2"/>
       <c r="I2242" s="1"/>
     </row>
     <row r="2243" spans="8:9" x14ac:dyDescent="0.3">
@@ -25240,10 +25215,10 @@
       <c r="I2249" s="1"/>
     </row>
     <row r="2250" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2250" s="2"/>
       <c r="I2250" s="1"/>
     </row>
     <row r="2251" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2251" s="2"/>
       <c r="I2251" s="1"/>
     </row>
     <row r="2252" spans="8:9" x14ac:dyDescent="0.3">
@@ -25263,10 +25238,10 @@
       <c r="I2255" s="1"/>
     </row>
     <row r="2256" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2256" s="2"/>
       <c r="I2256" s="1"/>
     </row>
     <row r="2257" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2257" s="2"/>
       <c r="I2257" s="1"/>
     </row>
     <row r="2258" spans="8:9" x14ac:dyDescent="0.3">
@@ -25362,10 +25337,10 @@
       <c r="I2280" s="1"/>
     </row>
     <row r="2281" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2281" s="2"/>
       <c r="I2281" s="1"/>
     </row>
     <row r="2282" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2282" s="2"/>
       <c r="I2282" s="1"/>
     </row>
     <row r="2283" spans="8:9" x14ac:dyDescent="0.3">
@@ -25377,10 +25352,10 @@
       <c r="I2284" s="1"/>
     </row>
     <row r="2285" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2285" s="2"/>
       <c r="I2285" s="1"/>
     </row>
     <row r="2286" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2286" s="2"/>
       <c r="I2286" s="1"/>
     </row>
     <row r="2287" spans="8:9" x14ac:dyDescent="0.3">
@@ -25448,10 +25423,10 @@
       <c r="I2302" s="1"/>
     </row>
     <row r="2303" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2303" s="2"/>
       <c r="I2303" s="1"/>
     </row>
     <row r="2304" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2304" s="2"/>
       <c r="I2304" s="1"/>
     </row>
     <row r="2305" spans="8:9" x14ac:dyDescent="0.3">
@@ -25495,10 +25470,10 @@
       <c r="I2314" s="1"/>
     </row>
     <row r="2315" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2315" s="2"/>
       <c r="I2315" s="1"/>
     </row>
     <row r="2316" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2316" s="2"/>
       <c r="I2316" s="1"/>
     </row>
     <row r="2317" spans="8:9" x14ac:dyDescent="0.3">
@@ -25594,17 +25569,17 @@
       <c r="I2339" s="1"/>
     </row>
     <row r="2340" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2340" s="2"/>
       <c r="I2340" s="1"/>
     </row>
     <row r="2341" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2341" s="2"/>
       <c r="I2341" s="1"/>
     </row>
     <row r="2342" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2342" s="2"/>
       <c r="I2342" s="1"/>
     </row>
     <row r="2343" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2343" s="2"/>
       <c r="I2343" s="1"/>
     </row>
     <row r="2344" spans="8:9" x14ac:dyDescent="0.3">
@@ -25668,10 +25643,10 @@
       <c r="I2358" s="1"/>
     </row>
     <row r="2359" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2359" s="2"/>
       <c r="I2359" s="1"/>
     </row>
     <row r="2360" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2360" s="2"/>
       <c r="I2360" s="1"/>
     </row>
     <row r="2361" spans="8:9" x14ac:dyDescent="0.3">
@@ -25743,10 +25718,10 @@
       <c r="I2377" s="1"/>
     </row>
     <row r="2378" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2378" s="2"/>
       <c r="I2378" s="1"/>
     </row>
     <row r="2379" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2379" s="2"/>
       <c r="I2379" s="1"/>
     </row>
     <row r="2380" spans="8:9" x14ac:dyDescent="0.3">
@@ -25798,10 +25773,10 @@
       <c r="I2391" s="1"/>
     </row>
     <row r="2392" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2392" s="2"/>
       <c r="I2392" s="1"/>
     </row>
     <row r="2393" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2393" s="2"/>
       <c r="I2393" s="1"/>
     </row>
     <row r="2394" spans="8:9" x14ac:dyDescent="0.3">
@@ -25849,10 +25824,10 @@
       <c r="I2404" s="1"/>
     </row>
     <row r="2405" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2405" s="2"/>
       <c r="I2405" s="1"/>
     </row>
     <row r="2406" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2406" s="2"/>
       <c r="I2406" s="1"/>
     </row>
     <row r="2407" spans="8:9" x14ac:dyDescent="0.3">
@@ -25868,10 +25843,10 @@
       <c r="I2409" s="1"/>
     </row>
     <row r="2410" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2410" s="2"/>
       <c r="I2410" s="1"/>
     </row>
     <row r="2411" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2411" s="2"/>
       <c r="I2411" s="1"/>
     </row>
     <row r="2412" spans="8:9" x14ac:dyDescent="0.3">
@@ -25879,10 +25854,10 @@
       <c r="I2412" s="1"/>
     </row>
     <row r="2413" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2413" s="2"/>
       <c r="I2413" s="1"/>
     </row>
     <row r="2414" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2414" s="2"/>
       <c r="I2414" s="1"/>
     </row>
     <row r="2415" spans="8:9" x14ac:dyDescent="0.3">
@@ -25890,10 +25865,10 @@
       <c r="I2415" s="1"/>
     </row>
     <row r="2416" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2416" s="2"/>
       <c r="I2416" s="1"/>
     </row>
     <row r="2417" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2417" s="2"/>
       <c r="I2417" s="1"/>
     </row>
     <row r="2418" spans="8:9" x14ac:dyDescent="0.3">
@@ -25905,10 +25880,10 @@
       <c r="I2419" s="1"/>
     </row>
     <row r="2420" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2420" s="2"/>
       <c r="I2420" s="1"/>
     </row>
     <row r="2421" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2421" s="2"/>
       <c r="I2421" s="1"/>
     </row>
     <row r="2422" spans="8:9" x14ac:dyDescent="0.3">
@@ -25920,10 +25895,10 @@
       <c r="I2423" s="1"/>
     </row>
     <row r="2424" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2424" s="2"/>
       <c r="I2424" s="1"/>
     </row>
     <row r="2425" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2425" s="2"/>
       <c r="I2425" s="1"/>
     </row>
     <row r="2426" spans="8:9" x14ac:dyDescent="0.3">
@@ -25931,10 +25906,10 @@
       <c r="I2426" s="1"/>
     </row>
     <row r="2427" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2427" s="2"/>
       <c r="I2427" s="1"/>
     </row>
     <row r="2428" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2428" s="2"/>
       <c r="I2428" s="1"/>
     </row>
     <row r="2429" spans="8:9" x14ac:dyDescent="0.3">
@@ -25966,7 +25941,6 @@
       <c r="I2435" s="1"/>
     </row>
     <row r="2436" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2436" s="2"/>
       <c r="I2436" s="1"/>
     </row>
     <row r="2437" spans="8:9" x14ac:dyDescent="0.3">
@@ -25976,6 +25950,7 @@
       <c r="I2438" s="1"/>
     </row>
     <row r="2439" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2439" s="2"/>
       <c r="I2439" s="1"/>
     </row>
     <row r="2440" spans="8:9" x14ac:dyDescent="0.3">
@@ -26051,10 +26026,10 @@
       <c r="I2457" s="1"/>
     </row>
     <row r="2458" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2458" s="2"/>
       <c r="I2458" s="1"/>
     </row>
     <row r="2459" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2459" s="2"/>
       <c r="I2459" s="1"/>
     </row>
     <row r="2460" spans="8:9" x14ac:dyDescent="0.3">
@@ -26102,10 +26077,10 @@
       <c r="I2470" s="1"/>
     </row>
     <row r="2471" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2471" s="2"/>
       <c r="I2471" s="1"/>
     </row>
     <row r="2472" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2472" s="2"/>
       <c r="I2472" s="1"/>
     </row>
     <row r="2473" spans="8:9" x14ac:dyDescent="0.3">
@@ -26145,10 +26120,10 @@
       <c r="I2481" s="1"/>
     </row>
     <row r="2482" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2482" s="2"/>
       <c r="I2482" s="1"/>
     </row>
     <row r="2483" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2483" s="2"/>
       <c r="I2483" s="1"/>
     </row>
     <row r="2484" spans="8:9" x14ac:dyDescent="0.3">
@@ -26164,10 +26139,10 @@
       <c r="I2486" s="1"/>
     </row>
     <row r="2487" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2487" s="2"/>
       <c r="I2487" s="1"/>
     </row>
     <row r="2488" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2488" s="2"/>
       <c r="I2488" s="1"/>
     </row>
     <row r="2489" spans="8:9" x14ac:dyDescent="0.3">
@@ -26187,13 +26162,13 @@
       <c r="I2492" s="1"/>
     </row>
     <row r="2493" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2493" s="2"/>
       <c r="I2493" s="1"/>
     </row>
     <row r="2494" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2494" s="1"/>
     </row>
     <row r="2495" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2495" s="2"/>
       <c r="I2495" s="1"/>
     </row>
     <row r="2496" spans="8:9" x14ac:dyDescent="0.3">
@@ -26249,10 +26224,10 @@
       <c r="I2508" s="1"/>
     </row>
     <row r="2509" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2509" s="2"/>
       <c r="I2509" s="1"/>
     </row>
     <row r="2510" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2510" s="2"/>
       <c r="I2510" s="1"/>
     </row>
     <row r="2511" spans="8:9" x14ac:dyDescent="0.3">
@@ -26308,10 +26283,10 @@
       <c r="I2523" s="1"/>
     </row>
     <row r="2524" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2524" s="2"/>
       <c r="I2524" s="1"/>
     </row>
     <row r="2525" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2525" s="2"/>
       <c r="I2525" s="1"/>
     </row>
     <row r="2526" spans="8:9" x14ac:dyDescent="0.3">
@@ -26359,10 +26334,10 @@
       <c r="I2536" s="1"/>
     </row>
     <row r="2537" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2537" s="2"/>
       <c r="I2537" s="1"/>
     </row>
     <row r="2538" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2538" s="2"/>
       <c r="I2538" s="1"/>
     </row>
     <row r="2539" spans="8:9" x14ac:dyDescent="0.3">
@@ -26370,10 +26345,10 @@
       <c r="I2539" s="1"/>
     </row>
     <row r="2540" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2540" s="2"/>
       <c r="I2540" s="1"/>
     </row>
     <row r="2541" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2541" s="2"/>
       <c r="I2541" s="1"/>
     </row>
     <row r="2542" spans="8:9" x14ac:dyDescent="0.3">
@@ -26425,10 +26400,10 @@
       <c r="I2553" s="1"/>
     </row>
     <row r="2554" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2554" s="2"/>
       <c r="I2554" s="1"/>
     </row>
     <row r="2555" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2555" s="2"/>
       <c r="I2555" s="1"/>
     </row>
     <row r="2556" spans="8:9" x14ac:dyDescent="0.3">
@@ -26444,10 +26419,10 @@
       <c r="I2558" s="1"/>
     </row>
     <row r="2559" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2559" s="2"/>
       <c r="I2559" s="1"/>
     </row>
     <row r="2560" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2560" s="2"/>
       <c r="I2560" s="1"/>
     </row>
     <row r="2561" spans="8:9" x14ac:dyDescent="0.3">
@@ -26459,10 +26434,10 @@
       <c r="I2562" s="1"/>
     </row>
     <row r="2563" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2563" s="2"/>
       <c r="I2563" s="1"/>
     </row>
     <row r="2564" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2564" s="2"/>
       <c r="I2564" s="1"/>
     </row>
     <row r="2565" spans="8:9" x14ac:dyDescent="0.3">
@@ -26510,10 +26485,10 @@
       <c r="I2575" s="1"/>
     </row>
     <row r="2576" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2576" s="2"/>
       <c r="I2576" s="1"/>
     </row>
     <row r="2577" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2577" s="2"/>
       <c r="I2577" s="1"/>
     </row>
     <row r="2578" spans="8:9" x14ac:dyDescent="0.3">
@@ -26561,17 +26536,17 @@
       <c r="I2588" s="1"/>
     </row>
     <row r="2589" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2589" s="2"/>
       <c r="I2589" s="1"/>
     </row>
     <row r="2590" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2590" s="2"/>
       <c r="I2590" s="1"/>
     </row>
     <row r="2591" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2591" s="2"/>
       <c r="I2591" s="1"/>
     </row>
     <row r="2592" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2592" s="2"/>
       <c r="I2592" s="1"/>
     </row>
     <row r="2593" spans="8:9" x14ac:dyDescent="0.3">
@@ -26595,10 +26570,10 @@
       <c r="I2597" s="1"/>
     </row>
     <row r="2598" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2598" s="2"/>
       <c r="I2598" s="1"/>
     </row>
     <row r="2599" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2599" s="2"/>
       <c r="I2599" s="1"/>
     </row>
     <row r="2600" spans="8:9" x14ac:dyDescent="0.3">
@@ -26634,10 +26609,10 @@
       <c r="I2607" s="1"/>
     </row>
     <row r="2608" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2608" s="2"/>
       <c r="I2608" s="1"/>
     </row>
     <row r="2609" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2609" s="2"/>
       <c r="I2609" s="1"/>
     </row>
     <row r="2610" spans="8:9" x14ac:dyDescent="0.3">
@@ -26713,10 +26688,10 @@
       <c r="I2627" s="1"/>
     </row>
     <row r="2628" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2628" s="2"/>
       <c r="I2628" s="1"/>
     </row>
     <row r="2629" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2629" s="2"/>
       <c r="I2629" s="1"/>
     </row>
     <row r="2630" spans="8:9" x14ac:dyDescent="0.3">
@@ -26724,10 +26699,10 @@
       <c r="I2630" s="1"/>
     </row>
     <row r="2631" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2631" s="2"/>
       <c r="I2631" s="1"/>
     </row>
     <row r="2632" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2632" s="2"/>
       <c r="I2632" s="1"/>
     </row>
     <row r="2633" spans="8:9" x14ac:dyDescent="0.3">
@@ -26759,10 +26734,10 @@
       <c r="I2639" s="1"/>
     </row>
     <row r="2640" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2640" s="2"/>
       <c r="I2640" s="1"/>
     </row>
     <row r="2641" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2641" s="2"/>
       <c r="I2641" s="1"/>
     </row>
     <row r="2642" spans="8:9" x14ac:dyDescent="0.3">
@@ -26794,17 +26769,17 @@
       <c r="I2648" s="1"/>
     </row>
     <row r="2649" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2649" s="2"/>
       <c r="I2649" s="1"/>
     </row>
     <row r="2650" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2650" s="2"/>
       <c r="I2650" s="1"/>
     </row>
     <row r="2651" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2651" s="2"/>
       <c r="I2651" s="1"/>
     </row>
     <row r="2652" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2652" s="2"/>
       <c r="I2652" s="1"/>
     </row>
     <row r="2653" spans="8:9" x14ac:dyDescent="0.3">
@@ -26828,10 +26803,10 @@
       <c r="I2657" s="1"/>
     </row>
     <row r="2658" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2658" s="2"/>
       <c r="I2658" s="1"/>
     </row>
     <row r="2659" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2659" s="2"/>
       <c r="I2659" s="1"/>
     </row>
     <row r="2660" spans="8:9" x14ac:dyDescent="0.3">
@@ -26839,10 +26814,10 @@
       <c r="I2660" s="1"/>
     </row>
     <row r="2661" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2661" s="2"/>
       <c r="I2661" s="1"/>
     </row>
     <row r="2662" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2662" s="2"/>
       <c r="I2662" s="1"/>
     </row>
     <row r="2663" spans="8:9" x14ac:dyDescent="0.3">
@@ -26870,13 +26845,13 @@
       <c r="I2668" s="1"/>
     </row>
     <row r="2669" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2669" s="2"/>
       <c r="I2669" s="1"/>
     </row>
     <row r="2670" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2670" s="1"/>
     </row>
     <row r="2671" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2671" s="2"/>
       <c r="I2671" s="1"/>
     </row>
     <row r="2672" spans="8:9" x14ac:dyDescent="0.3">
@@ -26920,10 +26895,10 @@
       <c r="I2681" s="1"/>
     </row>
     <row r="2682" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2682" s="2"/>
       <c r="I2682" s="1"/>
     </row>
     <row r="2683" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2683" s="2"/>
       <c r="I2683" s="1"/>
     </row>
     <row r="2684" spans="8:9" x14ac:dyDescent="0.3">
@@ -26943,10 +26918,10 @@
       <c r="I2687" s="1"/>
     </row>
     <row r="2688" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2688" s="2"/>
       <c r="I2688" s="1"/>
     </row>
     <row r="2689" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2689" s="2"/>
       <c r="I2689" s="1"/>
     </row>
     <row r="2690" spans="8:9" x14ac:dyDescent="0.3">
@@ -27010,10 +26985,10 @@
       <c r="I2704" s="1"/>
     </row>
     <row r="2705" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2705" s="2"/>
       <c r="I2705" s="1"/>
     </row>
     <row r="2706" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2706" s="2"/>
       <c r="I2706" s="1"/>
     </row>
     <row r="2707" spans="8:9" x14ac:dyDescent="0.3">
@@ -27045,10 +27020,10 @@
       <c r="I2713" s="1"/>
     </row>
     <row r="2714" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2714" s="2"/>
       <c r="I2714" s="1"/>
     </row>
     <row r="2715" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2715" s="2"/>
       <c r="I2715" s="1"/>
     </row>
     <row r="2716" spans="8:9" x14ac:dyDescent="0.3">
@@ -27092,10 +27067,10 @@
       <c r="I2725" s="1"/>
     </row>
     <row r="2726" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2726" s="2"/>
       <c r="I2726" s="1"/>
     </row>
     <row r="2727" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2727" s="2"/>
       <c r="I2727" s="1"/>
     </row>
     <row r="2728" spans="8:9" x14ac:dyDescent="0.3">
@@ -27167,10 +27142,10 @@
       <c r="I2744" s="1"/>
     </row>
     <row r="2745" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2745" s="2"/>
       <c r="I2745" s="1"/>
     </row>
     <row r="2746" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2746" s="2"/>
       <c r="I2746" s="1"/>
     </row>
     <row r="2747" spans="8:9" x14ac:dyDescent="0.3">
@@ -27186,10 +27161,10 @@
       <c r="I2749" s="1"/>
     </row>
     <row r="2750" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2750" s="2"/>
       <c r="I2750" s="1"/>
     </row>
     <row r="2751" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2751" s="2"/>
       <c r="I2751" s="1"/>
     </row>
     <row r="2752" spans="8:9" x14ac:dyDescent="0.3">
@@ -27305,10 +27280,10 @@
       <c r="I2779" s="1"/>
     </row>
     <row r="2780" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2780" s="2"/>
       <c r="I2780" s="1"/>
     </row>
     <row r="2781" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2781" s="2"/>
       <c r="I2781" s="1"/>
     </row>
     <row r="2782" spans="8:9" x14ac:dyDescent="0.3">
@@ -27368,13 +27343,13 @@
       <c r="I2795" s="1"/>
     </row>
     <row r="2796" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2796" s="2"/>
       <c r="I2796" s="1"/>
     </row>
     <row r="2797" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2797" s="1"/>
     </row>
     <row r="2798" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2798" s="2"/>
       <c r="I2798" s="1"/>
     </row>
     <row r="2799" spans="8:9" x14ac:dyDescent="0.3">
@@ -27402,13 +27377,13 @@
       <c r="I2804" s="1"/>
     </row>
     <row r="2805" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2805" s="2"/>
       <c r="I2805" s="1"/>
     </row>
     <row r="2806" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2806" s="1"/>
     </row>
     <row r="2807" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2807" s="2"/>
       <c r="I2807" s="1"/>
     </row>
     <row r="2808" spans="8:9" x14ac:dyDescent="0.3">
@@ -27508,10 +27483,10 @@
       <c r="I2831" s="1"/>
     </row>
     <row r="2832" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2832" s="2"/>
       <c r="I2832" s="1"/>
     </row>
     <row r="2833" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2833" s="2"/>
       <c r="I2833" s="1"/>
     </row>
     <row r="2834" spans="8:9" x14ac:dyDescent="0.3">
@@ -27535,10 +27510,10 @@
       <c r="I2838" s="1"/>
     </row>
     <row r="2839" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2839" s="2"/>
       <c r="I2839" s="1"/>
     </row>
     <row r="2840" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2840" s="2"/>
       <c r="I2840" s="1"/>
     </row>
     <row r="2841" spans="8:9" x14ac:dyDescent="0.3">
@@ -27706,10 +27681,10 @@
       <c r="I2881" s="1"/>
     </row>
     <row r="2882" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2882" s="2"/>
       <c r="I2882" s="1"/>
     </row>
     <row r="2883" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2883" s="2"/>
       <c r="I2883" s="1"/>
     </row>
     <row r="2884" spans="8:9" x14ac:dyDescent="0.3">
@@ -27741,20 +27716,20 @@
       <c r="I2890" s="1"/>
     </row>
     <row r="2891" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2891" s="2"/>
       <c r="I2891" s="1"/>
     </row>
     <row r="2892" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2892" s="2"/>
       <c r="I2892" s="1"/>
     </row>
     <row r="2893" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2893" s="2"/>
       <c r="I2893" s="1"/>
     </row>
     <row r="2894" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2894" s="1"/>
     </row>
     <row r="2895" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2895" s="2"/>
       <c r="I2895" s="1"/>
     </row>
     <row r="2896" spans="8:9" x14ac:dyDescent="0.3">
@@ -27782,10 +27757,10 @@
       <c r="I2901" s="1"/>
     </row>
     <row r="2902" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2902" s="2"/>
       <c r="I2902" s="1"/>
     </row>
     <row r="2903" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2903" s="2"/>
       <c r="I2903" s="1"/>
     </row>
     <row r="2904" spans="8:9" x14ac:dyDescent="0.3">
@@ -27797,10 +27772,10 @@
       <c r="I2905" s="1"/>
     </row>
     <row r="2906" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2906" s="2"/>
       <c r="I2906" s="1"/>
     </row>
     <row r="2907" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2907" s="2"/>
       <c r="I2907" s="1"/>
     </row>
     <row r="2908" spans="8:9" x14ac:dyDescent="0.3">
@@ -27836,10 +27811,10 @@
       <c r="I2915" s="1"/>
     </row>
     <row r="2916" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2916" s="2"/>
       <c r="I2916" s="1"/>
     </row>
     <row r="2917" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2917" s="2"/>
       <c r="I2917" s="1"/>
     </row>
     <row r="2918" spans="8:9" x14ac:dyDescent="0.3">
@@ -27847,10 +27822,10 @@
       <c r="I2918" s="1"/>
     </row>
     <row r="2919" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2919" s="2"/>
       <c r="I2919" s="1"/>
     </row>
     <row r="2920" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2920" s="2"/>
       <c r="I2920" s="1"/>
     </row>
     <row r="2921" spans="8:9" x14ac:dyDescent="0.3">
@@ -27990,10 +27965,10 @@
       <c r="I2954" s="1"/>
     </row>
     <row r="2955" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2955" s="2"/>
       <c r="I2955" s="1"/>
     </row>
     <row r="2956" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2956" s="2"/>
       <c r="I2956" s="1"/>
     </row>
     <row r="2957" spans="8:9" x14ac:dyDescent="0.3">
@@ -28073,10 +28048,10 @@
       <c r="I2975" s="1"/>
     </row>
     <row r="2976" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2976" s="2"/>
       <c r="I2976" s="1"/>
     </row>
     <row r="2977" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2977" s="2"/>
       <c r="I2977" s="1"/>
     </row>
     <row r="2978" spans="8:9" x14ac:dyDescent="0.3">
@@ -28124,10 +28099,10 @@
       <c r="I2988" s="1"/>
     </row>
     <row r="2989" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2989" s="2"/>
       <c r="I2989" s="1"/>
     </row>
     <row r="2990" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2990" s="2"/>
       <c r="I2990" s="1"/>
     </row>
     <row r="2991" spans="8:9" x14ac:dyDescent="0.3">
@@ -28283,10 +28258,10 @@
       <c r="I3028" s="1"/>
     </row>
     <row r="3029" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3029" s="2"/>
       <c r="I3029" s="1"/>
     </row>
     <row r="3030" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3030" s="2"/>
       <c r="I3030" s="1"/>
     </row>
     <row r="3031" spans="8:9" x14ac:dyDescent="0.3">
@@ -28342,10 +28317,10 @@
       <c r="I3043" s="1"/>
     </row>
     <row r="3044" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3044" s="2"/>
       <c r="I3044" s="1"/>
     </row>
     <row r="3045" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3045" s="2"/>
       <c r="I3045" s="1"/>
     </row>
     <row r="3046" spans="8:9" x14ac:dyDescent="0.3">
@@ -28485,10 +28460,10 @@
       <c r="I3079" s="1"/>
     </row>
     <row r="3080" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3080" s="2"/>
       <c r="I3080" s="1"/>
     </row>
     <row r="3081" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3081" s="2"/>
       <c r="I3081" s="1"/>
     </row>
     <row r="3082" spans="8:9" x14ac:dyDescent="0.3">
@@ -28604,10 +28579,10 @@
       <c r="I3109" s="1"/>
     </row>
     <row r="3110" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3110" s="2"/>
       <c r="I3110" s="1"/>
     </row>
     <row r="3111" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3111" s="2"/>
       <c r="I3111" s="1"/>
     </row>
     <row r="3112" spans="8:9" x14ac:dyDescent="0.3">
@@ -28735,10 +28710,10 @@
       <c r="I3142" s="1"/>
     </row>
     <row r="3143" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3143" s="2"/>
       <c r="I3143" s="1"/>
     </row>
     <row r="3144" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3144" s="2"/>
       <c r="I3144" s="1"/>
     </row>
     <row r="3145" spans="8:9" x14ac:dyDescent="0.3">
@@ -28754,10 +28729,10 @@
       <c r="I3147" s="1"/>
     </row>
     <row r="3148" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3148" s="2"/>
       <c r="I3148" s="1"/>
     </row>
     <row r="3149" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3149" s="2"/>
       <c r="I3149" s="1"/>
     </row>
     <row r="3150" spans="8:9" x14ac:dyDescent="0.3">
@@ -28765,10 +28740,10 @@
       <c r="I3150" s="1"/>
     </row>
     <row r="3151" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3151" s="2"/>
       <c r="I3151" s="1"/>
     </row>
     <row r="3152" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3152" s="2"/>
       <c r="I3152" s="1"/>
     </row>
     <row r="3153" spans="8:9" x14ac:dyDescent="0.3">
@@ -28788,10 +28763,10 @@
       <c r="I3156" s="1"/>
     </row>
     <row r="3157" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3157" s="2"/>
       <c r="I3157" s="1"/>
     </row>
     <row r="3158" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3158" s="2"/>
       <c r="I3158" s="1"/>
     </row>
     <row r="3159" spans="8:9" x14ac:dyDescent="0.3">
@@ -28827,10 +28802,10 @@
       <c r="I3166" s="1"/>
     </row>
     <row r="3167" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3167" s="2"/>
       <c r="I3167" s="1"/>
     </row>
     <row r="3168" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3168" s="2"/>
       <c r="I3168" s="1"/>
     </row>
     <row r="3169" spans="8:9" x14ac:dyDescent="0.3">
@@ -29346,10 +29321,10 @@
       <c r="I3296" s="1"/>
     </row>
     <row r="3297" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3297" s="2"/>
       <c r="I3297" s="1"/>
     </row>
     <row r="3298" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3298" s="2"/>
       <c r="I3298" s="1"/>
     </row>
     <row r="3299" spans="8:9" x14ac:dyDescent="0.3">
@@ -29485,10 +29460,10 @@
       <c r="I3331" s="1"/>
     </row>
     <row r="3332" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3332" s="2"/>
       <c r="I3332" s="1"/>
     </row>
     <row r="3333" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3333" s="2"/>
       <c r="I3333" s="1"/>
     </row>
     <row r="3334" spans="8:9" x14ac:dyDescent="0.3">
@@ -29608,10 +29583,10 @@
       <c r="I3362" s="1"/>
     </row>
     <row r="3363" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3363" s="2"/>
       <c r="I3363" s="1"/>
     </row>
     <row r="3364" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3364" s="2"/>
       <c r="I3364" s="1"/>
     </row>
     <row r="3365" spans="8:9" x14ac:dyDescent="0.3">
@@ -29643,10 +29618,10 @@
       <c r="I3371" s="1"/>
     </row>
     <row r="3372" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3372" s="2"/>
       <c r="I3372" s="1"/>
     </row>
     <row r="3373" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3373" s="2"/>
       <c r="I3373" s="1"/>
     </row>
     <row r="3374" spans="8:9" x14ac:dyDescent="0.3">
@@ -29774,10 +29749,10 @@
       <c r="I3404" s="1"/>
     </row>
     <row r="3405" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3405" s="2"/>
       <c r="I3405" s="1"/>
     </row>
     <row r="3406" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3406" s="2"/>
       <c r="I3406" s="1"/>
     </row>
     <row r="3407" spans="8:9" x14ac:dyDescent="0.3">
@@ -29797,10 +29772,10 @@
       <c r="I3410" s="1"/>
     </row>
     <row r="3411" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3411" s="2"/>
       <c r="I3411" s="1"/>
     </row>
     <row r="3412" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3412" s="2"/>
       <c r="I3412" s="1"/>
     </row>
     <row r="3413" spans="8:9" x14ac:dyDescent="0.3">
@@ -30252,10 +30227,10 @@
       <c r="I3524" s="1"/>
     </row>
     <row r="3525" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3525" s="2"/>
       <c r="I3525" s="1"/>
     </row>
     <row r="3526" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3526" s="2"/>
       <c r="I3526" s="1"/>
     </row>
     <row r="3527" spans="8:9" x14ac:dyDescent="0.3">
@@ -30315,10 +30290,10 @@
       <c r="I3540" s="1"/>
     </row>
     <row r="3541" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3541" s="2"/>
       <c r="I3541" s="1"/>
     </row>
     <row r="3542" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3542" s="2"/>
       <c r="I3542" s="1"/>
     </row>
     <row r="3543" spans="8:9" x14ac:dyDescent="0.3">
@@ -30450,10 +30425,10 @@
       <c r="I3574" s="1"/>
     </row>
     <row r="3575" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3575" s="2"/>
       <c r="I3575" s="1"/>
     </row>
     <row r="3576" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3576" s="2"/>
       <c r="I3576" s="1"/>
     </row>
     <row r="3577" spans="8:9" x14ac:dyDescent="0.3">
@@ -30573,10 +30548,10 @@
       <c r="I3605" s="1"/>
     </row>
     <row r="3606" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3606" s="2"/>
       <c r="I3606" s="1"/>
     </row>
     <row r="3607" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3607" s="2"/>
       <c r="I3607" s="1"/>
     </row>
     <row r="3608" spans="8:9" x14ac:dyDescent="0.3">
@@ -30688,13 +30663,13 @@
       <c r="I3634" s="1"/>
     </row>
     <row r="3635" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3635" s="2"/>
       <c r="I3635" s="1"/>
     </row>
     <row r="3636" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I3636" s="1"/>
     </row>
     <row r="3637" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3637" s="2"/>
       <c r="I3637" s="1"/>
     </row>
     <row r="3638" spans="8:9" x14ac:dyDescent="0.3">
@@ -30718,20 +30693,20 @@
       <c r="I3642" s="1"/>
     </row>
     <row r="3643" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3643" s="2"/>
       <c r="I3643" s="1"/>
     </row>
     <row r="3644" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I3644" s="1"/>
     </row>
     <row r="3645" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3645" s="2"/>
       <c r="I3645" s="1"/>
     </row>
     <row r="3646" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3646" s="2"/>
       <c r="I3646" s="1"/>
     </row>
     <row r="3647" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3647" s="2"/>
       <c r="I3647" s="1"/>
     </row>
     <row r="3648" spans="8:9" x14ac:dyDescent="0.3">
@@ -30995,10 +30970,10 @@
       <c r="I3712" s="1"/>
     </row>
     <row r="3713" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3713" s="2"/>
       <c r="I3713" s="1"/>
     </row>
     <row r="3714" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3714" s="2"/>
       <c r="I3714" s="1"/>
     </row>
     <row r="3715" spans="8:9" x14ac:dyDescent="0.3">
@@ -31250,10 +31225,10 @@
       <c r="I3776" s="1"/>
     </row>
     <row r="3777" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3777" s="2"/>
       <c r="I3777" s="1"/>
     </row>
     <row r="3778" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3778" s="2"/>
       <c r="I3778" s="1"/>
     </row>
     <row r="3779" spans="8:9" x14ac:dyDescent="0.3">
@@ -31297,10 +31272,10 @@
       <c r="I3788" s="1"/>
     </row>
     <row r="3789" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3789" s="2"/>
       <c r="I3789" s="1"/>
     </row>
     <row r="3790" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3790" s="2"/>
       <c r="I3790" s="1"/>
     </row>
     <row r="3791" spans="8:9" x14ac:dyDescent="0.3">
@@ -31332,10 +31307,10 @@
       <c r="I3797" s="1"/>
     </row>
     <row r="3798" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3798" s="2"/>
       <c r="I3798" s="1"/>
     </row>
     <row r="3799" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3799" s="2"/>
       <c r="I3799" s="1"/>
     </row>
     <row r="3800" spans="8:9" x14ac:dyDescent="0.3">
@@ -31555,10 +31530,10 @@
       <c r="I3853" s="1"/>
     </row>
     <row r="3854" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3854" s="2"/>
       <c r="I3854" s="1"/>
     </row>
     <row r="3855" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3855" s="2"/>
       <c r="I3855" s="1"/>
     </row>
     <row r="3856" spans="8:9" x14ac:dyDescent="0.3">
@@ -31670,10 +31645,10 @@
       <c r="I3882" s="1"/>
     </row>
     <row r="3883" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3883" s="2"/>
       <c r="I3883" s="1"/>
     </row>
     <row r="3884" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3884" s="2"/>
       <c r="I3884" s="1"/>
     </row>
     <row r="3885" spans="8:9" x14ac:dyDescent="0.3">
@@ -31697,10 +31672,10 @@
       <c r="I3889" s="1"/>
     </row>
     <row r="3890" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3890" s="2"/>
       <c r="I3890" s="1"/>
     </row>
     <row r="3891" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3891" s="2"/>
       <c r="I3891" s="1"/>
     </row>
     <row r="3892" spans="8:9" x14ac:dyDescent="0.3">
@@ -31844,10 +31819,10 @@
       <c r="I3926" s="1"/>
     </row>
     <row r="3927" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3927" s="2"/>
       <c r="I3927" s="1"/>
     </row>
     <row r="3928" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3928" s="2"/>
       <c r="I3928" s="1"/>
     </row>
     <row r="3929" spans="8:9" x14ac:dyDescent="0.3">
@@ -32163,10 +32138,10 @@
       <c r="I4006" s="1"/>
     </row>
     <row r="4007" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4007" s="2"/>
       <c r="I4007" s="1"/>
     </row>
     <row r="4008" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4008" s="2"/>
       <c r="I4008" s="1"/>
     </row>
     <row r="4009" spans="8:9" x14ac:dyDescent="0.3">
@@ -32282,10 +32257,10 @@
       <c r="I4036" s="1"/>
     </row>
     <row r="4037" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4037" s="2"/>
       <c r="I4037" s="1"/>
     </row>
     <row r="4038" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4038" s="2"/>
       <c r="I4038" s="1"/>
     </row>
     <row r="4039" spans="8:9" x14ac:dyDescent="0.3">
@@ -32357,10 +32332,10 @@
       <c r="I4055" s="1"/>
     </row>
     <row r="4056" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4056" s="2"/>
       <c r="I4056" s="1"/>
     </row>
     <row r="4057" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4057" s="2"/>
       <c r="I4057" s="1"/>
     </row>
     <row r="4058" spans="8:9" x14ac:dyDescent="0.3">
@@ -32528,10 +32503,10 @@
       <c r="I4098" s="1"/>
     </row>
     <row r="4099" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4099" s="2"/>
       <c r="I4099" s="1"/>
     </row>
     <row r="4100" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4100" s="2"/>
       <c r="I4100" s="1"/>
     </row>
     <row r="4101" spans="8:9" x14ac:dyDescent="0.3">
@@ -32655,10 +32630,10 @@
       <c r="I4130" s="1"/>
     </row>
     <row r="4131" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4131" s="2"/>
       <c r="I4131" s="1"/>
     </row>
     <row r="4132" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4132" s="2"/>
       <c r="I4132" s="1"/>
     </row>
     <row r="4133" spans="8:9" x14ac:dyDescent="0.3">
@@ -32666,10 +32641,10 @@
       <c r="I4133" s="1"/>
     </row>
     <row r="4134" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4134" s="2"/>
       <c r="I4134" s="1"/>
     </row>
     <row r="4135" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4135" s="2"/>
       <c r="I4135" s="1"/>
     </row>
     <row r="4136" spans="8:9" x14ac:dyDescent="0.3">
@@ -32693,10 +32668,10 @@
       <c r="I4140" s="1"/>
     </row>
     <row r="4141" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4141" s="2"/>
       <c r="I4141" s="1"/>
     </row>
     <row r="4142" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4142" s="2"/>
       <c r="I4142" s="1"/>
     </row>
     <row r="4143" spans="8:9" x14ac:dyDescent="0.3">
@@ -33228,10 +33203,10 @@
       <c r="I4274" s="1"/>
     </row>
     <row r="4275" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4275" s="2"/>
       <c r="I4275" s="1"/>
     </row>
     <row r="4276" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4276" s="2"/>
       <c r="I4276" s="1"/>
     </row>
     <row r="4277" spans="8:9" x14ac:dyDescent="0.3">
@@ -33255,10 +33230,10 @@
       <c r="I4281" s="1"/>
     </row>
     <row r="4282" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4282" s="2"/>
       <c r="I4282" s="1"/>
     </row>
     <row r="4283" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4283" s="2"/>
       <c r="I4283" s="1"/>
     </row>
     <row r="4284" spans="8:9" x14ac:dyDescent="0.3">
@@ -33550,10 +33525,10 @@
       <c r="I4355" s="1"/>
     </row>
     <row r="4356" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4356" s="2"/>
       <c r="I4356" s="1"/>
     </row>
     <row r="4357" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4357" s="2"/>
       <c r="I4357" s="1"/>
     </row>
     <row r="4358" spans="8:9" x14ac:dyDescent="0.3">
@@ -33693,13 +33668,13 @@
       <c r="I4391" s="1"/>
     </row>
     <row r="4392" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4392" s="2"/>
       <c r="I4392" s="1"/>
     </row>
     <row r="4393" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I4393" s="1"/>
     </row>
     <row r="4394" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4394" s="2"/>
       <c r="I4394" s="1"/>
     </row>
     <row r="4395" spans="8:9" x14ac:dyDescent="0.3">
@@ -33743,10 +33718,10 @@
       <c r="I4404" s="1"/>
     </row>
     <row r="4405" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4405" s="2"/>
       <c r="I4405" s="1"/>
     </row>
     <row r="4406" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4406" s="2"/>
       <c r="I4406" s="1"/>
     </row>
     <row r="4407" spans="8:9" x14ac:dyDescent="0.3">
@@ -33770,10 +33745,10 @@
       <c r="I4411" s="1"/>
     </row>
     <row r="4412" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4412" s="2"/>
       <c r="I4412" s="1"/>
     </row>
     <row r="4413" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4413" s="2"/>
       <c r="I4413" s="1"/>
     </row>
     <row r="4414" spans="8:9" x14ac:dyDescent="0.3">
@@ -34109,10 +34084,10 @@
       <c r="I4496" s="1"/>
     </row>
     <row r="4497" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4497" s="2"/>
       <c r="I4497" s="1"/>
     </row>
     <row r="4498" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4498" s="2"/>
       <c r="I4498" s="1"/>
     </row>
     <row r="4499" spans="8:9" x14ac:dyDescent="0.3">
@@ -34152,10 +34127,10 @@
       <c r="I4507" s="1"/>
     </row>
     <row r="4508" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4508" s="2"/>
       <c r="I4508" s="1"/>
     </row>
     <row r="4509" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4509" s="2"/>
       <c r="I4509" s="1"/>
     </row>
     <row r="4510" spans="8:9" x14ac:dyDescent="0.3">
@@ -34255,10 +34230,10 @@
       <c r="I4533" s="1"/>
     </row>
     <row r="4534" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4534" s="2"/>
       <c r="I4534" s="1"/>
     </row>
     <row r="4535" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4535" s="2"/>
       <c r="I4535" s="1"/>
     </row>
     <row r="4536" spans="8:9" x14ac:dyDescent="0.3">
@@ -34306,10 +34281,10 @@
       <c r="I4546" s="1"/>
     </row>
     <row r="4547" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4547" s="2"/>
       <c r="I4547" s="1"/>
     </row>
     <row r="4548" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4548" s="2"/>
       <c r="I4548" s="1"/>
     </row>
     <row r="4549" spans="8:9" x14ac:dyDescent="0.3">
@@ -34665,10 +34640,10 @@
       <c r="I4636" s="1"/>
     </row>
     <row r="4637" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4637" s="2"/>
       <c r="I4637" s="1"/>
     </row>
     <row r="4638" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4638" s="2"/>
       <c r="I4638" s="1"/>
     </row>
     <row r="4639" spans="8:9" x14ac:dyDescent="0.3">
@@ -34676,10 +34651,10 @@
       <c r="I4639" s="1"/>
     </row>
     <row r="4640" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4640" s="2"/>
       <c r="I4640" s="1"/>
     </row>
     <row r="4641" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4641" s="2"/>
       <c r="I4641" s="1"/>
     </row>
     <row r="4642" spans="8:9" x14ac:dyDescent="0.3">
@@ -34799,10 +34774,10 @@
       <c r="I4670" s="1"/>
     </row>
     <row r="4671" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4671" s="2"/>
       <c r="I4671" s="1"/>
     </row>
     <row r="4672" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4672" s="2"/>
       <c r="I4672" s="1"/>
     </row>
     <row r="4673" spans="8:9" x14ac:dyDescent="0.3">
@@ -34890,10 +34865,10 @@
       <c r="I4693" s="1"/>
     </row>
     <row r="4694" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4694" s="2"/>
       <c r="I4694" s="1"/>
     </row>
     <row r="4695" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4695" s="2"/>
       <c r="I4695" s="1"/>
     </row>
     <row r="4696" spans="8:9" x14ac:dyDescent="0.3">
@@ -35165,10 +35140,10 @@
       <c r="I4762" s="1"/>
     </row>
     <row r="4763" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4763" s="2"/>
       <c r="I4763" s="1"/>
     </row>
     <row r="4764" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4764" s="2"/>
       <c r="I4764" s="1"/>
     </row>
     <row r="4765" spans="8:9" x14ac:dyDescent="0.3">
@@ -35320,10 +35295,10 @@
       <c r="I4801" s="1"/>
     </row>
     <row r="4802" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4802" s="2"/>
       <c r="I4802" s="1"/>
     </row>
     <row r="4803" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4803" s="2"/>
       <c r="I4803" s="1"/>
     </row>
     <row r="4804" spans="8:9" x14ac:dyDescent="0.3">
@@ -35371,10 +35346,10 @@
       <c r="I4814" s="1"/>
     </row>
     <row r="4815" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4815" s="2"/>
       <c r="I4815" s="1"/>
     </row>
     <row r="4816" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4816" s="2"/>
       <c r="I4816" s="1"/>
     </row>
     <row r="4817" spans="8:9" x14ac:dyDescent="0.3">
@@ -35526,10 +35501,10 @@
       <c r="I4853" s="1"/>
     </row>
     <row r="4854" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4854" s="2"/>
       <c r="I4854" s="1"/>
     </row>
     <row r="4855" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4855" s="2"/>
       <c r="I4855" s="1"/>
     </row>
     <row r="4856" spans="8:9" x14ac:dyDescent="0.3">
@@ -35589,10 +35564,10 @@
       <c r="I4869" s="1"/>
     </row>
     <row r="4870" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4870" s="2"/>
       <c r="I4870" s="1"/>
     </row>
     <row r="4871" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4871" s="2"/>
       <c r="I4871" s="1"/>
     </row>
     <row r="4872" spans="8:9" x14ac:dyDescent="0.3">
@@ -35672,10 +35647,10 @@
       <c r="I4890" s="1"/>
     </row>
     <row r="4891" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4891" s="2"/>
       <c r="I4891" s="1"/>
     </row>
     <row r="4892" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4892" s="2"/>
       <c r="I4892" s="1"/>
     </row>
     <row r="4893" spans="8:9" x14ac:dyDescent="0.3">
@@ -35719,10 +35694,10 @@
       <c r="I4902" s="1"/>
     </row>
     <row r="4903" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4903" s="2"/>
       <c r="I4903" s="1"/>
     </row>
     <row r="4904" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4904" s="2"/>
       <c r="I4904" s="1"/>
     </row>
     <row r="4905" spans="8:9" x14ac:dyDescent="0.3">
@@ -35730,10 +35705,10 @@
       <c r="I4905" s="1"/>
     </row>
     <row r="4906" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4906" s="2"/>
       <c r="I4906" s="1"/>
     </row>
     <row r="4907" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4907" s="2"/>
       <c r="I4907" s="1"/>
     </row>
     <row r="4908" spans="8:9" x14ac:dyDescent="0.3">
@@ -35813,10 +35788,10 @@
       <c r="I4926" s="1"/>
     </row>
     <row r="4927" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4927" s="2"/>
       <c r="I4927" s="1"/>
     </row>
     <row r="4928" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4928" s="2"/>
       <c r="I4928" s="1"/>
     </row>
     <row r="4929" spans="8:9" x14ac:dyDescent="0.3">
@@ -36092,10 +36067,10 @@
       <c r="I4996" s="1"/>
     </row>
     <row r="4997" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4997" s="2"/>
       <c r="I4997" s="1"/>
     </row>
     <row r="4998" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4998" s="2"/>
       <c r="I4998" s="1"/>
     </row>
     <row r="4999" spans="8:9" x14ac:dyDescent="0.3">
@@ -36171,10 +36146,10 @@
       <c r="I5016" s="1"/>
     </row>
     <row r="5017" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5017" s="2"/>
       <c r="I5017" s="1"/>
     </row>
     <row r="5018" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5018" s="2"/>
       <c r="I5018" s="1"/>
     </row>
     <row r="5019" spans="8:9" x14ac:dyDescent="0.3">
@@ -36218,10 +36193,10 @@
       <c r="I5028" s="1"/>
     </row>
     <row r="5029" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5029" s="2"/>
       <c r="I5029" s="1"/>
     </row>
     <row r="5030" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5030" s="2"/>
       <c r="I5030" s="1"/>
     </row>
     <row r="5031" spans="8:9" x14ac:dyDescent="0.3">
@@ -36321,10 +36296,10 @@
       <c r="I5054" s="1"/>
     </row>
     <row r="5055" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5055" s="2"/>
       <c r="I5055" s="1"/>
     </row>
     <row r="5056" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5056" s="2"/>
       <c r="I5056" s="1"/>
     </row>
     <row r="5057" spans="8:9" x14ac:dyDescent="0.3">
@@ -36368,10 +36343,10 @@
       <c r="I5066" s="1"/>
     </row>
     <row r="5067" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5067" s="2"/>
       <c r="I5067" s="1"/>
     </row>
     <row r="5068" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5068" s="2"/>
       <c r="I5068" s="1"/>
     </row>
     <row r="5069" spans="8:9" x14ac:dyDescent="0.3">
@@ -36399,10 +36374,10 @@
       <c r="I5074" s="1"/>
     </row>
     <row r="5075" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5075" s="2"/>
       <c r="I5075" s="1"/>
     </row>
     <row r="5076" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5076" s="2"/>
       <c r="I5076" s="1"/>
     </row>
     <row r="5077" spans="8:9" x14ac:dyDescent="0.3">
@@ -36530,10 +36505,10 @@
       <c r="I5107" s="1"/>
     </row>
     <row r="5108" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5108" s="2"/>
       <c r="I5108" s="1"/>
     </row>
     <row r="5109" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5109" s="2"/>
       <c r="I5109" s="1"/>
     </row>
     <row r="5110" spans="8:9" x14ac:dyDescent="0.3">
@@ -36749,10 +36724,10 @@
       <c r="I5162" s="1"/>
     </row>
     <row r="5163" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5163" s="2"/>
       <c r="I5163" s="1"/>
     </row>
     <row r="5164" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5164" s="2"/>
       <c r="I5164" s="1"/>
     </row>
     <row r="5165" spans="8:9" x14ac:dyDescent="0.3">
@@ -37080,10 +37055,10 @@
       <c r="I5245" s="1"/>
     </row>
     <row r="5246" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5246" s="2"/>
       <c r="I5246" s="1"/>
     </row>
     <row r="5247" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5247" s="2"/>
       <c r="I5247" s="1"/>
     </row>
     <row r="5248" spans="8:9" x14ac:dyDescent="0.3">
@@ -37111,17 +37086,17 @@
       <c r="I5253" s="1"/>
     </row>
     <row r="5254" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5254" s="2"/>
       <c r="I5254" s="1"/>
     </row>
     <row r="5255" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5255" s="2"/>
       <c r="I5255" s="1"/>
     </row>
     <row r="5256" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5256" s="2"/>
       <c r="I5256" s="1"/>
     </row>
     <row r="5257" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5257" s="2"/>
       <c r="I5257" s="1"/>
     </row>
     <row r="5258" spans="8:9" x14ac:dyDescent="0.3">
@@ -37305,10 +37280,10 @@
       <c r="I5302" s="1"/>
     </row>
     <row r="5303" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5303" s="2"/>
       <c r="I5303" s="1"/>
     </row>
     <row r="5304" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5304" s="2"/>
       <c r="I5304" s="1"/>
     </row>
     <row r="5305" spans="8:9" x14ac:dyDescent="0.3">
@@ -37344,10 +37319,10 @@
       <c r="I5312" s="1"/>
     </row>
     <row r="5313" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5313" s="2"/>
       <c r="I5313" s="1"/>
     </row>
     <row r="5314" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5314" s="2"/>
       <c r="I5314" s="1"/>
     </row>
     <row r="5315" spans="8:9" x14ac:dyDescent="0.3">
@@ -37739,10 +37714,10 @@
       <c r="I5411" s="1"/>
     </row>
     <row r="5412" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5412" s="2"/>
       <c r="I5412" s="1"/>
     </row>
     <row r="5413" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5413" s="2"/>
       <c r="I5413" s="1"/>
     </row>
     <row r="5414" spans="8:9" x14ac:dyDescent="0.3">
@@ -37758,7 +37733,6 @@
       <c r="I5416" s="1"/>
     </row>
     <row r="5417" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5417" s="2"/>
       <c r="I5417" s="1"/>
     </row>
     <row r="5418" spans="8:9" x14ac:dyDescent="0.3">
@@ -37768,6 +37742,7 @@
       <c r="I5419" s="1"/>
     </row>
     <row r="5420" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5420" s="2"/>
       <c r="I5420" s="1"/>
     </row>
     <row r="5421" spans="8:9" x14ac:dyDescent="0.3">
@@ -37779,10 +37754,10 @@
       <c r="I5422" s="1"/>
     </row>
     <row r="5423" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5423" s="2"/>
       <c r="I5423" s="1"/>
     </row>
     <row r="5424" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5424" s="2"/>
       <c r="I5424" s="1"/>
     </row>
     <row r="5425" spans="8:9" x14ac:dyDescent="0.3">
@@ -38126,10 +38101,10 @@
       <c r="I5509" s="1"/>
     </row>
     <row r="5510" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5510" s="2"/>
       <c r="I5510" s="1"/>
     </row>
     <row r="5511" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5511" s="2"/>
       <c r="I5511" s="1"/>
     </row>
     <row r="5512" spans="8:9" x14ac:dyDescent="0.3">
@@ -38137,10 +38112,10 @@
       <c r="I5512" s="1"/>
     </row>
     <row r="5513" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5513" s="2"/>
       <c r="I5513" s="1"/>
     </row>
     <row r="5514" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5514" s="2"/>
       <c r="I5514" s="1"/>
     </row>
     <row r="5515" spans="8:9" x14ac:dyDescent="0.3">
@@ -38200,10 +38175,10 @@
       <c r="I5528" s="1"/>
     </row>
     <row r="5529" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5529" s="2"/>
       <c r="I5529" s="1"/>
     </row>
     <row r="5530" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5530" s="2"/>
       <c r="I5530" s="1"/>
     </row>
     <row r="5531" spans="8:9" x14ac:dyDescent="0.3">
@@ -38247,10 +38222,10 @@
       <c r="I5540" s="1"/>
     </row>
     <row r="5541" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5541" s="2"/>
       <c r="I5541" s="1"/>
     </row>
     <row r="5542" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5542" s="2"/>
       <c r="I5542" s="1"/>
     </row>
     <row r="5543" spans="8:9" x14ac:dyDescent="0.3">
@@ -38266,10 +38241,10 @@
       <c r="I5545" s="1"/>
     </row>
     <row r="5546" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5546" s="2"/>
       <c r="I5546" s="1"/>
     </row>
     <row r="5547" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5547" s="2"/>
       <c r="I5547" s="1"/>
     </row>
     <row r="5548" spans="8:9" x14ac:dyDescent="0.3">
@@ -38357,10 +38332,10 @@
       <c r="I5568" s="1"/>
     </row>
     <row r="5569" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5569" s="2"/>
       <c r="I5569" s="1"/>
     </row>
     <row r="5570" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5570" s="2"/>
       <c r="I5570" s="1"/>
     </row>
     <row r="5571" spans="8:9" x14ac:dyDescent="0.3">
@@ -38620,10 +38595,10 @@
       <c r="I5634" s="1"/>
     </row>
     <row r="5635" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5635" s="2"/>
       <c r="I5635" s="1"/>
     </row>
     <row r="5636" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5636" s="2"/>
       <c r="I5636" s="1"/>
     </row>
     <row r="5637" spans="8:9" x14ac:dyDescent="0.3">
@@ -38775,10 +38750,10 @@
       <c r="I5673" s="1"/>
     </row>
     <row r="5674" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5674" s="2"/>
       <c r="I5674" s="1"/>
     </row>
     <row r="5675" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5675" s="2"/>
       <c r="I5675" s="1"/>
     </row>
     <row r="5676" spans="8:9" x14ac:dyDescent="0.3">
@@ -38814,13 +38789,13 @@
       <c r="I5683" s="1"/>
     </row>
     <row r="5684" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5684" s="2"/>
       <c r="I5684" s="1"/>
     </row>
     <row r="5685" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I5685" s="1"/>
     </row>
     <row r="5686" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5686" s="2"/>
       <c r="I5686" s="1"/>
     </row>
     <row r="5687" spans="8:9" x14ac:dyDescent="0.3">
@@ -38928,10 +38903,10 @@
       <c r="I5712" s="1"/>
     </row>
     <row r="5713" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5713" s="2"/>
       <c r="I5713" s="1"/>
     </row>
     <row r="5714" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5714" s="2"/>
       <c r="I5714" s="1"/>
     </row>
     <row r="5715" spans="8:9" x14ac:dyDescent="0.3">
@@ -39003,10 +38978,10 @@
       <c r="I5731" s="1"/>
     </row>
     <row r="5732" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5732" s="2"/>
       <c r="I5732" s="1"/>
     </row>
     <row r="5733" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5733" s="2"/>
       <c r="I5733" s="1"/>
     </row>
     <row r="5734" spans="8:9" x14ac:dyDescent="0.3">
@@ -39054,10 +39029,10 @@
       <c r="I5744" s="1"/>
     </row>
     <row r="5745" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5745" s="2"/>
       <c r="I5745" s="1"/>
     </row>
     <row r="5746" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5746" s="2"/>
       <c r="I5746" s="1"/>
     </row>
     <row r="5747" spans="8:9" x14ac:dyDescent="0.3">
@@ -39097,13 +39072,13 @@
       <c r="I5755" s="1"/>
     </row>
     <row r="5756" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5756" s="2"/>
       <c r="I5756" s="1"/>
     </row>
     <row r="5757" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I5757" s="1"/>
     </row>
     <row r="5758" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5758" s="2"/>
       <c r="I5758" s="1"/>
     </row>
     <row r="5759" spans="8:9" x14ac:dyDescent="0.3">
@@ -39119,10 +39094,10 @@
       <c r="I5761" s="1"/>
     </row>
     <row r="5762" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5762" s="2"/>
       <c r="I5762" s="1"/>
     </row>
     <row r="5763" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5763" s="2"/>
       <c r="I5763" s="1"/>
     </row>
     <row r="5764" spans="8:9" x14ac:dyDescent="0.3">
@@ -39194,13 +39169,13 @@
       <c r="I5780" s="1"/>
     </row>
     <row r="5781" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5781" s="2"/>
       <c r="I5781" s="1"/>
     </row>
     <row r="5782" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I5782" s="1"/>
     </row>
     <row r="5783" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5783" s="2"/>
       <c r="I5783" s="1"/>
     </row>
     <row r="5784" spans="8:9" x14ac:dyDescent="0.3">
@@ -39260,10 +39235,10 @@
       <c r="I5797" s="1"/>
     </row>
     <row r="5798" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5798" s="2"/>
       <c r="I5798" s="1"/>
     </row>
     <row r="5799" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5799" s="2"/>
       <c r="I5799" s="1"/>
     </row>
     <row r="5800" spans="8:9" x14ac:dyDescent="0.3">
@@ -39279,10 +39254,10 @@
       <c r="I5802" s="1"/>
     </row>
     <row r="5803" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5803" s="2"/>
       <c r="I5803" s="1"/>
     </row>
     <row r="5804" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5804" s="2"/>
       <c r="I5804" s="1"/>
     </row>
     <row r="5805" spans="8:9" x14ac:dyDescent="0.3">
@@ -39310,10 +39285,10 @@
       <c r="I5810" s="1"/>
     </row>
     <row r="5811" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5811" s="2"/>
       <c r="I5811" s="1"/>
     </row>
     <row r="5812" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5812" s="2"/>
       <c r="I5812" s="1"/>
     </row>
     <row r="5813" spans="8:9" x14ac:dyDescent="0.3">
@@ -39413,10 +39388,10 @@
       <c r="I5836" s="1"/>
     </row>
     <row r="5837" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5837" s="2"/>
       <c r="I5837" s="1"/>
     </row>
     <row r="5838" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5838" s="2"/>
       <c r="I5838" s="1"/>
     </row>
     <row r="5839" spans="8:9" x14ac:dyDescent="0.3">
@@ -39452,10 +39427,10 @@
       <c r="I5846" s="1"/>
     </row>
     <row r="5847" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5847" s="2"/>
       <c r="I5847" s="1"/>
     </row>
     <row r="5848" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5848" s="2"/>
       <c r="I5848" s="1"/>
     </row>
     <row r="5849" spans="8:9" x14ac:dyDescent="0.3">
@@ -39467,10 +39442,10 @@
       <c r="I5850" s="1"/>
     </row>
     <row r="5851" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5851" s="2"/>
       <c r="I5851" s="1"/>
     </row>
     <row r="5852" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5852" s="2"/>
       <c r="I5852" s="1"/>
     </row>
     <row r="5853" spans="8:9" x14ac:dyDescent="0.3">
@@ -39482,10 +39457,10 @@
       <c r="I5854" s="1"/>
     </row>
     <row r="5855" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5855" s="2"/>
       <c r="I5855" s="1"/>
     </row>
     <row r="5856" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5856" s="2"/>
       <c r="I5856" s="1"/>
     </row>
     <row r="5857" spans="8:9" x14ac:dyDescent="0.3">
@@ -39505,10 +39480,10 @@
       <c r="I5860" s="1"/>
     </row>
     <row r="5861" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5861" s="2"/>
       <c r="I5861" s="1"/>
     </row>
     <row r="5862" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5862" s="2"/>
       <c r="I5862" s="1"/>
     </row>
     <row r="5863" spans="8:9" x14ac:dyDescent="0.3">
@@ -39536,10 +39511,10 @@
       <c r="I5868" s="1"/>
     </row>
     <row r="5869" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5869" s="2"/>
       <c r="I5869" s="1"/>
     </row>
     <row r="5870" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5870" s="2"/>
       <c r="I5870" s="1"/>
     </row>
     <row r="5871" spans="8:9" x14ac:dyDescent="0.3">
@@ -39559,10 +39534,10 @@
       <c r="I5874" s="1"/>
     </row>
     <row r="5875" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5875" s="2"/>
       <c r="I5875" s="1"/>
     </row>
     <row r="5876" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5876" s="2"/>
       <c r="I5876" s="1"/>
     </row>
     <row r="5877" spans="8:9" x14ac:dyDescent="0.3">
@@ -39630,10 +39605,10 @@
       <c r="I5892" s="1"/>
     </row>
     <row r="5893" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5893" s="2"/>
       <c r="I5893" s="1"/>
     </row>
     <row r="5894" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5894" s="2"/>
       <c r="I5894" s="1"/>
     </row>
     <row r="5895" spans="8:9" x14ac:dyDescent="0.3">
@@ -39685,10 +39660,10 @@
       <c r="I5906" s="1"/>
     </row>
     <row r="5907" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5907" s="2"/>
       <c r="I5907" s="1"/>
     </row>
     <row r="5908" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5908" s="2"/>
       <c r="I5908" s="1"/>
     </row>
     <row r="5909" spans="8:9" x14ac:dyDescent="0.3">
@@ -39728,13 +39703,13 @@
       <c r="I5917" s="1"/>
     </row>
     <row r="5918" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5918" s="2"/>
       <c r="I5918" s="1"/>
     </row>
     <row r="5919" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I5919" s="1"/>
     </row>
     <row r="5920" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5920" s="2"/>
       <c r="I5920" s="1"/>
     </row>
     <row r="5921" spans="8:9" x14ac:dyDescent="0.3">
@@ -39742,18 +39717,14 @@
       <c r="I5921" s="1"/>
     </row>
     <row r="5922" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5922" s="2"/>
       <c r="I5922" s="1"/>
     </row>
     <row r="5923" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I5923" s="1"/>
     </row>
     <row r="5924" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5924" s="2"/>
       <c r="I5924" s="1"/>
-    </row>
-    <row r="5925" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5925" s="2"/>
-      <c r="I5925" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B610:K635">

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\TNT Wrecker - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFD68EB-B08D-44FA-A6F6-B2A6131A6D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7500AB-0DAA-4D56-8E0F-83F29E18F418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5924</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$K$5916</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="91">
   <si>
     <t>Company Name</t>
   </si>
@@ -303,9 +303,6 @@
   </si>
   <si>
     <t>Jeremy Myers</t>
-  </si>
-  <si>
-    <t>Drew Templet</t>
   </si>
   <si>
     <t>Speed Management</t>
@@ -688,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K5924"/>
+  <dimension ref="B1:K5916"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -17887,25 +17884,25 @@
         <v>35</v>
       </c>
       <c r="C617">
-        <v>5350</v>
+        <v>76</v>
       </c>
       <c r="D617" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F617" t="s">
         <v>17</v>
       </c>
       <c r="G617" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H617" s="2">
-        <v>9.3981481481481485E-3</v>
+        <v>0</v>
       </c>
       <c r="I617" s="1">
-        <v>46146.712962962964</v>
+        <v>46146.71365740741</v>
       </c>
       <c r="J617">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K617" t="s">
         <v>11</v>
@@ -17916,25 +17913,25 @@
         <v>35</v>
       </c>
       <c r="C618">
-        <v>76</v>
+        <v>3726</v>
       </c>
       <c r="D618" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F618" t="s">
         <v>17</v>
       </c>
       <c r="G618" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H618" s="2">
-        <v>0</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I618" s="1">
         <v>46146.71365740741</v>
       </c>
       <c r="J618">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K618" t="s">
         <v>11</v>
@@ -17945,10 +17942,10 @@
         <v>35</v>
       </c>
       <c r="C619">
-        <v>3726</v>
+        <v>614</v>
       </c>
       <c r="D619" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="F619" t="s">
         <v>17</v>
@@ -17957,13 +17954,13 @@
         <v>10</v>
       </c>
       <c r="H619" s="2">
-        <v>4.5717592592592589E-3</v>
+        <v>4.7685185185185183E-3</v>
       </c>
       <c r="I619" s="1">
-        <v>46146.71365740741</v>
+        <v>46146.71435185185</v>
       </c>
       <c r="J619">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K619" t="s">
         <v>11</v>
@@ -17974,10 +17971,10 @@
         <v>35</v>
       </c>
       <c r="C620">
-        <v>614</v>
+        <v>772</v>
       </c>
       <c r="D620" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F620" t="s">
         <v>17</v>
@@ -17986,13 +17983,13 @@
         <v>10</v>
       </c>
       <c r="H620" s="2">
-        <v>4.7685185185185183E-3</v>
+        <v>4.9305555555555552E-3</v>
       </c>
       <c r="I620" s="1">
-        <v>46146.71435185185</v>
+        <v>46146.715046296296</v>
       </c>
       <c r="J620">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K620" t="s">
         <v>11</v>
@@ -18003,10 +18000,10 @@
         <v>35</v>
       </c>
       <c r="C621">
-        <v>772</v>
+        <v>623</v>
       </c>
       <c r="D621" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F621" t="s">
         <v>17</v>
@@ -18015,7 +18012,7 @@
         <v>10</v>
       </c>
       <c r="H621" s="2">
-        <v>4.9305555555555552E-3</v>
+        <v>5.2893518518518515E-3</v>
       </c>
       <c r="I621" s="1">
         <v>46146.715046296296</v>
@@ -18032,25 +18029,25 @@
         <v>35</v>
       </c>
       <c r="C622">
-        <v>623</v>
+        <v>72</v>
       </c>
       <c r="D622" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F622" t="s">
         <v>17</v>
       </c>
       <c r="G622" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H622" s="2">
-        <v>5.2893518518518515E-3</v>
+        <v>0</v>
       </c>
       <c r="I622" s="1">
-        <v>46146.715046296296</v>
+        <v>46146.715740740743</v>
       </c>
       <c r="J622">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K622" t="s">
         <v>11</v>
@@ -18061,25 +18058,25 @@
         <v>35</v>
       </c>
       <c r="C623">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="D623" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F623" t="s">
         <v>17</v>
       </c>
       <c r="G623" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H623" s="2">
-        <v>0</v>
+        <v>1.9675925925925926E-4</v>
       </c>
       <c r="I623" s="1">
-        <v>46146.715740740743</v>
+        <v>46146.716435185182</v>
       </c>
       <c r="J623">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K623" t="s">
         <v>11</v>
@@ -18090,10 +18087,10 @@
         <v>35</v>
       </c>
       <c r="C624">
-        <v>245</v>
+        <v>84</v>
       </c>
       <c r="D624" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F624" t="s">
         <v>17</v>
@@ -18102,13 +18099,13 @@
         <v>10</v>
       </c>
       <c r="H624" s="2">
-        <v>1.9675925925925926E-4</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I624" s="1">
         <v>46146.716435185182</v>
       </c>
       <c r="J624">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K624" t="s">
         <v>11</v>
@@ -18119,10 +18116,10 @@
         <v>35</v>
       </c>
       <c r="C625">
-        <v>84</v>
+        <v>3818</v>
       </c>
       <c r="D625" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F625" t="s">
         <v>17</v>
@@ -18131,13 +18128,13 @@
         <v>10</v>
       </c>
       <c r="H625" s="2">
-        <v>6.6550925925925927E-3</v>
+        <v>8.6574074074074071E-3</v>
       </c>
       <c r="I625" s="1">
-        <v>46146.716435185182</v>
+        <v>46146.717129629629</v>
       </c>
       <c r="J625">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K625" t="s">
         <v>11</v>
@@ -18148,25 +18145,25 @@
         <v>35</v>
       </c>
       <c r="C626">
-        <v>3818</v>
+        <v>80</v>
       </c>
       <c r="D626" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F626" t="s">
         <v>17</v>
       </c>
       <c r="G626" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H626" s="2">
-        <v>8.6574074074074071E-3</v>
+        <v>0</v>
       </c>
       <c r="I626" s="1">
-        <v>46146.717129629629</v>
+        <v>46146.717824074076</v>
       </c>
       <c r="J626">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K626" t="s">
         <v>11</v>
@@ -18177,13 +18174,13 @@
         <v>35</v>
       </c>
       <c r="C627">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D627" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F627" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="G627" t="s">
         <v>13</v>
@@ -18192,10 +18189,10 @@
         <v>0</v>
       </c>
       <c r="I627" s="1">
-        <v>46146.717824074076</v>
+        <v>46176.418402777781</v>
       </c>
       <c r="J627">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K627" t="s">
         <v>11</v>
@@ -18212,7 +18209,7 @@
         <v>38</v>
       </c>
       <c r="F628" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G628" t="s">
         <v>10</v>
@@ -18238,10 +18235,10 @@
         <v>5586</v>
       </c>
       <c r="D629" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F629" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G629" t="s">
         <v>10</v>
@@ -18264,25 +18261,25 @@
         <v>35</v>
       </c>
       <c r="C630">
-        <v>5217</v>
+        <v>622</v>
       </c>
       <c r="D630" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F630" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G630" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H630" s="2">
-        <v>1.53125E-2</v>
+        <v>0</v>
       </c>
       <c r="I630" s="1">
-        <v>46174.635879629626</v>
+        <v>46176.41909722222</v>
       </c>
       <c r="J630">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K630" t="s">
         <v>11</v>
@@ -18293,22 +18290,22 @@
         <v>35</v>
       </c>
       <c r="C631">
-        <v>205</v>
+        <v>5217</v>
       </c>
       <c r="D631" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="F631" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G631" t="s">
         <v>10</v>
       </c>
       <c r="H631" s="2">
-        <v>1.1145833333333334E-2</v>
+        <v>1.53125E-2</v>
       </c>
       <c r="I631" s="1">
-        <v>46174.63726851852</v>
+        <v>46174.635879629626</v>
       </c>
       <c r="J631">
         <v>0</v>
@@ -18322,22 +18319,22 @@
         <v>35</v>
       </c>
       <c r="C632">
-        <v>5037</v>
+        <v>204</v>
       </c>
       <c r="D632" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="F632" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G632" t="s">
         <v>10</v>
       </c>
       <c r="H632" s="2">
-        <v>1.0486111111111111E-2</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I632" s="1">
-        <v>46174.639351851853</v>
+        <v>46176.419791666667</v>
       </c>
       <c r="J632">
         <v>0</v>
@@ -18351,22 +18348,22 @@
         <v>35</v>
       </c>
       <c r="C633">
-        <v>772</v>
+        <v>205</v>
       </c>
       <c r="D633" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F633" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G633" t="s">
         <v>10</v>
       </c>
       <c r="H633" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>1.1145833333333334E-2</v>
       </c>
       <c r="I633" s="1">
-        <v>46174.642824074072</v>
+        <v>46174.63726851852</v>
       </c>
       <c r="J633">
         <v>0</v>
@@ -18380,22 +18377,25 @@
         <v>35</v>
       </c>
       <c r="C634">
-        <v>245</v>
+        <v>3741</v>
       </c>
       <c r="D634" t="s">
-        <v>52</v>
+        <v>78</v>
+      </c>
+      <c r="E634" t="s">
+        <v>63</v>
       </c>
       <c r="F634" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G634" t="s">
         <v>10</v>
       </c>
       <c r="H634" s="2">
-        <v>6.4814814814814813E-3</v>
+        <v>8.1134259259259267E-3</v>
       </c>
       <c r="I634" s="1">
-        <v>46174.644212962965</v>
+        <v>46176.420486111114</v>
       </c>
       <c r="J634">
         <v>0</v>
@@ -18409,22 +18409,22 @@
         <v>35</v>
       </c>
       <c r="C635">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D635" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F635" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G635" t="s">
         <v>10</v>
       </c>
       <c r="H635" s="2">
-        <v>6.2962962962962964E-3</v>
+        <v>1.275462962962963E-2</v>
       </c>
       <c r="I635" s="1">
-        <v>46174.644907407404</v>
+        <v>46176.421180555553</v>
       </c>
       <c r="J635">
         <v>0</v>
@@ -18438,25 +18438,25 @@
         <v>35</v>
       </c>
       <c r="C636">
-        <v>3818</v>
+        <v>73</v>
       </c>
       <c r="D636" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="F636" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G636" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H636" s="2">
-        <v>7.013888888888889E-3</v>
+        <v>0</v>
       </c>
       <c r="I636" s="1">
-        <v>46174.645601851851</v>
+        <v>46176.421180555553</v>
       </c>
       <c r="J636">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K636" t="s">
         <v>11</v>
@@ -18467,25 +18467,25 @@
         <v>35</v>
       </c>
       <c r="C637">
-        <v>77</v>
+        <v>5037</v>
       </c>
       <c r="D637" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="F637" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G637" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H637" s="2">
-        <v>0</v>
+        <v>1.0486111111111111E-2</v>
       </c>
       <c r="I637" s="1">
-        <v>46176.418402777781</v>
+        <v>46174.639351851853</v>
       </c>
       <c r="J637">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K637" t="s">
         <v>11</v>
@@ -18496,13 +18496,13 @@
         <v>35</v>
       </c>
       <c r="C638">
-        <v>622</v>
+        <v>75</v>
       </c>
       <c r="D638" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F638" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G638" t="s">
         <v>13</v>
@@ -18511,7 +18511,7 @@
         <v>0</v>
       </c>
       <c r="I638" s="1">
-        <v>46176.41909722222</v>
+        <v>46176.421875</v>
       </c>
       <c r="J638">
         <v>1</v>
@@ -18525,13 +18525,13 @@
         <v>35</v>
       </c>
       <c r="C639">
-        <v>5180</v>
+        <v>5350</v>
       </c>
       <c r="D639" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F639" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G639" t="s">
         <v>13</v>
@@ -18540,7 +18540,7 @@
         <v>0</v>
       </c>
       <c r="I639" s="1">
-        <v>46176.419791666667</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J639">
         <v>1</v>
@@ -18554,25 +18554,25 @@
         <v>35</v>
       </c>
       <c r="C640">
-        <v>204</v>
+        <v>76</v>
       </c>
       <c r="D640" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F640" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G640" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H640" s="2">
-        <v>8.0439814814814818E-3</v>
+        <v>0</v>
       </c>
       <c r="I640" s="1">
-        <v>46176.419791666667</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J640">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K640" t="s">
         <v>11</v>
@@ -18583,28 +18583,25 @@
         <v>35</v>
       </c>
       <c r="C641">
-        <v>3741</v>
+        <v>3726</v>
       </c>
       <c r="D641" t="s">
-        <v>78</v>
-      </c>
-      <c r="E641" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F641" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G641" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H641" s="2">
-        <v>8.1134259259259267E-3</v>
+        <v>0</v>
       </c>
       <c r="I641" s="1">
-        <v>46176.420486111114</v>
+        <v>46176.422569444447</v>
       </c>
       <c r="J641">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K641" t="s">
         <v>11</v>
@@ -18615,22 +18612,22 @@
         <v>35</v>
       </c>
       <c r="C642">
-        <v>78</v>
+        <v>614</v>
       </c>
       <c r="D642" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F642" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G642" t="s">
         <v>10</v>
       </c>
       <c r="H642" s="2">
-        <v>1.275462962962963E-2</v>
+        <v>7.789351851851852E-3</v>
       </c>
       <c r="I642" s="1">
-        <v>46176.421180555553</v>
+        <v>46176.423263888886</v>
       </c>
       <c r="J642">
         <v>0</v>
@@ -18644,25 +18641,25 @@
         <v>35</v>
       </c>
       <c r="C643">
-        <v>73</v>
+        <v>772</v>
       </c>
       <c r="D643" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F643" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G643" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H643" s="2">
-        <v>0</v>
+        <v>8.0439814814814818E-3</v>
       </c>
       <c r="I643" s="1">
-        <v>46176.421180555553</v>
+        <v>46174.642824074072</v>
       </c>
       <c r="J643">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K643" t="s">
         <v>11</v>
@@ -18673,22 +18670,22 @@
         <v>35</v>
       </c>
       <c r="C644">
-        <v>75</v>
+        <v>623</v>
       </c>
       <c r="D644" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F644" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G644" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H644" s="2">
-        <v>0</v>
+        <v>7.3495370370370372E-3</v>
       </c>
       <c r="I644" s="1">
-        <v>46176.421875</v>
+        <v>46176.423263888886</v>
       </c>
       <c r="J644">
         <v>1</v>
@@ -18702,13 +18699,13 @@
         <v>35</v>
       </c>
       <c r="C645">
-        <v>5350</v>
+        <v>72</v>
       </c>
       <c r="D645" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="F645" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G645" t="s">
         <v>13</v>
@@ -18717,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="I645" s="1">
-        <v>46176.422569444447</v>
+        <v>46176.423958333333</v>
       </c>
       <c r="J645">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K645" t="s">
         <v>11</v>
@@ -18731,25 +18728,25 @@
         <v>35</v>
       </c>
       <c r="C646">
-        <v>76</v>
+        <v>245</v>
       </c>
       <c r="D646" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F646" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G646" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H646" s="2">
-        <v>0</v>
+        <v>6.4814814814814813E-3</v>
       </c>
       <c r="I646" s="1">
-        <v>46176.422569444447</v>
+        <v>46174.644212962965</v>
       </c>
       <c r="J646">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K646" t="s">
         <v>11</v>
@@ -18760,25 +18757,25 @@
         <v>35</v>
       </c>
       <c r="C647">
-        <v>3726</v>
+        <v>84</v>
       </c>
       <c r="D647" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F647" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G647" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H647" s="2">
-        <v>0</v>
+        <v>6.2962962962962964E-3</v>
       </c>
       <c r="I647" s="1">
-        <v>46176.422569444447</v>
+        <v>46174.644907407404</v>
       </c>
       <c r="J647">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K647" t="s">
         <v>11</v>
@@ -18789,22 +18786,22 @@
         <v>35</v>
       </c>
       <c r="C648">
-        <v>614</v>
+        <v>3818</v>
       </c>
       <c r="D648" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F648" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G648" t="s">
         <v>10</v>
       </c>
       <c r="H648" s="2">
-        <v>7.789351851851852E-3</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I648" s="1">
-        <v>46176.423263888886</v>
+        <v>46174.645601851851</v>
       </c>
       <c r="J648">
         <v>0</v>
@@ -18818,22 +18815,22 @@
         <v>35</v>
       </c>
       <c r="C649">
-        <v>623</v>
+        <v>80</v>
       </c>
       <c r="D649" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F649" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G649" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H649" s="2">
-        <v>7.3495370370370372E-3</v>
+        <v>0</v>
       </c>
       <c r="I649" s="1">
-        <v>46176.423263888886</v>
+        <v>46176.42465277778</v>
       </c>
       <c r="J649">
         <v>1</v>
@@ -18843,294 +18840,94 @@
       </c>
     </row>
     <row r="650" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B650" t="s">
-        <v>35</v>
-      </c>
-      <c r="C650">
-        <v>80</v>
-      </c>
-      <c r="D650" t="s">
-        <v>56</v>
-      </c>
-      <c r="F650" t="s">
-        <v>91</v>
-      </c>
-      <c r="G650" t="s">
-        <v>13</v>
-      </c>
-      <c r="H650" s="2">
-        <v>0</v>
-      </c>
-      <c r="I650" s="1">
-        <v>46176.42465277778</v>
-      </c>
-      <c r="J650">
-        <v>1</v>
-      </c>
-      <c r="K650" t="s">
-        <v>11</v>
-      </c>
+      <c r="H650" s="2"/>
+      <c r="I650" s="1"/>
     </row>
     <row r="651" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B651" t="s">
-        <v>35</v>
-      </c>
-      <c r="C651">
-        <v>772</v>
-      </c>
-      <c r="D651" t="s">
-        <v>49</v>
-      </c>
-      <c r="F651" t="s">
-        <v>89</v>
-      </c>
-      <c r="G651" t="s">
-        <v>10</v>
-      </c>
-      <c r="H651" s="2">
-        <v>8.0439814814814818E-3</v>
-      </c>
-      <c r="I651" s="1">
-        <v>46174.642824074072</v>
-      </c>
-      <c r="J651">
-        <v>0</v>
-      </c>
-      <c r="K651" t="s">
-        <v>11</v>
-      </c>
+      <c r="H651" s="2"/>
+      <c r="I651" s="1"/>
     </row>
     <row r="652" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B652" t="s">
-        <v>35</v>
-      </c>
-      <c r="C652">
-        <v>623</v>
-      </c>
-      <c r="D652" t="s">
-        <v>50</v>
-      </c>
-      <c r="F652" t="s">
-        <v>91</v>
-      </c>
-      <c r="G652" t="s">
-        <v>13</v>
-      </c>
-      <c r="H652" s="2">
-        <v>0</v>
-      </c>
-      <c r="I652" s="1">
-        <v>46176.423263888886</v>
-      </c>
-      <c r="J652">
-        <v>0</v>
-      </c>
-      <c r="K652" t="s">
-        <v>11</v>
-      </c>
+      <c r="H652" s="2"/>
+      <c r="I652" s="1"/>
     </row>
     <row r="653" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B653" t="s">
-        <v>35</v>
-      </c>
-      <c r="C653">
-        <v>72</v>
-      </c>
-      <c r="D653" t="s">
-        <v>51</v>
-      </c>
-      <c r="F653" t="s">
-        <v>91</v>
-      </c>
-      <c r="G653" t="s">
-        <v>13</v>
-      </c>
-      <c r="H653" s="2">
-        <v>0</v>
-      </c>
-      <c r="I653" s="1">
-        <v>46176.423958333333</v>
-      </c>
-      <c r="J653">
-        <v>0</v>
-      </c>
-      <c r="K653" t="s">
-        <v>11</v>
-      </c>
+      <c r="H653" s="2"/>
+      <c r="I653" s="1"/>
     </row>
     <row r="654" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B654" t="s">
-        <v>35</v>
-      </c>
-      <c r="C654">
-        <v>245</v>
-      </c>
-      <c r="D654" t="s">
-        <v>52</v>
-      </c>
-      <c r="F654" t="s">
-        <v>89</v>
-      </c>
-      <c r="G654" t="s">
-        <v>10</v>
-      </c>
-      <c r="H654" s="2">
-        <v>6.4814814814814813E-3</v>
-      </c>
-      <c r="I654" s="1">
-        <v>46174.644212962965</v>
-      </c>
-      <c r="J654">
-        <v>0</v>
-      </c>
-      <c r="K654" t="s">
-        <v>11</v>
-      </c>
+      <c r="H654" s="2"/>
+      <c r="I654" s="1"/>
     </row>
     <row r="655" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B655" t="s">
-        <v>35</v>
-      </c>
-      <c r="C655">
-        <v>84</v>
-      </c>
-      <c r="D655" t="s">
-        <v>55</v>
-      </c>
-      <c r="F655" t="s">
-        <v>89</v>
-      </c>
-      <c r="G655" t="s">
-        <v>10</v>
-      </c>
-      <c r="H655" s="2">
-        <v>6.2962962962962964E-3</v>
-      </c>
-      <c r="I655" s="1">
-        <v>46174.644907407404</v>
-      </c>
-      <c r="J655">
-        <v>0</v>
-      </c>
-      <c r="K655" t="s">
-        <v>11</v>
-      </c>
+      <c r="H655" s="2"/>
+      <c r="I655" s="1"/>
     </row>
     <row r="656" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B656" t="s">
-        <v>35</v>
-      </c>
-      <c r="C656">
-        <v>3818</v>
-      </c>
-      <c r="D656" t="s">
-        <v>81</v>
-      </c>
-      <c r="F656" t="s">
-        <v>89</v>
-      </c>
-      <c r="G656" t="s">
-        <v>10</v>
-      </c>
-      <c r="H656" s="2">
-        <v>7.013888888888889E-3</v>
-      </c>
-      <c r="I656" s="1">
-        <v>46174.645601851851</v>
-      </c>
-      <c r="J656">
-        <v>0</v>
-      </c>
-      <c r="K656" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="657" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B657" t="s">
-        <v>35</v>
-      </c>
-      <c r="C657">
-        <v>80</v>
-      </c>
-      <c r="D657" t="s">
-        <v>56</v>
-      </c>
-      <c r="F657" t="s">
-        <v>91</v>
-      </c>
-      <c r="G657" t="s">
-        <v>13</v>
-      </c>
-      <c r="H657" s="2">
-        <v>0</v>
-      </c>
-      <c r="I657" s="1">
-        <v>46176.42465277778</v>
-      </c>
-      <c r="J657">
-        <v>0</v>
-      </c>
-      <c r="K657" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="658" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H656" s="2"/>
+      <c r="I656" s="1"/>
+    </row>
+    <row r="657" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H657" s="2"/>
+      <c r="I657" s="1"/>
+    </row>
+    <row r="658" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H658" s="2"/>
       <c r="I658" s="1"/>
     </row>
-    <row r="659" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="659" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H659" s="2"/>
       <c r="I659" s="1"/>
     </row>
-    <row r="660" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="660" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H660" s="2"/>
       <c r="I660" s="1"/>
     </row>
-    <row r="661" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="661" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H661" s="2"/>
       <c r="I661" s="1"/>
     </row>
-    <row r="662" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="662" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H662" s="2"/>
       <c r="I662" s="1"/>
     </row>
-    <row r="663" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="663" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H663" s="2"/>
       <c r="I663" s="1"/>
     </row>
-    <row r="664" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="664" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H664" s="2"/>
       <c r="I664" s="1"/>
     </row>
-    <row r="665" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="665" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H665" s="2"/>
       <c r="I665" s="1"/>
     </row>
-    <row r="666" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="666" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H666" s="2"/>
       <c r="I666" s="1"/>
     </row>
-    <row r="667" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="667" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H667" s="2"/>
       <c r="I667" s="1"/>
     </row>
-    <row r="668" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="668" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H668" s="2"/>
       <c r="I668" s="1"/>
     </row>
-    <row r="669" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="669" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H669" s="2"/>
       <c r="I669" s="1"/>
     </row>
-    <row r="670" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="670" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H670" s="2"/>
       <c r="I670" s="1"/>
     </row>
-    <row r="671" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="671" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H671" s="2"/>
       <c r="I671" s="1"/>
     </row>
-    <row r="672" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="672" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H672" s="2"/>
       <c r="I672" s="1"/>
     </row>
@@ -19287,7 +19084,6 @@
       <c r="I710" s="1"/>
     </row>
     <row r="711" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H711" s="2"/>
       <c r="I711" s="1"/>
     </row>
     <row r="712" spans="8:9" x14ac:dyDescent="0.3">
@@ -19319,6 +19115,7 @@
       <c r="I718" s="1"/>
     </row>
     <row r="719" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H719" s="2"/>
       <c r="I719" s="1"/>
     </row>
     <row r="720" spans="8:9" x14ac:dyDescent="0.3">
@@ -19374,7 +19171,6 @@
       <c r="I732" s="1"/>
     </row>
     <row r="733" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H733" s="2"/>
       <c r="I733" s="1"/>
     </row>
     <row r="734" spans="8:9" x14ac:dyDescent="0.3">
@@ -19406,6 +19202,7 @@
       <c r="I740" s="1"/>
     </row>
     <row r="741" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H741" s="2"/>
       <c r="I741" s="1"/>
     </row>
     <row r="742" spans="8:9" x14ac:dyDescent="0.3">
@@ -19517,7 +19314,6 @@
       <c r="I768" s="1"/>
     </row>
     <row r="769" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H769" s="2"/>
       <c r="I769" s="1"/>
     </row>
     <row r="770" spans="8:9" x14ac:dyDescent="0.3">
@@ -19549,6 +19345,7 @@
       <c r="I776" s="1"/>
     </row>
     <row r="777" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H777" s="2"/>
       <c r="I777" s="1"/>
     </row>
     <row r="778" spans="8:9" x14ac:dyDescent="0.3">
@@ -19580,7 +19377,6 @@
       <c r="I784" s="1"/>
     </row>
     <row r="785" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H785" s="2"/>
       <c r="I785" s="1"/>
     </row>
     <row r="786" spans="8:9" x14ac:dyDescent="0.3">
@@ -19612,6 +19408,7 @@
       <c r="I792" s="1"/>
     </row>
     <row r="793" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H793" s="2"/>
       <c r="I793" s="1"/>
     </row>
     <row r="794" spans="8:9" x14ac:dyDescent="0.3">
@@ -19875,7 +19672,6 @@
       <c r="I858" s="1"/>
     </row>
     <row r="859" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H859" s="2"/>
       <c r="I859" s="1"/>
     </row>
     <row r="860" spans="8:9" x14ac:dyDescent="0.3">
@@ -19903,10 +19699,10 @@
       <c r="I865" s="1"/>
     </row>
     <row r="866" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H866" s="2"/>
       <c r="I866" s="1"/>
     </row>
     <row r="867" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H867" s="2"/>
       <c r="I867" s="1"/>
     </row>
     <row r="868" spans="8:9" x14ac:dyDescent="0.3">
@@ -19934,6 +19730,7 @@
       <c r="I873" s="1"/>
     </row>
     <row r="874" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H874" s="2"/>
       <c r="I874" s="1"/>
     </row>
     <row r="875" spans="8:9" x14ac:dyDescent="0.3">
@@ -20013,7 +19810,6 @@
       <c r="I893" s="1"/>
     </row>
     <row r="894" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H894" s="2"/>
       <c r="I894" s="1"/>
     </row>
     <row r="895" spans="8:9" x14ac:dyDescent="0.3">
@@ -20045,6 +19841,7 @@
       <c r="I901" s="1"/>
     </row>
     <row r="902" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H902" s="2"/>
       <c r="I902" s="1"/>
     </row>
     <row r="903" spans="8:9" x14ac:dyDescent="0.3">
@@ -20116,7 +19913,6 @@
       <c r="I919" s="1"/>
     </row>
     <row r="920" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H920" s="2"/>
       <c r="I920" s="1"/>
     </row>
     <row r="921" spans="8:9" x14ac:dyDescent="0.3">
@@ -20132,7 +19928,6 @@
       <c r="I923" s="1"/>
     </row>
     <row r="924" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H924" s="2"/>
       <c r="I924" s="1"/>
     </row>
     <row r="925" spans="8:9" x14ac:dyDescent="0.3">
@@ -20148,6 +19943,7 @@
       <c r="I927" s="1"/>
     </row>
     <row r="928" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H928" s="2"/>
       <c r="I928" s="1"/>
     </row>
     <row r="929" spans="8:9" x14ac:dyDescent="0.3">
@@ -20163,6 +19959,7 @@
       <c r="I931" s="1"/>
     </row>
     <row r="932" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H932" s="2"/>
       <c r="I932" s="1"/>
     </row>
     <row r="933" spans="8:9" x14ac:dyDescent="0.3">
@@ -20278,7 +20075,6 @@
       <c r="I960" s="1"/>
     </row>
     <row r="961" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H961" s="2"/>
       <c r="I961" s="1"/>
     </row>
     <row r="962" spans="8:9" x14ac:dyDescent="0.3">
@@ -20310,6 +20106,7 @@
       <c r="I968" s="1"/>
     </row>
     <row r="969" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H969" s="2"/>
       <c r="I969" s="1"/>
     </row>
     <row r="970" spans="8:9" x14ac:dyDescent="0.3">
@@ -20441,7 +20238,6 @@
       <c r="I1001" s="1"/>
     </row>
     <row r="1002" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
     </row>
     <row r="1003" spans="8:9" x14ac:dyDescent="0.3">
@@ -20473,6 +20269,7 @@
       <c r="I1009" s="1"/>
     </row>
     <row r="1010" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1010" s="2"/>
       <c r="I1010" s="1"/>
     </row>
     <row r="1011" spans="8:9" x14ac:dyDescent="0.3">
@@ -20500,7 +20297,6 @@
       <c r="I1016" s="1"/>
     </row>
     <row r="1017" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1017" s="2"/>
       <c r="I1017" s="1"/>
     </row>
     <row r="1018" spans="8:9" x14ac:dyDescent="0.3">
@@ -20532,6 +20328,7 @@
       <c r="I1024" s="1"/>
     </row>
     <row r="1025" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1025" s="2"/>
       <c r="I1025" s="1"/>
     </row>
     <row r="1026" spans="8:9" x14ac:dyDescent="0.3">
@@ -20791,7 +20588,6 @@
       <c r="I1089" s="1"/>
     </row>
     <row r="1090" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1090" s="2"/>
       <c r="I1090" s="1"/>
     </row>
     <row r="1091" spans="8:9" x14ac:dyDescent="0.3">
@@ -20823,6 +20619,7 @@
       <c r="I1097" s="1"/>
     </row>
     <row r="1098" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1098" s="2"/>
       <c r="I1098" s="1"/>
     </row>
     <row r="1099" spans="8:9" x14ac:dyDescent="0.3">
@@ -21174,7 +20971,6 @@
       <c r="I1185" s="1"/>
     </row>
     <row r="1186" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1186" s="2"/>
       <c r="I1186" s="1"/>
     </row>
     <row r="1187" spans="8:9" x14ac:dyDescent="0.3">
@@ -21206,6 +21002,7 @@
       <c r="I1193" s="1"/>
     </row>
     <row r="1194" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
     </row>
     <row r="1195" spans="8:9" x14ac:dyDescent="0.3">
@@ -21369,7 +21166,6 @@
       <c r="I1234" s="1"/>
     </row>
     <row r="1235" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1235" s="2"/>
       <c r="I1235" s="1"/>
     </row>
     <row r="1236" spans="8:9" x14ac:dyDescent="0.3">
@@ -21401,6 +21197,7 @@
       <c r="I1242" s="1"/>
     </row>
     <row r="1243" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1243" s="2"/>
       <c r="I1243" s="1"/>
     </row>
     <row r="1244" spans="8:9" x14ac:dyDescent="0.3">
@@ -21408,7 +21205,6 @@
       <c r="I1244" s="1"/>
     </row>
     <row r="1245" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1245" s="2"/>
       <c r="I1245" s="1"/>
     </row>
     <row r="1246" spans="8:9" x14ac:dyDescent="0.3">
@@ -21420,7 +21216,6 @@
       <c r="I1247" s="1"/>
     </row>
     <row r="1248" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1248" s="2"/>
       <c r="I1248" s="1"/>
     </row>
     <row r="1249" spans="8:9" x14ac:dyDescent="0.3">
@@ -21440,6 +21235,7 @@
       <c r="I1252" s="1"/>
     </row>
     <row r="1253" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1253" s="2"/>
       <c r="I1253" s="1"/>
     </row>
     <row r="1254" spans="8:9" x14ac:dyDescent="0.3">
@@ -21451,6 +21247,7 @@
       <c r="I1255" s="1"/>
     </row>
     <row r="1256" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
     </row>
     <row r="1257" spans="8:9" x14ac:dyDescent="0.3">
@@ -21470,7 +21267,6 @@
       <c r="I1260" s="1"/>
     </row>
     <row r="1261" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1261" s="2"/>
       <c r="I1261" s="1"/>
     </row>
     <row r="1262" spans="8:9" x14ac:dyDescent="0.3">
@@ -21502,6 +21298,7 @@
       <c r="I1268" s="1"/>
     </row>
     <row r="1269" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1269" s="2"/>
       <c r="I1269" s="1"/>
     </row>
     <row r="1270" spans="8:9" x14ac:dyDescent="0.3">
@@ -21573,7 +21370,6 @@
       <c r="I1286" s="1"/>
     </row>
     <row r="1287" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1287" s="2"/>
       <c r="I1287" s="1"/>
     </row>
     <row r="1288" spans="8:9" x14ac:dyDescent="0.3">
@@ -21605,6 +21401,7 @@
       <c r="I1294" s="1"/>
     </row>
     <row r="1295" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1295" s="2"/>
       <c r="I1295" s="1"/>
     </row>
     <row r="1296" spans="8:9" x14ac:dyDescent="0.3">
@@ -21672,7 +21469,6 @@
       <c r="I1311" s="1"/>
     </row>
     <row r="1312" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
     </row>
     <row r="1313" spans="8:9" x14ac:dyDescent="0.3">
@@ -21704,6 +21500,7 @@
       <c r="I1319" s="1"/>
     </row>
     <row r="1320" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1320" s="2"/>
       <c r="I1320" s="1"/>
     </row>
     <row r="1321" spans="8:9" x14ac:dyDescent="0.3">
@@ -21751,7 +21548,6 @@
       <c r="I1331" s="1"/>
     </row>
     <row r="1332" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1332" s="2"/>
       <c r="I1332" s="1"/>
     </row>
     <row r="1333" spans="8:9" x14ac:dyDescent="0.3">
@@ -21806,7 +21602,6 @@
       <c r="I1345" s="1"/>
     </row>
     <row r="1346" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1346" s="2"/>
       <c r="I1346" s="1"/>
     </row>
     <row r="1347" spans="8:9" x14ac:dyDescent="0.3">
@@ -21814,6 +21609,7 @@
       <c r="I1347" s="1"/>
     </row>
     <row r="1348" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1348" s="2"/>
       <c r="I1348" s="1"/>
     </row>
     <row r="1349" spans="8:9" x14ac:dyDescent="0.3">
@@ -21837,6 +21633,7 @@
       <c r="I1353" s="1"/>
     </row>
     <row r="1354" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1354" s="2"/>
       <c r="I1354" s="1"/>
     </row>
     <row r="1355" spans="8:9" x14ac:dyDescent="0.3">
@@ -21864,7 +21661,6 @@
       <c r="I1360" s="1"/>
     </row>
     <row r="1361" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1361" s="2"/>
       <c r="I1361" s="1"/>
     </row>
     <row r="1362" spans="8:9" x14ac:dyDescent="0.3">
@@ -21876,7 +21672,6 @@
       <c r="I1363" s="1"/>
     </row>
     <row r="1364" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1364" s="2"/>
       <c r="I1364" s="1"/>
     </row>
     <row r="1365" spans="8:9" x14ac:dyDescent="0.3">
@@ -21896,6 +21691,7 @@
       <c r="I1368" s="1"/>
     </row>
     <row r="1369" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1369" s="2"/>
       <c r="I1369" s="1"/>
     </row>
     <row r="1370" spans="8:9" x14ac:dyDescent="0.3">
@@ -21903,10 +21699,10 @@
       <c r="I1370" s="1"/>
     </row>
     <row r="1371" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1371" s="2"/>
       <c r="I1371" s="1"/>
     </row>
     <row r="1372" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1372" s="2"/>
       <c r="I1372" s="1"/>
     </row>
     <row r="1373" spans="8:9" x14ac:dyDescent="0.3">
@@ -21918,7 +21714,6 @@
       <c r="I1374" s="1"/>
     </row>
     <row r="1375" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1375" s="2"/>
       <c r="I1375" s="1"/>
     </row>
     <row r="1376" spans="8:9" x14ac:dyDescent="0.3">
@@ -21934,10 +21729,10 @@
       <c r="I1378" s="1"/>
     </row>
     <row r="1379" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1379" s="2"/>
       <c r="I1379" s="1"/>
     </row>
     <row r="1380" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1380" s="2"/>
       <c r="I1380" s="1"/>
     </row>
     <row r="1381" spans="8:9" x14ac:dyDescent="0.3">
@@ -21949,6 +21744,7 @@
       <c r="I1382" s="1"/>
     </row>
     <row r="1383" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1383" s="2"/>
       <c r="I1383" s="1"/>
     </row>
     <row r="1384" spans="8:9" x14ac:dyDescent="0.3">
@@ -21956,7 +21752,6 @@
       <c r="I1384" s="1"/>
     </row>
     <row r="1385" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1385" s="2"/>
       <c r="I1385" s="1"/>
     </row>
     <row r="1386" spans="8:9" x14ac:dyDescent="0.3">
@@ -21968,6 +21763,7 @@
       <c r="I1387" s="1"/>
     </row>
     <row r="1388" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1388" s="2"/>
       <c r="I1388" s="1"/>
     </row>
     <row r="1389" spans="8:9" x14ac:dyDescent="0.3">
@@ -21987,6 +21783,7 @@
       <c r="I1392" s="1"/>
     </row>
     <row r="1393" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1393" s="2"/>
       <c r="I1393" s="1"/>
     </row>
     <row r="1394" spans="8:9" x14ac:dyDescent="0.3">
@@ -22018,7 +21815,6 @@
       <c r="I1400" s="1"/>
     </row>
     <row r="1401" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1401" s="2"/>
       <c r="I1401" s="1"/>
     </row>
     <row r="1402" spans="8:9" x14ac:dyDescent="0.3">
@@ -22050,6 +21846,7 @@
       <c r="I1408" s="1"/>
     </row>
     <row r="1409" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1409" s="2"/>
       <c r="I1409" s="1"/>
     </row>
     <row r="1410" spans="8:9" x14ac:dyDescent="0.3">
@@ -22089,7 +21886,6 @@
       <c r="I1418" s="1"/>
     </row>
     <row r="1419" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1419" s="2"/>
       <c r="I1419" s="1"/>
     </row>
     <row r="1420" spans="8:9" x14ac:dyDescent="0.3">
@@ -22121,6 +21917,7 @@
       <c r="I1426" s="1"/>
     </row>
     <row r="1427" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
     </row>
     <row r="1428" spans="8:9" x14ac:dyDescent="0.3">
@@ -22136,7 +21933,6 @@
       <c r="I1430" s="1"/>
     </row>
     <row r="1431" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1431" s="2"/>
       <c r="I1431" s="1"/>
     </row>
     <row r="1432" spans="8:9" x14ac:dyDescent="0.3">
@@ -22168,6 +21964,7 @@
       <c r="I1438" s="1"/>
     </row>
     <row r="1439" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1439" s="2"/>
       <c r="I1439" s="1"/>
     </row>
     <row r="1440" spans="8:9" x14ac:dyDescent="0.3">
@@ -22267,11 +22064,9 @@
       <c r="I1463" s="1"/>
     </row>
     <row r="1464" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1464" s="2"/>
       <c r="I1464" s="1"/>
     </row>
     <row r="1465" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1465" s="2"/>
       <c r="I1465" s="1"/>
     </row>
     <row r="1466" spans="8:9" x14ac:dyDescent="0.3">
@@ -22299,9 +22094,11 @@
       <c r="I1471" s="1"/>
     </row>
     <row r="1472" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1472" s="2"/>
       <c r="I1472" s="1"/>
     </row>
     <row r="1473" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1473" s="2"/>
       <c r="I1473" s="1"/>
     </row>
     <row r="1474" spans="8:9" x14ac:dyDescent="0.3">
@@ -22329,7 +22126,6 @@
       <c r="I1479" s="1"/>
     </row>
     <row r="1480" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1480" s="2"/>
       <c r="I1480" s="1"/>
     </row>
     <row r="1481" spans="8:9" x14ac:dyDescent="0.3">
@@ -22361,6 +22157,7 @@
       <c r="I1487" s="1"/>
     </row>
     <row r="1488" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1488" s="2"/>
       <c r="I1488" s="1"/>
     </row>
     <row r="1489" spans="8:9" x14ac:dyDescent="0.3">
@@ -22520,7 +22317,6 @@
       <c r="I1527" s="1"/>
     </row>
     <row r="1528" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1528" s="2"/>
       <c r="I1528" s="1"/>
     </row>
     <row r="1529" spans="8:9" x14ac:dyDescent="0.3">
@@ -22552,6 +22348,7 @@
       <c r="I1535" s="1"/>
     </row>
     <row r="1536" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1536" s="2"/>
       <c r="I1536" s="1"/>
     </row>
     <row r="1537" spans="8:9" x14ac:dyDescent="0.3">
@@ -22563,7 +22360,6 @@
       <c r="I1538" s="1"/>
     </row>
     <row r="1539" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1539" s="2"/>
       <c r="I1539" s="1"/>
     </row>
     <row r="1540" spans="8:9" x14ac:dyDescent="0.3">
@@ -22626,10 +22422,10 @@
       <c r="I1554" s="1"/>
     </row>
     <row r="1555" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1555" s="2"/>
       <c r="I1555" s="1"/>
     </row>
     <row r="1556" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1556" s="2"/>
       <c r="I1556" s="1"/>
     </row>
     <row r="1557" spans="8:9" x14ac:dyDescent="0.3">
@@ -22653,7 +22449,6 @@
       <c r="I1561" s="1"/>
     </row>
     <row r="1562" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1562" s="2"/>
       <c r="I1562" s="1"/>
     </row>
     <row r="1563" spans="8:9" x14ac:dyDescent="0.3">
@@ -22661,6 +22456,7 @@
       <c r="I1563" s="1"/>
     </row>
     <row r="1564" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1564" s="2"/>
       <c r="I1564" s="1"/>
     </row>
     <row r="1565" spans="8:9" x14ac:dyDescent="0.3">
@@ -22684,6 +22480,7 @@
       <c r="I1569" s="1"/>
     </row>
     <row r="1570" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1570" s="2"/>
       <c r="I1570" s="1"/>
     </row>
     <row r="1571" spans="8:9" x14ac:dyDescent="0.3">
@@ -22731,11 +22528,9 @@
       <c r="I1581" s="1"/>
     </row>
     <row r="1582" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1582" s="2"/>
       <c r="I1582" s="1"/>
     </row>
     <row r="1583" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1583" s="2"/>
       <c r="I1583" s="1"/>
     </row>
     <row r="1584" spans="8:9" x14ac:dyDescent="0.3">
@@ -22759,17 +22554,17 @@
       <c r="I1588" s="1"/>
     </row>
     <row r="1589" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1589" s="2"/>
       <c r="I1589" s="1"/>
     </row>
     <row r="1590" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1590" s="2"/>
       <c r="I1590" s="1"/>
     </row>
     <row r="1591" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1591" s="2"/>
       <c r="I1591" s="1"/>
     </row>
     <row r="1592" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
     </row>
     <row r="1593" spans="8:9" x14ac:dyDescent="0.3">
@@ -22785,10 +22580,10 @@
       <c r="I1595" s="1"/>
     </row>
     <row r="1596" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1596" s="2"/>
       <c r="I1596" s="1"/>
     </row>
     <row r="1597" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1597" s="2"/>
       <c r="I1597" s="1"/>
     </row>
     <row r="1598" spans="8:9" x14ac:dyDescent="0.3">
@@ -22796,10 +22591,10 @@
       <c r="I1598" s="1"/>
     </row>
     <row r="1599" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1599" s="2"/>
       <c r="I1599" s="1"/>
     </row>
     <row r="1600" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1600" s="2"/>
       <c r="I1600" s="1"/>
     </row>
     <row r="1601" spans="8:9" x14ac:dyDescent="0.3">
@@ -22822,10 +22617,10 @@
       <c r="I1605" s="1"/>
     </row>
     <row r="1606" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1606" s="2"/>
       <c r="I1606" s="1"/>
     </row>
     <row r="1607" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1607" s="2"/>
       <c r="I1607" s="1"/>
     </row>
     <row r="1608" spans="8:9" x14ac:dyDescent="0.3">
@@ -22845,17 +22640,17 @@
       <c r="I1611" s="1"/>
     </row>
     <row r="1612" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1612" s="2"/>
       <c r="I1612" s="1"/>
     </row>
     <row r="1613" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1613" s="2"/>
       <c r="I1613" s="1"/>
     </row>
     <row r="1614" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1614" s="2"/>
       <c r="I1614" s="1"/>
     </row>
     <row r="1615" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1615" s="2"/>
       <c r="I1615" s="1"/>
     </row>
     <row r="1616" spans="8:9" x14ac:dyDescent="0.3">
@@ -22863,7 +22658,6 @@
       <c r="I1616" s="1"/>
     </row>
     <row r="1617" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1617" s="2"/>
       <c r="I1617" s="1"/>
     </row>
     <row r="1618" spans="8:9" x14ac:dyDescent="0.3">
@@ -22879,13 +22673,14 @@
       <c r="I1620" s="1"/>
     </row>
     <row r="1621" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1621" s="2"/>
       <c r="I1621" s="1"/>
     </row>
     <row r="1622" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1622" s="2"/>
       <c r="I1622" s="1"/>
     </row>
     <row r="1623" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1623" s="2"/>
       <c r="I1623" s="1"/>
     </row>
     <row r="1624" spans="8:9" x14ac:dyDescent="0.3">
@@ -22896,7 +22691,6 @@
       <c r="I1625" s="1"/>
     </row>
     <row r="1626" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1626" s="2"/>
       <c r="I1626" s="1"/>
     </row>
     <row r="1627" spans="8:9" x14ac:dyDescent="0.3">
@@ -22912,6 +22706,7 @@
       <c r="I1629" s="1"/>
     </row>
     <row r="1630" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1630" s="2"/>
       <c r="I1630" s="1"/>
     </row>
     <row r="1631" spans="8:9" x14ac:dyDescent="0.3">
@@ -22923,9 +22718,11 @@
       <c r="I1632" s="1"/>
     </row>
     <row r="1633" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1633" s="2"/>
       <c r="I1633" s="1"/>
     </row>
     <row r="1634" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1634" s="2"/>
       <c r="I1634" s="1"/>
     </row>
     <row r="1635" spans="8:9" x14ac:dyDescent="0.3">
@@ -22953,7 +22750,6 @@
       <c r="I1640" s="1"/>
     </row>
     <row r="1641" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1641" s="2"/>
       <c r="I1641" s="1"/>
     </row>
     <row r="1642" spans="8:9" x14ac:dyDescent="0.3">
@@ -22969,7 +22765,6 @@
       <c r="I1644" s="1"/>
     </row>
     <row r="1645" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1645" s="2"/>
       <c r="I1645" s="1"/>
     </row>
     <row r="1646" spans="8:9" x14ac:dyDescent="0.3">
@@ -22985,6 +22780,7 @@
       <c r="I1648" s="1"/>
     </row>
     <row r="1649" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1649" s="2"/>
       <c r="I1649" s="1"/>
     </row>
     <row r="1650" spans="8:9" x14ac:dyDescent="0.3">
@@ -23000,6 +22796,7 @@
       <c r="I1652" s="1"/>
     </row>
     <row r="1653" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1653" s="2"/>
       <c r="I1653" s="1"/>
     </row>
     <row r="1654" spans="8:9" x14ac:dyDescent="0.3">
@@ -23575,11 +23372,9 @@
       <c r="I1796" s="1"/>
     </row>
     <row r="1797" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1797" s="2"/>
       <c r="I1797" s="1"/>
     </row>
     <row r="1798" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1798" s="2"/>
       <c r="I1798" s="1"/>
     </row>
     <row r="1799" spans="8:9" x14ac:dyDescent="0.3">
@@ -23587,15 +23382,12 @@
       <c r="I1799" s="1"/>
     </row>
     <row r="1800" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1800" s="2"/>
       <c r="I1800" s="1"/>
     </row>
     <row r="1801" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1801" s="2"/>
       <c r="I1801" s="1"/>
     </row>
     <row r="1802" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1802" s="2"/>
       <c r="I1802" s="1"/>
     </row>
     <row r="1803" spans="8:9" x14ac:dyDescent="0.3">
@@ -23620,9 +23412,11 @@
       <c r="I1808" s="1"/>
     </row>
     <row r="1809" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1809" s="2"/>
       <c r="I1809" s="1"/>
     </row>
     <row r="1810" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1810" s="2"/>
       <c r="I1810" s="1"/>
     </row>
     <row r="1811" spans="8:9" x14ac:dyDescent="0.3">
@@ -23630,7 +23424,6 @@
       <c r="I1811" s="1"/>
     </row>
     <row r="1812" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1812" s="2"/>
       <c r="I1812" s="1"/>
     </row>
     <row r="1813" spans="8:9" x14ac:dyDescent="0.3">
@@ -23647,15 +23440,12 @@
       <c r="I1816" s="1"/>
     </row>
     <row r="1817" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1817" s="2"/>
       <c r="I1817" s="1"/>
     </row>
     <row r="1818" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1818" s="2"/>
       <c r="I1818" s="1"/>
     </row>
     <row r="1819" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1819" s="2"/>
       <c r="I1819" s="1"/>
     </row>
     <row r="1820" spans="8:9" x14ac:dyDescent="0.3">
@@ -23665,6 +23455,7 @@
       <c r="I1821" s="1"/>
     </row>
     <row r="1822" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1822" s="2"/>
       <c r="I1822" s="1"/>
     </row>
     <row r="1823" spans="8:9" x14ac:dyDescent="0.3">
@@ -23678,19 +23469,21 @@
       <c r="I1825" s="1"/>
     </row>
     <row r="1826" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1826" s="2"/>
       <c r="I1826" s="1"/>
     </row>
     <row r="1827" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1827" s="1"/>
     </row>
     <row r="1828" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1828" s="2"/>
       <c r="I1828" s="1"/>
     </row>
     <row r="1829" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1829" s="2"/>
       <c r="I1829" s="1"/>
     </row>
     <row r="1830" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1830" s="2"/>
       <c r="I1830" s="1"/>
     </row>
     <row r="1831" spans="8:9" x14ac:dyDescent="0.3">
@@ -23701,6 +23494,7 @@
       <c r="I1832" s="1"/>
     </row>
     <row r="1833" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1833" s="2"/>
       <c r="I1833" s="1"/>
     </row>
     <row r="1834" spans="8:9" x14ac:dyDescent="0.3">
@@ -23708,6 +23502,7 @@
       <c r="I1834" s="1"/>
     </row>
     <row r="1835" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1835" s="2"/>
       <c r="I1835" s="1"/>
     </row>
     <row r="1836" spans="8:9" x14ac:dyDescent="0.3">
@@ -23715,7 +23510,6 @@
       <c r="I1836" s="1"/>
     </row>
     <row r="1837" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1837" s="2"/>
       <c r="I1837" s="1"/>
     </row>
     <row r="1838" spans="8:9" x14ac:dyDescent="0.3">
@@ -23726,6 +23520,7 @@
       <c r="I1839" s="1"/>
     </row>
     <row r="1840" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1840" s="2"/>
       <c r="I1840" s="1"/>
     </row>
     <row r="1841" spans="8:9" x14ac:dyDescent="0.3">
@@ -23733,11 +23528,9 @@
       <c r="I1841" s="1"/>
     </row>
     <row r="1842" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1842" s="2"/>
       <c r="I1842" s="1"/>
     </row>
     <row r="1843" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1843" s="2"/>
       <c r="I1843" s="1"/>
     </row>
     <row r="1844" spans="8:9" x14ac:dyDescent="0.3">
@@ -23748,31 +23541,31 @@
       <c r="I1845" s="1"/>
     </row>
     <row r="1846" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1846" s="2"/>
       <c r="I1846" s="1"/>
     </row>
     <row r="1847" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1847" s="2"/>
       <c r="I1847" s="1"/>
     </row>
     <row r="1848" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1848" s="2"/>
       <c r="I1848" s="1"/>
     </row>
     <row r="1849" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1849" s="2"/>
       <c r="I1849" s="1"/>
     </row>
     <row r="1850" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1850" s="2"/>
       <c r="I1850" s="1"/>
     </row>
     <row r="1851" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1851" s="2"/>
       <c r="I1851" s="1"/>
     </row>
     <row r="1852" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1852" s="2"/>
       <c r="I1852" s="1"/>
     </row>
     <row r="1853" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1853" s="2"/>
       <c r="I1853" s="1"/>
     </row>
     <row r="1854" spans="8:9" x14ac:dyDescent="0.3">
@@ -23780,16 +23573,17 @@
       <c r="I1854" s="1"/>
     </row>
     <row r="1855" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1855" s="2"/>
       <c r="I1855" s="1"/>
     </row>
     <row r="1856" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1856" s="2"/>
       <c r="I1856" s="1"/>
     </row>
     <row r="1857" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1857" s="1"/>
     </row>
     <row r="1858" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1858" s="2"/>
       <c r="I1858" s="1"/>
     </row>
     <row r="1859" spans="8:9" x14ac:dyDescent="0.3">
@@ -23804,7 +23598,6 @@
       <c r="I1861" s="1"/>
     </row>
     <row r="1862" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1862" s="2"/>
       <c r="I1862" s="1"/>
     </row>
     <row r="1863" spans="8:9" x14ac:dyDescent="0.3">
@@ -23822,10 +23615,10 @@
       <c r="I1866" s="1"/>
     </row>
     <row r="1867" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1867" s="2"/>
       <c r="I1867" s="1"/>
     </row>
     <row r="1868" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1868" s="2"/>
       <c r="I1868" s="1"/>
     </row>
     <row r="1869" spans="8:9" x14ac:dyDescent="0.3">
@@ -23840,24 +23633,23 @@
       <c r="I1871" s="1"/>
     </row>
     <row r="1872" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1872" s="2"/>
       <c r="I1872" s="1"/>
     </row>
     <row r="1873" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1873" s="1"/>
     </row>
     <row r="1874" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1874" s="2"/>
       <c r="I1874" s="1"/>
     </row>
     <row r="1875" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1875" s="2"/>
       <c r="I1875" s="1"/>
     </row>
     <row r="1876" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1876" s="2"/>
       <c r="I1876" s="1"/>
     </row>
     <row r="1877" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1877" s="2"/>
       <c r="I1877" s="1"/>
     </row>
     <row r="1878" spans="8:9" x14ac:dyDescent="0.3">
@@ -23868,13 +23660,13 @@
       <c r="I1879" s="1"/>
     </row>
     <row r="1880" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1880" s="2"/>
       <c r="I1880" s="1"/>
     </row>
     <row r="1881" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1881" s="1"/>
     </row>
     <row r="1882" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1882" s="2"/>
       <c r="I1882" s="1"/>
     </row>
     <row r="1883" spans="8:9" x14ac:dyDescent="0.3">
@@ -23882,12 +23674,15 @@
       <c r="I1883" s="1"/>
     </row>
     <row r="1884" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1884" s="2"/>
       <c r="I1884" s="1"/>
     </row>
     <row r="1885" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1885" s="2"/>
       <c r="I1885" s="1"/>
     </row>
     <row r="1886" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1886" s="2"/>
       <c r="I1886" s="1"/>
     </row>
     <row r="1887" spans="8:9" x14ac:dyDescent="0.3">
@@ -23895,17 +23690,17 @@
       <c r="I1887" s="1"/>
     </row>
     <row r="1888" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1888" s="2"/>
       <c r="I1888" s="1"/>
     </row>
     <row r="1889" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1889" s="2"/>
       <c r="I1889" s="1"/>
     </row>
     <row r="1890" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1890" s="2"/>
       <c r="I1890" s="1"/>
     </row>
     <row r="1891" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1891" s="2"/>
       <c r="I1891" s="1"/>
     </row>
     <row r="1892" spans="8:9" x14ac:dyDescent="0.3">
@@ -23921,10 +23716,10 @@
       <c r="I1894" s="1"/>
     </row>
     <row r="1895" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1895" s="2"/>
       <c r="I1895" s="1"/>
     </row>
     <row r="1896" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1896" s="2"/>
       <c r="I1896" s="1"/>
     </row>
     <row r="1897" spans="8:9" x14ac:dyDescent="0.3">
@@ -23936,6 +23731,7 @@
       <c r="I1898" s="1"/>
     </row>
     <row r="1899" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1899" s="2"/>
       <c r="I1899" s="1"/>
     </row>
     <row r="1900" spans="8:9" x14ac:dyDescent="0.3">
@@ -23951,6 +23747,7 @@
       <c r="I1902" s="1"/>
     </row>
     <row r="1903" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1903" s="2"/>
       <c r="I1903" s="1"/>
     </row>
     <row r="1904" spans="8:9" x14ac:dyDescent="0.3">
@@ -24006,7 +23803,6 @@
       <c r="I1916" s="1"/>
     </row>
     <row r="1917" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1917" s="2"/>
       <c r="I1917" s="1"/>
     </row>
     <row r="1918" spans="8:9" x14ac:dyDescent="0.3">
@@ -24014,7 +23810,6 @@
       <c r="I1918" s="1"/>
     </row>
     <row r="1919" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1919" s="2"/>
       <c r="I1919" s="1"/>
     </row>
     <row r="1920" spans="8:9" x14ac:dyDescent="0.3">
@@ -24022,11 +23817,9 @@
       <c r="I1920" s="1"/>
     </row>
     <row r="1921" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1921" s="2"/>
       <c r="I1921" s="1"/>
     </row>
     <row r="1922" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1922" s="2"/>
       <c r="I1922" s="1"/>
     </row>
     <row r="1923" spans="8:9" x14ac:dyDescent="0.3">
@@ -24048,31 +23841,30 @@
       <c r="I1927" s="1"/>
     </row>
     <row r="1928" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1928" s="2"/>
       <c r="I1928" s="1"/>
     </row>
     <row r="1929" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1929" s="2"/>
       <c r="I1929" s="1"/>
     </row>
     <row r="1930" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1930" s="2"/>
       <c r="I1930" s="1"/>
     </row>
     <row r="1931" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1931" s="2"/>
       <c r="I1931" s="1"/>
     </row>
     <row r="1932" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1932" s="2"/>
       <c r="I1932" s="1"/>
     </row>
     <row r="1933" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1933" s="1"/>
     </row>
     <row r="1934" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1934" s="2"/>
       <c r="I1934" s="1"/>
     </row>
     <row r="1935" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1935" s="2"/>
       <c r="I1935" s="1"/>
     </row>
     <row r="1936" spans="8:9" x14ac:dyDescent="0.3">
@@ -24087,12 +23879,14 @@
       <c r="I1938" s="1"/>
     </row>
     <row r="1939" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1939" s="2"/>
       <c r="I1939" s="1"/>
     </row>
     <row r="1940" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1940" s="1"/>
     </row>
     <row r="1941" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1941" s="2"/>
       <c r="I1941" s="1"/>
     </row>
     <row r="1942" spans="8:9" x14ac:dyDescent="0.3">
@@ -24106,11 +23900,9 @@
       <c r="I1944" s="1"/>
     </row>
     <row r="1945" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1945" s="2"/>
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1946" s="2"/>
       <c r="I1946" s="1"/>
     </row>
     <row r="1947" spans="8:9" x14ac:dyDescent="0.3">
@@ -24118,6 +23910,7 @@
       <c r="I1947" s="1"/>
     </row>
     <row r="1948" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1948" s="2"/>
       <c r="I1948" s="1"/>
     </row>
     <row r="1949" spans="8:9" x14ac:dyDescent="0.3">
@@ -24125,6 +23918,7 @@
       <c r="I1949" s="1"/>
     </row>
     <row r="1950" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1950" s="2"/>
       <c r="I1950" s="1"/>
     </row>
     <row r="1951" spans="8:9" x14ac:dyDescent="0.3">
@@ -24149,11 +23943,9 @@
       <c r="I1956" s="1"/>
     </row>
     <row r="1957" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
     </row>
     <row r="1958" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
     </row>
     <row r="1959" spans="8:9" x14ac:dyDescent="0.3">
@@ -24161,30 +23953,32 @@
       <c r="I1959" s="1"/>
     </row>
     <row r="1960" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1960" s="2"/>
       <c r="I1960" s="1"/>
     </row>
     <row r="1961" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1961" s="2"/>
       <c r="I1961" s="1"/>
     </row>
     <row r="1962" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1962" s="2"/>
       <c r="I1962" s="1"/>
     </row>
     <row r="1963" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1963" s="2"/>
       <c r="I1963" s="1"/>
     </row>
     <row r="1964" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1964" s="2"/>
       <c r="I1964" s="1"/>
     </row>
     <row r="1965" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
     </row>
     <row r="1966" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1966" s="2"/>
       <c r="I1966" s="1"/>
     </row>
     <row r="1967" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1967" s="2"/>
       <c r="I1967" s="1"/>
     </row>
     <row r="1968" spans="8:9" x14ac:dyDescent="0.3">
@@ -24196,7 +23990,6 @@
       <c r="I1969" s="1"/>
     </row>
     <row r="1970" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1970" s="2"/>
       <c r="I1970" s="1"/>
     </row>
     <row r="1971" spans="8:9" x14ac:dyDescent="0.3">
@@ -24206,7 +23999,6 @@
       <c r="I1972" s="1"/>
     </row>
     <row r="1973" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1973" s="2"/>
       <c r="I1973" s="1"/>
     </row>
     <row r="1974" spans="8:9" x14ac:dyDescent="0.3">
@@ -24214,10 +24006,10 @@
       <c r="I1974" s="1"/>
     </row>
     <row r="1975" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1975" s="2"/>
       <c r="I1975" s="1"/>
     </row>
     <row r="1976" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1976" s="2"/>
       <c r="I1976" s="1"/>
     </row>
     <row r="1977" spans="8:9" x14ac:dyDescent="0.3">
@@ -24234,6 +24026,7 @@
       <c r="I1980" s="1"/>
     </row>
     <row r="1981" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1981" s="2"/>
       <c r="I1981" s="1"/>
     </row>
     <row r="1982" spans="8:9" x14ac:dyDescent="0.3">
@@ -24241,27 +24034,27 @@
       <c r="I1982" s="1"/>
     </row>
     <row r="1983" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
     </row>
     <row r="1984" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
     </row>
     <row r="1985" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1985" s="2"/>
       <c r="I1985" s="1"/>
     </row>
     <row r="1986" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
     </row>
     <row r="1987" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I1987" s="1"/>
     </row>
     <row r="1988" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1988" s="2"/>
       <c r="I1988" s="1"/>
     </row>
     <row r="1989" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H1989" s="2"/>
       <c r="I1989" s="1"/>
     </row>
     <row r="1990" spans="8:9" x14ac:dyDescent="0.3">
@@ -24276,6 +24069,7 @@
       <c r="I1992" s="1"/>
     </row>
     <row r="1993" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:9" x14ac:dyDescent="0.3">
@@ -24290,6 +24084,7 @@
       <c r="I1996" s="1"/>
     </row>
     <row r="1997" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1997" s="2"/>
       <c r="I1997" s="1"/>
     </row>
     <row r="1998" spans="8:9" x14ac:dyDescent="0.3">
@@ -24297,10 +24092,10 @@
       <c r="I1998" s="1"/>
     </row>
     <row r="1999" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H1999" s="2"/>
       <c r="I1999" s="1"/>
     </row>
     <row r="2000" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
     </row>
     <row r="2001" spans="8:9" x14ac:dyDescent="0.3">
@@ -24308,22 +24103,19 @@
       <c r="I2001" s="1"/>
     </row>
     <row r="2002" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2003" s="2"/>
       <c r="I2003" s="1"/>
     </row>
     <row r="2004" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2004" s="2"/>
       <c r="I2004" s="1"/>
     </row>
     <row r="2005" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2005" s="2"/>
       <c r="I2005" s="1"/>
     </row>
     <row r="2006" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2006" s="2"/>
       <c r="I2006" s="1"/>
     </row>
     <row r="2007" spans="8:9" x14ac:dyDescent="0.3">
@@ -24338,30 +24130,32 @@
       <c r="I2009" s="1"/>
     </row>
     <row r="2010" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2010" s="2"/>
       <c r="I2010" s="1"/>
     </row>
     <row r="2011" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2011" s="2"/>
       <c r="I2011" s="1"/>
     </row>
     <row r="2012" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2012" s="2"/>
       <c r="I2012" s="1"/>
     </row>
     <row r="2013" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2013" s="2"/>
       <c r="I2013" s="1"/>
     </row>
     <row r="2014" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2014" s="2"/>
       <c r="I2014" s="1"/>
     </row>
     <row r="2015" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2015" s="2"/>
       <c r="I2015" s="1"/>
     </row>
     <row r="2016" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2016" s="2"/>
       <c r="I2016" s="1"/>
     </row>
     <row r="2017" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2017" s="2"/>
       <c r="I2017" s="1"/>
     </row>
     <row r="2018" spans="8:9" x14ac:dyDescent="0.3">
@@ -24372,7 +24166,6 @@
       <c r="I2019" s="1"/>
     </row>
     <row r="2020" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2020" s="2"/>
       <c r="I2020" s="1"/>
     </row>
     <row r="2021" spans="8:9" x14ac:dyDescent="0.3">
@@ -24384,6 +24177,7 @@
       <c r="I2022" s="1"/>
     </row>
     <row r="2023" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2023" s="2"/>
       <c r="I2023" s="1"/>
     </row>
     <row r="2024" spans="8:9" x14ac:dyDescent="0.3">
@@ -24401,18 +24195,16 @@
       <c r="I2027" s="1"/>
     </row>
     <row r="2028" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2028" s="2"/>
       <c r="I2028" s="1"/>
     </row>
     <row r="2029" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2029" s="2"/>
       <c r="I2029" s="1"/>
     </row>
     <row r="2030" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2030" s="2"/>
       <c r="I2030" s="1"/>
     </row>
     <row r="2031" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2031" s="2"/>
       <c r="I2031" s="1"/>
     </row>
     <row r="2032" spans="8:9" x14ac:dyDescent="0.3">
@@ -24423,20 +24215,20 @@
       <c r="I2033" s="1"/>
     </row>
     <row r="2034" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2034" s="2"/>
       <c r="I2034" s="1"/>
     </row>
     <row r="2035" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2035" s="2"/>
       <c r="I2035" s="1"/>
     </row>
     <row r="2036" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2036" s="2"/>
       <c r="I2036" s="1"/>
     </row>
     <row r="2037" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2037" s="1"/>
     </row>
     <row r="2038" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2038" s="2"/>
       <c r="I2038" s="1"/>
     </row>
     <row r="2039" spans="8:9" x14ac:dyDescent="0.3">
@@ -24447,26 +24239,28 @@
       <c r="I2040" s="1"/>
     </row>
     <row r="2041" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2041" s="2"/>
       <c r="I2041" s="1"/>
     </row>
     <row r="2042" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2042" s="2"/>
       <c r="I2042" s="1"/>
     </row>
     <row r="2043" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2043" s="2"/>
       <c r="I2043" s="1"/>
     </row>
     <row r="2044" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2044" s="1"/>
     </row>
     <row r="2045" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2045" s="2"/>
       <c r="I2045" s="1"/>
     </row>
     <row r="2046" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2046" s="2"/>
       <c r="I2046" s="1"/>
     </row>
     <row r="2047" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2047" s="2"/>
       <c r="I2047" s="1"/>
     </row>
     <row r="2048" spans="8:9" x14ac:dyDescent="0.3">
@@ -24474,49 +24268,46 @@
       <c r="I2048" s="1"/>
     </row>
     <row r="2049" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2049" s="2"/>
       <c r="I2049" s="1"/>
     </row>
     <row r="2050" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2050" s="2"/>
       <c r="I2050" s="1"/>
     </row>
     <row r="2051" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2051" s="2"/>
       <c r="I2051" s="1"/>
     </row>
     <row r="2052" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2052" s="2"/>
       <c r="I2052" s="1"/>
     </row>
     <row r="2053" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2053" s="2"/>
       <c r="I2053" s="1"/>
     </row>
     <row r="2054" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2054" s="1"/>
     </row>
     <row r="2055" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2055" s="2"/>
       <c r="I2055" s="1"/>
     </row>
     <row r="2056" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2056" s="2"/>
       <c r="I2056" s="1"/>
     </row>
     <row r="2057" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2057" s="1"/>
     </row>
     <row r="2058" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2058" s="2"/>
       <c r="I2058" s="1"/>
     </row>
     <row r="2059" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2059" s="2"/>
       <c r="I2059" s="1"/>
     </row>
     <row r="2060" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2060" s="2"/>
       <c r="I2060" s="1"/>
     </row>
     <row r="2061" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2061" s="2"/>
       <c r="I2061" s="1"/>
     </row>
     <row r="2062" spans="8:9" x14ac:dyDescent="0.3">
@@ -24526,23 +24317,25 @@
       <c r="I2063" s="1"/>
     </row>
     <row r="2064" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2064" s="2"/>
       <c r="I2064" s="1"/>
     </row>
     <row r="2065" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2065" s="2"/>
       <c r="I2065" s="1"/>
     </row>
     <row r="2066" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2066" s="2"/>
       <c r="I2066" s="1"/>
     </row>
     <row r="2067" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2067" s="2"/>
       <c r="I2067" s="1"/>
     </row>
     <row r="2068" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2068" s="2"/>
       <c r="I2068" s="1"/>
     </row>
     <row r="2069" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2069" s="2"/>
       <c r="I2069" s="1"/>
     </row>
     <row r="2070" spans="8:9" x14ac:dyDescent="0.3">
@@ -24552,7 +24345,6 @@
       <c r="I2071" s="1"/>
     </row>
     <row r="2072" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2072" s="2"/>
       <c r="I2072" s="1"/>
     </row>
     <row r="2073" spans="8:9" x14ac:dyDescent="0.3">
@@ -24560,6 +24352,7 @@
       <c r="I2073" s="1"/>
     </row>
     <row r="2074" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2074" s="2"/>
       <c r="I2074" s="1"/>
     </row>
     <row r="2075" spans="8:9" x14ac:dyDescent="0.3">
@@ -24577,13 +24370,13 @@
       <c r="I2078" s="1"/>
     </row>
     <row r="2079" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2079" s="2"/>
       <c r="I2079" s="1"/>
     </row>
     <row r="2080" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2080" s="1"/>
     </row>
     <row r="2081" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2081" s="2"/>
       <c r="I2081" s="1"/>
     </row>
     <row r="2082" spans="8:9" x14ac:dyDescent="0.3">
@@ -24591,17 +24384,17 @@
       <c r="I2082" s="1"/>
     </row>
     <row r="2083" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2083" s="2"/>
       <c r="I2083" s="1"/>
     </row>
     <row r="2084" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2084" s="2"/>
       <c r="I2084" s="1"/>
     </row>
     <row r="2085" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2085" s="2"/>
       <c r="I2085" s="1"/>
     </row>
     <row r="2086" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2086" s="2"/>
       <c r="I2086" s="1"/>
     </row>
     <row r="2087" spans="8:9" x14ac:dyDescent="0.3">
@@ -24609,9 +24402,11 @@
       <c r="I2087" s="1"/>
     </row>
     <row r="2088" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2088" s="2"/>
       <c r="I2088" s="1"/>
     </row>
     <row r="2089" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2089" s="2"/>
       <c r="I2089" s="1"/>
     </row>
     <row r="2090" spans="8:9" x14ac:dyDescent="0.3">
@@ -24619,6 +24414,7 @@
       <c r="I2090" s="1"/>
     </row>
     <row r="2091" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2091" s="2"/>
       <c r="I2091" s="1"/>
     </row>
     <row r="2092" spans="8:9" x14ac:dyDescent="0.3">
@@ -24633,11 +24429,9 @@
       <c r="I2094" s="1"/>
     </row>
     <row r="2095" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2095" s="2"/>
       <c r="I2095" s="1"/>
     </row>
     <row r="2096" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2096" s="2"/>
       <c r="I2096" s="1"/>
     </row>
     <row r="2097" spans="8:9" x14ac:dyDescent="0.3">
@@ -24645,14 +24439,13 @@
       <c r="I2097" s="1"/>
     </row>
     <row r="2098" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2098" s="2"/>
       <c r="I2098" s="1"/>
     </row>
     <row r="2099" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2099" s="2"/>
       <c r="I2099" s="1"/>
     </row>
     <row r="2100" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2100" s="2"/>
       <c r="I2100" s="1"/>
     </row>
     <row r="2101" spans="8:9" x14ac:dyDescent="0.3">
@@ -24664,19 +24457,22 @@
       <c r="I2102" s="1"/>
     </row>
     <row r="2103" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2103" s="2"/>
       <c r="I2103" s="1"/>
     </row>
     <row r="2104" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2104" s="2"/>
       <c r="I2104" s="1"/>
     </row>
     <row r="2105" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2105" s="2"/>
       <c r="I2105" s="1"/>
     </row>
     <row r="2106" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2106" s="2"/>
       <c r="I2106" s="1"/>
     </row>
     <row r="2107" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2107" s="2"/>
       <c r="I2107" s="1"/>
     </row>
     <row r="2108" spans="8:9" x14ac:dyDescent="0.3">
@@ -24688,11 +24484,9 @@
       <c r="I2109" s="1"/>
     </row>
     <row r="2110" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2110" s="2"/>
       <c r="I2110" s="1"/>
     </row>
     <row r="2111" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2111" s="2"/>
       <c r="I2111" s="1"/>
     </row>
     <row r="2112" spans="8:9" x14ac:dyDescent="0.3">
@@ -24711,7 +24505,6 @@
       <c r="I2115" s="1"/>
     </row>
     <row r="2116" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2116" s="2"/>
       <c r="I2116" s="1"/>
     </row>
     <row r="2117" spans="8:9" x14ac:dyDescent="0.3">
@@ -24719,6 +24512,7 @@
       <c r="I2117" s="1"/>
     </row>
     <row r="2118" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2118" s="2"/>
       <c r="I2118" s="1"/>
     </row>
     <row r="2119" spans="8:9" x14ac:dyDescent="0.3">
@@ -24732,14 +24526,13 @@
       <c r="I2121" s="1"/>
     </row>
     <row r="2122" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2122" s="2"/>
       <c r="I2122" s="1"/>
     </row>
     <row r="2123" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2123" s="2"/>
       <c r="I2123" s="1"/>
     </row>
     <row r="2124" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2124" s="2"/>
       <c r="I2124" s="1"/>
     </row>
     <row r="2125" spans="8:9" x14ac:dyDescent="0.3">
@@ -24751,6 +24544,7 @@
       <c r="I2126" s="1"/>
     </row>
     <row r="2127" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2127" s="2"/>
       <c r="I2127" s="1"/>
     </row>
     <row r="2128" spans="8:9" x14ac:dyDescent="0.3">
@@ -24758,20 +24552,20 @@
       <c r="I2128" s="1"/>
     </row>
     <row r="2129" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2129" s="2"/>
       <c r="I2129" s="1"/>
     </row>
     <row r="2130" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2130" s="2"/>
       <c r="I2130" s="1"/>
     </row>
     <row r="2131" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2131" s="1"/>
     </row>
     <row r="2132" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2132" s="2"/>
       <c r="I2132" s="1"/>
     </row>
     <row r="2133" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2133" s="2"/>
       <c r="I2133" s="1"/>
     </row>
     <row r="2134" spans="8:9" x14ac:dyDescent="0.3">
@@ -24779,7 +24573,6 @@
       <c r="I2134" s="1"/>
     </row>
     <row r="2135" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2135" s="2"/>
       <c r="I2135" s="1"/>
     </row>
     <row r="2136" spans="8:9" x14ac:dyDescent="0.3">
@@ -24787,7 +24580,6 @@
       <c r="I2136" s="1"/>
     </row>
     <row r="2137" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2137" s="2"/>
       <c r="I2137" s="1"/>
     </row>
     <row r="2138" spans="8:9" x14ac:dyDescent="0.3">
@@ -24798,9 +24590,11 @@
       <c r="I2139" s="1"/>
     </row>
     <row r="2140" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2140" s="2"/>
       <c r="I2140" s="1"/>
     </row>
     <row r="2141" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2141" s="2"/>
       <c r="I2141" s="1"/>
     </row>
     <row r="2142" spans="8:9" x14ac:dyDescent="0.3">
@@ -24811,14 +24605,12 @@
       <c r="I2143" s="1"/>
     </row>
     <row r="2144" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2144" s="2"/>
       <c r="I2144" s="1"/>
     </row>
     <row r="2145" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2145" s="1"/>
     </row>
     <row r="2146" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2146" s="2"/>
       <c r="I2146" s="1"/>
     </row>
     <row r="2147" spans="8:9" x14ac:dyDescent="0.3">
@@ -24829,7 +24621,6 @@
       <c r="I2148" s="1"/>
     </row>
     <row r="2149" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2149" s="2"/>
       <c r="I2149" s="1"/>
     </row>
     <row r="2150" spans="8:9" x14ac:dyDescent="0.3">
@@ -24840,22 +24631,25 @@
       <c r="I2151" s="1"/>
     </row>
     <row r="2152" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2152" s="2"/>
       <c r="I2152" s="1"/>
     </row>
     <row r="2153" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2153" s="1"/>
     </row>
     <row r="2154" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2154" s="2"/>
       <c r="I2154" s="1"/>
     </row>
     <row r="2155" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2155" s="2"/>
       <c r="I2155" s="1"/>
     </row>
     <row r="2156" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2156" s="2"/>
       <c r="I2156" s="1"/>
     </row>
     <row r="2157" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2157" s="2"/>
       <c r="I2157" s="1"/>
     </row>
     <row r="2158" spans="8:9" x14ac:dyDescent="0.3">
@@ -24863,6 +24657,7 @@
       <c r="I2158" s="1"/>
     </row>
     <row r="2159" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2159" s="2"/>
       <c r="I2159" s="1"/>
     </row>
     <row r="2160" spans="8:9" x14ac:dyDescent="0.3">
@@ -24870,6 +24665,7 @@
       <c r="I2160" s="1"/>
     </row>
     <row r="2161" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2161" s="2"/>
       <c r="I2161" s="1"/>
     </row>
     <row r="2162" spans="8:9" x14ac:dyDescent="0.3">
@@ -24877,10 +24673,10 @@
       <c r="I2162" s="1"/>
     </row>
     <row r="2163" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2163" s="2"/>
       <c r="I2163" s="1"/>
     </row>
     <row r="2164" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2164" s="2"/>
       <c r="I2164" s="1"/>
     </row>
     <row r="2165" spans="8:9" x14ac:dyDescent="0.3">
@@ -24892,7 +24688,6 @@
       <c r="I2166" s="1"/>
     </row>
     <row r="2167" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2167" s="2"/>
       <c r="I2167" s="1"/>
     </row>
     <row r="2168" spans="8:9" x14ac:dyDescent="0.3">
@@ -24908,6 +24703,7 @@
       <c r="I2170" s="1"/>
     </row>
     <row r="2171" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2171" s="2"/>
       <c r="I2171" s="1"/>
     </row>
     <row r="2172" spans="8:9" x14ac:dyDescent="0.3">
@@ -24923,6 +24719,7 @@
       <c r="I2174" s="1"/>
     </row>
     <row r="2175" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2175" s="2"/>
       <c r="I2175" s="1"/>
     </row>
     <row r="2176" spans="8:9" x14ac:dyDescent="0.3">
@@ -24930,7 +24727,6 @@
       <c r="I2176" s="1"/>
     </row>
     <row r="2177" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2177" s="2"/>
       <c r="I2177" s="1"/>
     </row>
     <row r="2178" spans="8:9" x14ac:dyDescent="0.3">
@@ -24962,6 +24758,7 @@
       <c r="I2184" s="1"/>
     </row>
     <row r="2185" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2185" s="2"/>
       <c r="I2185" s="1"/>
     </row>
     <row r="2186" spans="8:9" x14ac:dyDescent="0.3">
@@ -24981,7 +24778,6 @@
       <c r="I2189" s="1"/>
     </row>
     <row r="2190" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2190" s="2"/>
       <c r="I2190" s="1"/>
     </row>
     <row r="2191" spans="8:9" x14ac:dyDescent="0.3">
@@ -25013,6 +24809,7 @@
       <c r="I2197" s="1"/>
     </row>
     <row r="2198" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2198" s="2"/>
       <c r="I2198" s="1"/>
     </row>
     <row r="2199" spans="8:9" x14ac:dyDescent="0.3">
@@ -25040,7 +24837,6 @@
       <c r="I2204" s="1"/>
     </row>
     <row r="2205" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2205" s="2"/>
       <c r="I2205" s="1"/>
     </row>
     <row r="2206" spans="8:9" x14ac:dyDescent="0.3">
@@ -25056,7 +24852,6 @@
       <c r="I2208" s="1"/>
     </row>
     <row r="2209" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2209" s="2"/>
       <c r="I2209" s="1"/>
     </row>
     <row r="2210" spans="8:9" x14ac:dyDescent="0.3">
@@ -25072,6 +24867,7 @@
       <c r="I2212" s="1"/>
     </row>
     <row r="2213" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2213" s="2"/>
       <c r="I2213" s="1"/>
     </row>
     <row r="2214" spans="8:9" x14ac:dyDescent="0.3">
@@ -25087,6 +24883,7 @@
       <c r="I2216" s="1"/>
     </row>
     <row r="2217" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2217" s="2"/>
       <c r="I2217" s="1"/>
     </row>
     <row r="2218" spans="8:9" x14ac:dyDescent="0.3">
@@ -25102,7 +24899,6 @@
       <c r="I2220" s="1"/>
     </row>
     <row r="2221" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2221" s="2"/>
       <c r="I2221" s="1"/>
     </row>
     <row r="2222" spans="8:9" x14ac:dyDescent="0.3">
@@ -25134,10 +24930,10 @@
       <c r="I2228" s="1"/>
     </row>
     <row r="2229" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2229" s="2"/>
       <c r="I2229" s="1"/>
     </row>
     <row r="2230" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2230" s="2"/>
       <c r="I2230" s="1"/>
     </row>
     <row r="2231" spans="8:9" x14ac:dyDescent="0.3">
@@ -25149,7 +24945,6 @@
       <c r="I2232" s="1"/>
     </row>
     <row r="2233" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2233" s="2"/>
       <c r="I2233" s="1"/>
     </row>
     <row r="2234" spans="8:9" x14ac:dyDescent="0.3">
@@ -25169,6 +24964,7 @@
       <c r="I2237" s="1"/>
     </row>
     <row r="2238" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2238" s="2"/>
       <c r="I2238" s="1"/>
     </row>
     <row r="2239" spans="8:9" x14ac:dyDescent="0.3">
@@ -25180,10 +24976,10 @@
       <c r="I2240" s="1"/>
     </row>
     <row r="2241" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2241" s="2"/>
       <c r="I2241" s="1"/>
     </row>
     <row r="2242" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2242" s="2"/>
       <c r="I2242" s="1"/>
     </row>
     <row r="2243" spans="8:9" x14ac:dyDescent="0.3">
@@ -25207,7 +25003,6 @@
       <c r="I2247" s="1"/>
     </row>
     <row r="2248" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2248" s="2"/>
       <c r="I2248" s="1"/>
     </row>
     <row r="2249" spans="8:9" x14ac:dyDescent="0.3">
@@ -25215,6 +25010,7 @@
       <c r="I2249" s="1"/>
     </row>
     <row r="2250" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2250" s="2"/>
       <c r="I2250" s="1"/>
     </row>
     <row r="2251" spans="8:9" x14ac:dyDescent="0.3">
@@ -25238,6 +25034,7 @@
       <c r="I2255" s="1"/>
     </row>
     <row r="2256" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2256" s="2"/>
       <c r="I2256" s="1"/>
     </row>
     <row r="2257" spans="8:9" x14ac:dyDescent="0.3">
@@ -25305,7 +25102,6 @@
       <c r="I2272" s="1"/>
     </row>
     <row r="2273" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2273" s="2"/>
       <c r="I2273" s="1"/>
     </row>
     <row r="2274" spans="8:9" x14ac:dyDescent="0.3">
@@ -25321,7 +25117,6 @@
       <c r="I2276" s="1"/>
     </row>
     <row r="2277" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2277" s="2"/>
       <c r="I2277" s="1"/>
     </row>
     <row r="2278" spans="8:9" x14ac:dyDescent="0.3">
@@ -25337,6 +25132,7 @@
       <c r="I2280" s="1"/>
     </row>
     <row r="2281" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2281" s="2"/>
       <c r="I2281" s="1"/>
     </row>
     <row r="2282" spans="8:9" x14ac:dyDescent="0.3">
@@ -25352,6 +25148,7 @@
       <c r="I2284" s="1"/>
     </row>
     <row r="2285" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2285" s="2"/>
       <c r="I2285" s="1"/>
     </row>
     <row r="2286" spans="8:9" x14ac:dyDescent="0.3">
@@ -25391,7 +25188,6 @@
       <c r="I2294" s="1"/>
     </row>
     <row r="2295" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2295" s="2"/>
       <c r="I2295" s="1"/>
     </row>
     <row r="2296" spans="8:9" x14ac:dyDescent="0.3">
@@ -25423,6 +25219,7 @@
       <c r="I2302" s="1"/>
     </row>
     <row r="2303" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2303" s="2"/>
       <c r="I2303" s="1"/>
     </row>
     <row r="2304" spans="8:9" x14ac:dyDescent="0.3">
@@ -25438,7 +25235,6 @@
       <c r="I2306" s="1"/>
     </row>
     <row r="2307" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2307" s="2"/>
       <c r="I2307" s="1"/>
     </row>
     <row r="2308" spans="8:9" x14ac:dyDescent="0.3">
@@ -25470,6 +25266,7 @@
       <c r="I2314" s="1"/>
     </row>
     <row r="2315" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2315" s="2"/>
       <c r="I2315" s="1"/>
     </row>
     <row r="2316" spans="8:9" x14ac:dyDescent="0.3">
@@ -25537,7 +25334,6 @@
       <c r="I2331" s="1"/>
     </row>
     <row r="2332" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2332" s="2"/>
       <c r="I2332" s="1"/>
     </row>
     <row r="2333" spans="8:9" x14ac:dyDescent="0.3">
@@ -25545,7 +25341,6 @@
       <c r="I2333" s="1"/>
     </row>
     <row r="2334" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2334" s="2"/>
       <c r="I2334" s="1"/>
     </row>
     <row r="2335" spans="8:9" x14ac:dyDescent="0.3">
@@ -25569,6 +25364,7 @@
       <c r="I2339" s="1"/>
     </row>
     <row r="2340" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2340" s="2"/>
       <c r="I2340" s="1"/>
     </row>
     <row r="2341" spans="8:9" x14ac:dyDescent="0.3">
@@ -25576,6 +25372,7 @@
       <c r="I2341" s="1"/>
     </row>
     <row r="2342" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2342" s="2"/>
       <c r="I2342" s="1"/>
     </row>
     <row r="2343" spans="8:9" x14ac:dyDescent="0.3">
@@ -25611,7 +25408,6 @@
       <c r="I2350" s="1"/>
     </row>
     <row r="2351" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2351" s="2"/>
       <c r="I2351" s="1"/>
     </row>
     <row r="2352" spans="8:9" x14ac:dyDescent="0.3">
@@ -25643,6 +25439,7 @@
       <c r="I2358" s="1"/>
     </row>
     <row r="2359" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2359" s="2"/>
       <c r="I2359" s="1"/>
     </row>
     <row r="2360" spans="8:9" x14ac:dyDescent="0.3">
@@ -25686,7 +25483,6 @@
       <c r="I2369" s="1"/>
     </row>
     <row r="2370" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2370" s="2"/>
       <c r="I2370" s="1"/>
     </row>
     <row r="2371" spans="8:9" x14ac:dyDescent="0.3">
@@ -25718,6 +25514,7 @@
       <c r="I2377" s="1"/>
     </row>
     <row r="2378" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2378" s="2"/>
       <c r="I2378" s="1"/>
     </row>
     <row r="2379" spans="8:9" x14ac:dyDescent="0.3">
@@ -25741,7 +25538,6 @@
       <c r="I2383" s="1"/>
     </row>
     <row r="2384" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2384" s="2"/>
       <c r="I2384" s="1"/>
     </row>
     <row r="2385" spans="8:9" x14ac:dyDescent="0.3">
@@ -25773,6 +25569,7 @@
       <c r="I2391" s="1"/>
     </row>
     <row r="2392" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2392" s="2"/>
       <c r="I2392" s="1"/>
     </row>
     <row r="2393" spans="8:9" x14ac:dyDescent="0.3">
@@ -25792,7 +25589,6 @@
       <c r="I2396" s="1"/>
     </row>
     <row r="2397" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2397" s="2"/>
       <c r="I2397" s="1"/>
     </row>
     <row r="2398" spans="8:9" x14ac:dyDescent="0.3">
@@ -25812,7 +25608,6 @@
       <c r="I2401" s="1"/>
     </row>
     <row r="2402" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2402" s="2"/>
       <c r="I2402" s="1"/>
     </row>
     <row r="2403" spans="8:9" x14ac:dyDescent="0.3">
@@ -25835,7 +25630,6 @@
       <c r="I2407" s="1"/>
     </row>
     <row r="2408" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2408" s="2"/>
       <c r="I2408" s="1"/>
     </row>
     <row r="2409" spans="8:9" x14ac:dyDescent="0.3">
@@ -25843,6 +25637,7 @@
       <c r="I2409" s="1"/>
     </row>
     <row r="2410" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2410" s="2"/>
       <c r="I2410" s="1"/>
     </row>
     <row r="2411" spans="8:9" x14ac:dyDescent="0.3">
@@ -25850,10 +25645,10 @@
       <c r="I2411" s="1"/>
     </row>
     <row r="2412" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2412" s="2"/>
       <c r="I2412" s="1"/>
     </row>
     <row r="2413" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2413" s="2"/>
       <c r="I2413" s="1"/>
     </row>
     <row r="2414" spans="8:9" x14ac:dyDescent="0.3">
@@ -25876,10 +25671,10 @@
       <c r="I2418" s="1"/>
     </row>
     <row r="2419" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2419" s="2"/>
       <c r="I2419" s="1"/>
     </row>
     <row r="2420" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2420" s="2"/>
       <c r="I2420" s="1"/>
     </row>
     <row r="2421" spans="8:9" x14ac:dyDescent="0.3">
@@ -25895,6 +25690,7 @@
       <c r="I2423" s="1"/>
     </row>
     <row r="2424" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2424" s="2"/>
       <c r="I2424" s="1"/>
     </row>
     <row r="2425" spans="8:9" x14ac:dyDescent="0.3">
@@ -25906,18 +25702,16 @@
       <c r="I2426" s="1"/>
     </row>
     <row r="2427" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2427" s="2"/>
       <c r="I2427" s="1"/>
     </row>
     <row r="2428" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2428" s="2"/>
       <c r="I2428" s="1"/>
     </row>
     <row r="2429" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2429" s="2"/>
       <c r="I2429" s="1"/>
     </row>
     <row r="2430" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2430" s="2"/>
       <c r="I2430" s="1"/>
     </row>
     <row r="2431" spans="8:9" x14ac:dyDescent="0.3">
@@ -25941,12 +25735,15 @@
       <c r="I2435" s="1"/>
     </row>
     <row r="2436" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2436" s="2"/>
       <c r="I2436" s="1"/>
     </row>
     <row r="2437" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2437" s="2"/>
       <c r="I2437" s="1"/>
     </row>
     <row r="2438" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2438" s="2"/>
       <c r="I2438" s="1"/>
     </row>
     <row r="2439" spans="8:9" x14ac:dyDescent="0.3">
@@ -25994,7 +25791,6 @@
       <c r="I2449" s="1"/>
     </row>
     <row r="2450" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2450" s="2"/>
       <c r="I2450" s="1"/>
     </row>
     <row r="2451" spans="8:9" x14ac:dyDescent="0.3">
@@ -26026,6 +25822,7 @@
       <c r="I2457" s="1"/>
     </row>
     <row r="2458" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2458" s="2"/>
       <c r="I2458" s="1"/>
     </row>
     <row r="2459" spans="8:9" x14ac:dyDescent="0.3">
@@ -26045,7 +25842,6 @@
       <c r="I2462" s="1"/>
     </row>
     <row r="2463" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2463" s="2"/>
       <c r="I2463" s="1"/>
     </row>
     <row r="2464" spans="8:9" x14ac:dyDescent="0.3">
@@ -26077,6 +25873,7 @@
       <c r="I2470" s="1"/>
     </row>
     <row r="2471" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2471" s="2"/>
       <c r="I2471" s="1"/>
     </row>
     <row r="2472" spans="8:9" x14ac:dyDescent="0.3">
@@ -26088,7 +25885,6 @@
       <c r="I2473" s="1"/>
     </row>
     <row r="2474" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2474" s="2"/>
       <c r="I2474" s="1"/>
     </row>
     <row r="2475" spans="8:9" x14ac:dyDescent="0.3">
@@ -26108,7 +25904,6 @@
       <c r="I2478" s="1"/>
     </row>
     <row r="2479" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2479" s="2"/>
       <c r="I2479" s="1"/>
     </row>
     <row r="2480" spans="8:9" x14ac:dyDescent="0.3">
@@ -26120,6 +25915,7 @@
       <c r="I2481" s="1"/>
     </row>
     <row r="2482" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2482" s="2"/>
       <c r="I2482" s="1"/>
     </row>
     <row r="2483" spans="8:9" x14ac:dyDescent="0.3">
@@ -26131,14 +25927,13 @@
       <c r="I2484" s="1"/>
     </row>
     <row r="2485" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2485" s="2"/>
       <c r="I2485" s="1"/>
     </row>
     <row r="2486" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2486" s="2"/>
       <c r="I2486" s="1"/>
     </row>
     <row r="2487" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2487" s="2"/>
       <c r="I2487" s="1"/>
     </row>
     <row r="2488" spans="8:9" x14ac:dyDescent="0.3">
@@ -26162,9 +25957,11 @@
       <c r="I2492" s="1"/>
     </row>
     <row r="2493" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2493" s="2"/>
       <c r="I2493" s="1"/>
     </row>
     <row r="2494" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2494" s="2"/>
       <c r="I2494" s="1"/>
     </row>
     <row r="2495" spans="8:9" x14ac:dyDescent="0.3">
@@ -26192,7 +25989,6 @@
       <c r="I2500" s="1"/>
     </row>
     <row r="2501" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2501" s="2"/>
       <c r="I2501" s="1"/>
     </row>
     <row r="2502" spans="8:9" x14ac:dyDescent="0.3">
@@ -26224,6 +26020,7 @@
       <c r="I2508" s="1"/>
     </row>
     <row r="2509" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2509" s="2"/>
       <c r="I2509" s="1"/>
     </row>
     <row r="2510" spans="8:9" x14ac:dyDescent="0.3">
@@ -26251,7 +26048,6 @@
       <c r="I2515" s="1"/>
     </row>
     <row r="2516" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2516" s="2"/>
       <c r="I2516" s="1"/>
     </row>
     <row r="2517" spans="8:9" x14ac:dyDescent="0.3">
@@ -26283,6 +26079,7 @@
       <c r="I2523" s="1"/>
     </row>
     <row r="2524" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2524" s="2"/>
       <c r="I2524" s="1"/>
     </row>
     <row r="2525" spans="8:9" x14ac:dyDescent="0.3">
@@ -26302,7 +26099,6 @@
       <c r="I2528" s="1"/>
     </row>
     <row r="2529" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2529" s="2"/>
       <c r="I2529" s="1"/>
     </row>
     <row r="2530" spans="8:9" x14ac:dyDescent="0.3">
@@ -26314,7 +26110,6 @@
       <c r="I2531" s="1"/>
     </row>
     <row r="2532" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2532" s="2"/>
       <c r="I2532" s="1"/>
     </row>
     <row r="2533" spans="8:9" x14ac:dyDescent="0.3">
@@ -26334,6 +26129,7 @@
       <c r="I2536" s="1"/>
     </row>
     <row r="2537" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2537" s="2"/>
       <c r="I2537" s="1"/>
     </row>
     <row r="2538" spans="8:9" x14ac:dyDescent="0.3">
@@ -26345,6 +26141,7 @@
       <c r="I2539" s="1"/>
     </row>
     <row r="2540" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2540" s="2"/>
       <c r="I2540" s="1"/>
     </row>
     <row r="2541" spans="8:9" x14ac:dyDescent="0.3">
@@ -26368,7 +26165,6 @@
       <c r="I2545" s="1"/>
     </row>
     <row r="2546" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2546" s="2"/>
       <c r="I2546" s="1"/>
     </row>
     <row r="2547" spans="8:9" x14ac:dyDescent="0.3">
@@ -26388,7 +26184,6 @@
       <c r="I2550" s="1"/>
     </row>
     <row r="2551" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2551" s="2"/>
       <c r="I2551" s="1"/>
     </row>
     <row r="2552" spans="8:9" x14ac:dyDescent="0.3">
@@ -26400,10 +26195,10 @@
       <c r="I2553" s="1"/>
     </row>
     <row r="2554" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2554" s="2"/>
       <c r="I2554" s="1"/>
     </row>
     <row r="2555" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2555" s="2"/>
       <c r="I2555" s="1"/>
     </row>
     <row r="2556" spans="8:9" x14ac:dyDescent="0.3">
@@ -26419,6 +26214,7 @@
       <c r="I2558" s="1"/>
     </row>
     <row r="2559" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2559" s="2"/>
       <c r="I2559" s="1"/>
     </row>
     <row r="2560" spans="8:9" x14ac:dyDescent="0.3">
@@ -26434,6 +26230,7 @@
       <c r="I2562" s="1"/>
     </row>
     <row r="2563" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2563" s="2"/>
       <c r="I2563" s="1"/>
     </row>
     <row r="2564" spans="8:9" x14ac:dyDescent="0.3">
@@ -26453,7 +26250,6 @@
       <c r="I2567" s="1"/>
     </row>
     <row r="2568" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2568" s="2"/>
       <c r="I2568" s="1"/>
     </row>
     <row r="2569" spans="8:9" x14ac:dyDescent="0.3">
@@ -26485,6 +26281,7 @@
       <c r="I2575" s="1"/>
     </row>
     <row r="2576" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2576" s="2"/>
       <c r="I2576" s="1"/>
     </row>
     <row r="2577" spans="8:9" x14ac:dyDescent="0.3">
@@ -26504,7 +26301,6 @@
       <c r="I2580" s="1"/>
     </row>
     <row r="2581" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2581" s="2"/>
       <c r="I2581" s="1"/>
     </row>
     <row r="2582" spans="8:9" x14ac:dyDescent="0.3">
@@ -26512,7 +26308,6 @@
       <c r="I2582" s="1"/>
     </row>
     <row r="2583" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2583" s="2"/>
       <c r="I2583" s="1"/>
     </row>
     <row r="2584" spans="8:9" x14ac:dyDescent="0.3">
@@ -26536,13 +26331,14 @@
       <c r="I2588" s="1"/>
     </row>
     <row r="2589" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2589" s="2"/>
       <c r="I2589" s="1"/>
     </row>
     <row r="2590" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2590" s="2"/>
       <c r="I2590" s="1"/>
     </row>
     <row r="2591" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2591" s="2"/>
       <c r="I2591" s="1"/>
     </row>
     <row r="2592" spans="8:9" x14ac:dyDescent="0.3">
@@ -26570,6 +26366,7 @@
       <c r="I2597" s="1"/>
     </row>
     <row r="2598" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2598" s="2"/>
       <c r="I2598" s="1"/>
     </row>
     <row r="2599" spans="8:9" x14ac:dyDescent="0.3">
@@ -26577,7 +26374,6 @@
       <c r="I2599" s="1"/>
     </row>
     <row r="2600" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2600" s="2"/>
       <c r="I2600" s="1"/>
     </row>
     <row r="2601" spans="8:9" x14ac:dyDescent="0.3">
@@ -26609,6 +26405,7 @@
       <c r="I2607" s="1"/>
     </row>
     <row r="2608" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2608" s="2"/>
       <c r="I2608" s="1"/>
     </row>
     <row r="2609" spans="8:9" x14ac:dyDescent="0.3">
@@ -26656,7 +26453,6 @@
       <c r="I2619" s="1"/>
     </row>
     <row r="2620" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2620" s="2"/>
       <c r="I2620" s="1"/>
     </row>
     <row r="2621" spans="8:9" x14ac:dyDescent="0.3">
@@ -26668,7 +26464,6 @@
       <c r="I2622" s="1"/>
     </row>
     <row r="2623" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2623" s="2"/>
       <c r="I2623" s="1"/>
     </row>
     <row r="2624" spans="8:9" x14ac:dyDescent="0.3">
@@ -26688,6 +26483,7 @@
       <c r="I2627" s="1"/>
     </row>
     <row r="2628" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2628" s="2"/>
       <c r="I2628" s="1"/>
     </row>
     <row r="2629" spans="8:9" x14ac:dyDescent="0.3">
@@ -26699,10 +26495,10 @@
       <c r="I2630" s="1"/>
     </row>
     <row r="2631" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2631" s="2"/>
       <c r="I2631" s="1"/>
     </row>
     <row r="2632" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2632" s="2"/>
       <c r="I2632" s="1"/>
     </row>
     <row r="2633" spans="8:9" x14ac:dyDescent="0.3">
@@ -26734,10 +26530,10 @@
       <c r="I2639" s="1"/>
     </row>
     <row r="2640" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2640" s="2"/>
       <c r="I2640" s="1"/>
     </row>
     <row r="2641" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2641" s="2"/>
       <c r="I2641" s="1"/>
     </row>
     <row r="2642" spans="8:9" x14ac:dyDescent="0.3">
@@ -26745,7 +26541,6 @@
       <c r="I2642" s="1"/>
     </row>
     <row r="2643" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2643" s="2"/>
       <c r="I2643" s="1"/>
     </row>
     <row r="2644" spans="8:9" x14ac:dyDescent="0.3">
@@ -26769,13 +26564,14 @@
       <c r="I2648" s="1"/>
     </row>
     <row r="2649" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2649" s="2"/>
       <c r="I2649" s="1"/>
     </row>
     <row r="2650" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2650" s="2"/>
       <c r="I2650" s="1"/>
     </row>
     <row r="2651" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2651" s="2"/>
       <c r="I2651" s="1"/>
     </row>
     <row r="2652" spans="8:9" x14ac:dyDescent="0.3">
@@ -26783,7 +26579,6 @@
       <c r="I2652" s="1"/>
     </row>
     <row r="2653" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2653" s="2"/>
       <c r="I2653" s="1"/>
     </row>
     <row r="2654" spans="8:9" x14ac:dyDescent="0.3">
@@ -26803,6 +26598,7 @@
       <c r="I2657" s="1"/>
     </row>
     <row r="2658" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2658" s="2"/>
       <c r="I2658" s="1"/>
     </row>
     <row r="2659" spans="8:9" x14ac:dyDescent="0.3">
@@ -26817,7 +26613,6 @@
       <c r="I2661" s="1"/>
     </row>
     <row r="2662" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2662" s="2"/>
       <c r="I2662" s="1"/>
     </row>
     <row r="2663" spans="8:9" x14ac:dyDescent="0.3">
@@ -26845,9 +26640,11 @@
       <c r="I2668" s="1"/>
     </row>
     <row r="2669" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2669" s="2"/>
       <c r="I2669" s="1"/>
     </row>
     <row r="2670" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2670" s="2"/>
       <c r="I2670" s="1"/>
     </row>
     <row r="2671" spans="8:9" x14ac:dyDescent="0.3">
@@ -26863,7 +26660,6 @@
       <c r="I2673" s="1"/>
     </row>
     <row r="2674" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2674" s="2"/>
       <c r="I2674" s="1"/>
     </row>
     <row r="2675" spans="8:9" x14ac:dyDescent="0.3">
@@ -26887,7 +26683,6 @@
       <c r="I2679" s="1"/>
     </row>
     <row r="2680" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2680" s="2"/>
       <c r="I2680" s="1"/>
     </row>
     <row r="2681" spans="8:9" x14ac:dyDescent="0.3">
@@ -26895,6 +26690,7 @@
       <c r="I2681" s="1"/>
     </row>
     <row r="2682" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2682" s="2"/>
       <c r="I2682" s="1"/>
     </row>
     <row r="2683" spans="8:9" x14ac:dyDescent="0.3">
@@ -26918,6 +26714,7 @@
       <c r="I2687" s="1"/>
     </row>
     <row r="2688" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2688" s="2"/>
       <c r="I2688" s="1"/>
     </row>
     <row r="2689" spans="8:9" x14ac:dyDescent="0.3">
@@ -26953,7 +26750,6 @@
       <c r="I2696" s="1"/>
     </row>
     <row r="2697" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2697" s="2"/>
       <c r="I2697" s="1"/>
     </row>
     <row r="2698" spans="8:9" x14ac:dyDescent="0.3">
@@ -26985,10 +26781,10 @@
       <c r="I2704" s="1"/>
     </row>
     <row r="2705" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2705" s="2"/>
       <c r="I2705" s="1"/>
     </row>
     <row r="2706" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2706" s="2"/>
       <c r="I2706" s="1"/>
     </row>
     <row r="2707" spans="8:9" x14ac:dyDescent="0.3">
@@ -27020,6 +26816,7 @@
       <c r="I2713" s="1"/>
     </row>
     <row r="2714" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2714" s="2"/>
       <c r="I2714" s="1"/>
     </row>
     <row r="2715" spans="8:9" x14ac:dyDescent="0.3">
@@ -27035,7 +26832,6 @@
       <c r="I2717" s="1"/>
     </row>
     <row r="2718" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2718" s="2"/>
       <c r="I2718" s="1"/>
     </row>
     <row r="2719" spans="8:9" x14ac:dyDescent="0.3">
@@ -27067,6 +26863,7 @@
       <c r="I2725" s="1"/>
     </row>
     <row r="2726" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2726" s="2"/>
       <c r="I2726" s="1"/>
     </row>
     <row r="2727" spans="8:9" x14ac:dyDescent="0.3">
@@ -27110,7 +26907,6 @@
       <c r="I2736" s="1"/>
     </row>
     <row r="2737" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2737" s="2"/>
       <c r="I2737" s="1"/>
     </row>
     <row r="2738" spans="8:9" x14ac:dyDescent="0.3">
@@ -27130,7 +26926,6 @@
       <c r="I2741" s="1"/>
     </row>
     <row r="2742" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2742" s="2"/>
       <c r="I2742" s="1"/>
     </row>
     <row r="2743" spans="8:9" x14ac:dyDescent="0.3">
@@ -27142,6 +26937,7 @@
       <c r="I2744" s="1"/>
     </row>
     <row r="2745" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2745" s="2"/>
       <c r="I2745" s="1"/>
     </row>
     <row r="2746" spans="8:9" x14ac:dyDescent="0.3">
@@ -27161,6 +26957,7 @@
       <c r="I2749" s="1"/>
     </row>
     <row r="2750" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2750" s="2"/>
       <c r="I2750" s="1"/>
     </row>
     <row r="2751" spans="8:9" x14ac:dyDescent="0.3">
@@ -27248,7 +27045,6 @@
       <c r="I2771" s="1"/>
     </row>
     <row r="2772" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2772" s="2"/>
       <c r="I2772" s="1"/>
     </row>
     <row r="2773" spans="8:9" x14ac:dyDescent="0.3">
@@ -27280,6 +27076,7 @@
       <c r="I2779" s="1"/>
     </row>
     <row r="2780" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2780" s="2"/>
       <c r="I2780" s="1"/>
     </row>
     <row r="2781" spans="8:9" x14ac:dyDescent="0.3">
@@ -27311,11 +27108,9 @@
       <c r="I2787" s="1"/>
     </row>
     <row r="2788" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2788" s="2"/>
       <c r="I2788" s="1"/>
     </row>
     <row r="2789" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2789" s="2"/>
       <c r="I2789" s="1"/>
     </row>
     <row r="2790" spans="8:9" x14ac:dyDescent="0.3">
@@ -27343,13 +27138,13 @@
       <c r="I2795" s="1"/>
     </row>
     <row r="2796" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2796" s="2"/>
       <c r="I2796" s="1"/>
     </row>
     <row r="2797" spans="8:9" x14ac:dyDescent="0.3">
       <c r="I2797" s="1"/>
     </row>
     <row r="2798" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2798" s="2"/>
       <c r="I2798" s="1"/>
     </row>
     <row r="2799" spans="8:9" x14ac:dyDescent="0.3">
@@ -27377,9 +27172,11 @@
       <c r="I2804" s="1"/>
     </row>
     <row r="2805" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2805" s="2"/>
       <c r="I2805" s="1"/>
     </row>
     <row r="2806" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2806" s="2"/>
       <c r="I2806" s="1"/>
     </row>
     <row r="2807" spans="8:9" x14ac:dyDescent="0.3">
@@ -27451,7 +27248,6 @@
       <c r="I2823" s="1"/>
     </row>
     <row r="2824" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2824" s="2"/>
       <c r="I2824" s="1"/>
     </row>
     <row r="2825" spans="8:9" x14ac:dyDescent="0.3">
@@ -27479,10 +27275,10 @@
       <c r="I2830" s="1"/>
     </row>
     <row r="2831" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2831" s="2"/>
       <c r="I2831" s="1"/>
     </row>
     <row r="2832" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2832" s="2"/>
       <c r="I2832" s="1"/>
     </row>
     <row r="2833" spans="8:9" x14ac:dyDescent="0.3">
@@ -27510,6 +27306,7 @@
       <c r="I2838" s="1"/>
     </row>
     <row r="2839" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2839" s="2"/>
       <c r="I2839" s="1"/>
     </row>
     <row r="2840" spans="8:9" x14ac:dyDescent="0.3">
@@ -27649,7 +27446,6 @@
       <c r="I2873" s="1"/>
     </row>
     <row r="2874" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2874" s="2"/>
       <c r="I2874" s="1"/>
     </row>
     <row r="2875" spans="8:9" x14ac:dyDescent="0.3">
@@ -27681,10 +27477,10 @@
       <c r="I2881" s="1"/>
     </row>
     <row r="2882" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2882" s="2"/>
       <c r="I2882" s="1"/>
     </row>
     <row r="2883" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2883" s="2"/>
       <c r="I2883" s="1"/>
     </row>
     <row r="2884" spans="8:9" x14ac:dyDescent="0.3">
@@ -27692,11 +27488,9 @@
       <c r="I2884" s="1"/>
     </row>
     <row r="2885" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2885" s="2"/>
       <c r="I2885" s="1"/>
     </row>
     <row r="2886" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2886" s="2"/>
       <c r="I2886" s="1"/>
     </row>
     <row r="2887" spans="8:9" x14ac:dyDescent="0.3">
@@ -27716,6 +27510,7 @@
       <c r="I2890" s="1"/>
     </row>
     <row r="2891" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2891" s="2"/>
       <c r="I2891" s="1"/>
     </row>
     <row r="2892" spans="8:9" x14ac:dyDescent="0.3">
@@ -27723,6 +27518,7 @@
       <c r="I2892" s="1"/>
     </row>
     <row r="2893" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2893" s="2"/>
       <c r="I2893" s="1"/>
     </row>
     <row r="2894" spans="8:9" x14ac:dyDescent="0.3">
@@ -27741,7 +27537,6 @@
       <c r="I2897" s="1"/>
     </row>
     <row r="2898" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2898" s="2"/>
       <c r="I2898" s="1"/>
     </row>
     <row r="2899" spans="8:9" x14ac:dyDescent="0.3">
@@ -27757,6 +27552,7 @@
       <c r="I2901" s="1"/>
     </row>
     <row r="2902" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2902" s="2"/>
       <c r="I2902" s="1"/>
     </row>
     <row r="2903" spans="8:9" x14ac:dyDescent="0.3">
@@ -27772,6 +27568,7 @@
       <c r="I2905" s="1"/>
     </row>
     <row r="2906" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2906" s="2"/>
       <c r="I2906" s="1"/>
     </row>
     <row r="2907" spans="8:9" x14ac:dyDescent="0.3">
@@ -27779,7 +27576,6 @@
       <c r="I2907" s="1"/>
     </row>
     <row r="2908" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2908" s="2"/>
       <c r="I2908" s="1"/>
     </row>
     <row r="2909" spans="8:9" x14ac:dyDescent="0.3">
@@ -27791,7 +27587,6 @@
       <c r="I2910" s="1"/>
     </row>
     <row r="2911" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2911" s="2"/>
       <c r="I2911" s="1"/>
     </row>
     <row r="2912" spans="8:9" x14ac:dyDescent="0.3">
@@ -27811,6 +27606,7 @@
       <c r="I2915" s="1"/>
     </row>
     <row r="2916" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2916" s="2"/>
       <c r="I2916" s="1"/>
     </row>
     <row r="2917" spans="8:9" x14ac:dyDescent="0.3">
@@ -27822,6 +27618,7 @@
       <c r="I2918" s="1"/>
     </row>
     <row r="2919" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2919" s="2"/>
       <c r="I2919" s="1"/>
     </row>
     <row r="2920" spans="8:9" x14ac:dyDescent="0.3">
@@ -27933,7 +27730,6 @@
       <c r="I2946" s="1"/>
     </row>
     <row r="2947" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2947" s="2"/>
       <c r="I2947" s="1"/>
     </row>
     <row r="2948" spans="8:9" x14ac:dyDescent="0.3">
@@ -27965,6 +27761,7 @@
       <c r="I2954" s="1"/>
     </row>
     <row r="2955" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2955" s="2"/>
       <c r="I2955" s="1"/>
     </row>
     <row r="2956" spans="8:9" x14ac:dyDescent="0.3">
@@ -28016,7 +27813,6 @@
       <c r="I2967" s="1"/>
     </row>
     <row r="2968" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2968" s="2"/>
       <c r="I2968" s="1"/>
     </row>
     <row r="2969" spans="8:9" x14ac:dyDescent="0.3">
@@ -28048,6 +27844,7 @@
       <c r="I2975" s="1"/>
     </row>
     <row r="2976" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2976" s="2"/>
       <c r="I2976" s="1"/>
     </row>
     <row r="2977" spans="8:9" x14ac:dyDescent="0.3">
@@ -28067,7 +27864,6 @@
       <c r="I2980" s="1"/>
     </row>
     <row r="2981" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H2981" s="2"/>
       <c r="I2981" s="1"/>
     </row>
     <row r="2982" spans="8:9" x14ac:dyDescent="0.3">
@@ -28099,6 +27895,7 @@
       <c r="I2988" s="1"/>
     </row>
     <row r="2989" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H2989" s="2"/>
       <c r="I2989" s="1"/>
     </row>
     <row r="2990" spans="8:9" x14ac:dyDescent="0.3">
@@ -28226,7 +28023,6 @@
       <c r="I3020" s="1"/>
     </row>
     <row r="3021" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3021" s="2"/>
       <c r="I3021" s="1"/>
     </row>
     <row r="3022" spans="8:9" x14ac:dyDescent="0.3">
@@ -28258,6 +28054,7 @@
       <c r="I3028" s="1"/>
     </row>
     <row r="3029" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3029" s="2"/>
       <c r="I3029" s="1"/>
     </row>
     <row r="3030" spans="8:9" x14ac:dyDescent="0.3">
@@ -28285,7 +28082,6 @@
       <c r="I3035" s="1"/>
     </row>
     <row r="3036" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3036" s="2"/>
       <c r="I3036" s="1"/>
     </row>
     <row r="3037" spans="8:9" x14ac:dyDescent="0.3">
@@ -28317,6 +28113,7 @@
       <c r="I3043" s="1"/>
     </row>
     <row r="3044" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3044" s="2"/>
       <c r="I3044" s="1"/>
     </row>
     <row r="3045" spans="8:9" x14ac:dyDescent="0.3">
@@ -28428,7 +28225,6 @@
       <c r="I3071" s="1"/>
     </row>
     <row r="3072" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3072" s="2"/>
       <c r="I3072" s="1"/>
     </row>
     <row r="3073" spans="8:9" x14ac:dyDescent="0.3">
@@ -28460,6 +28256,7 @@
       <c r="I3079" s="1"/>
     </row>
     <row r="3080" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3080" s="2"/>
       <c r="I3080" s="1"/>
     </row>
     <row r="3081" spans="8:9" x14ac:dyDescent="0.3">
@@ -28547,7 +28344,6 @@
       <c r="I3101" s="1"/>
     </row>
     <row r="3102" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3102" s="2"/>
       <c r="I3102" s="1"/>
     </row>
     <row r="3103" spans="8:9" x14ac:dyDescent="0.3">
@@ -28579,6 +28375,7 @@
       <c r="I3109" s="1"/>
     </row>
     <row r="3110" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3110" s="2"/>
       <c r="I3110" s="1"/>
     </row>
     <row r="3111" spans="8:9" x14ac:dyDescent="0.3">
@@ -28678,7 +28475,6 @@
       <c r="I3134" s="1"/>
     </row>
     <row r="3135" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3135" s="2"/>
       <c r="I3135" s="1"/>
     </row>
     <row r="3136" spans="8:9" x14ac:dyDescent="0.3">
@@ -28698,7 +28494,6 @@
       <c r="I3139" s="1"/>
     </row>
     <row r="3140" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3140" s="2"/>
       <c r="I3140" s="1"/>
     </row>
     <row r="3141" spans="8:9" x14ac:dyDescent="0.3">
@@ -28729,10 +28524,10 @@
       <c r="I3147" s="1"/>
     </row>
     <row r="3148" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3148" s="2"/>
       <c r="I3148" s="1"/>
     </row>
     <row r="3149" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3149" s="2"/>
       <c r="I3149" s="1"/>
     </row>
     <row r="3150" spans="8:9" x14ac:dyDescent="0.3">
@@ -28740,6 +28535,7 @@
       <c r="I3150" s="1"/>
     </row>
     <row r="3151" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3151" s="2"/>
       <c r="I3151" s="1"/>
     </row>
     <row r="3152" spans="8:9" x14ac:dyDescent="0.3">
@@ -28763,6 +28559,7 @@
       <c r="I3156" s="1"/>
     </row>
     <row r="3157" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3157" s="2"/>
       <c r="I3157" s="1"/>
     </row>
     <row r="3158" spans="8:9" x14ac:dyDescent="0.3">
@@ -28770,7 +28567,6 @@
       <c r="I3158" s="1"/>
     </row>
     <row r="3159" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3159" s="2"/>
       <c r="I3159" s="1"/>
     </row>
     <row r="3160" spans="8:9" x14ac:dyDescent="0.3">
@@ -28802,6 +28598,7 @@
       <c r="I3166" s="1"/>
     </row>
     <row r="3167" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3167" s="2"/>
       <c r="I3167" s="1"/>
     </row>
     <row r="3168" spans="8:9" x14ac:dyDescent="0.3">
@@ -29289,7 +29086,6 @@
       <c r="I3288" s="1"/>
     </row>
     <row r="3289" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3289" s="2"/>
       <c r="I3289" s="1"/>
     </row>
     <row r="3290" spans="8:9" x14ac:dyDescent="0.3">
@@ -29321,6 +29117,7 @@
       <c r="I3296" s="1"/>
     </row>
     <row r="3297" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3297" s="2"/>
       <c r="I3297" s="1"/>
     </row>
     <row r="3298" spans="8:9" x14ac:dyDescent="0.3">
@@ -29428,7 +29225,6 @@
       <c r="I3323" s="1"/>
     </row>
     <row r="3324" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3324" s="2"/>
       <c r="I3324" s="1"/>
     </row>
     <row r="3325" spans="8:9" x14ac:dyDescent="0.3">
@@ -29460,6 +29256,7 @@
       <c r="I3331" s="1"/>
     </row>
     <row r="3332" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3332" s="2"/>
       <c r="I3332" s="1"/>
     </row>
     <row r="3333" spans="8:9" x14ac:dyDescent="0.3">
@@ -29551,7 +29348,6 @@
       <c r="I3354" s="1"/>
     </row>
     <row r="3355" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3355" s="2"/>
       <c r="I3355" s="1"/>
     </row>
     <row r="3356" spans="8:9" x14ac:dyDescent="0.3">
@@ -29583,10 +29379,10 @@
       <c r="I3362" s="1"/>
     </row>
     <row r="3363" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3363" s="2"/>
       <c r="I3363" s="1"/>
     </row>
     <row r="3364" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3364" s="2"/>
       <c r="I3364" s="1"/>
     </row>
     <row r="3365" spans="8:9" x14ac:dyDescent="0.3">
@@ -29618,6 +29414,7 @@
       <c r="I3371" s="1"/>
     </row>
     <row r="3372" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3372" s="2"/>
       <c r="I3372" s="1"/>
     </row>
     <row r="3373" spans="8:9" x14ac:dyDescent="0.3">
@@ -29717,7 +29514,6 @@
       <c r="I3396" s="1"/>
     </row>
     <row r="3397" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3397" s="2"/>
       <c r="I3397" s="1"/>
     </row>
     <row r="3398" spans="8:9" x14ac:dyDescent="0.3">
@@ -29741,7 +29537,6 @@
       <c r="I3402" s="1"/>
     </row>
     <row r="3403" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3403" s="2"/>
       <c r="I3403" s="1"/>
     </row>
     <row r="3404" spans="8:9" x14ac:dyDescent="0.3">
@@ -29749,6 +29544,7 @@
       <c r="I3404" s="1"/>
     </row>
     <row r="3405" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3405" s="2"/>
       <c r="I3405" s="1"/>
     </row>
     <row r="3406" spans="8:9" x14ac:dyDescent="0.3">
@@ -29772,6 +29568,7 @@
       <c r="I3410" s="1"/>
     </row>
     <row r="3411" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3411" s="2"/>
       <c r="I3411" s="1"/>
     </row>
     <row r="3412" spans="8:9" x14ac:dyDescent="0.3">
@@ -30195,7 +29992,6 @@
       <c r="I3516" s="1"/>
     </row>
     <row r="3517" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3517" s="2"/>
       <c r="I3517" s="1"/>
     </row>
     <row r="3518" spans="8:9" x14ac:dyDescent="0.3">
@@ -30227,6 +30023,7 @@
       <c r="I3524" s="1"/>
     </row>
     <row r="3525" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3525" s="2"/>
       <c r="I3525" s="1"/>
     </row>
     <row r="3526" spans="8:9" x14ac:dyDescent="0.3">
@@ -30258,7 +30055,6 @@
       <c r="I3532" s="1"/>
     </row>
     <row r="3533" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3533" s="2"/>
       <c r="I3533" s="1"/>
     </row>
     <row r="3534" spans="8:9" x14ac:dyDescent="0.3">
@@ -30290,6 +30086,7 @@
       <c r="I3540" s="1"/>
     </row>
     <row r="3541" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3541" s="2"/>
       <c r="I3541" s="1"/>
     </row>
     <row r="3542" spans="8:9" x14ac:dyDescent="0.3">
@@ -30393,7 +30190,6 @@
       <c r="I3566" s="1"/>
     </row>
     <row r="3567" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3567" s="2"/>
       <c r="I3567" s="1"/>
     </row>
     <row r="3568" spans="8:9" x14ac:dyDescent="0.3">
@@ -30425,6 +30221,7 @@
       <c r="I3574" s="1"/>
     </row>
     <row r="3575" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3575" s="2"/>
       <c r="I3575" s="1"/>
     </row>
     <row r="3576" spans="8:9" x14ac:dyDescent="0.3">
@@ -30516,7 +30313,6 @@
       <c r="I3597" s="1"/>
     </row>
     <row r="3598" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3598" s="2"/>
       <c r="I3598" s="1"/>
     </row>
     <row r="3599" spans="8:9" x14ac:dyDescent="0.3">
@@ -30548,6 +30344,7 @@
       <c r="I3605" s="1"/>
     </row>
     <row r="3606" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3606" s="2"/>
       <c r="I3606" s="1"/>
     </row>
     <row r="3607" spans="8:9" x14ac:dyDescent="0.3">
@@ -30631,11 +30428,9 @@
       <c r="I3626" s="1"/>
     </row>
     <row r="3627" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3627" s="2"/>
       <c r="I3627" s="1"/>
     </row>
     <row r="3628" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3628" s="2"/>
       <c r="I3628" s="1"/>
     </row>
     <row r="3629" spans="8:9" x14ac:dyDescent="0.3">
@@ -30673,7 +30468,6 @@
       <c r="I3637" s="1"/>
     </row>
     <row r="3638" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3638" s="2"/>
       <c r="I3638" s="1"/>
     </row>
     <row r="3639" spans="8:9" x14ac:dyDescent="0.3">
@@ -30693,9 +30487,11 @@
       <c r="I3642" s="1"/>
     </row>
     <row r="3643" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3643" s="2"/>
       <c r="I3643" s="1"/>
     </row>
     <row r="3644" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3644" s="2"/>
       <c r="I3644" s="1"/>
     </row>
     <row r="3645" spans="8:9" x14ac:dyDescent="0.3">
@@ -30703,6 +30499,7 @@
       <c r="I3645" s="1"/>
     </row>
     <row r="3646" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3646" s="2"/>
       <c r="I3646" s="1"/>
     </row>
     <row r="3647" spans="8:9" x14ac:dyDescent="0.3">
@@ -30938,7 +30735,6 @@
       <c r="I3704" s="1"/>
     </row>
     <row r="3705" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3705" s="2"/>
       <c r="I3705" s="1"/>
     </row>
     <row r="3706" spans="8:9" x14ac:dyDescent="0.3">
@@ -30970,6 +30766,7 @@
       <c r="I3712" s="1"/>
     </row>
     <row r="3713" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3713" s="2"/>
       <c r="I3713" s="1"/>
     </row>
     <row r="3714" spans="8:9" x14ac:dyDescent="0.3">
@@ -31193,7 +30990,6 @@
       <c r="I3768" s="1"/>
     </row>
     <row r="3769" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3769" s="2"/>
       <c r="I3769" s="1"/>
     </row>
     <row r="3770" spans="8:9" x14ac:dyDescent="0.3">
@@ -31225,6 +31021,7 @@
       <c r="I3776" s="1"/>
     </row>
     <row r="3777" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3777" s="2"/>
       <c r="I3777" s="1"/>
     </row>
     <row r="3778" spans="8:9" x14ac:dyDescent="0.3">
@@ -31240,7 +31037,6 @@
       <c r="I3780" s="1"/>
     </row>
     <row r="3781" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3781" s="2"/>
       <c r="I3781" s="1"/>
     </row>
     <row r="3782" spans="8:9" x14ac:dyDescent="0.3">
@@ -31272,10 +31068,10 @@
       <c r="I3788" s="1"/>
     </row>
     <row r="3789" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3789" s="2"/>
       <c r="I3789" s="1"/>
     </row>
     <row r="3790" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3790" s="2"/>
       <c r="I3790" s="1"/>
     </row>
     <row r="3791" spans="8:9" x14ac:dyDescent="0.3">
@@ -31307,6 +31103,7 @@
       <c r="I3797" s="1"/>
     </row>
     <row r="3798" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3798" s="2"/>
       <c r="I3798" s="1"/>
     </row>
     <row r="3799" spans="8:9" x14ac:dyDescent="0.3">
@@ -31498,7 +31295,6 @@
       <c r="I3845" s="1"/>
     </row>
     <row r="3846" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3846" s="2"/>
       <c r="I3846" s="1"/>
     </row>
     <row r="3847" spans="8:9" x14ac:dyDescent="0.3">
@@ -31530,6 +31326,7 @@
       <c r="I3853" s="1"/>
     </row>
     <row r="3854" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3854" s="2"/>
       <c r="I3854" s="1"/>
     </row>
     <row r="3855" spans="8:9" x14ac:dyDescent="0.3">
@@ -31613,7 +31410,6 @@
       <c r="I3874" s="1"/>
     </row>
     <row r="3875" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3875" s="2"/>
       <c r="I3875" s="1"/>
     </row>
     <row r="3876" spans="8:9" x14ac:dyDescent="0.3">
@@ -31641,10 +31437,10 @@
       <c r="I3881" s="1"/>
     </row>
     <row r="3882" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3882" s="2"/>
       <c r="I3882" s="1"/>
     </row>
     <row r="3883" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3883" s="2"/>
       <c r="I3883" s="1"/>
     </row>
     <row r="3884" spans="8:9" x14ac:dyDescent="0.3">
@@ -31672,6 +31468,7 @@
       <c r="I3889" s="1"/>
     </row>
     <row r="3890" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3890" s="2"/>
       <c r="I3890" s="1"/>
     </row>
     <row r="3891" spans="8:9" x14ac:dyDescent="0.3">
@@ -31787,7 +31584,6 @@
       <c r="I3918" s="1"/>
     </row>
     <row r="3919" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3919" s="2"/>
       <c r="I3919" s="1"/>
     </row>
     <row r="3920" spans="8:9" x14ac:dyDescent="0.3">
@@ -31819,6 +31615,7 @@
       <c r="I3926" s="1"/>
     </row>
     <row r="3927" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H3927" s="2"/>
       <c r="I3927" s="1"/>
     </row>
     <row r="3928" spans="8:9" x14ac:dyDescent="0.3">
@@ -32106,7 +31903,6 @@
       <c r="I3998" s="1"/>
     </row>
     <row r="3999" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H3999" s="2"/>
       <c r="I3999" s="1"/>
     </row>
     <row r="4000" spans="8:9" x14ac:dyDescent="0.3">
@@ -32138,6 +31934,7 @@
       <c r="I4006" s="1"/>
     </row>
     <row r="4007" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4007" s="2"/>
       <c r="I4007" s="1"/>
     </row>
     <row r="4008" spans="8:9" x14ac:dyDescent="0.3">
@@ -32225,7 +32022,6 @@
       <c r="I4028" s="1"/>
     </row>
     <row r="4029" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4029" s="2"/>
       <c r="I4029" s="1"/>
     </row>
     <row r="4030" spans="8:9" x14ac:dyDescent="0.3">
@@ -32257,6 +32053,7 @@
       <c r="I4036" s="1"/>
     </row>
     <row r="4037" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4037" s="2"/>
       <c r="I4037" s="1"/>
     </row>
     <row r="4038" spans="8:9" x14ac:dyDescent="0.3">
@@ -32300,7 +32097,6 @@
       <c r="I4047" s="1"/>
     </row>
     <row r="4048" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4048" s="2"/>
       <c r="I4048" s="1"/>
     </row>
     <row r="4049" spans="8:9" x14ac:dyDescent="0.3">
@@ -32332,6 +32128,7 @@
       <c r="I4055" s="1"/>
     </row>
     <row r="4056" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4056" s="2"/>
       <c r="I4056" s="1"/>
     </row>
     <row r="4057" spans="8:9" x14ac:dyDescent="0.3">
@@ -32471,7 +32268,6 @@
       <c r="I4090" s="1"/>
     </row>
     <row r="4091" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4091" s="2"/>
       <c r="I4091" s="1"/>
     </row>
     <row r="4092" spans="8:9" x14ac:dyDescent="0.3">
@@ -32503,6 +32299,7 @@
       <c r="I4098" s="1"/>
     </row>
     <row r="4099" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4099" s="2"/>
       <c r="I4099" s="1"/>
     </row>
     <row r="4100" spans="8:9" x14ac:dyDescent="0.3">
@@ -32598,7 +32395,6 @@
       <c r="I4122" s="1"/>
     </row>
     <row r="4123" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4123" s="2"/>
       <c r="I4123" s="1"/>
     </row>
     <row r="4124" spans="8:9" x14ac:dyDescent="0.3">
@@ -32610,7 +32406,6 @@
       <c r="I4125" s="1"/>
     </row>
     <row r="4126" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4126" s="2"/>
       <c r="I4126" s="1"/>
     </row>
     <row r="4127" spans="8:9" x14ac:dyDescent="0.3">
@@ -32630,6 +32425,7 @@
       <c r="I4130" s="1"/>
     </row>
     <row r="4131" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4131" s="2"/>
       <c r="I4131" s="1"/>
     </row>
     <row r="4132" spans="8:9" x14ac:dyDescent="0.3">
@@ -32637,10 +32433,10 @@
       <c r="I4132" s="1"/>
     </row>
     <row r="4133" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4133" s="2"/>
       <c r="I4133" s="1"/>
     </row>
     <row r="4134" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4134" s="2"/>
       <c r="I4134" s="1"/>
     </row>
     <row r="4135" spans="8:9" x14ac:dyDescent="0.3">
@@ -32668,6 +32464,7 @@
       <c r="I4140" s="1"/>
     </row>
     <row r="4141" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4141" s="2"/>
       <c r="I4141" s="1"/>
     </row>
     <row r="4142" spans="8:9" x14ac:dyDescent="0.3">
@@ -33171,7 +32968,6 @@
       <c r="I4266" s="1"/>
     </row>
     <row r="4267" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4267" s="2"/>
       <c r="I4267" s="1"/>
     </row>
     <row r="4268" spans="8:9" x14ac:dyDescent="0.3">
@@ -33199,10 +32995,10 @@
       <c r="I4273" s="1"/>
     </row>
     <row r="4274" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4274" s="2"/>
       <c r="I4274" s="1"/>
     </row>
     <row r="4275" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4275" s="2"/>
       <c r="I4275" s="1"/>
     </row>
     <row r="4276" spans="8:9" x14ac:dyDescent="0.3">
@@ -33230,6 +33026,7 @@
       <c r="I4281" s="1"/>
     </row>
     <row r="4282" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4282" s="2"/>
       <c r="I4282" s="1"/>
     </row>
     <row r="4283" spans="8:9" x14ac:dyDescent="0.3">
@@ -33493,7 +33290,6 @@
       <c r="I4347" s="1"/>
     </row>
     <row r="4348" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4348" s="2"/>
       <c r="I4348" s="1"/>
     </row>
     <row r="4349" spans="8:9" x14ac:dyDescent="0.3">
@@ -33525,6 +33321,7 @@
       <c r="I4355" s="1"/>
     </row>
     <row r="4356" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4356" s="2"/>
       <c r="I4356" s="1"/>
     </row>
     <row r="4357" spans="8:9" x14ac:dyDescent="0.3">
@@ -33636,11 +33433,9 @@
       <c r="I4383" s="1"/>
     </row>
     <row r="4384" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4384" s="2"/>
       <c r="I4384" s="1"/>
     </row>
     <row r="4385" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4385" s="2"/>
       <c r="I4385" s="1"/>
     </row>
     <row r="4386" spans="8:9" x14ac:dyDescent="0.3">
@@ -33668,9 +33463,11 @@
       <c r="I4391" s="1"/>
     </row>
     <row r="4392" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4392" s="2"/>
       <c r="I4392" s="1"/>
     </row>
     <row r="4393" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4393" s="2"/>
       <c r="I4393" s="1"/>
     </row>
     <row r="4394" spans="8:9" x14ac:dyDescent="0.3">
@@ -33686,7 +33483,6 @@
       <c r="I4396" s="1"/>
     </row>
     <row r="4397" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4397" s="2"/>
       <c r="I4397" s="1"/>
     </row>
     <row r="4398" spans="8:9" x14ac:dyDescent="0.3">
@@ -33714,10 +33510,10 @@
       <c r="I4403" s="1"/>
     </row>
     <row r="4404" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4404" s="2"/>
       <c r="I4404" s="1"/>
     </row>
     <row r="4405" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4405" s="2"/>
       <c r="I4405" s="1"/>
     </row>
     <row r="4406" spans="8:9" x14ac:dyDescent="0.3">
@@ -33745,6 +33541,7 @@
       <c r="I4411" s="1"/>
     </row>
     <row r="4412" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4412" s="2"/>
       <c r="I4412" s="1"/>
     </row>
     <row r="4413" spans="8:9" x14ac:dyDescent="0.3">
@@ -34052,7 +33849,6 @@
       <c r="I4488" s="1"/>
     </row>
     <row r="4489" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4489" s="2"/>
       <c r="I4489" s="1"/>
     </row>
     <row r="4490" spans="8:9" x14ac:dyDescent="0.3">
@@ -34084,6 +33880,7 @@
       <c r="I4496" s="1"/>
     </row>
     <row r="4497" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4497" s="2"/>
       <c r="I4497" s="1"/>
     </row>
     <row r="4498" spans="8:9" x14ac:dyDescent="0.3">
@@ -34095,7 +33892,6 @@
       <c r="I4499" s="1"/>
     </row>
     <row r="4500" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4500" s="2"/>
       <c r="I4500" s="1"/>
     </row>
     <row r="4501" spans="8:9" x14ac:dyDescent="0.3">
@@ -34127,6 +33923,7 @@
       <c r="I4507" s="1"/>
     </row>
     <row r="4508" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4508" s="2"/>
       <c r="I4508" s="1"/>
     </row>
     <row r="4509" spans="8:9" x14ac:dyDescent="0.3">
@@ -34198,7 +33995,6 @@
       <c r="I4525" s="1"/>
     </row>
     <row r="4526" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4526" s="2"/>
       <c r="I4526" s="1"/>
     </row>
     <row r="4527" spans="8:9" x14ac:dyDescent="0.3">
@@ -34230,6 +34026,7 @@
       <c r="I4533" s="1"/>
     </row>
     <row r="4534" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4534" s="2"/>
       <c r="I4534" s="1"/>
     </row>
     <row r="4535" spans="8:9" x14ac:dyDescent="0.3">
@@ -34249,7 +34046,6 @@
       <c r="I4538" s="1"/>
     </row>
     <row r="4539" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4539" s="2"/>
       <c r="I4539" s="1"/>
     </row>
     <row r="4540" spans="8:9" x14ac:dyDescent="0.3">
@@ -34281,6 +34077,7 @@
       <c r="I4546" s="1"/>
     </row>
     <row r="4547" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4547" s="2"/>
       <c r="I4547" s="1"/>
     </row>
     <row r="4548" spans="8:9" x14ac:dyDescent="0.3">
@@ -34608,7 +34405,6 @@
       <c r="I4628" s="1"/>
     </row>
     <row r="4629" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4629" s="2"/>
       <c r="I4629" s="1"/>
     </row>
     <row r="4630" spans="8:9" x14ac:dyDescent="0.3">
@@ -34620,7 +34416,6 @@
       <c r="I4631" s="1"/>
     </row>
     <row r="4632" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4632" s="2"/>
       <c r="I4632" s="1"/>
     </row>
     <row r="4633" spans="8:9" x14ac:dyDescent="0.3">
@@ -34640,6 +34435,7 @@
       <c r="I4636" s="1"/>
     </row>
     <row r="4637" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4637" s="2"/>
       <c r="I4637" s="1"/>
     </row>
     <row r="4638" spans="8:9" x14ac:dyDescent="0.3">
@@ -34651,6 +34447,7 @@
       <c r="I4639" s="1"/>
     </row>
     <row r="4640" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4640" s="2"/>
       <c r="I4640" s="1"/>
     </row>
     <row r="4641" spans="8:9" x14ac:dyDescent="0.3">
@@ -34742,7 +34539,6 @@
       <c r="I4662" s="1"/>
     </row>
     <row r="4663" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4663" s="2"/>
       <c r="I4663" s="1"/>
     </row>
     <row r="4664" spans="8:9" x14ac:dyDescent="0.3">
@@ -34774,6 +34570,7 @@
       <c r="I4670" s="1"/>
     </row>
     <row r="4671" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4671" s="2"/>
       <c r="I4671" s="1"/>
     </row>
     <row r="4672" spans="8:9" x14ac:dyDescent="0.3">
@@ -34833,7 +34630,6 @@
       <c r="I4685" s="1"/>
     </row>
     <row r="4686" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4686" s="2"/>
       <c r="I4686" s="1"/>
     </row>
     <row r="4687" spans="8:9" x14ac:dyDescent="0.3">
@@ -34865,6 +34661,7 @@
       <c r="I4693" s="1"/>
     </row>
     <row r="4694" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4694" s="2"/>
       <c r="I4694" s="1"/>
     </row>
     <row r="4695" spans="8:9" x14ac:dyDescent="0.3">
@@ -35108,7 +34905,6 @@
       <c r="I4754" s="1"/>
     </row>
     <row r="4755" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4755" s="2"/>
       <c r="I4755" s="1"/>
     </row>
     <row r="4756" spans="8:9" x14ac:dyDescent="0.3">
@@ -35140,6 +34936,7 @@
       <c r="I4762" s="1"/>
     </row>
     <row r="4763" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4763" s="2"/>
       <c r="I4763" s="1"/>
     </row>
     <row r="4764" spans="8:9" x14ac:dyDescent="0.3">
@@ -35263,7 +35060,6 @@
       <c r="I4793" s="1"/>
     </row>
     <row r="4794" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4794" s="2"/>
       <c r="I4794" s="1"/>
     </row>
     <row r="4795" spans="8:9" x14ac:dyDescent="0.3">
@@ -35295,6 +35091,7 @@
       <c r="I4801" s="1"/>
     </row>
     <row r="4802" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4802" s="2"/>
       <c r="I4802" s="1"/>
     </row>
     <row r="4803" spans="8:9" x14ac:dyDescent="0.3">
@@ -35314,7 +35111,6 @@
       <c r="I4806" s="1"/>
     </row>
     <row r="4807" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4807" s="2"/>
       <c r="I4807" s="1"/>
     </row>
     <row r="4808" spans="8:9" x14ac:dyDescent="0.3">
@@ -35346,6 +35142,7 @@
       <c r="I4814" s="1"/>
     </row>
     <row r="4815" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4815" s="2"/>
       <c r="I4815" s="1"/>
     </row>
     <row r="4816" spans="8:9" x14ac:dyDescent="0.3">
@@ -35469,7 +35266,6 @@
       <c r="I4845" s="1"/>
     </row>
     <row r="4846" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4846" s="2"/>
       <c r="I4846" s="1"/>
     </row>
     <row r="4847" spans="8:9" x14ac:dyDescent="0.3">
@@ -35501,6 +35297,7 @@
       <c r="I4853" s="1"/>
     </row>
     <row r="4854" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4854" s="2"/>
       <c r="I4854" s="1"/>
     </row>
     <row r="4855" spans="8:9" x14ac:dyDescent="0.3">
@@ -35532,7 +35329,6 @@
       <c r="I4861" s="1"/>
     </row>
     <row r="4862" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4862" s="2"/>
       <c r="I4862" s="1"/>
     </row>
     <row r="4863" spans="8:9" x14ac:dyDescent="0.3">
@@ -35564,6 +35360,7 @@
       <c r="I4869" s="1"/>
     </row>
     <row r="4870" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4870" s="2"/>
       <c r="I4870" s="1"/>
     </row>
     <row r="4871" spans="8:9" x14ac:dyDescent="0.3">
@@ -35615,7 +35412,6 @@
       <c r="I4882" s="1"/>
     </row>
     <row r="4883" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4883" s="2"/>
       <c r="I4883" s="1"/>
     </row>
     <row r="4884" spans="8:9" x14ac:dyDescent="0.3">
@@ -35647,6 +35443,7 @@
       <c r="I4890" s="1"/>
     </row>
     <row r="4891" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4891" s="2"/>
       <c r="I4891" s="1"/>
     </row>
     <row r="4892" spans="8:9" x14ac:dyDescent="0.3">
@@ -35662,7 +35459,6 @@
       <c r="I4894" s="1"/>
     </row>
     <row r="4895" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4895" s="2"/>
       <c r="I4895" s="1"/>
     </row>
     <row r="4896" spans="8:9" x14ac:dyDescent="0.3">
@@ -35674,7 +35470,6 @@
       <c r="I4897" s="1"/>
     </row>
     <row r="4898" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4898" s="2"/>
       <c r="I4898" s="1"/>
     </row>
     <row r="4899" spans="8:9" x14ac:dyDescent="0.3">
@@ -35694,6 +35489,7 @@
       <c r="I4902" s="1"/>
     </row>
     <row r="4903" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4903" s="2"/>
       <c r="I4903" s="1"/>
     </row>
     <row r="4904" spans="8:9" x14ac:dyDescent="0.3">
@@ -35705,6 +35501,7 @@
       <c r="I4905" s="1"/>
     </row>
     <row r="4906" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4906" s="2"/>
       <c r="I4906" s="1"/>
     </row>
     <row r="4907" spans="8:9" x14ac:dyDescent="0.3">
@@ -35756,7 +35553,6 @@
       <c r="I4918" s="1"/>
     </row>
     <row r="4919" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4919" s="2"/>
       <c r="I4919" s="1"/>
     </row>
     <row r="4920" spans="8:9" x14ac:dyDescent="0.3">
@@ -35788,6 +35584,7 @@
       <c r="I4926" s="1"/>
     </row>
     <row r="4927" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4927" s="2"/>
       <c r="I4927" s="1"/>
     </row>
     <row r="4928" spans="8:9" x14ac:dyDescent="0.3">
@@ -36035,7 +35832,6 @@
       <c r="I4988" s="1"/>
     </row>
     <row r="4989" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H4989" s="2"/>
       <c r="I4989" s="1"/>
     </row>
     <row r="4990" spans="8:9" x14ac:dyDescent="0.3">
@@ -36067,6 +35863,7 @@
       <c r="I4996" s="1"/>
     </row>
     <row r="4997" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H4997" s="2"/>
       <c r="I4997" s="1"/>
     </row>
     <row r="4998" spans="8:9" x14ac:dyDescent="0.3">
@@ -36114,7 +35911,6 @@
       <c r="I5008" s="1"/>
     </row>
     <row r="5009" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5009" s="2"/>
       <c r="I5009" s="1"/>
     </row>
     <row r="5010" spans="8:9" x14ac:dyDescent="0.3">
@@ -36146,6 +35942,7 @@
       <c r="I5016" s="1"/>
     </row>
     <row r="5017" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5017" s="2"/>
       <c r="I5017" s="1"/>
     </row>
     <row r="5018" spans="8:9" x14ac:dyDescent="0.3">
@@ -36161,7 +35958,6 @@
       <c r="I5020" s="1"/>
     </row>
     <row r="5021" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5021" s="2"/>
       <c r="I5021" s="1"/>
     </row>
     <row r="5022" spans="8:9" x14ac:dyDescent="0.3">
@@ -36193,6 +35989,7 @@
       <c r="I5028" s="1"/>
     </row>
     <row r="5029" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5029" s="2"/>
       <c r="I5029" s="1"/>
     </row>
     <row r="5030" spans="8:9" x14ac:dyDescent="0.3">
@@ -36264,7 +36061,6 @@
       <c r="I5046" s="1"/>
     </row>
     <row r="5047" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5047" s="2"/>
       <c r="I5047" s="1"/>
     </row>
     <row r="5048" spans="8:9" x14ac:dyDescent="0.3">
@@ -36296,6 +36092,7 @@
       <c r="I5054" s="1"/>
     </row>
     <row r="5055" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5055" s="2"/>
       <c r="I5055" s="1"/>
     </row>
     <row r="5056" spans="8:9" x14ac:dyDescent="0.3">
@@ -36311,7 +36108,6 @@
       <c r="I5058" s="1"/>
     </row>
     <row r="5059" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5059" s="2"/>
       <c r="I5059" s="1"/>
     </row>
     <row r="5060" spans="8:9" x14ac:dyDescent="0.3">
@@ -36374,6 +36170,7 @@
       <c r="I5074" s="1"/>
     </row>
     <row r="5075" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5075" s="2"/>
       <c r="I5075" s="1"/>
     </row>
     <row r="5076" spans="8:9" x14ac:dyDescent="0.3">
@@ -36473,7 +36270,6 @@
       <c r="I5099" s="1"/>
     </row>
     <row r="5100" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5100" s="2"/>
       <c r="I5100" s="1"/>
     </row>
     <row r="5101" spans="8:9" x14ac:dyDescent="0.3">
@@ -36505,6 +36301,7 @@
       <c r="I5107" s="1"/>
     </row>
     <row r="5108" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5108" s="2"/>
       <c r="I5108" s="1"/>
     </row>
     <row r="5109" spans="8:9" x14ac:dyDescent="0.3">
@@ -36692,7 +36489,6 @@
       <c r="I5154" s="1"/>
     </row>
     <row r="5155" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5155" s="2"/>
       <c r="I5155" s="1"/>
     </row>
     <row r="5156" spans="8:9" x14ac:dyDescent="0.3">
@@ -36724,6 +36520,7 @@
       <c r="I5162" s="1"/>
     </row>
     <row r="5163" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5163" s="2"/>
       <c r="I5163" s="1"/>
     </row>
     <row r="5164" spans="8:9" x14ac:dyDescent="0.3">
@@ -37023,7 +36820,6 @@
       <c r="I5237" s="1"/>
     </row>
     <row r="5238" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5238" s="2"/>
       <c r="I5238" s="1"/>
     </row>
     <row r="5239" spans="8:9" x14ac:dyDescent="0.3">
@@ -37062,7 +36858,6 @@
       <c r="I5247" s="1"/>
     </row>
     <row r="5248" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5248" s="2"/>
       <c r="I5248" s="1"/>
     </row>
     <row r="5249" spans="8:9" x14ac:dyDescent="0.3">
@@ -37086,6 +36881,7 @@
       <c r="I5253" s="1"/>
     </row>
     <row r="5254" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5254" s="2"/>
       <c r="I5254" s="1"/>
     </row>
     <row r="5255" spans="8:9" x14ac:dyDescent="0.3">
@@ -37093,6 +36889,7 @@
       <c r="I5255" s="1"/>
     </row>
     <row r="5256" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5256" s="2"/>
       <c r="I5256" s="1"/>
     </row>
     <row r="5257" spans="8:9" x14ac:dyDescent="0.3">
@@ -37248,7 +37045,6 @@
       <c r="I5294" s="1"/>
     </row>
     <row r="5295" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5295" s="2"/>
       <c r="I5295" s="1"/>
     </row>
     <row r="5296" spans="8:9" x14ac:dyDescent="0.3">
@@ -37280,6 +37076,7 @@
       <c r="I5302" s="1"/>
     </row>
     <row r="5303" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5303" s="2"/>
       <c r="I5303" s="1"/>
     </row>
     <row r="5304" spans="8:9" x14ac:dyDescent="0.3">
@@ -37287,7 +37084,6 @@
       <c r="I5304" s="1"/>
     </row>
     <row r="5305" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5305" s="2"/>
       <c r="I5305" s="1"/>
     </row>
     <row r="5306" spans="8:9" x14ac:dyDescent="0.3">
@@ -37319,6 +37115,7 @@
       <c r="I5312" s="1"/>
     </row>
     <row r="5313" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5313" s="2"/>
       <c r="I5313" s="1"/>
     </row>
     <row r="5314" spans="8:9" x14ac:dyDescent="0.3">
@@ -37682,7 +37479,6 @@
       <c r="I5403" s="1"/>
     </row>
     <row r="5404" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5404" s="2"/>
       <c r="I5404" s="1"/>
     </row>
     <row r="5405" spans="8:9" x14ac:dyDescent="0.3">
@@ -37702,18 +37498,16 @@
       <c r="I5408" s="1"/>
     </row>
     <row r="5409" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5409" s="2"/>
       <c r="I5409" s="1"/>
     </row>
     <row r="5410" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5410" s="2"/>
       <c r="I5410" s="1"/>
     </row>
     <row r="5411" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5411" s="2"/>
       <c r="I5411" s="1"/>
     </row>
     <row r="5412" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5412" s="2"/>
       <c r="I5412" s="1"/>
     </row>
     <row r="5413" spans="8:9" x14ac:dyDescent="0.3">
@@ -37725,7 +37519,6 @@
       <c r="I5414" s="1"/>
     </row>
     <row r="5415" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5415" s="2"/>
       <c r="I5415" s="1"/>
     </row>
     <row r="5416" spans="8:9" x14ac:dyDescent="0.3">
@@ -37733,12 +37526,15 @@
       <c r="I5416" s="1"/>
     </row>
     <row r="5417" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5417" s="2"/>
       <c r="I5417" s="1"/>
     </row>
     <row r="5418" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5418" s="2"/>
       <c r="I5418" s="1"/>
     </row>
     <row r="5419" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5419" s="2"/>
       <c r="I5419" s="1"/>
     </row>
     <row r="5420" spans="8:9" x14ac:dyDescent="0.3">
@@ -37754,6 +37550,7 @@
       <c r="I5422" s="1"/>
     </row>
     <row r="5423" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5423" s="2"/>
       <c r="I5423" s="1"/>
     </row>
     <row r="5424" spans="8:9" x14ac:dyDescent="0.3">
@@ -38069,7 +37866,6 @@
       <c r="I5501" s="1"/>
     </row>
     <row r="5502" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5502" s="2"/>
       <c r="I5502" s="1"/>
     </row>
     <row r="5503" spans="8:9" x14ac:dyDescent="0.3">
@@ -38081,7 +37877,6 @@
       <c r="I5504" s="1"/>
     </row>
     <row r="5505" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5505" s="2"/>
       <c r="I5505" s="1"/>
     </row>
     <row r="5506" spans="8:9" x14ac:dyDescent="0.3">
@@ -38101,6 +37896,7 @@
       <c r="I5509" s="1"/>
     </row>
     <row r="5510" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5510" s="2"/>
       <c r="I5510" s="1"/>
     </row>
     <row r="5511" spans="8:9" x14ac:dyDescent="0.3">
@@ -38112,6 +37908,7 @@
       <c r="I5512" s="1"/>
     </row>
     <row r="5513" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5513" s="2"/>
       <c r="I5513" s="1"/>
     </row>
     <row r="5514" spans="8:9" x14ac:dyDescent="0.3">
@@ -38143,7 +37940,6 @@
       <c r="I5520" s="1"/>
     </row>
     <row r="5521" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5521" s="2"/>
       <c r="I5521" s="1"/>
     </row>
     <row r="5522" spans="8:9" x14ac:dyDescent="0.3">
@@ -38175,6 +37971,7 @@
       <c r="I5528" s="1"/>
     </row>
     <row r="5529" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5529" s="2"/>
       <c r="I5529" s="1"/>
     </row>
     <row r="5530" spans="8:9" x14ac:dyDescent="0.3">
@@ -38190,7 +37987,6 @@
       <c r="I5532" s="1"/>
     </row>
     <row r="5533" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5533" s="2"/>
       <c r="I5533" s="1"/>
     </row>
     <row r="5534" spans="8:9" x14ac:dyDescent="0.3">
@@ -38210,7 +38006,6 @@
       <c r="I5537" s="1"/>
     </row>
     <row r="5538" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5538" s="2"/>
       <c r="I5538" s="1"/>
     </row>
     <row r="5539" spans="8:9" x14ac:dyDescent="0.3">
@@ -38222,6 +38017,7 @@
       <c r="I5540" s="1"/>
     </row>
     <row r="5541" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5541" s="2"/>
       <c r="I5541" s="1"/>
     </row>
     <row r="5542" spans="8:9" x14ac:dyDescent="0.3">
@@ -38241,6 +38037,7 @@
       <c r="I5545" s="1"/>
     </row>
     <row r="5546" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5546" s="2"/>
       <c r="I5546" s="1"/>
     </row>
     <row r="5547" spans="8:9" x14ac:dyDescent="0.3">
@@ -38300,7 +38097,6 @@
       <c r="I5560" s="1"/>
     </row>
     <row r="5561" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5561" s="2"/>
       <c r="I5561" s="1"/>
     </row>
     <row r="5562" spans="8:9" x14ac:dyDescent="0.3">
@@ -38332,6 +38128,7 @@
       <c r="I5568" s="1"/>
     </row>
     <row r="5569" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5569" s="2"/>
       <c r="I5569" s="1"/>
     </row>
     <row r="5570" spans="8:9" x14ac:dyDescent="0.3">
@@ -38563,7 +38360,6 @@
       <c r="I5626" s="1"/>
     </row>
     <row r="5627" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5627" s="2"/>
       <c r="I5627" s="1"/>
     </row>
     <row r="5628" spans="8:9" x14ac:dyDescent="0.3">
@@ -38595,6 +38391,7 @@
       <c r="I5634" s="1"/>
     </row>
     <row r="5635" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5635" s="2"/>
       <c r="I5635" s="1"/>
     </row>
     <row r="5636" spans="8:9" x14ac:dyDescent="0.3">
@@ -38718,7 +38515,6 @@
       <c r="I5665" s="1"/>
     </row>
     <row r="5666" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5666" s="2"/>
       <c r="I5666" s="1"/>
     </row>
     <row r="5667" spans="8:9" x14ac:dyDescent="0.3">
@@ -38750,6 +38546,7 @@
       <c r="I5673" s="1"/>
     </row>
     <row r="5674" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5674" s="2"/>
       <c r="I5674" s="1"/>
     </row>
     <row r="5675" spans="8:9" x14ac:dyDescent="0.3">
@@ -38757,11 +38554,9 @@
       <c r="I5675" s="1"/>
     </row>
     <row r="5676" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5676" s="2"/>
       <c r="I5676" s="1"/>
     </row>
     <row r="5677" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5677" s="2"/>
       <c r="I5677" s="1"/>
     </row>
     <row r="5678" spans="8:9" x14ac:dyDescent="0.3">
@@ -38789,9 +38584,11 @@
       <c r="I5683" s="1"/>
     </row>
     <row r="5684" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5684" s="2"/>
       <c r="I5684" s="1"/>
     </row>
     <row r="5685" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5685" s="2"/>
       <c r="I5685" s="1"/>
     </row>
     <row r="5686" spans="8:9" x14ac:dyDescent="0.3">
@@ -38871,7 +38668,6 @@
       <c r="I5704" s="1"/>
     </row>
     <row r="5705" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5705" s="2"/>
       <c r="I5705" s="1"/>
     </row>
     <row r="5706" spans="8:9" x14ac:dyDescent="0.3">
@@ -38903,6 +38699,7 @@
       <c r="I5712" s="1"/>
     </row>
     <row r="5713" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5713" s="2"/>
       <c r="I5713" s="1"/>
     </row>
     <row r="5714" spans="8:9" x14ac:dyDescent="0.3">
@@ -38946,7 +38743,6 @@
       <c r="I5723" s="1"/>
     </row>
     <row r="5724" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5724" s="2"/>
       <c r="I5724" s="1"/>
     </row>
     <row r="5725" spans="8:9" x14ac:dyDescent="0.3">
@@ -38978,6 +38774,7 @@
       <c r="I5731" s="1"/>
     </row>
     <row r="5732" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5732" s="2"/>
       <c r="I5732" s="1"/>
     </row>
     <row r="5733" spans="8:9" x14ac:dyDescent="0.3">
@@ -38997,7 +38794,6 @@
       <c r="I5736" s="1"/>
     </row>
     <row r="5737" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5737" s="2"/>
       <c r="I5737" s="1"/>
     </row>
     <row r="5738" spans="8:9" x14ac:dyDescent="0.3">
@@ -39029,6 +38825,7 @@
       <c r="I5744" s="1"/>
     </row>
     <row r="5745" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5745" s="2"/>
       <c r="I5745" s="1"/>
     </row>
     <row r="5746" spans="8:9" x14ac:dyDescent="0.3">
@@ -39040,11 +38837,9 @@
       <c r="I5747" s="1"/>
     </row>
     <row r="5748" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5748" s="2"/>
       <c r="I5748" s="1"/>
     </row>
     <row r="5749" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5749" s="2"/>
       <c r="I5749" s="1"/>
     </row>
     <row r="5750" spans="8:9" x14ac:dyDescent="0.3">
@@ -39064,7 +38859,6 @@
       <c r="I5753" s="1"/>
     </row>
     <row r="5754" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5754" s="2"/>
       <c r="I5754" s="1"/>
     </row>
     <row r="5755" spans="8:9" x14ac:dyDescent="0.3">
@@ -39072,9 +38866,11 @@
       <c r="I5755" s="1"/>
     </row>
     <row r="5756" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5756" s="2"/>
       <c r="I5756" s="1"/>
     </row>
     <row r="5757" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5757" s="2"/>
       <c r="I5757" s="1"/>
     </row>
     <row r="5758" spans="8:9" x14ac:dyDescent="0.3">
@@ -39094,6 +38890,7 @@
       <c r="I5761" s="1"/>
     </row>
     <row r="5762" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5762" s="2"/>
       <c r="I5762" s="1"/>
     </row>
     <row r="5763" spans="8:9" x14ac:dyDescent="0.3">
@@ -39137,11 +38934,9 @@
       <c r="I5772" s="1"/>
     </row>
     <row r="5773" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5773" s="2"/>
       <c r="I5773" s="1"/>
     </row>
     <row r="5774" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5774" s="2"/>
       <c r="I5774" s="1"/>
     </row>
     <row r="5775" spans="8:9" x14ac:dyDescent="0.3">
@@ -39169,9 +38964,11 @@
       <c r="I5780" s="1"/>
     </row>
     <row r="5781" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5781" s="2"/>
       <c r="I5781" s="1"/>
     </row>
     <row r="5782" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5782" s="2"/>
       <c r="I5782" s="1"/>
     </row>
     <row r="5783" spans="8:9" x14ac:dyDescent="0.3">
@@ -39203,7 +39000,6 @@
       <c r="I5789" s="1"/>
     </row>
     <row r="5790" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5790" s="2"/>
       <c r="I5790" s="1"/>
     </row>
     <row r="5791" spans="8:9" x14ac:dyDescent="0.3">
@@ -39223,7 +39019,6 @@
       <c r="I5794" s="1"/>
     </row>
     <row r="5795" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5795" s="2"/>
       <c r="I5795" s="1"/>
     </row>
     <row r="5796" spans="8:9" x14ac:dyDescent="0.3">
@@ -39235,6 +39030,7 @@
       <c r="I5797" s="1"/>
     </row>
     <row r="5798" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5798" s="2"/>
       <c r="I5798" s="1"/>
     </row>
     <row r="5799" spans="8:9" x14ac:dyDescent="0.3">
@@ -39285,6 +39081,7 @@
       <c r="I5810" s="1"/>
     </row>
     <row r="5811" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5811" s="2"/>
       <c r="I5811" s="1"/>
     </row>
     <row r="5812" spans="8:9" x14ac:dyDescent="0.3">
@@ -39356,7 +39153,6 @@
       <c r="I5828" s="1"/>
     </row>
     <row r="5829" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5829" s="2"/>
       <c r="I5829" s="1"/>
     </row>
     <row r="5830" spans="8:9" x14ac:dyDescent="0.3">
@@ -39388,6 +39184,7 @@
       <c r="I5836" s="1"/>
     </row>
     <row r="5837" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5837" s="2"/>
       <c r="I5837" s="1"/>
     </row>
     <row r="5838" spans="8:9" x14ac:dyDescent="0.3">
@@ -39395,7 +39192,6 @@
       <c r="I5838" s="1"/>
     </row>
     <row r="5839" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5839" s="2"/>
       <c r="I5839" s="1"/>
     </row>
     <row r="5840" spans="8:9" x14ac:dyDescent="0.3">
@@ -39411,7 +39207,6 @@
       <c r="I5842" s="1"/>
     </row>
     <row r="5843" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5843" s="2"/>
       <c r="I5843" s="1"/>
     </row>
     <row r="5844" spans="8:9" x14ac:dyDescent="0.3">
@@ -39442,6 +39237,7 @@
       <c r="I5850" s="1"/>
     </row>
     <row r="5851" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5851" s="2"/>
       <c r="I5851" s="1"/>
     </row>
     <row r="5852" spans="8:9" x14ac:dyDescent="0.3">
@@ -39449,7 +39245,6 @@
       <c r="I5852" s="1"/>
     </row>
     <row r="5853" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5853" s="2"/>
       <c r="I5853" s="1"/>
     </row>
     <row r="5854" spans="8:9" x14ac:dyDescent="0.3">
@@ -39457,6 +39252,7 @@
       <c r="I5854" s="1"/>
     </row>
     <row r="5855" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5855" s="2"/>
       <c r="I5855" s="1"/>
     </row>
     <row r="5856" spans="8:9" x14ac:dyDescent="0.3">
@@ -39503,7 +39299,6 @@
       <c r="I5866" s="1"/>
     </row>
     <row r="5867" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5867" s="2"/>
       <c r="I5867" s="1"/>
     </row>
     <row r="5868" spans="8:9" x14ac:dyDescent="0.3">
@@ -39511,6 +39306,7 @@
       <c r="I5868" s="1"/>
     </row>
     <row r="5869" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5869" s="2"/>
       <c r="I5869" s="1"/>
     </row>
     <row r="5870" spans="8:9" x14ac:dyDescent="0.3">
@@ -39534,6 +39330,7 @@
       <c r="I5874" s="1"/>
     </row>
     <row r="5875" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5875" s="2"/>
       <c r="I5875" s="1"/>
     </row>
     <row r="5876" spans="8:9" x14ac:dyDescent="0.3">
@@ -39573,7 +39370,6 @@
       <c r="I5884" s="1"/>
     </row>
     <row r="5885" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5885" s="2"/>
       <c r="I5885" s="1"/>
     </row>
     <row r="5886" spans="8:9" x14ac:dyDescent="0.3">
@@ -39605,6 +39401,7 @@
       <c r="I5892" s="1"/>
     </row>
     <row r="5893" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5893" s="2"/>
       <c r="I5893" s="1"/>
     </row>
     <row r="5894" spans="8:9" x14ac:dyDescent="0.3">
@@ -39628,7 +39425,6 @@
       <c r="I5898" s="1"/>
     </row>
     <row r="5899" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5899" s="2"/>
       <c r="I5899" s="1"/>
     </row>
     <row r="5900" spans="8:9" x14ac:dyDescent="0.3">
@@ -39660,6 +39456,7 @@
       <c r="I5906" s="1"/>
     </row>
     <row r="5907" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H5907" s="2"/>
       <c r="I5907" s="1"/>
     </row>
     <row r="5908" spans="8:9" x14ac:dyDescent="0.3">
@@ -39671,11 +39468,9 @@
       <c r="I5909" s="1"/>
     </row>
     <row r="5910" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5910" s="2"/>
       <c r="I5910" s="1"/>
     </row>
     <row r="5911" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5911" s="2"/>
       <c r="I5911" s="1"/>
     </row>
     <row r="5912" spans="8:9" x14ac:dyDescent="0.3">
@@ -39687,48 +39482,18 @@
       <c r="I5913" s="1"/>
     </row>
     <row r="5914" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5914" s="2"/>
       <c r="I5914" s="1"/>
     </row>
     <row r="5915" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5915" s="2"/>
       <c r="I5915" s="1"/>
     </row>
     <row r="5916" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H5916" s="2"/>
       <c r="I5916" s="1"/>
     </row>
-    <row r="5917" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5917" s="2"/>
-      <c r="I5917" s="1"/>
-    </row>
-    <row r="5918" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I5918" s="1"/>
-    </row>
-    <row r="5919" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I5919" s="1"/>
-    </row>
-    <row r="5920" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5920" s="2"/>
-      <c r="I5920" s="1"/>
-    </row>
-    <row r="5921" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5921" s="2"/>
-      <c r="I5921" s="1"/>
-    </row>
-    <row r="5922" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I5922" s="1"/>
-    </row>
-    <row r="5923" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="I5923" s="1"/>
-    </row>
-    <row r="5924" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H5924" s="2"/>
-      <c r="I5924" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B610:K635">
-    <sortCondition ref="B610:B635"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B605:K626">
+    <sortCondition ref="D605:D626"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\TNT Wrecker - Samsara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\tnt-wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3583209A-A34D-4D1C-9E1A-7415876F1D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BBCDC1-49AE-421D-B80B-FD3C6743FFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18552,7 +18552,7 @@
         <v>46176.418402777781</v>
       </c>
       <c r="J637">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K637" t="s">
         <v>11</v>
@@ -18581,7 +18581,7 @@
         <v>46176.41909722222</v>
       </c>
       <c r="J638">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K638" t="s">
         <v>11</v>
@@ -18610,7 +18610,7 @@
         <v>46176.419791666667</v>
       </c>
       <c r="J639">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K639" t="s">
         <v>11</v>
@@ -18729,7 +18729,7 @@
         <v>46176.421180555553</v>
       </c>
       <c r="J643">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K643" t="s">
         <v>11</v>
@@ -18758,7 +18758,7 @@
         <v>46176.421875</v>
       </c>
       <c r="J644">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K644" t="s">
         <v>11</v>
@@ -18787,7 +18787,7 @@
         <v>46176.422569444447</v>
       </c>
       <c r="J645">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K645" t="s">
         <v>11</v>
@@ -18816,7 +18816,7 @@
         <v>46176.422569444447</v>
       </c>
       <c r="J646">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K646" t="s">
         <v>11</v>
@@ -18836,16 +18836,16 @@
         <v>25</v>
       </c>
       <c r="G647" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H647" s="2">
-        <v>0</v>
+        <v>6.7245370370370367E-3</v>
       </c>
       <c r="I647" s="1">
         <v>46176.422569444447</v>
       </c>
       <c r="J647">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K647" t="s">
         <v>11</v>
@@ -18932,7 +18932,7 @@
         <v>46176.423958333333</v>
       </c>
       <c r="J650">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K650" t="s">
         <v>11</v>
@@ -18961,7 +18961,7 @@
         <v>46176.42465277778</v>
       </c>
       <c r="J651">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K651" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\tnt-wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E0F4A11-6E58-4B48-A1F3-31E0C132CB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A8F591A-8501-4705-BE39-2F240BEAA081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>42</v>
       </c>
@@ -947,7 +947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>42</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>42</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>42</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>42</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>42</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
@@ -2643,7 +2643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>42</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>42</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>42</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>42</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>42</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>42</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>42</v>
       </c>
@@ -5568,7 +5568,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>42</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>42</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>42</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>42</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>42</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>42</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>42</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>42</v>
       </c>
@@ -10653,7 +10653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>42</v>
       </c>
@@ -11099,7 +11099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>42</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>42</v>
       </c>
@@ -19656,16 +19656,16 @@
         <v>32</v>
       </c>
       <c r="G676" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H676" s="2">
-        <v>0</v>
+        <v>6.0416666666666665E-3</v>
       </c>
       <c r="I676" s="1">
         <v>46237.851851851854</v>
       </c>
       <c r="J676" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K676" s="1" t="s">
         <v>11</v>
@@ -19710,6 +19710,9 @@
       <c r="D678" t="s">
         <v>93</v>
       </c>
+      <c r="E678" t="s">
+        <v>67</v>
+      </c>
       <c r="F678" t="s">
         <v>32</v>
       </c>
@@ -19752,7 +19755,7 @@
         <v>46237.85324074074</v>
       </c>
       <c r="J679" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K679" s="1" t="s">
         <v>11</v>
@@ -19772,16 +19775,16 @@
         <v>32</v>
       </c>
       <c r="G680" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H680" s="2">
-        <v>0</v>
+        <v>7.3842592592592597E-3</v>
       </c>
       <c r="I680" s="1">
         <v>46237.853935185187</v>
       </c>
       <c r="J680" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K680" s="1" t="s">
         <v>11</v>
@@ -19810,7 +19813,7 @@
         <v>46237.853935185187</v>
       </c>
       <c r="J681" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K681" s="1" t="s">
         <v>11</v>
@@ -19830,16 +19833,16 @@
         <v>32</v>
       </c>
       <c r="G682" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H682" s="2">
-        <v>0</v>
+        <v>6.875E-3</v>
       </c>
       <c r="I682" s="1">
         <v>46237.854629629626</v>
       </c>
       <c r="J682" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K682" s="1" t="s">
         <v>11</v>
@@ -19859,10 +19862,10 @@
         <v>32</v>
       </c>
       <c r="G683" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H683" s="2">
-        <v>0</v>
+        <v>6.2037037037037035E-3</v>
       </c>
       <c r="I683" s="1">
         <v>46237.855324074073</v>
@@ -19926,7 +19929,7 @@
         <v>46237.85601851852</v>
       </c>
       <c r="J685" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K685" s="1" t="s">
         <v>11</v>
@@ -19955,7 +19958,7 @@
         <v>46237.856712962966</v>
       </c>
       <c r="J686" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K686" s="1" t="s">
         <v>11</v>
@@ -19984,7 +19987,7 @@
         <v>46237.856712962966</v>
       </c>
       <c r="J687" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K687" s="1" t="s">
         <v>11</v>
@@ -20013,7 +20016,7 @@
         <v>46237.857407407406</v>
       </c>
       <c r="J688" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K688" s="1" t="s">
         <v>11</v>
@@ -20050,7 +20053,7 @@
         <v>46237.858101851853</v>
       </c>
       <c r="J690" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K690" s="1" t="s">
         <v>11</v>
@@ -20070,27 +20073,48 @@
         <v>32</v>
       </c>
       <c r="G691" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H691" s="2">
-        <v>1.0416666666666667E-4</v>
+        <v>5.9837962962962961E-3</v>
       </c>
       <c r="I691" s="1">
         <v>46237.858101851853</v>
       </c>
       <c r="J691" s="2">
+        <v>1</v>
+      </c>
+      <c r="K691" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="692" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B692" t="s">
+        <v>42</v>
+      </c>
+      <c r="C692">
+        <v>3726</v>
+      </c>
+      <c r="D692" t="s">
+        <v>83</v>
+      </c>
+      <c r="F692" t="s">
+        <v>32</v>
+      </c>
+      <c r="G692" t="s">
+        <v>10</v>
+      </c>
+      <c r="H692" s="2">
+        <v>9.5023148148148141E-3</v>
+      </c>
+      <c r="I692" s="1">
+        <v>46237.835995370369</v>
+      </c>
+      <c r="J692" s="2">
         <v>0</v>
       </c>
-      <c r="K691" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="692" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H692" s="2"/>
-      <c r="I692" s="1"/>
-      <c r="J692" s="2"/>
       <c r="K692" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="693" spans="2:11" x14ac:dyDescent="0.25">
@@ -20098,10 +20122,10 @@
         <v>42</v>
       </c>
       <c r="C693">
-        <v>3726</v>
+        <v>614</v>
       </c>
       <c r="D693" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F693" t="s">
         <v>32</v>
@@ -20110,10 +20134,10 @@
         <v>10</v>
       </c>
       <c r="H693" s="2">
-        <v>9.5023148148148141E-3</v>
+        <v>7.3148148148148148E-3</v>
       </c>
       <c r="I693" s="1">
-        <v>46237.835995370369</v>
+        <v>46237.836689814816</v>
       </c>
       <c r="J693" s="2">
         <v>0</v>
@@ -20127,65 +20151,65 @@
         <v>42</v>
       </c>
       <c r="C694">
-        <v>614</v>
+        <v>772</v>
       </c>
       <c r="D694" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F694" t="s">
         <v>32</v>
       </c>
       <c r="G694" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H694" s="2">
-        <v>7.3148148148148148E-3</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="I694" s="1">
         <v>46237.836689814816</v>
       </c>
       <c r="J694" s="2">
+        <v>3</v>
+      </c>
+      <c r="K694" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="695" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H695" s="2"/>
+      <c r="I695" s="1"/>
+      <c r="J695" s="2"/>
+      <c r="K695" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="696" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B696" t="s">
+        <v>42</v>
+      </c>
+      <c r="C696">
+        <v>623</v>
+      </c>
+      <c r="D696" t="s">
+        <v>57</v>
+      </c>
+      <c r="F696" t="s">
+        <v>32</v>
+      </c>
+      <c r="G696" t="s">
+        <v>10</v>
+      </c>
+      <c r="H696" s="2">
+        <v>5.6481481481481478E-3</v>
+      </c>
+      <c r="I696" s="1">
+        <v>46237.837384259263</v>
+      </c>
+      <c r="J696" s="2">
         <v>0</v>
       </c>
-      <c r="K694" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="695" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B695" t="s">
-        <v>42</v>
-      </c>
-      <c r="C695">
-        <v>772</v>
-      </c>
-      <c r="D695" t="s">
-        <v>56</v>
-      </c>
-      <c r="F695" t="s">
-        <v>32</v>
-      </c>
-      <c r="G695" t="s">
-        <v>12</v>
-      </c>
-      <c r="H695" s="2">
-        <v>2.0833333333333335E-4</v>
-      </c>
-      <c r="I695" s="1">
-        <v>46237.836689814816</v>
-      </c>
-      <c r="J695" s="2">
-        <v>0</v>
-      </c>
-      <c r="K695" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="696" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H696" s="2"/>
-      <c r="I696" s="1"/>
-      <c r="J696" s="2"/>
       <c r="K696" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="697" spans="2:11" x14ac:dyDescent="0.25">
@@ -20193,25 +20217,25 @@
         <v>42</v>
       </c>
       <c r="C697">
-        <v>623</v>
+        <v>72</v>
       </c>
       <c r="D697" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F697" t="s">
         <v>32</v>
       </c>
       <c r="G697" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H697" s="2">
-        <v>5.6481481481481478E-3</v>
+        <v>0</v>
       </c>
       <c r="I697" s="1">
-        <v>46237.837384259263</v>
+        <v>46237.838078703702</v>
       </c>
       <c r="J697" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K697" s="1" t="s">
         <v>11</v>
@@ -20222,25 +20246,25 @@
         <v>42</v>
       </c>
       <c r="C698">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D698" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F698" t="s">
         <v>32</v>
       </c>
       <c r="G698" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H698" s="2">
-        <v>0</v>
+        <v>8.819444444444444E-3</v>
       </c>
       <c r="I698" s="1">
         <v>46237.838078703702</v>
       </c>
       <c r="J698" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K698" s="1" t="s">
         <v>11</v>
@@ -20251,25 +20275,25 @@
         <v>42</v>
       </c>
       <c r="C699">
-        <v>84</v>
+        <v>3818</v>
       </c>
       <c r="D699" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F699" t="s">
         <v>32</v>
       </c>
       <c r="G699" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H699" s="2">
-        <v>0</v>
+        <v>1.9872685185185184E-2</v>
       </c>
       <c r="I699" s="1">
-        <v>46237.838078703702</v>
+        <v>46237.838773148149</v>
       </c>
       <c r="J699" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K699" s="1" t="s">
         <v>11</v>
@@ -20280,10 +20304,10 @@
         <v>42</v>
       </c>
       <c r="C700">
-        <v>3818</v>
+        <v>80</v>
       </c>
       <c r="D700" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F700" t="s">
         <v>32</v>
@@ -20295,43 +20319,20 @@
         <v>0</v>
       </c>
       <c r="I700" s="1">
-        <v>46237.838773148149</v>
+        <v>46237.839467592596</v>
       </c>
       <c r="J700" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K700" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="701" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B701" t="s">
-        <v>42</v>
-      </c>
-      <c r="C701">
-        <v>80</v>
-      </c>
-      <c r="D701" t="s">
-        <v>63</v>
-      </c>
-      <c r="F701" t="s">
-        <v>32</v>
-      </c>
-      <c r="G701" t="s">
-        <v>13</v>
-      </c>
-      <c r="H701" s="2">
-        <v>0</v>
-      </c>
-      <c r="I701" s="1">
-        <v>46237.839467592596</v>
-      </c>
-      <c r="J701" s="2">
-        <v>0</v>
-      </c>
-      <c r="K701" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H701" s="2"/>
+      <c r="I701" s="1"/>
+      <c r="J701" s="2"/>
+      <c r="K701" s="1"/>
     </row>
     <row r="702" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H702" s="2"/>
@@ -27827,6 +27828,7 @@
       <c r="K1957" s="1"/>
     </row>
     <row r="1958" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
       <c r="K1958" s="1"/>
     </row>
@@ -27864,6 +27866,7 @@
       <c r="K1964" s="1"/>
     </row>
     <row r="1965" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
       <c r="K1965" s="1"/>
     </row>
@@ -27928,6 +27931,7 @@
       <c r="K1976" s="1"/>
     </row>
     <row r="1977" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:11" x14ac:dyDescent="0.25">
@@ -27959,11 +27963,11 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
     <row r="1984" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
       <c r="K1984" s="1"/>
     </row>
@@ -27974,6 +27978,7 @@
       <c r="K1985" s="1"/>
     </row>
     <row r="1986" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
       <c r="K1986" s="1"/>
     </row>
@@ -28049,6 +28054,7 @@
       <c r="K1999" s="1"/>
     </row>
     <row r="2000" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
       <c r="K2000" s="1"/>
     </row>
@@ -28059,6 +28065,7 @@
       <c r="K2001" s="1"/>
     </row>
     <row r="2002" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:11" x14ac:dyDescent="0.25">
@@ -28090,7 +28097,6 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -57383,6 +57389,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -57675,6 +57682,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -57985,6 +57994,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -58109,6 +58119,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -58120,6 +58131,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -58268,6 +58280,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -58278,10 +58291,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -58315,15 +58330,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -58364,18 +58382,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -58391,6 +58413,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -58400,10 +58423,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -58439,10 +58464,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -58468,6 +58495,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -58482,6 +58510,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -58516,6 +58545,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -58525,6 +58555,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -58534,6 +58565,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -58548,15 +58580,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -58586,6 +58619,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -58606,11 +58640,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -58619,6 +58655,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -58648,6 +58685,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -58657,10 +58695,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -58675,14 +58715,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -58702,10 +58745,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -58725,9 +58770,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -58762,18 +58810,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -58788,12 +58840,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -58808,10 +58860,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -58831,6 +58885,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -58850,6 +58905,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -58859,6 +58915,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -58904,6 +58961,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -58913,6 +58971,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -58927,6 +58986,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -58936,10 +58996,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -58954,6 +59016,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -58963,6 +59026,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -58982,6 +59046,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -59001,10 +59066,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -59014,6 +59081,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -59024,10 +59092,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -59042,18 +59112,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -59073,10 +59147,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -59096,6 +59172,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -59126,7 +59203,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -59141,10 +59217,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -59159,6 +59237,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -59173,11 +59252,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -59187,6 +59266,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -59202,6 +59282,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -59216,6 +59297,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -59236,6 +59318,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -59261,11 +59344,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -59284,15 +59369,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -59302,6 +59388,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -59321,6 +59408,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -59335,6 +59423,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -59354,10 +59443,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -59367,6 +59458,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -59377,6 +59469,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -59413,7 +59506,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -59422,6 +59514,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -59435,10 +59528,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\tnt-wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A8F591A-8501-4705-BE39-2F240BEAA081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BF2596A-D0C1-4026-9B50-2BC2A2681DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3384" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3383" uniqueCount="95">
   <si>
     <t>Company Name</t>
   </si>
@@ -146,19 +146,19 @@
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>DNU-Speed Management</t>
+    <t>DNU-Fatigue</t>
   </si>
   <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>3 points of contact</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
+    <t>DNU-Speed Management</t>
   </si>
   <si>
-    <t>DNU-Fatigue</t>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>DNU-NEW-Rules for Safe Driving</t>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>42</v>
       </c>
@@ -947,7 +947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>42</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>42</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
@@ -1440,7 +1440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>42</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1480,7 +1480,7 @@
         <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1509,7 +1509,7 @@
         <v>47</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -1546,7 +1546,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G30" t="s">
         <v>10</v>
@@ -1575,7 +1575,7 @@
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G31" t="s">
         <v>10</v>
@@ -1593,7 +1593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>42</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>50</v>
       </c>
       <c r="F32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G32" t="s">
         <v>12</v>
@@ -1641,7 +1641,7 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -1670,7 +1670,7 @@
         <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G35" t="s">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G36" t="s">
         <v>10</v>
@@ -1728,7 +1728,7 @@
         <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G37" t="s">
         <v>10</v>
@@ -1757,7 +1757,7 @@
         <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G38" t="s">
         <v>10</v>
@@ -1786,7 +1786,7 @@
         <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
@@ -1815,7 +1815,7 @@
         <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G40" t="s">
         <v>10</v>
@@ -1844,7 +1844,7 @@
         <v>58</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G41" t="s">
         <v>10</v>
@@ -1862,7 +1862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>42</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>59</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G42" t="s">
         <v>10</v>
@@ -1902,7 +1902,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -1931,7 +1931,7 @@
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1960,7 +1960,7 @@
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G45" t="s">
         <v>10</v>
@@ -1989,7 +1989,7 @@
         <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G46" t="s">
         <v>13</v>
@@ -2018,7 +2018,7 @@
         <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -2055,7 +2055,7 @@
         <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
@@ -2092,7 +2092,7 @@
         <v>44</v>
       </c>
       <c r="F51" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2121,7 +2121,7 @@
         <v>45</v>
       </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2150,7 +2150,7 @@
         <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -2168,7 +2168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
@@ -2187,7 +2187,7 @@
         <v>47</v>
       </c>
       <c r="F55" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2216,7 +2216,7 @@
         <v>48</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -2253,7 +2253,7 @@
         <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G58" t="s">
         <v>10</v>
@@ -2282,7 +2282,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2311,7 +2311,7 @@
         <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G60" t="s">
         <v>14</v>
@@ -2348,7 +2348,7 @@
         <v>52</v>
       </c>
       <c r="F62" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G62" t="s">
         <v>12</v>
@@ -2385,7 +2385,7 @@
         <v>53</v>
       </c>
       <c r="F64" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
@@ -2414,7 +2414,7 @@
         <v>54</v>
       </c>
       <c r="F65" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2443,7 +2443,7 @@
         <v>55</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2472,7 +2472,7 @@
         <v>56</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G67" t="s">
         <v>13</v>
@@ -2501,7 +2501,7 @@
         <v>57</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G68" t="s">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>58</v>
       </c>
       <c r="F69" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G69" t="s">
         <v>12</v>
@@ -2567,7 +2567,7 @@
         <v>59</v>
       </c>
       <c r="F71" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2596,7 +2596,7 @@
         <v>60</v>
       </c>
       <c r="F72" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -2625,7 +2625,7 @@
         <v>62</v>
       </c>
       <c r="F73" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2643,7 +2643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>42</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>63</v>
       </c>
       <c r="F74" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G74" t="s">
         <v>13</v>
@@ -2683,7 +2683,7 @@
         <v>64</v>
       </c>
       <c r="F75" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G75" t="s">
         <v>10</v>
@@ -2875,7 +2875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>42</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>42</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>42</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>42</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>42</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>42</v>
       </c>
@@ -5568,7 +5568,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>42</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>42</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>42</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>43</v>
       </c>
       <c r="F210" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G210" t="s">
         <v>10</v>
@@ -6507,7 +6507,7 @@
         <v>44</v>
       </c>
       <c r="F211" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G211" t="s">
         <v>10</v>
@@ -6536,7 +6536,7 @@
         <v>45</v>
       </c>
       <c r="F212" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G212" t="s">
         <v>10</v>
@@ -6565,7 +6565,7 @@
         <v>69</v>
       </c>
       <c r="F213" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G213" t="s">
         <v>10</v>
@@ -6594,7 +6594,7 @@
         <v>46</v>
       </c>
       <c r="F214" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G214" t="s">
         <v>13</v>
@@ -6623,7 +6623,7 @@
         <v>47</v>
       </c>
       <c r="F215" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G215" t="s">
         <v>10</v>
@@ -6652,7 +6652,7 @@
         <v>48</v>
       </c>
       <c r="F216" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G216" t="s">
         <v>10</v>
@@ -6681,7 +6681,7 @@
         <v>49</v>
       </c>
       <c r="F217" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G217" t="s">
         <v>10</v>
@@ -6710,7 +6710,7 @@
         <v>50</v>
       </c>
       <c r="F218" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G218" t="s">
         <v>10</v>
@@ -6739,7 +6739,7 @@
         <v>51</v>
       </c>
       <c r="F219" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G219" t="s">
         <v>13</v>
@@ -6768,7 +6768,7 @@
         <v>52</v>
       </c>
       <c r="F220" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G220" t="s">
         <v>10</v>
@@ -6797,7 +6797,7 @@
         <v>53</v>
       </c>
       <c r="F221" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G221" t="s">
         <v>13</v>
@@ -6826,7 +6826,7 @@
         <v>54</v>
       </c>
       <c r="F222" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G222" t="s">
         <v>10</v>
@@ -6855,7 +6855,7 @@
         <v>55</v>
       </c>
       <c r="F223" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G223" t="s">
         <v>10</v>
@@ -6884,7 +6884,7 @@
         <v>56</v>
       </c>
       <c r="F224" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G224" t="s">
         <v>10</v>
@@ -6913,7 +6913,7 @@
         <v>57</v>
       </c>
       <c r="F225" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G225" t="s">
         <v>10</v>
@@ -6942,7 +6942,7 @@
         <v>58</v>
       </c>
       <c r="F226" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G226" t="s">
         <v>13</v>
@@ -6971,7 +6971,7 @@
         <v>59</v>
       </c>
       <c r="F227" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G227" t="s">
         <v>10</v>
@@ -7000,7 +7000,7 @@
         <v>60</v>
       </c>
       <c r="F228" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G228" t="s">
         <v>13</v>
@@ -7029,7 +7029,7 @@
         <v>62</v>
       </c>
       <c r="F229" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G229" t="s">
         <v>10</v>
@@ -7058,7 +7058,7 @@
         <v>63</v>
       </c>
       <c r="F230" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G230" t="s">
         <v>13</v>
@@ -7087,7 +7087,7 @@
         <v>64</v>
       </c>
       <c r="F231" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G231" t="s">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>42</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>48</v>
       </c>
       <c r="F320" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G320" t="s">
         <v>13</v>
@@ -9751,7 +9751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>42</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>42</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>42</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>43</v>
       </c>
       <c r="F346" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G346" t="s">
         <v>13</v>
@@ -10403,7 +10403,7 @@
         <v>44</v>
       </c>
       <c r="F347" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G347" t="s">
         <v>13</v>
@@ -10432,7 +10432,7 @@
         <v>45</v>
       </c>
       <c r="F348" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G348" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>73</v>
       </c>
       <c r="F349" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G349" t="s">
         <v>10</v>
@@ -10490,7 +10490,7 @@
         <v>79</v>
       </c>
       <c r="F350" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G350" t="s">
         <v>10</v>
@@ -10519,7 +10519,7 @@
         <v>80</v>
       </c>
       <c r="F351" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G351" t="s">
         <v>13</v>
@@ -10548,7 +10548,7 @@
         <v>46</v>
       </c>
       <c r="F352" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G352" t="s">
         <v>13</v>
@@ -10577,7 +10577,7 @@
         <v>47</v>
       </c>
       <c r="F353" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G353" t="s">
         <v>10</v>
@@ -10595,7 +10595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>42</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>48</v>
       </c>
       <c r="F354" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G354" t="s">
         <v>10</v>
@@ -10635,7 +10635,7 @@
         <v>49</v>
       </c>
       <c r="F355" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G355" t="s">
         <v>10</v>
@@ -10653,7 +10653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>42</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>50</v>
       </c>
       <c r="F356" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G356" t="s">
         <v>13</v>
@@ -10696,7 +10696,7 @@
         <v>67</v>
       </c>
       <c r="F357" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G357" t="s">
         <v>10</v>
@@ -10725,7 +10725,7 @@
         <v>53</v>
       </c>
       <c r="F358" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G358" t="s">
         <v>10</v>
@@ -10754,7 +10754,7 @@
         <v>54</v>
       </c>
       <c r="F359" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G359" t="s">
         <v>13</v>
@@ -10783,7 +10783,7 @@
         <v>76</v>
       </c>
       <c r="F360" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G360" t="s">
         <v>10</v>
@@ -10812,7 +10812,7 @@
         <v>55</v>
       </c>
       <c r="F361" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G361" t="s">
         <v>10</v>
@@ -10841,7 +10841,7 @@
         <v>56</v>
       </c>
       <c r="F362" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G362" t="s">
         <v>10</v>
@@ -10870,7 +10870,7 @@
         <v>57</v>
       </c>
       <c r="F363" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G363" t="s">
         <v>10</v>
@@ -10899,7 +10899,7 @@
         <v>58</v>
       </c>
       <c r="F364" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G364" t="s">
         <v>13</v>
@@ -10928,7 +10928,7 @@
         <v>59</v>
       </c>
       <c r="F365" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G365" t="s">
         <v>10</v>
@@ -10957,7 +10957,7 @@
         <v>74</v>
       </c>
       <c r="F366" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G366" t="s">
         <v>10</v>
@@ -10986,7 +10986,7 @@
         <v>74</v>
       </c>
       <c r="F367" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G367" t="s">
         <v>10</v>
@@ -11015,7 +11015,7 @@
         <v>77</v>
       </c>
       <c r="F368" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G368" t="s">
         <v>12</v>
@@ -11052,7 +11052,7 @@
         <v>62</v>
       </c>
       <c r="F370" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G370" t="s">
         <v>10</v>
@@ -11081,7 +11081,7 @@
         <v>63</v>
       </c>
       <c r="F371" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G371" t="s">
         <v>13</v>
@@ -11099,7 +11099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>42</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>78</v>
       </c>
       <c r="F372" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G372" t="s">
         <v>13</v>
@@ -11139,7 +11139,7 @@
         <v>75</v>
       </c>
       <c r="F373" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G373" t="s">
         <v>13</v>
@@ -11368,7 +11368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>42</v>
       </c>
@@ -19920,10 +19920,10 @@
         <v>32</v>
       </c>
       <c r="G685" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H685" s="2">
-        <v>0</v>
+        <v>6.2268518518518515E-3</v>
       </c>
       <c r="I685" s="1">
         <v>46237.85601851852</v>
@@ -20160,10 +20160,10 @@
         <v>32</v>
       </c>
       <c r="G694" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H694" s="2">
-        <v>2.0833333333333335E-4</v>
+        <v>7.0949074074074074E-3</v>
       </c>
       <c r="I694" s="1">
         <v>46237.836689814816</v>
@@ -20176,11 +20176,32 @@
       </c>
     </row>
     <row r="695" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H695" s="2"/>
-      <c r="I695" s="1"/>
-      <c r="J695" s="2"/>
+      <c r="B695" t="s">
+        <v>42</v>
+      </c>
+      <c r="C695">
+        <v>623</v>
+      </c>
+      <c r="D695" t="s">
+        <v>57</v>
+      </c>
+      <c r="F695" t="s">
+        <v>32</v>
+      </c>
+      <c r="G695" t="s">
+        <v>10</v>
+      </c>
+      <c r="H695" s="2">
+        <v>5.6481481481481478E-3</v>
+      </c>
+      <c r="I695" s="1">
+        <v>46237.837384259263</v>
+      </c>
+      <c r="J695" s="2">
+        <v>0</v>
+      </c>
       <c r="K695" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="696" spans="2:11" x14ac:dyDescent="0.25">
@@ -20188,25 +20209,25 @@
         <v>42</v>
       </c>
       <c r="C696">
-        <v>623</v>
+        <v>72</v>
       </c>
       <c r="D696" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F696" t="s">
         <v>32</v>
       </c>
       <c r="G696" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H696" s="2">
-        <v>5.6481481481481478E-3</v>
+        <v>0</v>
       </c>
       <c r="I696" s="1">
-        <v>46237.837384259263</v>
+        <v>46237.838078703702</v>
       </c>
       <c r="J696" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K696" s="1" t="s">
         <v>11</v>
@@ -20217,25 +20238,25 @@
         <v>42</v>
       </c>
       <c r="C697">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D697" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F697" t="s">
         <v>32</v>
       </c>
       <c r="G697" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H697" s="2">
-        <v>0</v>
+        <v>8.819444444444444E-3</v>
       </c>
       <c r="I697" s="1">
         <v>46237.838078703702</v>
       </c>
       <c r="J697" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K697" s="1" t="s">
         <v>11</v>
@@ -20246,10 +20267,10 @@
         <v>42</v>
       </c>
       <c r="C698">
-        <v>84</v>
+        <v>3818</v>
       </c>
       <c r="D698" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F698" t="s">
         <v>32</v>
@@ -20258,13 +20279,13 @@
         <v>10</v>
       </c>
       <c r="H698" s="2">
-        <v>8.819444444444444E-3</v>
+        <v>1.9872685185185184E-2</v>
       </c>
       <c r="I698" s="1">
-        <v>46237.838078703702</v>
+        <v>46237.838773148149</v>
       </c>
       <c r="J698" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K698" s="1" t="s">
         <v>11</v>
@@ -20275,58 +20296,35 @@
         <v>42</v>
       </c>
       <c r="C699">
-        <v>3818</v>
+        <v>80</v>
       </c>
       <c r="D699" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F699" t="s">
         <v>32</v>
       </c>
       <c r="G699" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H699" s="2">
-        <v>1.9872685185185184E-2</v>
+        <v>0</v>
       </c>
       <c r="I699" s="1">
-        <v>46237.838773148149</v>
+        <v>46237.839467592596</v>
       </c>
       <c r="J699" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K699" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="700" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B700" t="s">
-        <v>42</v>
-      </c>
-      <c r="C700">
-        <v>80</v>
-      </c>
-      <c r="D700" t="s">
-        <v>63</v>
-      </c>
-      <c r="F700" t="s">
-        <v>32</v>
-      </c>
-      <c r="G700" t="s">
-        <v>13</v>
-      </c>
-      <c r="H700" s="2">
-        <v>0</v>
-      </c>
-      <c r="I700" s="1">
-        <v>46237.839467592596</v>
-      </c>
-      <c r="J700" s="2">
-        <v>3</v>
-      </c>
-      <c r="K700" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H700" s="2"/>
+      <c r="I700" s="1"/>
+      <c r="J700" s="2"/>
+      <c r="K700" s="1"/>
     </row>
     <row r="701" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H701" s="2"/>
@@ -27815,6 +27813,7 @@
       <c r="K1954" s="1"/>
     </row>
     <row r="1955" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1955" s="2"/>
       <c r="I1955" s="1"/>
       <c r="K1955" s="1"/>
     </row>
@@ -27824,6 +27823,7 @@
       <c r="K1956" s="1"/>
     </row>
     <row r="1957" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1957" s="2"/>
       <c r="I1957" s="1"/>
       <c r="K1957" s="1"/>
     </row>
@@ -27963,6 +27963,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -28016,7 +28017,6 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -57389,7 +57389,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -57682,8 +57681,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -57994,7 +57991,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -58119,7 +58115,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -58131,7 +58126,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -58280,35 +58274,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -58319,44 +58307,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -58367,37 +58346,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -58408,52 +58380,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -58464,17 +58426,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -58485,32 +58444,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -58520,106 +58473,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -58629,7 +58562,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -58640,127 +58572,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -58770,62 +58676,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -58845,67 +58738,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -58915,38 +58795,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -58961,117 +58834,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -59080,99 +58930,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -59182,23 +59013,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -59207,52 +59034,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -59266,38 +59083,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -59307,7 +59117,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -59318,23 +59127,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -59344,37 +59149,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -59383,72 +59181,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -59458,76 +59242,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\tnt-wrecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BF2596A-D0C1-4026-9B50-2BC2A2681DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A23086F7-89F4-4F5C-AD30-9EF417D133BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -146,19 +146,19 @@
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>DNU-Fatigue</t>
+    <t>DNU-Speed Management</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
   </si>
   <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>DNU-Speed Management</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>DNU-NEW-Rules for Safe Driving</t>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1393,7 +1393,7 @@
         <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
@@ -1451,7 +1451,7 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1480,7 +1480,7 @@
         <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1509,7 +1509,7 @@
         <v>47</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -1546,7 +1546,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G30" t="s">
         <v>10</v>
@@ -1575,7 +1575,7 @@
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
         <v>10</v>
@@ -1604,7 +1604,7 @@
         <v>50</v>
       </c>
       <c r="F32" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G32" t="s">
         <v>12</v>
@@ -1641,7 +1641,7 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -1670,7 +1670,7 @@
         <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G35" t="s">
         <v>10</v>
@@ -1699,7 +1699,7 @@
         <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G36" t="s">
         <v>10</v>
@@ -1728,7 +1728,7 @@
         <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G37" t="s">
         <v>10</v>
@@ -1757,7 +1757,7 @@
         <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G38" t="s">
         <v>10</v>
@@ -1786,7 +1786,7 @@
         <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
@@ -1815,7 +1815,7 @@
         <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G40" t="s">
         <v>10</v>
@@ -1844,7 +1844,7 @@
         <v>58</v>
       </c>
       <c r="F41" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
         <v>10</v>
@@ -1873,7 +1873,7 @@
         <v>59</v>
       </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G42" t="s">
         <v>10</v>
@@ -1902,7 +1902,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -1931,7 +1931,7 @@
         <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1960,7 +1960,7 @@
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G45" t="s">
         <v>10</v>
@@ -1989,7 +1989,7 @@
         <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
         <v>13</v>
@@ -2018,7 +2018,7 @@
         <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -2055,7 +2055,7 @@
         <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
@@ -2092,7 +2092,7 @@
         <v>44</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2121,7 +2121,7 @@
         <v>45</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2150,7 +2150,7 @@
         <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -2187,7 +2187,7 @@
         <v>47</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2216,7 +2216,7 @@
         <v>48</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -2253,7 +2253,7 @@
         <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G58" t="s">
         <v>10</v>
@@ -2282,7 +2282,7 @@
         <v>50</v>
       </c>
       <c r="F59" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2311,7 +2311,7 @@
         <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G60" t="s">
         <v>14</v>
@@ -2348,7 +2348,7 @@
         <v>52</v>
       </c>
       <c r="F62" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G62" t="s">
         <v>12</v>
@@ -2385,7 +2385,7 @@
         <v>53</v>
       </c>
       <c r="F64" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
@@ -2414,7 +2414,7 @@
         <v>54</v>
       </c>
       <c r="F65" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2443,7 +2443,7 @@
         <v>55</v>
       </c>
       <c r="F66" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2472,7 +2472,7 @@
         <v>56</v>
       </c>
       <c r="F67" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G67" t="s">
         <v>13</v>
@@ -2501,7 +2501,7 @@
         <v>57</v>
       </c>
       <c r="F68" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G68" t="s">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>58</v>
       </c>
       <c r="F69" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G69" t="s">
         <v>12</v>
@@ -2567,7 +2567,7 @@
         <v>59</v>
       </c>
       <c r="F71" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2596,7 +2596,7 @@
         <v>60</v>
       </c>
       <c r="F72" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -2625,7 +2625,7 @@
         <v>62</v>
       </c>
       <c r="F73" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2654,7 +2654,7 @@
         <v>63</v>
       </c>
       <c r="F74" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G74" t="s">
         <v>13</v>
@@ -2683,7 +2683,7 @@
         <v>64</v>
       </c>
       <c r="F75" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G75" t="s">
         <v>10</v>
@@ -6478,7 +6478,7 @@
         <v>43</v>
       </c>
       <c r="F210" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G210" t="s">
         <v>10</v>
@@ -6507,7 +6507,7 @@
         <v>44</v>
       </c>
       <c r="F211" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G211" t="s">
         <v>10</v>
@@ -6536,7 +6536,7 @@
         <v>45</v>
       </c>
       <c r="F212" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G212" t="s">
         <v>10</v>
@@ -6565,7 +6565,7 @@
         <v>69</v>
       </c>
       <c r="F213" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G213" t="s">
         <v>10</v>
@@ -6594,7 +6594,7 @@
         <v>46</v>
       </c>
       <c r="F214" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G214" t="s">
         <v>13</v>
@@ -6623,7 +6623,7 @@
         <v>47</v>
       </c>
       <c r="F215" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G215" t="s">
         <v>10</v>
@@ -6652,7 +6652,7 @@
         <v>48</v>
       </c>
       <c r="F216" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G216" t="s">
         <v>10</v>
@@ -6681,7 +6681,7 @@
         <v>49</v>
       </c>
       <c r="F217" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G217" t="s">
         <v>10</v>
@@ -6710,7 +6710,7 @@
         <v>50</v>
       </c>
       <c r="F218" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G218" t="s">
         <v>10</v>
@@ -6739,7 +6739,7 @@
         <v>51</v>
       </c>
       <c r="F219" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G219" t="s">
         <v>13</v>
@@ -6768,7 +6768,7 @@
         <v>52</v>
       </c>
       <c r="F220" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G220" t="s">
         <v>10</v>
@@ -6797,7 +6797,7 @@
         <v>53</v>
       </c>
       <c r="F221" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G221" t="s">
         <v>13</v>
@@ -6826,7 +6826,7 @@
         <v>54</v>
       </c>
       <c r="F222" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G222" t="s">
         <v>10</v>
@@ -6855,7 +6855,7 @@
         <v>55</v>
       </c>
       <c r="F223" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G223" t="s">
         <v>10</v>
@@ -6884,7 +6884,7 @@
         <v>56</v>
       </c>
       <c r="F224" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G224" t="s">
         <v>10</v>
@@ -6913,7 +6913,7 @@
         <v>57</v>
       </c>
       <c r="F225" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G225" t="s">
         <v>10</v>
@@ -6942,7 +6942,7 @@
         <v>58</v>
       </c>
       <c r="F226" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G226" t="s">
         <v>13</v>
@@ -6971,7 +6971,7 @@
         <v>59</v>
       </c>
       <c r="F227" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G227" t="s">
         <v>10</v>
@@ -7000,7 +7000,7 @@
         <v>60</v>
       </c>
       <c r="F228" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G228" t="s">
         <v>13</v>
@@ -7029,7 +7029,7 @@
         <v>62</v>
       </c>
       <c r="F229" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G229" t="s">
         <v>10</v>
@@ -7058,7 +7058,7 @@
         <v>63</v>
       </c>
       <c r="F230" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G230" t="s">
         <v>13</v>
@@ -7087,7 +7087,7 @@
         <v>64</v>
       </c>
       <c r="F231" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G231" t="s">
         <v>10</v>
@@ -9638,7 +9638,7 @@
         <v>48</v>
       </c>
       <c r="F320" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G320" t="s">
         <v>13</v>
@@ -10374,7 +10374,7 @@
         <v>43</v>
       </c>
       <c r="F346" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G346" t="s">
         <v>13</v>
@@ -10403,7 +10403,7 @@
         <v>44</v>
       </c>
       <c r="F347" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G347" t="s">
         <v>13</v>
@@ -10432,7 +10432,7 @@
         <v>45</v>
       </c>
       <c r="F348" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G348" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>73</v>
       </c>
       <c r="F349" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G349" t="s">
         <v>10</v>
@@ -10490,7 +10490,7 @@
         <v>79</v>
       </c>
       <c r="F350" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G350" t="s">
         <v>10</v>
@@ -10519,7 +10519,7 @@
         <v>80</v>
       </c>
       <c r="F351" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G351" t="s">
         <v>13</v>
@@ -10548,7 +10548,7 @@
         <v>46</v>
       </c>
       <c r="F352" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G352" t="s">
         <v>13</v>
@@ -10577,7 +10577,7 @@
         <v>47</v>
       </c>
       <c r="F353" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G353" t="s">
         <v>10</v>
@@ -10606,7 +10606,7 @@
         <v>48</v>
       </c>
       <c r="F354" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G354" t="s">
         <v>10</v>
@@ -10635,7 +10635,7 @@
         <v>49</v>
       </c>
       <c r="F355" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G355" t="s">
         <v>10</v>
@@ -10664,7 +10664,7 @@
         <v>50</v>
       </c>
       <c r="F356" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G356" t="s">
         <v>13</v>
@@ -10696,7 +10696,7 @@
         <v>67</v>
       </c>
       <c r="F357" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G357" t="s">
         <v>10</v>
@@ -10725,7 +10725,7 @@
         <v>53</v>
       </c>
       <c r="F358" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G358" t="s">
         <v>10</v>
@@ -10754,7 +10754,7 @@
         <v>54</v>
       </c>
       <c r="F359" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G359" t="s">
         <v>13</v>
@@ -10783,7 +10783,7 @@
         <v>76</v>
       </c>
       <c r="F360" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G360" t="s">
         <v>10</v>
@@ -10812,7 +10812,7 @@
         <v>55</v>
       </c>
       <c r="F361" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G361" t="s">
         <v>10</v>
@@ -10841,7 +10841,7 @@
         <v>56</v>
       </c>
       <c r="F362" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G362" t="s">
         <v>10</v>
@@ -10870,7 +10870,7 @@
         <v>57</v>
       </c>
       <c r="F363" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G363" t="s">
         <v>10</v>
@@ -10899,7 +10899,7 @@
         <v>58</v>
       </c>
       <c r="F364" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G364" t="s">
         <v>13</v>
@@ -10928,7 +10928,7 @@
         <v>59</v>
       </c>
       <c r="F365" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G365" t="s">
         <v>10</v>
@@ -10957,7 +10957,7 @@
         <v>74</v>
       </c>
       <c r="F366" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G366" t="s">
         <v>10</v>
@@ -10986,7 +10986,7 @@
         <v>74</v>
       </c>
       <c r="F367" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G367" t="s">
         <v>10</v>
@@ -11015,7 +11015,7 @@
         <v>77</v>
       </c>
       <c r="F368" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G368" t="s">
         <v>12</v>
@@ -11052,7 +11052,7 @@
         <v>62</v>
       </c>
       <c r="F370" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G370" t="s">
         <v>10</v>
@@ -11081,7 +11081,7 @@
         <v>63</v>
       </c>
       <c r="F371" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G371" t="s">
         <v>13</v>
@@ -11110,7 +11110,7 @@
         <v>78</v>
       </c>
       <c r="F372" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G372" t="s">
         <v>13</v>
@@ -11139,7 +11139,7 @@
         <v>75</v>
       </c>
       <c r="F373" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G373" t="s">
         <v>13</v>
@@ -57389,6 +57389,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -57681,6 +57682,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -57991,6 +57994,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -58115,6 +58119,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -58126,6 +58131,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -58274,29 +58280,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -58307,35 +58319,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -58346,30 +58367,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -58380,42 +58408,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -58426,14 +58464,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -58444,26 +58485,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -58473,86 +58520,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -58562,6 +58630,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -58572,101 +58641,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -58676,49 +58771,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -58733,59 +58841,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -58795,31 +58917,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -58829,99 +58958,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -58930,80 +59083,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -59013,67 +59185,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -59083,31 +59271,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -59117,6 +59312,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -59127,19 +59323,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -59149,90 +59349,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -59242,51 +59464,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
